--- a/es/es-global-request.xlsx
+++ b/es/es-global-request.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CNXK\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961C319E-65DE-48CB-8F8C-F84DB7A7AC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ACE12F1-344E-4841-9DDF-F1F76F9F5F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,10 +46,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>W26</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>LG DUALCOOL AI microsite Open</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -141,6 +137,10 @@
   </si>
   <si>
     <t>Status</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>W30</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -437,7 +437,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
@@ -461,32 +461,32 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>19</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" s="3">
         <v>46206</v>
@@ -494,13 +494,13 @@
     </row>
     <row r="8" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="D8" s="3">
         <v>46212</v>
@@ -508,13 +508,13 @@
     </row>
     <row r="9" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" s="3">
         <v>46219</v>
@@ -522,27 +522,27 @@
     </row>
     <row r="10" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" s="3">
         <v>46212</v>
@@ -550,13 +550,13 @@
     </row>
     <row r="12" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" s="3">
         <v>46210</v>
@@ -564,13 +564,13 @@
     </row>
     <row r="13" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13" s="3">
         <v>46219</v>
@@ -578,13 +578,13 @@
     </row>
     <row r="14" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D14" s="3">
         <v>46212</v>

--- a/es/es-global-request.xlsx
+++ b/es/es-global-request.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CNXK\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78AF5B33-8D06-466C-800C-2EB114EE539C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFBFA05-B65A-42B0-9C15-1BB8362A5C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
   <si>
     <t>Title</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -157,6 +157,14 @@
   </si>
   <si>
     <t>EU</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Project Name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG DUALCOOL AI</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -441,14 +449,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{208B41D5-0159-4AEB-BF1C-F11A0E733526}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -456,7 +465,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -464,7 +473,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -472,7 +481,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
@@ -480,183 +489,210 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="3">
+      <c r="G7" s="3">
         <v>46206</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>14</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>46212</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>46219</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>24</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>26</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="3">
+      <c r="G11" s="3">
         <v>46212</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>21</v>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>46210</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>22</v>
       </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="3">
+      <c r="G13" s="3">
         <v>46219</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>23</v>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>46212</v>
       </c>
     </row>

--- a/es/es-global-request.xlsx
+++ b/es/es-global-request.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CNXK\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F014375D-97BC-4CBA-8A2E-78E518BDC171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1725" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LG DUALCOOL AI" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3968" uniqueCount="1173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4614" uniqueCount="1180">
   <si>
     <t>Title</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -3590,6 +3590,27 @@
   </si>
   <si>
     <t>https://www.lg.com/ca_fr/systemes-de-climatisation/climatiseurs-portatifs/lp1419ivsm</t>
+  </si>
+  <si>
+    <t>Asia</t>
+  </si>
+  <si>
+    <t>CIS</t>
+  </si>
+  <si>
+    <t>EU</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>LATAM</t>
+  </si>
+  <si>
+    <t>MEA</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -4203,6 +4224,9 @@
       <c r="A7" t="s">
         <v>43</v>
       </c>
+      <c r="B7" t="s">
+        <v>1173</v>
+      </c>
       <c r="C7" t="s">
         <v>45</v>
       </c>
@@ -4229,6 +4253,9 @@
       <c r="A8" t="s">
         <v>43</v>
       </c>
+      <c r="B8" t="s">
+        <v>1173</v>
+      </c>
       <c r="C8" t="s">
         <v>46</v>
       </c>
@@ -4255,6 +4282,9 @@
       <c r="A9" t="s">
         <v>43</v>
       </c>
+      <c r="B9" t="s">
+        <v>1173</v>
+      </c>
       <c r="C9" t="s">
         <v>46</v>
       </c>
@@ -4281,6 +4311,9 @@
       <c r="A10" t="s">
         <v>43</v>
       </c>
+      <c r="B10" t="s">
+        <v>1173</v>
+      </c>
       <c r="C10" t="s">
         <v>46</v>
       </c>
@@ -4307,6 +4340,9 @@
       <c r="A11" t="s">
         <v>43</v>
       </c>
+      <c r="B11" t="s">
+        <v>1173</v>
+      </c>
       <c r="C11" t="s">
         <v>46</v>
       </c>
@@ -4333,6 +4369,9 @@
       <c r="A12" t="s">
         <v>43</v>
       </c>
+      <c r="B12" t="s">
+        <v>1173</v>
+      </c>
       <c r="C12" t="s">
         <v>47</v>
       </c>
@@ -4359,6 +4398,9 @@
       <c r="A13" t="s">
         <v>43</v>
       </c>
+      <c r="B13" t="s">
+        <v>1173</v>
+      </c>
       <c r="C13" t="s">
         <v>47</v>
       </c>
@@ -4385,6 +4427,9 @@
       <c r="A14" t="s">
         <v>43</v>
       </c>
+      <c r="B14" t="s">
+        <v>1173</v>
+      </c>
       <c r="C14" t="s">
         <v>47</v>
       </c>
@@ -4411,6 +4456,9 @@
       <c r="A15" t="s">
         <v>43</v>
       </c>
+      <c r="B15" t="s">
+        <v>1173</v>
+      </c>
       <c r="C15" t="s">
         <v>47</v>
       </c>
@@ -4437,6 +4485,9 @@
       <c r="A16" t="s">
         <v>43</v>
       </c>
+      <c r="B16" t="s">
+        <v>1173</v>
+      </c>
       <c r="C16" t="s">
         <v>47</v>
       </c>
@@ -4463,6 +4514,9 @@
       <c r="A17" t="s">
         <v>43</v>
       </c>
+      <c r="B17" t="s">
+        <v>1173</v>
+      </c>
       <c r="C17" t="s">
         <v>47</v>
       </c>
@@ -4489,6 +4543,9 @@
       <c r="A18" t="s">
         <v>43</v>
       </c>
+      <c r="B18" t="s">
+        <v>1173</v>
+      </c>
       <c r="C18" t="s">
         <v>47</v>
       </c>
@@ -4515,6 +4572,9 @@
       <c r="A19" t="s">
         <v>43</v>
       </c>
+      <c r="B19" t="s">
+        <v>1173</v>
+      </c>
       <c r="C19" t="s">
         <v>47</v>
       </c>
@@ -4541,6 +4601,9 @@
       <c r="A20" t="s">
         <v>43</v>
       </c>
+      <c r="B20" t="s">
+        <v>1173</v>
+      </c>
       <c r="C20" t="s">
         <v>48</v>
       </c>
@@ -4567,6 +4630,9 @@
       <c r="A21" t="s">
         <v>43</v>
       </c>
+      <c r="B21" t="s">
+        <v>1173</v>
+      </c>
       <c r="C21" t="s">
         <v>48</v>
       </c>
@@ -4593,6 +4659,9 @@
       <c r="A22" t="s">
         <v>43</v>
       </c>
+      <c r="B22" t="s">
+        <v>1173</v>
+      </c>
       <c r="C22" t="s">
         <v>49</v>
       </c>
@@ -4619,6 +4688,9 @@
       <c r="A23" t="s">
         <v>44</v>
       </c>
+      <c r="B23" t="s">
+        <v>1173</v>
+      </c>
       <c r="C23" t="s">
         <v>50</v>
       </c>
@@ -4645,6 +4717,9 @@
       <c r="A24" t="s">
         <v>44</v>
       </c>
+      <c r="B24" t="s">
+        <v>1173</v>
+      </c>
       <c r="C24" t="s">
         <v>50</v>
       </c>
@@ -4671,6 +4746,9 @@
       <c r="A25" t="s">
         <v>44</v>
       </c>
+      <c r="B25" t="s">
+        <v>1173</v>
+      </c>
       <c r="C25" t="s">
         <v>50</v>
       </c>
@@ -4697,6 +4775,9 @@
       <c r="A26" t="s">
         <v>44</v>
       </c>
+      <c r="B26" t="s">
+        <v>1173</v>
+      </c>
       <c r="C26" t="s">
         <v>50</v>
       </c>
@@ -4723,6 +4804,9 @@
       <c r="A27" t="s">
         <v>44</v>
       </c>
+      <c r="B27" t="s">
+        <v>1173</v>
+      </c>
       <c r="C27" t="s">
         <v>50</v>
       </c>
@@ -4749,6 +4833,9 @@
       <c r="A28" t="s">
         <v>44</v>
       </c>
+      <c r="B28" t="s">
+        <v>1173</v>
+      </c>
       <c r="C28" t="s">
         <v>50</v>
       </c>
@@ -4775,6 +4862,9 @@
       <c r="A29" t="s">
         <v>44</v>
       </c>
+      <c r="B29" t="s">
+        <v>1173</v>
+      </c>
       <c r="C29" t="s">
         <v>50</v>
       </c>
@@ -4801,6 +4891,9 @@
       <c r="A30" t="s">
         <v>44</v>
       </c>
+      <c r="B30" t="s">
+        <v>1173</v>
+      </c>
       <c r="C30" t="s">
         <v>50</v>
       </c>
@@ -4827,6 +4920,9 @@
       <c r="A31" t="s">
         <v>44</v>
       </c>
+      <c r="B31" t="s">
+        <v>1173</v>
+      </c>
       <c r="C31" t="s">
         <v>51</v>
       </c>
@@ -4853,6 +4949,9 @@
       <c r="A32" t="s">
         <v>44</v>
       </c>
+      <c r="B32" t="s">
+        <v>1173</v>
+      </c>
       <c r="C32" t="s">
         <v>51</v>
       </c>
@@ -4879,6 +4978,9 @@
       <c r="A33" t="s">
         <v>44</v>
       </c>
+      <c r="B33" t="s">
+        <v>1173</v>
+      </c>
       <c r="C33" t="s">
         <v>51</v>
       </c>
@@ -4905,6 +5007,9 @@
       <c r="A34" t="s">
         <v>44</v>
       </c>
+      <c r="B34" t="s">
+        <v>1173</v>
+      </c>
       <c r="C34" t="s">
         <v>51</v>
       </c>
@@ -4931,6 +5036,9 @@
       <c r="A35" t="s">
         <v>44</v>
       </c>
+      <c r="B35" t="s">
+        <v>1173</v>
+      </c>
       <c r="C35" t="s">
         <v>51</v>
       </c>
@@ -4957,6 +5065,9 @@
       <c r="A36" t="s">
         <v>44</v>
       </c>
+      <c r="B36" t="s">
+        <v>1173</v>
+      </c>
       <c r="C36" t="s">
         <v>51</v>
       </c>
@@ -4983,6 +5094,9 @@
       <c r="A37" t="s">
         <v>44</v>
       </c>
+      <c r="B37" t="s">
+        <v>1173</v>
+      </c>
       <c r="C37" t="s">
         <v>51</v>
       </c>
@@ -5009,6 +5123,9 @@
       <c r="A38" t="s">
         <v>44</v>
       </c>
+      <c r="B38" t="s">
+        <v>1173</v>
+      </c>
       <c r="C38" t="s">
         <v>52</v>
       </c>
@@ -5035,6 +5152,9 @@
       <c r="A39" t="s">
         <v>44</v>
       </c>
+      <c r="B39" t="s">
+        <v>1173</v>
+      </c>
       <c r="C39" t="s">
         <v>52</v>
       </c>
@@ -5061,6 +5181,9 @@
       <c r="A40" t="s">
         <v>44</v>
       </c>
+      <c r="B40" t="s">
+        <v>1173</v>
+      </c>
       <c r="C40" t="s">
         <v>52</v>
       </c>
@@ -5087,6 +5210,9 @@
       <c r="A41" t="s">
         <v>44</v>
       </c>
+      <c r="B41" t="s">
+        <v>1173</v>
+      </c>
       <c r="C41" t="s">
         <v>52</v>
       </c>
@@ -5113,6 +5239,9 @@
       <c r="A42" t="s">
         <v>44</v>
       </c>
+      <c r="B42" t="s">
+        <v>1173</v>
+      </c>
       <c r="C42" t="s">
         <v>52</v>
       </c>
@@ -5139,6 +5268,9 @@
       <c r="A43" t="s">
         <v>44</v>
       </c>
+      <c r="B43" t="s">
+        <v>1173</v>
+      </c>
       <c r="C43" t="s">
         <v>52</v>
       </c>
@@ -5165,6 +5297,9 @@
       <c r="A44" t="s">
         <v>44</v>
       </c>
+      <c r="B44" t="s">
+        <v>1173</v>
+      </c>
       <c r="C44" t="s">
         <v>52</v>
       </c>
@@ -5191,6 +5326,9 @@
       <c r="A45" t="s">
         <v>44</v>
       </c>
+      <c r="B45" t="s">
+        <v>1173</v>
+      </c>
       <c r="C45" t="s">
         <v>52</v>
       </c>
@@ -5217,6 +5355,9 @@
       <c r="A46" t="s">
         <v>44</v>
       </c>
+      <c r="B46" t="s">
+        <v>1173</v>
+      </c>
       <c r="C46" t="s">
         <v>52</v>
       </c>
@@ -5243,6 +5384,9 @@
       <c r="A47" t="s">
         <v>44</v>
       </c>
+      <c r="B47" t="s">
+        <v>1173</v>
+      </c>
       <c r="C47" t="s">
         <v>52</v>
       </c>
@@ -5269,6 +5413,9 @@
       <c r="A48" t="s">
         <v>44</v>
       </c>
+      <c r="B48" t="s">
+        <v>1173</v>
+      </c>
       <c r="C48" t="s">
         <v>52</v>
       </c>
@@ -5295,6 +5442,9 @@
       <c r="A49" t="s">
         <v>44</v>
       </c>
+      <c r="B49" t="s">
+        <v>1173</v>
+      </c>
       <c r="C49" t="s">
         <v>52</v>
       </c>
@@ -5321,6 +5471,9 @@
       <c r="A50" t="s">
         <v>44</v>
       </c>
+      <c r="B50" t="s">
+        <v>1173</v>
+      </c>
       <c r="C50" t="s">
         <v>46</v>
       </c>
@@ -5347,6 +5500,9 @@
       <c r="A51" t="s">
         <v>44</v>
       </c>
+      <c r="B51" t="s">
+        <v>1173</v>
+      </c>
       <c r="C51" t="s">
         <v>46</v>
       </c>
@@ -5373,6 +5529,9 @@
       <c r="A52" t="s">
         <v>44</v>
       </c>
+      <c r="B52" t="s">
+        <v>1173</v>
+      </c>
       <c r="C52" t="s">
         <v>46</v>
       </c>
@@ -5399,6 +5558,9 @@
       <c r="A53" t="s">
         <v>44</v>
       </c>
+      <c r="B53" t="s">
+        <v>1173</v>
+      </c>
       <c r="C53" t="s">
         <v>46</v>
       </c>
@@ -5425,6 +5587,9 @@
       <c r="A54" t="s">
         <v>44</v>
       </c>
+      <c r="B54" t="s">
+        <v>1173</v>
+      </c>
       <c r="C54" t="s">
         <v>46</v>
       </c>
@@ -5451,6 +5616,9 @@
       <c r="A55" t="s">
         <v>44</v>
       </c>
+      <c r="B55" t="s">
+        <v>1173</v>
+      </c>
       <c r="C55" t="s">
         <v>46</v>
       </c>
@@ -5477,6 +5645,9 @@
       <c r="A56" t="s">
         <v>44</v>
       </c>
+      <c r="B56" t="s">
+        <v>1173</v>
+      </c>
       <c r="C56" t="s">
         <v>47</v>
       </c>
@@ -5503,6 +5674,9 @@
       <c r="A57" t="s">
         <v>44</v>
       </c>
+      <c r="B57" t="s">
+        <v>1173</v>
+      </c>
       <c r="C57" t="s">
         <v>47</v>
       </c>
@@ -5529,6 +5703,9 @@
       <c r="A58" t="s">
         <v>44</v>
       </c>
+      <c r="B58" t="s">
+        <v>1173</v>
+      </c>
       <c r="C58" t="s">
         <v>47</v>
       </c>
@@ -5555,6 +5732,9 @@
       <c r="A59" t="s">
         <v>44</v>
       </c>
+      <c r="B59" t="s">
+        <v>1173</v>
+      </c>
       <c r="C59" t="s">
         <v>47</v>
       </c>
@@ -5581,6 +5761,9 @@
       <c r="A60" t="s">
         <v>44</v>
       </c>
+      <c r="B60" t="s">
+        <v>1173</v>
+      </c>
       <c r="C60" t="s">
         <v>47</v>
       </c>
@@ -5607,6 +5790,9 @@
       <c r="A61" t="s">
         <v>44</v>
       </c>
+      <c r="B61" t="s">
+        <v>1173</v>
+      </c>
       <c r="C61" t="s">
         <v>47</v>
       </c>
@@ -5633,6 +5819,9 @@
       <c r="A62" t="s">
         <v>44</v>
       </c>
+      <c r="B62" t="s">
+        <v>1173</v>
+      </c>
       <c r="C62" t="s">
         <v>47</v>
       </c>
@@ -5659,6 +5848,9 @@
       <c r="A63" t="s">
         <v>44</v>
       </c>
+      <c r="B63" t="s">
+        <v>1173</v>
+      </c>
       <c r="C63" t="s">
         <v>47</v>
       </c>
@@ -5685,6 +5877,9 @@
       <c r="A64" t="s">
         <v>44</v>
       </c>
+      <c r="B64" t="s">
+        <v>1173</v>
+      </c>
       <c r="C64" t="s">
         <v>47</v>
       </c>
@@ -5711,6 +5906,9 @@
       <c r="A65" t="s">
         <v>44</v>
       </c>
+      <c r="B65" t="s">
+        <v>1173</v>
+      </c>
       <c r="C65" t="s">
         <v>47</v>
       </c>
@@ -5737,6 +5935,9 @@
       <c r="A66" t="s">
         <v>44</v>
       </c>
+      <c r="B66" t="s">
+        <v>1173</v>
+      </c>
       <c r="C66" t="s">
         <v>47</v>
       </c>
@@ -5763,6 +5964,9 @@
       <c r="A67" t="s">
         <v>44</v>
       </c>
+      <c r="B67" t="s">
+        <v>1173</v>
+      </c>
       <c r="C67" t="s">
         <v>47</v>
       </c>
@@ -5789,6 +5993,9 @@
       <c r="A68" t="s">
         <v>44</v>
       </c>
+      <c r="B68" t="s">
+        <v>1173</v>
+      </c>
       <c r="C68" t="s">
         <v>47</v>
       </c>
@@ -5815,6 +6022,9 @@
       <c r="A69" t="s">
         <v>44</v>
       </c>
+      <c r="B69" t="s">
+        <v>1173</v>
+      </c>
       <c r="C69" t="s">
         <v>47</v>
       </c>
@@ -5841,6 +6051,9 @@
       <c r="A70" t="s">
         <v>44</v>
       </c>
+      <c r="B70" t="s">
+        <v>1173</v>
+      </c>
       <c r="C70" t="s">
         <v>47</v>
       </c>
@@ -5867,6 +6080,9 @@
       <c r="A71" t="s">
         <v>44</v>
       </c>
+      <c r="B71" t="s">
+        <v>1173</v>
+      </c>
       <c r="C71" t="s">
         <v>47</v>
       </c>
@@ -5893,6 +6109,9 @@
       <c r="A72" t="s">
         <v>44</v>
       </c>
+      <c r="B72" t="s">
+        <v>1173</v>
+      </c>
       <c r="C72" t="s">
         <v>47</v>
       </c>
@@ -5919,6 +6138,9 @@
       <c r="A73" t="s">
         <v>44</v>
       </c>
+      <c r="B73" t="s">
+        <v>1173</v>
+      </c>
       <c r="C73" t="s">
         <v>47</v>
       </c>
@@ -5945,6 +6167,9 @@
       <c r="A74" t="s">
         <v>44</v>
       </c>
+      <c r="B74" t="s">
+        <v>1173</v>
+      </c>
       <c r="C74" t="s">
         <v>47</v>
       </c>
@@ -5971,6 +6196,9 @@
       <c r="A75" t="s">
         <v>44</v>
       </c>
+      <c r="B75" t="s">
+        <v>1173</v>
+      </c>
       <c r="C75" t="s">
         <v>47</v>
       </c>
@@ -5997,6 +6225,9 @@
       <c r="A76" t="s">
         <v>44</v>
       </c>
+      <c r="B76" t="s">
+        <v>1173</v>
+      </c>
       <c r="C76" t="s">
         <v>47</v>
       </c>
@@ -6023,6 +6254,9 @@
       <c r="A77" t="s">
         <v>44</v>
       </c>
+      <c r="B77" t="s">
+        <v>1173</v>
+      </c>
       <c r="C77" t="s">
         <v>47</v>
       </c>
@@ -6049,6 +6283,9 @@
       <c r="A78" t="s">
         <v>44</v>
       </c>
+      <c r="B78" t="s">
+        <v>1173</v>
+      </c>
       <c r="C78" t="s">
         <v>47</v>
       </c>
@@ -6075,6 +6312,9 @@
       <c r="A79" t="s">
         <v>44</v>
       </c>
+      <c r="B79" t="s">
+        <v>1173</v>
+      </c>
       <c r="C79" t="s">
         <v>47</v>
       </c>
@@ -6101,6 +6341,9 @@
       <c r="A80" t="s">
         <v>44</v>
       </c>
+      <c r="B80" t="s">
+        <v>1173</v>
+      </c>
       <c r="C80" t="s">
         <v>47</v>
       </c>
@@ -6127,6 +6370,9 @@
       <c r="A81" t="s">
         <v>44</v>
       </c>
+      <c r="B81" t="s">
+        <v>1174</v>
+      </c>
       <c r="C81" t="s">
         <v>53</v>
       </c>
@@ -6153,6 +6399,9 @@
       <c r="A82" t="s">
         <v>44</v>
       </c>
+      <c r="B82" t="s">
+        <v>1175</v>
+      </c>
       <c r="C82" t="s">
         <v>54</v>
       </c>
@@ -6179,6 +6428,9 @@
       <c r="A83" t="s">
         <v>44</v>
       </c>
+      <c r="B83" t="s">
+        <v>1175</v>
+      </c>
       <c r="C83" t="s">
         <v>54</v>
       </c>
@@ -6205,6 +6457,9 @@
       <c r="A84" t="s">
         <v>44</v>
       </c>
+      <c r="B84" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="C84" t="s">
         <v>55</v>
       </c>
@@ -6231,6 +6486,9 @@
       <c r="A85" t="s">
         <v>44</v>
       </c>
+      <c r="B85" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="C85" t="s">
         <v>55</v>
       </c>
@@ -6257,6 +6515,9 @@
       <c r="A86" t="s">
         <v>44</v>
       </c>
+      <c r="B86" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="C86" t="s">
         <v>55</v>
       </c>
@@ -6283,6 +6544,9 @@
       <c r="A87" t="s">
         <v>44</v>
       </c>
+      <c r="B87" t="s">
+        <v>1175</v>
+      </c>
       <c r="C87" t="s">
         <v>56</v>
       </c>
@@ -6309,6 +6573,9 @@
       <c r="A88" t="s">
         <v>44</v>
       </c>
+      <c r="B88" t="s">
+        <v>1175</v>
+      </c>
       <c r="C88" t="s">
         <v>56</v>
       </c>
@@ -6335,6 +6602,9 @@
       <c r="A89" t="s">
         <v>44</v>
       </c>
+      <c r="B89" t="s">
+        <v>1175</v>
+      </c>
       <c r="C89" t="s">
         <v>56</v>
       </c>
@@ -6361,6 +6631,9 @@
       <c r="A90" t="s">
         <v>44</v>
       </c>
+      <c r="B90" t="s">
+        <v>1175</v>
+      </c>
       <c r="C90" t="s">
         <v>57</v>
       </c>
@@ -6387,6 +6660,9 @@
       <c r="A91" t="s">
         <v>44</v>
       </c>
+      <c r="B91" t="s">
+        <v>1175</v>
+      </c>
       <c r="C91" t="s">
         <v>58</v>
       </c>
@@ -6413,6 +6689,9 @@
       <c r="A92" t="s">
         <v>44</v>
       </c>
+      <c r="B92" t="s">
+        <v>1175</v>
+      </c>
       <c r="C92" t="s">
         <v>58</v>
       </c>
@@ -6439,6 +6718,9 @@
       <c r="A93" t="s">
         <v>44</v>
       </c>
+      <c r="B93" t="s">
+        <v>1175</v>
+      </c>
       <c r="C93" t="s">
         <v>58</v>
       </c>
@@ -6465,6 +6747,9 @@
       <c r="A94" t="s">
         <v>44</v>
       </c>
+      <c r="B94" t="s">
+        <v>1175</v>
+      </c>
       <c r="C94" t="s">
         <v>58</v>
       </c>
@@ -6491,6 +6776,9 @@
       <c r="A95" t="s">
         <v>44</v>
       </c>
+      <c r="B95" t="s">
+        <v>1175</v>
+      </c>
       <c r="C95" t="s">
         <v>59</v>
       </c>
@@ -6517,6 +6805,9 @@
       <c r="A96" t="s">
         <v>44</v>
       </c>
+      <c r="B96" t="s">
+        <v>1175</v>
+      </c>
       <c r="C96" t="s">
         <v>59</v>
       </c>
@@ -6543,6 +6834,9 @@
       <c r="A97" t="s">
         <v>44</v>
       </c>
+      <c r="B97" t="s">
+        <v>1175</v>
+      </c>
       <c r="C97" t="s">
         <v>60</v>
       </c>
@@ -6569,6 +6863,9 @@
       <c r="A98" t="s">
         <v>44</v>
       </c>
+      <c r="B98" t="s">
+        <v>1175</v>
+      </c>
       <c r="C98" t="s">
         <v>60</v>
       </c>
@@ -6595,6 +6892,9 @@
       <c r="A99" t="s">
         <v>44</v>
       </c>
+      <c r="B99" t="s">
+        <v>1175</v>
+      </c>
       <c r="C99" t="s">
         <v>60</v>
       </c>
@@ -6621,6 +6921,9 @@
       <c r="A100" t="s">
         <v>44</v>
       </c>
+      <c r="B100" t="s">
+        <v>1175</v>
+      </c>
       <c r="C100" t="s">
         <v>61</v>
       </c>
@@ -6647,6 +6950,9 @@
       <c r="A101" t="s">
         <v>44</v>
       </c>
+      <c r="B101" t="s">
+        <v>1175</v>
+      </c>
       <c r="C101" t="s">
         <v>61</v>
       </c>
@@ -6673,6 +6979,9 @@
       <c r="A102" t="s">
         <v>44</v>
       </c>
+      <c r="B102" t="s">
+        <v>1175</v>
+      </c>
       <c r="C102" t="s">
         <v>61</v>
       </c>
@@ -6699,6 +7008,9 @@
       <c r="A103" t="s">
         <v>44</v>
       </c>
+      <c r="B103" t="s">
+        <v>1175</v>
+      </c>
       <c r="C103" t="s">
         <v>61</v>
       </c>
@@ -6725,6 +7037,9 @@
       <c r="A104" t="s">
         <v>44</v>
       </c>
+      <c r="B104" t="s">
+        <v>1175</v>
+      </c>
       <c r="C104" t="s">
         <v>61</v>
       </c>
@@ -6751,6 +7066,9 @@
       <c r="A105" t="s">
         <v>44</v>
       </c>
+      <c r="B105" t="s">
+        <v>1175</v>
+      </c>
       <c r="C105" t="s">
         <v>61</v>
       </c>
@@ -6777,6 +7095,9 @@
       <c r="A106" t="s">
         <v>44</v>
       </c>
+      <c r="B106" t="s">
+        <v>1175</v>
+      </c>
       <c r="C106" t="s">
         <v>61</v>
       </c>
@@ -6803,6 +7124,9 @@
       <c r="A107" t="s">
         <v>44</v>
       </c>
+      <c r="B107" t="s">
+        <v>1175</v>
+      </c>
       <c r="C107" t="s">
         <v>61</v>
       </c>
@@ -6829,6 +7153,9 @@
       <c r="A108" t="s">
         <v>44</v>
       </c>
+      <c r="B108" t="s">
+        <v>1175</v>
+      </c>
       <c r="C108" t="s">
         <v>61</v>
       </c>
@@ -6855,6 +7182,9 @@
       <c r="A109" t="s">
         <v>44</v>
       </c>
+      <c r="B109" t="s">
+        <v>1175</v>
+      </c>
       <c r="C109" t="s">
         <v>61</v>
       </c>
@@ -6881,6 +7211,9 @@
       <c r="A110" t="s">
         <v>44</v>
       </c>
+      <c r="B110" t="s">
+        <v>1175</v>
+      </c>
       <c r="C110" t="s">
         <v>61</v>
       </c>
@@ -6907,6 +7240,9 @@
       <c r="A111" t="s">
         <v>44</v>
       </c>
+      <c r="B111" t="s">
+        <v>1175</v>
+      </c>
       <c r="C111" t="s">
         <v>61</v>
       </c>
@@ -6933,6 +7269,9 @@
       <c r="A112" t="s">
         <v>44</v>
       </c>
+      <c r="B112" t="s">
+        <v>1175</v>
+      </c>
       <c r="C112" t="s">
         <v>61</v>
       </c>
@@ -6959,6 +7298,9 @@
       <c r="A113" t="s">
         <v>44</v>
       </c>
+      <c r="B113" t="s">
+        <v>1175</v>
+      </c>
       <c r="C113" t="s">
         <v>61</v>
       </c>
@@ -6985,6 +7327,9 @@
       <c r="A114" t="s">
         <v>44</v>
       </c>
+      <c r="B114" t="s">
+        <v>1175</v>
+      </c>
       <c r="C114" t="s">
         <v>61</v>
       </c>
@@ -7011,6 +7356,9 @@
       <c r="A115" t="s">
         <v>44</v>
       </c>
+      <c r="B115" t="s">
+        <v>1175</v>
+      </c>
       <c r="C115" t="s">
         <v>61</v>
       </c>
@@ -7037,6 +7385,9 @@
       <c r="A116" t="s">
         <v>44</v>
       </c>
+      <c r="B116" t="s">
+        <v>1175</v>
+      </c>
       <c r="C116" t="s">
         <v>61</v>
       </c>
@@ -7063,6 +7414,9 @@
       <c r="A117" t="s">
         <v>44</v>
       </c>
+      <c r="B117" t="s">
+        <v>1175</v>
+      </c>
       <c r="C117" t="s">
         <v>61</v>
       </c>
@@ -7089,6 +7443,9 @@
       <c r="A118" t="s">
         <v>44</v>
       </c>
+      <c r="B118" t="s">
+        <v>1175</v>
+      </c>
       <c r="C118" t="s">
         <v>61</v>
       </c>
@@ -7115,6 +7472,9 @@
       <c r="A119" t="s">
         <v>44</v>
       </c>
+      <c r="B119" t="s">
+        <v>1175</v>
+      </c>
       <c r="C119" t="s">
         <v>61</v>
       </c>
@@ -7141,6 +7501,9 @@
       <c r="A120" t="s">
         <v>44</v>
       </c>
+      <c r="B120" t="s">
+        <v>1175</v>
+      </c>
       <c r="C120" t="s">
         <v>61</v>
       </c>
@@ -7167,6 +7530,9 @@
       <c r="A121" t="s">
         <v>44</v>
       </c>
+      <c r="B121" t="s">
+        <v>1175</v>
+      </c>
       <c r="C121" t="s">
         <v>61</v>
       </c>
@@ -7193,6 +7559,9 @@
       <c r="A122" t="s">
         <v>44</v>
       </c>
+      <c r="B122" t="s">
+        <v>1175</v>
+      </c>
       <c r="C122" t="s">
         <v>62</v>
       </c>
@@ -7219,6 +7588,9 @@
       <c r="A123" t="s">
         <v>44</v>
       </c>
+      <c r="B123" t="s">
+        <v>1175</v>
+      </c>
       <c r="C123" t="s">
         <v>63</v>
       </c>
@@ -7245,6 +7617,9 @@
       <c r="A124" t="s">
         <v>44</v>
       </c>
+      <c r="B124" t="s">
+        <v>1175</v>
+      </c>
       <c r="C124" t="s">
         <v>63</v>
       </c>
@@ -7271,6 +7646,9 @@
       <c r="A125" t="s">
         <v>44</v>
       </c>
+      <c r="B125" t="s">
+        <v>1175</v>
+      </c>
       <c r="C125" t="s">
         <v>63</v>
       </c>
@@ -7297,6 +7675,9 @@
       <c r="A126" t="s">
         <v>44</v>
       </c>
+      <c r="B126" t="s">
+        <v>1175</v>
+      </c>
       <c r="C126" t="s">
         <v>63</v>
       </c>
@@ -7323,6 +7704,9 @@
       <c r="A127" t="s">
         <v>44</v>
       </c>
+      <c r="B127" t="s">
+        <v>1175</v>
+      </c>
       <c r="C127" t="s">
         <v>64</v>
       </c>
@@ -7349,6 +7733,9 @@
       <c r="A128" t="s">
         <v>44</v>
       </c>
+      <c r="B128" t="s">
+        <v>1175</v>
+      </c>
       <c r="C128" t="s">
         <v>64</v>
       </c>
@@ -7375,6 +7762,9 @@
       <c r="A129" t="s">
         <v>44</v>
       </c>
+      <c r="B129" t="s">
+        <v>1175</v>
+      </c>
       <c r="C129" t="s">
         <v>64</v>
       </c>
@@ -7401,6 +7791,9 @@
       <c r="A130" t="s">
         <v>44</v>
       </c>
+      <c r="B130" t="s">
+        <v>1175</v>
+      </c>
       <c r="C130" t="s">
         <v>64</v>
       </c>
@@ -7427,6 +7820,9 @@
       <c r="A131" t="s">
         <v>44</v>
       </c>
+      <c r="B131" t="s">
+        <v>1175</v>
+      </c>
       <c r="C131" t="s">
         <v>64</v>
       </c>
@@ -7453,6 +7849,9 @@
       <c r="A132" t="s">
         <v>44</v>
       </c>
+      <c r="B132" t="s">
+        <v>1175</v>
+      </c>
       <c r="C132" t="s">
         <v>64</v>
       </c>
@@ -7479,6 +7878,9 @@
       <c r="A133" t="s">
         <v>44</v>
       </c>
+      <c r="B133" t="s">
+        <v>1175</v>
+      </c>
       <c r="C133" t="s">
         <v>64</v>
       </c>
@@ -7505,6 +7907,9 @@
       <c r="A134" t="s">
         <v>44</v>
       </c>
+      <c r="B134" t="s">
+        <v>1175</v>
+      </c>
       <c r="C134" t="s">
         <v>64</v>
       </c>
@@ -7531,6 +7936,9 @@
       <c r="A135" t="s">
         <v>44</v>
       </c>
+      <c r="B135" t="s">
+        <v>1175</v>
+      </c>
       <c r="C135" t="s">
         <v>64</v>
       </c>
@@ -7557,6 +7965,9 @@
       <c r="A136" t="s">
         <v>44</v>
       </c>
+      <c r="B136" t="s">
+        <v>1175</v>
+      </c>
       <c r="C136" t="s">
         <v>64</v>
       </c>
@@ -7583,6 +7994,9 @@
       <c r="A137" t="s">
         <v>44</v>
       </c>
+      <c r="B137" t="s">
+        <v>1175</v>
+      </c>
       <c r="C137" t="s">
         <v>64</v>
       </c>
@@ -7609,6 +8023,9 @@
       <c r="A138" t="s">
         <v>44</v>
       </c>
+      <c r="B138" t="s">
+        <v>1175</v>
+      </c>
       <c r="C138" t="s">
         <v>64</v>
       </c>
@@ -7635,6 +8052,9 @@
       <c r="A139" t="s">
         <v>44</v>
       </c>
+      <c r="B139" t="s">
+        <v>1175</v>
+      </c>
       <c r="C139" t="s">
         <v>64</v>
       </c>
@@ -7661,6 +8081,9 @@
       <c r="A140" t="s">
         <v>44</v>
       </c>
+      <c r="B140" t="s">
+        <v>1175</v>
+      </c>
       <c r="C140" t="s">
         <v>64</v>
       </c>
@@ -7687,6 +8110,9 @@
       <c r="A141" t="s">
         <v>44</v>
       </c>
+      <c r="B141" t="s">
+        <v>1175</v>
+      </c>
       <c r="C141" t="s">
         <v>64</v>
       </c>
@@ -7713,6 +8139,9 @@
       <c r="A142" t="s">
         <v>44</v>
       </c>
+      <c r="B142" t="s">
+        <v>1175</v>
+      </c>
       <c r="C142" t="s">
         <v>64</v>
       </c>
@@ -7739,6 +8168,9 @@
       <c r="A143" t="s">
         <v>44</v>
       </c>
+      <c r="B143" t="s">
+        <v>1175</v>
+      </c>
       <c r="C143" t="s">
         <v>64</v>
       </c>
@@ -7765,6 +8197,9 @@
       <c r="A144" t="s">
         <v>44</v>
       </c>
+      <c r="B144" t="s">
+        <v>1175</v>
+      </c>
       <c r="C144" t="s">
         <v>64</v>
       </c>
@@ -7791,6 +8226,9 @@
       <c r="A145" t="s">
         <v>44</v>
       </c>
+      <c r="B145" t="s">
+        <v>1175</v>
+      </c>
       <c r="C145" t="s">
         <v>65</v>
       </c>
@@ -7817,6 +8255,9 @@
       <c r="A146" t="s">
         <v>44</v>
       </c>
+      <c r="B146" t="s">
+        <v>1175</v>
+      </c>
       <c r="C146" t="s">
         <v>65</v>
       </c>
@@ -7843,6 +8284,9 @@
       <c r="A147" t="s">
         <v>44</v>
       </c>
+      <c r="B147" t="s">
+        <v>1175</v>
+      </c>
       <c r="C147" t="s">
         <v>65</v>
       </c>
@@ -7869,6 +8313,9 @@
       <c r="A148" t="s">
         <v>44</v>
       </c>
+      <c r="B148" t="s">
+        <v>1175</v>
+      </c>
       <c r="C148" t="s">
         <v>65</v>
       </c>
@@ -7895,6 +8342,9 @@
       <c r="A149" t="s">
         <v>44</v>
       </c>
+      <c r="B149" t="s">
+        <v>1175</v>
+      </c>
       <c r="C149" t="s">
         <v>65</v>
       </c>
@@ -7921,6 +8371,9 @@
       <c r="A150" t="s">
         <v>44</v>
       </c>
+      <c r="B150" t="s">
+        <v>1175</v>
+      </c>
       <c r="C150" t="s">
         <v>65</v>
       </c>
@@ -7947,6 +8400,9 @@
       <c r="A151" t="s">
         <v>44</v>
       </c>
+      <c r="B151" t="s">
+        <v>1175</v>
+      </c>
       <c r="C151" t="s">
         <v>65</v>
       </c>
@@ -7973,6 +8429,9 @@
       <c r="A152" t="s">
         <v>44</v>
       </c>
+      <c r="B152" t="s">
+        <v>1175</v>
+      </c>
       <c r="C152" t="s">
         <v>66</v>
       </c>
@@ -7999,6 +8458,9 @@
       <c r="A153" t="s">
         <v>44</v>
       </c>
+      <c r="B153" t="s">
+        <v>1175</v>
+      </c>
       <c r="C153" t="s">
         <v>66</v>
       </c>
@@ -8025,6 +8487,9 @@
       <c r="A154" t="s">
         <v>44</v>
       </c>
+      <c r="B154" t="s">
+        <v>1175</v>
+      </c>
       <c r="C154" t="s">
         <v>66</v>
       </c>
@@ -8051,6 +8516,9 @@
       <c r="A155" t="s">
         <v>44</v>
       </c>
+      <c r="B155" t="s">
+        <v>1175</v>
+      </c>
       <c r="C155" t="s">
         <v>66</v>
       </c>
@@ -8077,6 +8545,9 @@
       <c r="A156" t="s">
         <v>44</v>
       </c>
+      <c r="B156" t="s">
+        <v>1175</v>
+      </c>
       <c r="C156" t="s">
         <v>66</v>
       </c>
@@ -8103,6 +8574,9 @@
       <c r="A157" t="s">
         <v>44</v>
       </c>
+      <c r="B157" t="s">
+        <v>1176</v>
+      </c>
       <c r="C157" t="s">
         <v>67</v>
       </c>
@@ -8129,6 +8603,9 @@
       <c r="A158" t="s">
         <v>44</v>
       </c>
+      <c r="B158" t="s">
+        <v>1176</v>
+      </c>
       <c r="C158" t="s">
         <v>67</v>
       </c>
@@ -8155,6 +8632,9 @@
       <c r="A159" t="s">
         <v>44</v>
       </c>
+      <c r="B159" t="s">
+        <v>1176</v>
+      </c>
       <c r="C159" t="s">
         <v>67</v>
       </c>
@@ -8181,6 +8661,9 @@
       <c r="A160" t="s">
         <v>44</v>
       </c>
+      <c r="B160" t="s">
+        <v>1177</v>
+      </c>
       <c r="C160" t="s">
         <v>68</v>
       </c>
@@ -8207,6 +8690,9 @@
       <c r="A161" t="s">
         <v>44</v>
       </c>
+      <c r="B161" t="s">
+        <v>1177</v>
+      </c>
       <c r="C161" t="s">
         <v>68</v>
       </c>
@@ -8233,6 +8719,9 @@
       <c r="A162" t="s">
         <v>44</v>
       </c>
+      <c r="B162" t="s">
+        <v>1177</v>
+      </c>
       <c r="C162" t="s">
         <v>68</v>
       </c>
@@ -8259,6 +8748,9 @@
       <c r="A163" t="s">
         <v>44</v>
       </c>
+      <c r="B163" t="s">
+        <v>1177</v>
+      </c>
       <c r="C163" t="s">
         <v>68</v>
       </c>
@@ -8285,6 +8777,9 @@
       <c r="A164" t="s">
         <v>44</v>
       </c>
+      <c r="B164" t="s">
+        <v>1177</v>
+      </c>
       <c r="C164" t="s">
         <v>69</v>
       </c>
@@ -8311,6 +8806,9 @@
       <c r="A165" t="s">
         <v>44</v>
       </c>
+      <c r="B165" t="s">
+        <v>1177</v>
+      </c>
       <c r="C165" t="s">
         <v>69</v>
       </c>
@@ -8337,6 +8835,9 @@
       <c r="A166" t="s">
         <v>44</v>
       </c>
+      <c r="B166" t="s">
+        <v>1177</v>
+      </c>
       <c r="C166" t="s">
         <v>69</v>
       </c>
@@ -8363,6 +8864,9 @@
       <c r="A167" t="s">
         <v>44</v>
       </c>
+      <c r="B167" t="s">
+        <v>1177</v>
+      </c>
       <c r="C167" t="s">
         <v>69</v>
       </c>
@@ -8389,6 +8893,9 @@
       <c r="A168" t="s">
         <v>44</v>
       </c>
+      <c r="B168" t="s">
+        <v>1177</v>
+      </c>
       <c r="C168" t="s">
         <v>69</v>
       </c>
@@ -8415,6 +8922,9 @@
       <c r="A169" t="s">
         <v>44</v>
       </c>
+      <c r="B169" t="s">
+        <v>1177</v>
+      </c>
       <c r="C169" t="s">
         <v>69</v>
       </c>
@@ -8441,6 +8951,9 @@
       <c r="A170" t="s">
         <v>44</v>
       </c>
+      <c r="B170" t="s">
+        <v>1177</v>
+      </c>
       <c r="C170" t="s">
         <v>69</v>
       </c>
@@ -8467,6 +8980,9 @@
       <c r="A171" t="s">
         <v>44</v>
       </c>
+      <c r="B171" t="s">
+        <v>1177</v>
+      </c>
       <c r="C171" t="s">
         <v>69</v>
       </c>
@@ -8493,6 +9009,9 @@
       <c r="A172" t="s">
         <v>44</v>
       </c>
+      <c r="B172" t="s">
+        <v>1177</v>
+      </c>
       <c r="C172" t="s">
         <v>69</v>
       </c>
@@ -8519,6 +9038,9 @@
       <c r="A173" t="s">
         <v>44</v>
       </c>
+      <c r="B173" t="s">
+        <v>1177</v>
+      </c>
       <c r="C173" t="s">
         <v>69</v>
       </c>
@@ -8545,6 +9067,9 @@
       <c r="A174" t="s">
         <v>44</v>
       </c>
+      <c r="B174" t="s">
+        <v>1177</v>
+      </c>
       <c r="C174" t="s">
         <v>70</v>
       </c>
@@ -8571,6 +9096,9 @@
       <c r="A175" t="s">
         <v>44</v>
       </c>
+      <c r="B175" t="s">
+        <v>1177</v>
+      </c>
       <c r="C175" t="s">
         <v>70</v>
       </c>
@@ -8597,6 +9125,9 @@
       <c r="A176" t="s">
         <v>44</v>
       </c>
+      <c r="B176" t="s">
+        <v>1177</v>
+      </c>
       <c r="C176" t="s">
         <v>70</v>
       </c>
@@ -8623,6 +9154,9 @@
       <c r="A177" t="s">
         <v>44</v>
       </c>
+      <c r="B177" t="s">
+        <v>1177</v>
+      </c>
       <c r="C177" t="s">
         <v>70</v>
       </c>
@@ -8649,6 +9183,9 @@
       <c r="A178" t="s">
         <v>44</v>
       </c>
+      <c r="B178" t="s">
+        <v>1177</v>
+      </c>
       <c r="C178" t="s">
         <v>70</v>
       </c>
@@ -8675,6 +9212,9 @@
       <c r="A179" t="s">
         <v>44</v>
       </c>
+      <c r="B179" t="s">
+        <v>1177</v>
+      </c>
       <c r="C179" t="s">
         <v>70</v>
       </c>
@@ -8701,6 +9241,9 @@
       <c r="A180" t="s">
         <v>44</v>
       </c>
+      <c r="B180" t="s">
+        <v>1177</v>
+      </c>
       <c r="C180" t="s">
         <v>70</v>
       </c>
@@ -8727,6 +9270,9 @@
       <c r="A181" t="s">
         <v>44</v>
       </c>
+      <c r="B181" t="s">
+        <v>1177</v>
+      </c>
       <c r="C181" t="s">
         <v>70</v>
       </c>
@@ -8753,6 +9299,9 @@
       <c r="A182" t="s">
         <v>44</v>
       </c>
+      <c r="B182" t="s">
+        <v>1177</v>
+      </c>
       <c r="C182" t="s">
         <v>70</v>
       </c>
@@ -8779,6 +9328,9 @@
       <c r="A183" t="s">
         <v>44</v>
       </c>
+      <c r="B183" t="s">
+        <v>1177</v>
+      </c>
       <c r="C183" t="s">
         <v>70</v>
       </c>
@@ -8805,6 +9357,9 @@
       <c r="A184" t="s">
         <v>44</v>
       </c>
+      <c r="B184" t="s">
+        <v>1177</v>
+      </c>
       <c r="C184" t="s">
         <v>70</v>
       </c>
@@ -8831,6 +9386,9 @@
       <c r="A185" t="s">
         <v>44</v>
       </c>
+      <c r="B185" t="s">
+        <v>1177</v>
+      </c>
       <c r="C185" t="s">
         <v>70</v>
       </c>
@@ -8857,6 +9415,9 @@
       <c r="A186" t="s">
         <v>44</v>
       </c>
+      <c r="B186" t="s">
+        <v>1177</v>
+      </c>
       <c r="C186" t="s">
         <v>70</v>
       </c>
@@ -8883,6 +9444,9 @@
       <c r="A187" t="s">
         <v>44</v>
       </c>
+      <c r="B187" t="s">
+        <v>1177</v>
+      </c>
       <c r="C187" t="s">
         <v>70</v>
       </c>
@@ -8909,6 +9473,9 @@
       <c r="A188" t="s">
         <v>44</v>
       </c>
+      <c r="B188" t="s">
+        <v>1177</v>
+      </c>
       <c r="C188" t="s">
         <v>70</v>
       </c>
@@ -8935,6 +9502,9 @@
       <c r="A189" t="s">
         <v>44</v>
       </c>
+      <c r="B189" t="s">
+        <v>1177</v>
+      </c>
       <c r="C189" t="s">
         <v>71</v>
       </c>
@@ -8961,6 +9531,9 @@
       <c r="A190" t="s">
         <v>44</v>
       </c>
+      <c r="B190" t="s">
+        <v>1177</v>
+      </c>
       <c r="C190" t="s">
         <v>71</v>
       </c>
@@ -8987,6 +9560,9 @@
       <c r="A191" t="s">
         <v>44</v>
       </c>
+      <c r="B191" t="s">
+        <v>1177</v>
+      </c>
       <c r="C191" t="s">
         <v>71</v>
       </c>
@@ -9013,6 +9589,9 @@
       <c r="A192" t="s">
         <v>44</v>
       </c>
+      <c r="B192" t="s">
+        <v>1177</v>
+      </c>
       <c r="C192" t="s">
         <v>71</v>
       </c>
@@ -9039,6 +9618,9 @@
       <c r="A193" t="s">
         <v>44</v>
       </c>
+      <c r="B193" t="s">
+        <v>1177</v>
+      </c>
       <c r="C193" t="s">
         <v>71</v>
       </c>
@@ -9065,6 +9647,9 @@
       <c r="A194" t="s">
         <v>44</v>
       </c>
+      <c r="B194" t="s">
+        <v>1177</v>
+      </c>
       <c r="C194" t="s">
         <v>71</v>
       </c>
@@ -9091,6 +9676,9 @@
       <c r="A195" t="s">
         <v>44</v>
       </c>
+      <c r="B195" t="s">
+        <v>1177</v>
+      </c>
       <c r="C195" t="s">
         <v>71</v>
       </c>
@@ -9117,6 +9705,9 @@
       <c r="A196" t="s">
         <v>44</v>
       </c>
+      <c r="B196" t="s">
+        <v>1177</v>
+      </c>
       <c r="C196" t="s">
         <v>72</v>
       </c>
@@ -9143,6 +9734,9 @@
       <c r="A197" t="s">
         <v>44</v>
       </c>
+      <c r="B197" t="s">
+        <v>1177</v>
+      </c>
       <c r="C197" t="s">
         <v>72</v>
       </c>
@@ -9169,6 +9763,9 @@
       <c r="A198" t="s">
         <v>44</v>
       </c>
+      <c r="B198" t="s">
+        <v>1177</v>
+      </c>
       <c r="C198" t="s">
         <v>72</v>
       </c>
@@ -9195,6 +9792,9 @@
       <c r="A199" t="s">
         <v>44</v>
       </c>
+      <c r="B199" t="s">
+        <v>1177</v>
+      </c>
       <c r="C199" t="s">
         <v>72</v>
       </c>
@@ -9221,6 +9821,9 @@
       <c r="A200" t="s">
         <v>44</v>
       </c>
+      <c r="B200" t="s">
+        <v>1177</v>
+      </c>
       <c r="C200" t="s">
         <v>72</v>
       </c>
@@ -9247,6 +9850,9 @@
       <c r="A201" t="s">
         <v>44</v>
       </c>
+      <c r="B201" t="s">
+        <v>1177</v>
+      </c>
       <c r="C201" t="s">
         <v>72</v>
       </c>
@@ -9273,6 +9879,9 @@
       <c r="A202" t="s">
         <v>44</v>
       </c>
+      <c r="B202" t="s">
+        <v>1177</v>
+      </c>
       <c r="C202" t="s">
         <v>72</v>
       </c>
@@ -9299,6 +9908,9 @@
       <c r="A203" t="s">
         <v>44</v>
       </c>
+      <c r="B203" t="s">
+        <v>1177</v>
+      </c>
       <c r="C203" t="s">
         <v>73</v>
       </c>
@@ -9325,6 +9937,9 @@
       <c r="A204" t="s">
         <v>44</v>
       </c>
+      <c r="B204" t="s">
+        <v>1177</v>
+      </c>
       <c r="C204" t="s">
         <v>73</v>
       </c>
@@ -9351,6 +9966,9 @@
       <c r="A205" t="s">
         <v>44</v>
       </c>
+      <c r="B205" t="s">
+        <v>1177</v>
+      </c>
       <c r="C205" t="s">
         <v>73</v>
       </c>
@@ -9377,6 +9995,9 @@
       <c r="A206" t="s">
         <v>44</v>
       </c>
+      <c r="B206" t="s">
+        <v>1177</v>
+      </c>
       <c r="C206" t="s">
         <v>73</v>
       </c>
@@ -9403,6 +10024,9 @@
       <c r="A207" t="s">
         <v>44</v>
       </c>
+      <c r="B207" t="s">
+        <v>1177</v>
+      </c>
       <c r="C207" t="s">
         <v>73</v>
       </c>
@@ -9429,6 +10053,9 @@
       <c r="A208" t="s">
         <v>44</v>
       </c>
+      <c r="B208" t="s">
+        <v>1177</v>
+      </c>
       <c r="C208" t="s">
         <v>73</v>
       </c>
@@ -9455,6 +10082,9 @@
       <c r="A209" t="s">
         <v>44</v>
       </c>
+      <c r="B209" t="s">
+        <v>1177</v>
+      </c>
       <c r="C209" t="s">
         <v>73</v>
       </c>
@@ -9481,6 +10111,9 @@
       <c r="A210" t="s">
         <v>44</v>
       </c>
+      <c r="B210" t="s">
+        <v>1177</v>
+      </c>
       <c r="C210" t="s">
         <v>73</v>
       </c>
@@ -9507,6 +10140,9 @@
       <c r="A211" t="s">
         <v>44</v>
       </c>
+      <c r="B211" t="s">
+        <v>1177</v>
+      </c>
       <c r="C211" t="s">
         <v>73</v>
       </c>
@@ -9533,6 +10169,9 @@
       <c r="A212" t="s">
         <v>44</v>
       </c>
+      <c r="B212" t="s">
+        <v>1177</v>
+      </c>
       <c r="C212" t="s">
         <v>73</v>
       </c>
@@ -9559,6 +10198,9 @@
       <c r="A213" t="s">
         <v>44</v>
       </c>
+      <c r="B213" t="s">
+        <v>1177</v>
+      </c>
       <c r="C213" t="s">
         <v>73</v>
       </c>
@@ -9585,6 +10227,9 @@
       <c r="A214" t="s">
         <v>44</v>
       </c>
+      <c r="B214" t="s">
+        <v>1177</v>
+      </c>
       <c r="C214" t="s">
         <v>74</v>
       </c>
@@ -9611,6 +10256,9 @@
       <c r="A215" t="s">
         <v>44</v>
       </c>
+      <c r="B215" t="s">
+        <v>1177</v>
+      </c>
       <c r="C215" t="s">
         <v>74</v>
       </c>
@@ -9637,6 +10285,9 @@
       <c r="A216" t="s">
         <v>44</v>
       </c>
+      <c r="B216" t="s">
+        <v>1177</v>
+      </c>
       <c r="C216" t="s">
         <v>74</v>
       </c>
@@ -9663,6 +10314,9 @@
       <c r="A217" t="s">
         <v>44</v>
       </c>
+      <c r="B217" t="s">
+        <v>1177</v>
+      </c>
       <c r="C217" t="s">
         <v>74</v>
       </c>
@@ -9689,6 +10343,9 @@
       <c r="A218" t="s">
         <v>44</v>
       </c>
+      <c r="B218" t="s">
+        <v>1177</v>
+      </c>
       <c r="C218" t="s">
         <v>74</v>
       </c>
@@ -9715,6 +10372,9 @@
       <c r="A219" t="s">
         <v>44</v>
       </c>
+      <c r="B219" t="s">
+        <v>1177</v>
+      </c>
       <c r="C219" t="s">
         <v>74</v>
       </c>
@@ -9741,6 +10401,9 @@
       <c r="A220" t="s">
         <v>44</v>
       </c>
+      <c r="B220" t="s">
+        <v>1177</v>
+      </c>
       <c r="C220" t="s">
         <v>74</v>
       </c>
@@ -9767,6 +10430,9 @@
       <c r="A221" t="s">
         <v>44</v>
       </c>
+      <c r="B221" t="s">
+        <v>1177</v>
+      </c>
       <c r="C221" t="s">
         <v>74</v>
       </c>
@@ -9793,6 +10459,9 @@
       <c r="A222" t="s">
         <v>44</v>
       </c>
+      <c r="B222" t="s">
+        <v>1177</v>
+      </c>
       <c r="C222" t="s">
         <v>74</v>
       </c>
@@ -9819,6 +10488,9 @@
       <c r="A223" t="s">
         <v>44</v>
       </c>
+      <c r="B223" t="s">
+        <v>1177</v>
+      </c>
       <c r="C223" t="s">
         <v>74</v>
       </c>
@@ -9845,6 +10517,9 @@
       <c r="A224" t="s">
         <v>44</v>
       </c>
+      <c r="B224" t="s">
+        <v>1177</v>
+      </c>
       <c r="C224" t="s">
         <v>74</v>
       </c>
@@ -9871,6 +10546,9 @@
       <c r="A225" t="s">
         <v>44</v>
       </c>
+      <c r="B225" t="s">
+        <v>1177</v>
+      </c>
       <c r="C225" t="s">
         <v>74</v>
       </c>
@@ -9897,6 +10575,9 @@
       <c r="A226" t="s">
         <v>44</v>
       </c>
+      <c r="B226" t="s">
+        <v>1177</v>
+      </c>
       <c r="C226" t="s">
         <v>74</v>
       </c>
@@ -9923,6 +10604,9 @@
       <c r="A227" t="s">
         <v>44</v>
       </c>
+      <c r="B227" t="s">
+        <v>1177</v>
+      </c>
       <c r="C227" t="s">
         <v>74</v>
       </c>
@@ -9949,6 +10633,9 @@
       <c r="A228" t="s">
         <v>44</v>
       </c>
+      <c r="B228" t="s">
+        <v>1177</v>
+      </c>
       <c r="C228" t="s">
         <v>74</v>
       </c>
@@ -9975,6 +10662,9 @@
       <c r="A229" t="s">
         <v>44</v>
       </c>
+      <c r="B229" t="s">
+        <v>1177</v>
+      </c>
       <c r="C229" t="s">
         <v>74</v>
       </c>
@@ -10001,6 +10691,9 @@
       <c r="A230" t="s">
         <v>44</v>
       </c>
+      <c r="B230" t="s">
+        <v>1177</v>
+      </c>
       <c r="C230" t="s">
         <v>74</v>
       </c>
@@ -10027,6 +10720,9 @@
       <c r="A231" t="s">
         <v>44</v>
       </c>
+      <c r="B231" t="s">
+        <v>1177</v>
+      </c>
       <c r="C231" t="s">
         <v>74</v>
       </c>
@@ -10053,6 +10749,9 @@
       <c r="A232" t="s">
         <v>44</v>
       </c>
+      <c r="B232" t="s">
+        <v>1177</v>
+      </c>
       <c r="C232" t="s">
         <v>74</v>
       </c>
@@ -10079,6 +10778,9 @@
       <c r="A233" t="s">
         <v>44</v>
       </c>
+      <c r="B233" t="s">
+        <v>1177</v>
+      </c>
       <c r="C233" t="s">
         <v>74</v>
       </c>
@@ -10105,6 +10807,9 @@
       <c r="A234" t="s">
         <v>44</v>
       </c>
+      <c r="B234" t="s">
+        <v>1177</v>
+      </c>
       <c r="C234" t="s">
         <v>74</v>
       </c>
@@ -10131,6 +10836,9 @@
       <c r="A235" t="s">
         <v>44</v>
       </c>
+      <c r="B235" t="s">
+        <v>1177</v>
+      </c>
       <c r="C235" t="s">
         <v>74</v>
       </c>
@@ -10157,6 +10865,9 @@
       <c r="A236" t="s">
         <v>44</v>
       </c>
+      <c r="B236" t="s">
+        <v>1177</v>
+      </c>
       <c r="C236" t="s">
         <v>74</v>
       </c>
@@ -10183,6 +10894,9 @@
       <c r="A237" t="s">
         <v>44</v>
       </c>
+      <c r="B237" t="s">
+        <v>1177</v>
+      </c>
       <c r="C237" t="s">
         <v>74</v>
       </c>
@@ -10209,6 +10923,9 @@
       <c r="A238" t="s">
         <v>44</v>
       </c>
+      <c r="B238" t="s">
+        <v>1177</v>
+      </c>
       <c r="C238" t="s">
         <v>74</v>
       </c>
@@ -10235,6 +10952,9 @@
       <c r="A239" t="s">
         <v>44</v>
       </c>
+      <c r="B239" t="s">
+        <v>1177</v>
+      </c>
       <c r="C239" t="s">
         <v>74</v>
       </c>
@@ -10261,6 +10981,9 @@
       <c r="A240" t="s">
         <v>44</v>
       </c>
+      <c r="B240" t="s">
+        <v>1177</v>
+      </c>
       <c r="C240" t="s">
         <v>74</v>
       </c>
@@ -10287,6 +11010,9 @@
       <c r="A241" t="s">
         <v>44</v>
       </c>
+      <c r="B241" t="s">
+        <v>1177</v>
+      </c>
       <c r="C241" t="s">
         <v>74</v>
       </c>
@@ -10313,6 +11039,9 @@
       <c r="A242" t="s">
         <v>44</v>
       </c>
+      <c r="B242" t="s">
+        <v>1177</v>
+      </c>
       <c r="C242" t="s">
         <v>74</v>
       </c>
@@ -10339,6 +11068,9 @@
       <c r="A243" t="s">
         <v>44</v>
       </c>
+      <c r="B243" t="s">
+        <v>1177</v>
+      </c>
       <c r="C243" t="s">
         <v>74</v>
       </c>
@@ -10365,6 +11097,9 @@
       <c r="A244" t="s">
         <v>44</v>
       </c>
+      <c r="B244" t="s">
+        <v>1177</v>
+      </c>
       <c r="C244" t="s">
         <v>74</v>
       </c>
@@ -10391,6 +11126,9 @@
       <c r="A245" t="s">
         <v>44</v>
       </c>
+      <c r="B245" t="s">
+        <v>1177</v>
+      </c>
       <c r="C245" t="s">
         <v>74</v>
       </c>
@@ -10417,6 +11155,9 @@
       <c r="A246" t="s">
         <v>44</v>
       </c>
+      <c r="B246" t="s">
+        <v>1177</v>
+      </c>
       <c r="C246" t="s">
         <v>75</v>
       </c>
@@ -10443,6 +11184,9 @@
       <c r="A247" t="s">
         <v>44</v>
       </c>
+      <c r="B247" t="s">
+        <v>1177</v>
+      </c>
       <c r="C247" t="s">
         <v>75</v>
       </c>
@@ -10469,6 +11213,9 @@
       <c r="A248" t="s">
         <v>44</v>
       </c>
+      <c r="B248" t="s">
+        <v>1177</v>
+      </c>
       <c r="C248" t="s">
         <v>75</v>
       </c>
@@ -10495,6 +11242,9 @@
       <c r="A249" t="s">
         <v>44</v>
       </c>
+      <c r="B249" t="s">
+        <v>1177</v>
+      </c>
       <c r="C249" t="s">
         <v>76</v>
       </c>
@@ -10521,6 +11271,9 @@
       <c r="A250" t="s">
         <v>44</v>
       </c>
+      <c r="B250" t="s">
+        <v>1178</v>
+      </c>
       <c r="C250" t="s">
         <v>77</v>
       </c>
@@ -10547,6 +11300,9 @@
       <c r="A251" t="s">
         <v>44</v>
       </c>
+      <c r="B251" t="s">
+        <v>1178</v>
+      </c>
       <c r="C251" t="s">
         <v>77</v>
       </c>
@@ -10573,6 +11329,9 @@
       <c r="A252" t="s">
         <v>44</v>
       </c>
+      <c r="B252" t="s">
+        <v>1178</v>
+      </c>
       <c r="C252" t="s">
         <v>77</v>
       </c>
@@ -10599,6 +11358,9 @@
       <c r="A253" t="s">
         <v>44</v>
       </c>
+      <c r="B253" t="s">
+        <v>1178</v>
+      </c>
       <c r="C253" t="s">
         <v>78</v>
       </c>
@@ -10625,6 +11387,9 @@
       <c r="A254" t="s">
         <v>44</v>
       </c>
+      <c r="B254" t="s">
+        <v>1178</v>
+      </c>
       <c r="C254" t="s">
         <v>78</v>
       </c>
@@ -10651,6 +11416,9 @@
       <c r="A255" t="s">
         <v>44</v>
       </c>
+      <c r="B255" t="s">
+        <v>1178</v>
+      </c>
       <c r="C255" t="s">
         <v>78</v>
       </c>
@@ -10677,6 +11445,9 @@
       <c r="A256" t="s">
         <v>44</v>
       </c>
+      <c r="B256" t="s">
+        <v>1178</v>
+      </c>
       <c r="C256" t="s">
         <v>78</v>
       </c>
@@ -10703,6 +11474,9 @@
       <c r="A257" t="s">
         <v>44</v>
       </c>
+      <c r="B257" t="s">
+        <v>1178</v>
+      </c>
       <c r="C257" t="s">
         <v>78</v>
       </c>
@@ -10729,6 +11503,9 @@
       <c r="A258" t="s">
         <v>44</v>
       </c>
+      <c r="B258" t="s">
+        <v>1178</v>
+      </c>
       <c r="C258" t="s">
         <v>79</v>
       </c>
@@ -10755,6 +11532,9 @@
       <c r="A259" t="s">
         <v>44</v>
       </c>
+      <c r="B259" t="s">
+        <v>1178</v>
+      </c>
       <c r="C259" t="s">
         <v>79</v>
       </c>
@@ -10781,6 +11561,9 @@
       <c r="A260" t="s">
         <v>44</v>
       </c>
+      <c r="B260" t="s">
+        <v>1178</v>
+      </c>
       <c r="C260" t="s">
         <v>79</v>
       </c>
@@ -10807,6 +11590,9 @@
       <c r="A261" t="s">
         <v>44</v>
       </c>
+      <c r="B261" t="s">
+        <v>1178</v>
+      </c>
       <c r="C261" t="s">
         <v>79</v>
       </c>
@@ -10833,6 +11619,9 @@
       <c r="A262" t="s">
         <v>44</v>
       </c>
+      <c r="B262" t="s">
+        <v>1178</v>
+      </c>
       <c r="C262" t="s">
         <v>79</v>
       </c>
@@ -10859,6 +11648,9 @@
       <c r="A263" t="s">
         <v>44</v>
       </c>
+      <c r="B263" t="s">
+        <v>1178</v>
+      </c>
       <c r="C263" t="s">
         <v>79</v>
       </c>
@@ -10885,6 +11677,9 @@
       <c r="A264" t="s">
         <v>44</v>
       </c>
+      <c r="B264" t="s">
+        <v>1178</v>
+      </c>
       <c r="C264" t="s">
         <v>80</v>
       </c>
@@ -10911,6 +11706,9 @@
       <c r="A265" t="s">
         <v>44</v>
       </c>
+      <c r="B265" t="s">
+        <v>1178</v>
+      </c>
       <c r="C265" t="s">
         <v>80</v>
       </c>
@@ -10937,6 +11735,9 @@
       <c r="A266" t="s">
         <v>44</v>
       </c>
+      <c r="B266" t="s">
+        <v>1178</v>
+      </c>
       <c r="C266" t="s">
         <v>80</v>
       </c>
@@ -10963,6 +11764,9 @@
       <c r="A267" t="s">
         <v>44</v>
       </c>
+      <c r="B267" t="s">
+        <v>1178</v>
+      </c>
       <c r="C267" t="s">
         <v>80</v>
       </c>
@@ -10989,6 +11793,9 @@
       <c r="A268" t="s">
         <v>44</v>
       </c>
+      <c r="B268" t="s">
+        <v>1178</v>
+      </c>
       <c r="C268" t="s">
         <v>80</v>
       </c>
@@ -11015,6 +11822,9 @@
       <c r="A269" t="s">
         <v>44</v>
       </c>
+      <c r="B269" t="s">
+        <v>1178</v>
+      </c>
       <c r="C269" t="s">
         <v>80</v>
       </c>
@@ -11041,6 +11851,9 @@
       <c r="A270" t="s">
         <v>44</v>
       </c>
+      <c r="B270" t="s">
+        <v>1178</v>
+      </c>
       <c r="C270" t="s">
         <v>80</v>
       </c>
@@ -11067,6 +11880,9 @@
       <c r="A271" t="s">
         <v>44</v>
       </c>
+      <c r="B271" t="s">
+        <v>1178</v>
+      </c>
       <c r="C271" t="s">
         <v>80</v>
       </c>
@@ -11093,6 +11909,9 @@
       <c r="A272" t="s">
         <v>44</v>
       </c>
+      <c r="B272" t="s">
+        <v>1178</v>
+      </c>
       <c r="C272" t="s">
         <v>80</v>
       </c>
@@ -11119,6 +11938,9 @@
       <c r="A273" t="s">
         <v>44</v>
       </c>
+      <c r="B273" t="s">
+        <v>1178</v>
+      </c>
       <c r="C273" t="s">
         <v>80</v>
       </c>
@@ -11145,6 +11967,9 @@
       <c r="A274" t="s">
         <v>44</v>
       </c>
+      <c r="B274" t="s">
+        <v>1178</v>
+      </c>
       <c r="C274" t="s">
         <v>80</v>
       </c>
@@ -11171,6 +11996,9 @@
       <c r="A275" t="s">
         <v>44</v>
       </c>
+      <c r="B275" t="s">
+        <v>1178</v>
+      </c>
       <c r="C275" t="s">
         <v>80</v>
       </c>
@@ -11197,6 +12025,9 @@
       <c r="A276" t="s">
         <v>44</v>
       </c>
+      <c r="B276" t="s">
+        <v>1178</v>
+      </c>
       <c r="C276" t="s">
         <v>80</v>
       </c>
@@ -11223,6 +12054,9 @@
       <c r="A277" t="s">
         <v>44</v>
       </c>
+      <c r="B277" t="s">
+        <v>1178</v>
+      </c>
       <c r="C277" t="s">
         <v>80</v>
       </c>
@@ -11249,6 +12083,9 @@
       <c r="A278" t="s">
         <v>44</v>
       </c>
+      <c r="B278" t="s">
+        <v>1178</v>
+      </c>
       <c r="C278" t="s">
         <v>80</v>
       </c>
@@ -11275,6 +12112,9 @@
       <c r="A279" t="s">
         <v>44</v>
       </c>
+      <c r="B279" t="s">
+        <v>1178</v>
+      </c>
       <c r="C279" t="s">
         <v>80</v>
       </c>
@@ -11301,6 +12141,9 @@
       <c r="A280" t="s">
         <v>44</v>
       </c>
+      <c r="B280" t="s">
+        <v>1178</v>
+      </c>
       <c r="C280" t="s">
         <v>80</v>
       </c>
@@ -11327,6 +12170,9 @@
       <c r="A281" t="s">
         <v>44</v>
       </c>
+      <c r="B281" t="s">
+        <v>1178</v>
+      </c>
       <c r="C281" t="s">
         <v>80</v>
       </c>
@@ -11353,6 +12199,9 @@
       <c r="A282" t="s">
         <v>44</v>
       </c>
+      <c r="B282" t="s">
+        <v>1178</v>
+      </c>
       <c r="C282" t="s">
         <v>80</v>
       </c>
@@ -11379,6 +12228,9 @@
       <c r="A283" t="s">
         <v>44</v>
       </c>
+      <c r="B283" t="s">
+        <v>1178</v>
+      </c>
       <c r="C283" t="s">
         <v>80</v>
       </c>
@@ -11405,6 +12257,9 @@
       <c r="A284" t="s">
         <v>44</v>
       </c>
+      <c r="B284" t="s">
+        <v>1178</v>
+      </c>
       <c r="C284" t="s">
         <v>80</v>
       </c>
@@ -11431,6 +12286,9 @@
       <c r="A285" t="s">
         <v>44</v>
       </c>
+      <c r="B285" t="s">
+        <v>1178</v>
+      </c>
       <c r="C285" t="s">
         <v>80</v>
       </c>
@@ -11457,6 +12315,9 @@
       <c r="A286" t="s">
         <v>44</v>
       </c>
+      <c r="B286" t="s">
+        <v>1178</v>
+      </c>
       <c r="C286" t="s">
         <v>80</v>
       </c>
@@ -11483,6 +12344,9 @@
       <c r="A287" t="s">
         <v>44</v>
       </c>
+      <c r="B287" t="s">
+        <v>1178</v>
+      </c>
       <c r="C287" t="s">
         <v>80</v>
       </c>
@@ -11509,6 +12373,9 @@
       <c r="A288" t="s">
         <v>44</v>
       </c>
+      <c r="B288" t="s">
+        <v>1178</v>
+      </c>
       <c r="C288" t="s">
         <v>81</v>
       </c>
@@ -11535,6 +12402,9 @@
       <c r="A289" t="s">
         <v>44</v>
       </c>
+      <c r="B289" t="s">
+        <v>1178</v>
+      </c>
       <c r="C289" t="s">
         <v>81</v>
       </c>
@@ -11561,6 +12431,9 @@
       <c r="A290" t="s">
         <v>44</v>
       </c>
+      <c r="B290" t="s">
+        <v>1178</v>
+      </c>
       <c r="C290" t="s">
         <v>81</v>
       </c>
@@ -11587,6 +12460,9 @@
       <c r="A291" t="s">
         <v>44</v>
       </c>
+      <c r="B291" t="s">
+        <v>1178</v>
+      </c>
       <c r="C291" t="s">
         <v>81</v>
       </c>
@@ -11613,6 +12489,9 @@
       <c r="A292" t="s">
         <v>44</v>
       </c>
+      <c r="B292" t="s">
+        <v>1178</v>
+      </c>
       <c r="C292" t="s">
         <v>81</v>
       </c>
@@ -11639,6 +12518,9 @@
       <c r="A293" t="s">
         <v>44</v>
       </c>
+      <c r="B293" t="s">
+        <v>1178</v>
+      </c>
       <c r="C293" t="s">
         <v>81</v>
       </c>
@@ -11665,6 +12547,9 @@
       <c r="A294" t="s">
         <v>44</v>
       </c>
+      <c r="B294" t="s">
+        <v>1178</v>
+      </c>
       <c r="C294" t="s">
         <v>81</v>
       </c>
@@ -11691,6 +12576,9 @@
       <c r="A295" t="s">
         <v>44</v>
       </c>
+      <c r="B295" t="s">
+        <v>1178</v>
+      </c>
       <c r="C295" t="s">
         <v>81</v>
       </c>
@@ -11717,6 +12605,9 @@
       <c r="A296" t="s">
         <v>44</v>
       </c>
+      <c r="B296" t="s">
+        <v>1178</v>
+      </c>
       <c r="C296" t="s">
         <v>81</v>
       </c>
@@ -11743,6 +12634,9 @@
       <c r="A297" t="s">
         <v>44</v>
       </c>
+      <c r="B297" t="s">
+        <v>1178</v>
+      </c>
       <c r="C297" t="s">
         <v>81</v>
       </c>
@@ -11769,6 +12663,9 @@
       <c r="A298" t="s">
         <v>44</v>
       </c>
+      <c r="B298" t="s">
+        <v>1178</v>
+      </c>
       <c r="C298" t="s">
         <v>81</v>
       </c>
@@ -11795,6 +12692,9 @@
       <c r="A299" t="s">
         <v>44</v>
       </c>
+      <c r="B299" t="s">
+        <v>1178</v>
+      </c>
       <c r="C299" t="s">
         <v>81</v>
       </c>
@@ -11821,6 +12721,9 @@
       <c r="A300" t="s">
         <v>44</v>
       </c>
+      <c r="B300" t="s">
+        <v>1178</v>
+      </c>
       <c r="C300" t="s">
         <v>81</v>
       </c>
@@ -11847,6 +12750,9 @@
       <c r="A301" t="s">
         <v>44</v>
       </c>
+      <c r="B301" t="s">
+        <v>1178</v>
+      </c>
       <c r="C301" t="s">
         <v>81</v>
       </c>
@@ -11873,6 +12779,9 @@
       <c r="A302" t="s">
         <v>44</v>
       </c>
+      <c r="B302" t="s">
+        <v>1178</v>
+      </c>
       <c r="C302" t="s">
         <v>81</v>
       </c>
@@ -11899,6 +12808,9 @@
       <c r="A303" t="s">
         <v>44</v>
       </c>
+      <c r="B303" t="s">
+        <v>1178</v>
+      </c>
       <c r="C303" t="s">
         <v>81</v>
       </c>
@@ -11925,6 +12837,9 @@
       <c r="A304" t="s">
         <v>44</v>
       </c>
+      <c r="B304" t="s">
+        <v>1178</v>
+      </c>
       <c r="C304" t="s">
         <v>81</v>
       </c>
@@ -11951,6 +12866,9 @@
       <c r="A305" t="s">
         <v>44</v>
       </c>
+      <c r="B305" t="s">
+        <v>1178</v>
+      </c>
       <c r="C305" t="s">
         <v>81</v>
       </c>
@@ -11977,6 +12895,9 @@
       <c r="A306" t="s">
         <v>44</v>
       </c>
+      <c r="B306" t="s">
+        <v>1178</v>
+      </c>
       <c r="C306" t="s">
         <v>81</v>
       </c>
@@ -12003,6 +12924,9 @@
       <c r="A307" t="s">
         <v>44</v>
       </c>
+      <c r="B307" t="s">
+        <v>1178</v>
+      </c>
       <c r="C307" t="s">
         <v>81</v>
       </c>
@@ -12029,6 +12953,9 @@
       <c r="A308" t="s">
         <v>44</v>
       </c>
+      <c r="B308" t="s">
+        <v>1178</v>
+      </c>
       <c r="C308" t="s">
         <v>81</v>
       </c>
@@ -12055,6 +12982,9 @@
       <c r="A309" t="s">
         <v>44</v>
       </c>
+      <c r="B309" t="s">
+        <v>1178</v>
+      </c>
       <c r="C309" t="s">
         <v>82</v>
       </c>
@@ -12081,6 +13011,9 @@
       <c r="A310" t="s">
         <v>44</v>
       </c>
+      <c r="B310" t="s">
+        <v>1178</v>
+      </c>
       <c r="C310" t="s">
         <v>83</v>
       </c>
@@ -12107,6 +13040,9 @@
       <c r="A311" t="s">
         <v>44</v>
       </c>
+      <c r="B311" t="s">
+        <v>1178</v>
+      </c>
       <c r="C311" t="s">
         <v>83</v>
       </c>
@@ -12133,6 +13069,9 @@
       <c r="A312" t="s">
         <v>44</v>
       </c>
+      <c r="B312" t="s">
+        <v>1178</v>
+      </c>
       <c r="C312" t="s">
         <v>83</v>
       </c>
@@ -12159,6 +13098,9 @@
       <c r="A313" t="s">
         <v>44</v>
       </c>
+      <c r="B313" t="s">
+        <v>1178</v>
+      </c>
       <c r="C313" t="s">
         <v>83</v>
       </c>
@@ -12185,6 +13127,9 @@
       <c r="A314" t="s">
         <v>44</v>
       </c>
+      <c r="B314" t="s">
+        <v>1178</v>
+      </c>
       <c r="C314" t="s">
         <v>83</v>
       </c>
@@ -12211,6 +13156,9 @@
       <c r="A315" t="s">
         <v>44</v>
       </c>
+      <c r="B315" t="s">
+        <v>1178</v>
+      </c>
       <c r="C315" t="s">
         <v>83</v>
       </c>
@@ -12237,6 +13185,9 @@
       <c r="A316" t="s">
         <v>44</v>
       </c>
+      <c r="B316" t="s">
+        <v>1178</v>
+      </c>
       <c r="C316" t="s">
         <v>83</v>
       </c>
@@ -12263,6 +13214,9 @@
       <c r="A317" t="s">
         <v>44</v>
       </c>
+      <c r="B317" t="s">
+        <v>1178</v>
+      </c>
       <c r="C317" t="s">
         <v>83</v>
       </c>
@@ -12289,6 +13243,9 @@
       <c r="A318" t="s">
         <v>44</v>
       </c>
+      <c r="B318" t="s">
+        <v>1178</v>
+      </c>
       <c r="C318" t="s">
         <v>83</v>
       </c>
@@ -12315,6 +13272,9 @@
       <c r="A319" t="s">
         <v>44</v>
       </c>
+      <c r="B319" t="s">
+        <v>1178</v>
+      </c>
       <c r="C319" t="s">
         <v>83</v>
       </c>
@@ -12341,6 +13301,9 @@
       <c r="A320" t="s">
         <v>44</v>
       </c>
+      <c r="B320" t="s">
+        <v>1178</v>
+      </c>
       <c r="C320" t="s">
         <v>83</v>
       </c>
@@ -12367,6 +13330,9 @@
       <c r="A321" t="s">
         <v>44</v>
       </c>
+      <c r="B321" t="s">
+        <v>1178</v>
+      </c>
       <c r="C321" t="s">
         <v>83</v>
       </c>
@@ -12393,6 +13359,9 @@
       <c r="A322" t="s">
         <v>44</v>
       </c>
+      <c r="B322" t="s">
+        <v>1178</v>
+      </c>
       <c r="C322" t="s">
         <v>83</v>
       </c>
@@ -12419,6 +13388,9 @@
       <c r="A323" t="s">
         <v>44</v>
       </c>
+      <c r="B323" t="s">
+        <v>1178</v>
+      </c>
       <c r="C323" t="s">
         <v>84</v>
       </c>
@@ -12445,6 +13417,9 @@
       <c r="A324" t="s">
         <v>44</v>
       </c>
+      <c r="B324" t="s">
+        <v>1178</v>
+      </c>
       <c r="C324" t="s">
         <v>84</v>
       </c>
@@ -12471,6 +13446,9 @@
       <c r="A325" t="s">
         <v>44</v>
       </c>
+      <c r="B325" t="s">
+        <v>1178</v>
+      </c>
       <c r="C325" t="s">
         <v>84</v>
       </c>
@@ -12497,6 +13475,9 @@
       <c r="A326" t="s">
         <v>44</v>
       </c>
+      <c r="B326" t="s">
+        <v>1178</v>
+      </c>
       <c r="C326" t="s">
         <v>85</v>
       </c>
@@ -12523,6 +13504,9 @@
       <c r="A327" t="s">
         <v>44</v>
       </c>
+      <c r="B327" t="s">
+        <v>1178</v>
+      </c>
       <c r="C327" t="s">
         <v>85</v>
       </c>
@@ -12549,6 +13533,9 @@
       <c r="A328" t="s">
         <v>44</v>
       </c>
+      <c r="B328" t="s">
+        <v>1178</v>
+      </c>
       <c r="C328" t="s">
         <v>85</v>
       </c>
@@ -12575,6 +13562,9 @@
       <c r="A329" t="s">
         <v>44</v>
       </c>
+      <c r="B329" t="s">
+        <v>1179</v>
+      </c>
       <c r="C329" t="s">
         <v>86</v>
       </c>
@@ -12601,6 +13591,9 @@
       <c r="A330" t="s">
         <v>44</v>
       </c>
+      <c r="B330" t="s">
+        <v>1179</v>
+      </c>
       <c r="C330" t="s">
         <v>86</v>
       </c>
@@ -12627,6 +13620,9 @@
       <c r="A331" t="s">
         <v>44</v>
       </c>
+      <c r="B331" t="s">
+        <v>1179</v>
+      </c>
       <c r="C331" t="s">
         <v>86</v>
       </c>
@@ -12653,6 +13649,9 @@
       <c r="A332" t="s">
         <v>44</v>
       </c>
+      <c r="B332" t="s">
+        <v>1179</v>
+      </c>
       <c r="C332" t="s">
         <v>86</v>
       </c>
@@ -12679,6 +13678,9 @@
       <c r="A333" t="s">
         <v>44</v>
       </c>
+      <c r="B333" t="s">
+        <v>1179</v>
+      </c>
       <c r="C333" t="s">
         <v>86</v>
       </c>
@@ -12705,6 +13707,9 @@
       <c r="A334" t="s">
         <v>44</v>
       </c>
+      <c r="B334" t="s">
+        <v>1179</v>
+      </c>
       <c r="C334" t="s">
         <v>86</v>
       </c>
@@ -12731,6 +13736,9 @@
       <c r="A335" t="s">
         <v>44</v>
       </c>
+      <c r="B335" t="s">
+        <v>1179</v>
+      </c>
       <c r="C335" t="s">
         <v>86</v>
       </c>
@@ -12757,6 +13765,9 @@
       <c r="A336" t="s">
         <v>44</v>
       </c>
+      <c r="B336" t="s">
+        <v>1179</v>
+      </c>
       <c r="C336" t="s">
         <v>86</v>
       </c>
@@ -12783,6 +13794,9 @@
       <c r="A337" t="s">
         <v>44</v>
       </c>
+      <c r="B337" t="s">
+        <v>1179</v>
+      </c>
       <c r="C337" t="s">
         <v>86</v>
       </c>
@@ -12809,6 +13823,9 @@
       <c r="A338" t="s">
         <v>44</v>
       </c>
+      <c r="B338" t="s">
+        <v>1179</v>
+      </c>
       <c r="C338" t="s">
         <v>87</v>
       </c>
@@ -12835,6 +13852,9 @@
       <c r="A339" t="s">
         <v>44</v>
       </c>
+      <c r="B339" t="s">
+        <v>1179</v>
+      </c>
       <c r="C339" t="s">
         <v>87</v>
       </c>
@@ -12861,6 +13881,9 @@
       <c r="A340" t="s">
         <v>44</v>
       </c>
+      <c r="B340" t="s">
+        <v>1179</v>
+      </c>
       <c r="C340" t="s">
         <v>87</v>
       </c>
@@ -12887,6 +13910,9 @@
       <c r="A341" t="s">
         <v>44</v>
       </c>
+      <c r="B341" t="s">
+        <v>1179</v>
+      </c>
       <c r="C341" t="s">
         <v>87</v>
       </c>
@@ -12913,6 +13939,9 @@
       <c r="A342" t="s">
         <v>44</v>
       </c>
+      <c r="B342" t="s">
+        <v>1179</v>
+      </c>
       <c r="C342" t="s">
         <v>87</v>
       </c>
@@ -12939,6 +13968,9 @@
       <c r="A343" t="s">
         <v>44</v>
       </c>
+      <c r="B343" t="s">
+        <v>1179</v>
+      </c>
       <c r="C343" t="s">
         <v>87</v>
       </c>
@@ -12965,6 +13997,9 @@
       <c r="A344" t="s">
         <v>44</v>
       </c>
+      <c r="B344" t="s">
+        <v>1173</v>
+      </c>
       <c r="C344" t="s">
         <v>45</v>
       </c>
@@ -12991,6 +14026,9 @@
       <c r="A345" t="s">
         <v>44</v>
       </c>
+      <c r="B345" t="s">
+        <v>1173</v>
+      </c>
       <c r="C345" t="s">
         <v>45</v>
       </c>
@@ -13017,6 +14055,9 @@
       <c r="A346" t="s">
         <v>44</v>
       </c>
+      <c r="B346" t="s">
+        <v>1173</v>
+      </c>
       <c r="C346" t="s">
         <v>45</v>
       </c>
@@ -13043,6 +14084,9 @@
       <c r="A347" t="s">
         <v>44</v>
       </c>
+      <c r="B347" t="s">
+        <v>1173</v>
+      </c>
       <c r="C347" t="s">
         <v>45</v>
       </c>
@@ -13069,6 +14113,9 @@
       <c r="A348" t="s">
         <v>44</v>
       </c>
+      <c r="B348" t="s">
+        <v>1173</v>
+      </c>
       <c r="C348" t="s">
         <v>45</v>
       </c>
@@ -13095,6 +14142,9 @@
       <c r="A349" t="s">
         <v>44</v>
       </c>
+      <c r="B349" t="s">
+        <v>1173</v>
+      </c>
       <c r="C349" t="s">
         <v>45</v>
       </c>
@@ -13121,6 +14171,9 @@
       <c r="A350" t="s">
         <v>44</v>
       </c>
+      <c r="B350" t="s">
+        <v>1173</v>
+      </c>
       <c r="C350" t="s">
         <v>45</v>
       </c>
@@ -13147,6 +14200,9 @@
       <c r="A351" t="s">
         <v>44</v>
       </c>
+      <c r="B351" t="s">
+        <v>1173</v>
+      </c>
       <c r="C351" t="s">
         <v>45</v>
       </c>
@@ -13173,6 +14229,9 @@
       <c r="A352" t="s">
         <v>44</v>
       </c>
+      <c r="B352" t="s">
+        <v>1173</v>
+      </c>
       <c r="C352" t="s">
         <v>45</v>
       </c>
@@ -13199,6 +14258,9 @@
       <c r="A353" t="s">
         <v>44</v>
       </c>
+      <c r="B353" t="s">
+        <v>1173</v>
+      </c>
       <c r="C353" t="s">
         <v>45</v>
       </c>
@@ -13225,6 +14287,9 @@
       <c r="A354" t="s">
         <v>44</v>
       </c>
+      <c r="B354" t="s">
+        <v>1173</v>
+      </c>
       <c r="C354" t="s">
         <v>88</v>
       </c>
@@ -13251,6 +14316,9 @@
       <c r="A355" t="s">
         <v>44</v>
       </c>
+      <c r="B355" t="s">
+        <v>1173</v>
+      </c>
       <c r="C355" t="s">
         <v>88</v>
       </c>
@@ -13277,6 +14345,9 @@
       <c r="A356" t="s">
         <v>44</v>
       </c>
+      <c r="B356" t="s">
+        <v>1173</v>
+      </c>
       <c r="C356" t="s">
         <v>88</v>
       </c>
@@ -13303,6 +14374,9 @@
       <c r="A357" t="s">
         <v>44</v>
       </c>
+      <c r="B357" t="s">
+        <v>1173</v>
+      </c>
       <c r="C357" t="s">
         <v>88</v>
       </c>
@@ -13329,6 +14403,9 @@
       <c r="A358" t="s">
         <v>44</v>
       </c>
+      <c r="B358" t="s">
+        <v>1173</v>
+      </c>
       <c r="C358" t="s">
         <v>88</v>
       </c>
@@ -13355,6 +14432,9 @@
       <c r="A359" t="s">
         <v>44</v>
       </c>
+      <c r="B359" t="s">
+        <v>1173</v>
+      </c>
       <c r="C359" t="s">
         <v>88</v>
       </c>
@@ -13381,6 +14461,9 @@
       <c r="A360" t="s">
         <v>44</v>
       </c>
+      <c r="B360" t="s">
+        <v>1173</v>
+      </c>
       <c r="C360" t="s">
         <v>88</v>
       </c>
@@ -13407,6 +14490,9 @@
       <c r="A361" t="s">
         <v>44</v>
       </c>
+      <c r="B361" t="s">
+        <v>1173</v>
+      </c>
       <c r="C361" t="s">
         <v>88</v>
       </c>
@@ -13433,6 +14519,9 @@
       <c r="A362" t="s">
         <v>44</v>
       </c>
+      <c r="B362" t="s">
+        <v>1173</v>
+      </c>
       <c r="C362" t="s">
         <v>88</v>
       </c>
@@ -13459,6 +14548,9 @@
       <c r="A363" t="s">
         <v>44</v>
       </c>
+      <c r="B363" t="s">
+        <v>1173</v>
+      </c>
       <c r="C363" t="s">
         <v>88</v>
       </c>
@@ -13485,6 +14577,9 @@
       <c r="A364" t="s">
         <v>44</v>
       </c>
+      <c r="B364" t="s">
+        <v>1173</v>
+      </c>
       <c r="C364" t="s">
         <v>88</v>
       </c>
@@ -13511,6 +14606,9 @@
       <c r="A365" t="s">
         <v>44</v>
       </c>
+      <c r="B365" t="s">
+        <v>1173</v>
+      </c>
       <c r="C365" t="s">
         <v>88</v>
       </c>
@@ -13537,6 +14635,9 @@
       <c r="A366" t="s">
         <v>44</v>
       </c>
+      <c r="B366" t="s">
+        <v>1173</v>
+      </c>
       <c r="C366" t="s">
         <v>89</v>
       </c>
@@ -13563,6 +14664,9 @@
       <c r="A367" t="s">
         <v>44</v>
       </c>
+      <c r="B367" t="s">
+        <v>1173</v>
+      </c>
       <c r="C367" t="s">
         <v>89</v>
       </c>
@@ -13589,6 +14693,9 @@
       <c r="A368" t="s">
         <v>44</v>
       </c>
+      <c r="B368" t="s">
+        <v>1173</v>
+      </c>
       <c r="C368" t="s">
         <v>89</v>
       </c>
@@ -13615,6 +14722,9 @@
       <c r="A369" t="s">
         <v>44</v>
       </c>
+      <c r="B369" t="s">
+        <v>1173</v>
+      </c>
       <c r="C369" t="s">
         <v>89</v>
       </c>
@@ -13641,6 +14751,9 @@
       <c r="A370" t="s">
         <v>44</v>
       </c>
+      <c r="B370" t="s">
+        <v>1173</v>
+      </c>
       <c r="C370" t="s">
         <v>89</v>
       </c>
@@ -13667,6 +14780,9 @@
       <c r="A371" t="s">
         <v>44</v>
       </c>
+      <c r="B371" t="s">
+        <v>1173</v>
+      </c>
       <c r="C371" t="s">
         <v>89</v>
       </c>
@@ -13693,6 +14809,9 @@
       <c r="A372" t="s">
         <v>44</v>
       </c>
+      <c r="B372" t="s">
+        <v>1173</v>
+      </c>
       <c r="C372" t="s">
         <v>89</v>
       </c>
@@ -13719,6 +14838,9 @@
       <c r="A373" t="s">
         <v>44</v>
       </c>
+      <c r="B373" t="s">
+        <v>1173</v>
+      </c>
       <c r="C373" t="s">
         <v>89</v>
       </c>
@@ -13745,6 +14867,9 @@
       <c r="A374" t="s">
         <v>44</v>
       </c>
+      <c r="B374" t="s">
+        <v>1173</v>
+      </c>
       <c r="C374" t="s">
         <v>89</v>
       </c>
@@ -13771,6 +14896,9 @@
       <c r="A375" t="s">
         <v>44</v>
       </c>
+      <c r="B375" t="s">
+        <v>1173</v>
+      </c>
       <c r="C375" t="s">
         <v>89</v>
       </c>
@@ -13797,6 +14925,9 @@
       <c r="A376" t="s">
         <v>44</v>
       </c>
+      <c r="B376" t="s">
+        <v>1173</v>
+      </c>
       <c r="C376" t="s">
         <v>89</v>
       </c>
@@ -13823,6 +14954,9 @@
       <c r="A377" t="s">
         <v>44</v>
       </c>
+      <c r="B377" t="s">
+        <v>1173</v>
+      </c>
       <c r="C377" t="s">
         <v>46</v>
       </c>
@@ -13849,6 +14983,9 @@
       <c r="A378" t="s">
         <v>44</v>
       </c>
+      <c r="B378" t="s">
+        <v>1173</v>
+      </c>
       <c r="C378" t="s">
         <v>46</v>
       </c>
@@ -13875,6 +15012,9 @@
       <c r="A379" t="s">
         <v>44</v>
       </c>
+      <c r="B379" t="s">
+        <v>1173</v>
+      </c>
       <c r="C379" t="s">
         <v>46</v>
       </c>
@@ -13901,6 +15041,9 @@
       <c r="A380" t="s">
         <v>44</v>
       </c>
+      <c r="B380" t="s">
+        <v>1173</v>
+      </c>
       <c r="C380" t="s">
         <v>46</v>
       </c>
@@ -13927,6 +15070,9 @@
       <c r="A381" t="s">
         <v>44</v>
       </c>
+      <c r="B381" t="s">
+        <v>1173</v>
+      </c>
       <c r="C381" t="s">
         <v>46</v>
       </c>
@@ -13953,6 +15099,9 @@
       <c r="A382" t="s">
         <v>44</v>
       </c>
+      <c r="B382" t="s">
+        <v>1173</v>
+      </c>
       <c r="C382" t="s">
         <v>46</v>
       </c>
@@ -13979,6 +15128,9 @@
       <c r="A383" t="s">
         <v>44</v>
       </c>
+      <c r="B383" t="s">
+        <v>1173</v>
+      </c>
       <c r="C383" t="s">
         <v>46</v>
       </c>
@@ -14005,6 +15157,9 @@
       <c r="A384" t="s">
         <v>44</v>
       </c>
+      <c r="B384" t="s">
+        <v>1173</v>
+      </c>
       <c r="C384" t="s">
         <v>46</v>
       </c>
@@ -14031,6 +15186,9 @@
       <c r="A385" t="s">
         <v>44</v>
       </c>
+      <c r="B385" t="s">
+        <v>1173</v>
+      </c>
       <c r="C385" t="s">
         <v>46</v>
       </c>
@@ -14057,6 +15215,9 @@
       <c r="A386" t="s">
         <v>44</v>
       </c>
+      <c r="B386" t="s">
+        <v>1173</v>
+      </c>
       <c r="C386" t="s">
         <v>46</v>
       </c>
@@ -14083,6 +15244,9 @@
       <c r="A387" t="s">
         <v>44</v>
       </c>
+      <c r="B387" t="s">
+        <v>1173</v>
+      </c>
       <c r="C387" t="s">
         <v>46</v>
       </c>
@@ -14109,6 +15273,9 @@
       <c r="A388" t="s">
         <v>44</v>
       </c>
+      <c r="B388" t="s">
+        <v>1173</v>
+      </c>
       <c r="C388" t="s">
         <v>46</v>
       </c>
@@ -14135,6 +15302,9 @@
       <c r="A389" t="s">
         <v>44</v>
       </c>
+      <c r="B389" t="s">
+        <v>1173</v>
+      </c>
       <c r="C389" t="s">
         <v>47</v>
       </c>
@@ -14161,6 +15331,9 @@
       <c r="A390" t="s">
         <v>44</v>
       </c>
+      <c r="B390" t="s">
+        <v>1173</v>
+      </c>
       <c r="C390" t="s">
         <v>47</v>
       </c>
@@ -14187,6 +15360,9 @@
       <c r="A391" t="s">
         <v>44</v>
       </c>
+      <c r="B391" t="s">
+        <v>1173</v>
+      </c>
       <c r="C391" t="s">
         <v>47</v>
       </c>
@@ -14213,6 +15389,9 @@
       <c r="A392" t="s">
         <v>44</v>
       </c>
+      <c r="B392" t="s">
+        <v>1173</v>
+      </c>
       <c r="C392" t="s">
         <v>47</v>
       </c>
@@ -14239,6 +15418,9 @@
       <c r="A393" t="s">
         <v>44</v>
       </c>
+      <c r="B393" t="s">
+        <v>1173</v>
+      </c>
       <c r="C393" t="s">
         <v>47</v>
       </c>
@@ -14265,6 +15447,9 @@
       <c r="A394" t="s">
         <v>44</v>
       </c>
+      <c r="B394" t="s">
+        <v>1173</v>
+      </c>
       <c r="C394" t="s">
         <v>47</v>
       </c>
@@ -14291,6 +15476,9 @@
       <c r="A395" t="s">
         <v>44</v>
       </c>
+      <c r="B395" t="s">
+        <v>1173</v>
+      </c>
       <c r="C395" t="s">
         <v>47</v>
       </c>
@@ -14317,6 +15505,9 @@
       <c r="A396" t="s">
         <v>44</v>
       </c>
+      <c r="B396" t="s">
+        <v>1173</v>
+      </c>
       <c r="C396" t="s">
         <v>47</v>
       </c>
@@ -14343,6 +15534,9 @@
       <c r="A397" t="s">
         <v>44</v>
       </c>
+      <c r="B397" t="s">
+        <v>1173</v>
+      </c>
       <c r="C397" t="s">
         <v>47</v>
       </c>
@@ -14369,6 +15563,9 @@
       <c r="A398" t="s">
         <v>44</v>
       </c>
+      <c r="B398" t="s">
+        <v>1173</v>
+      </c>
       <c r="C398" t="s">
         <v>47</v>
       </c>
@@ -14395,6 +15592,9 @@
       <c r="A399" t="s">
         <v>44</v>
       </c>
+      <c r="B399" t="s">
+        <v>1173</v>
+      </c>
       <c r="C399" t="s">
         <v>47</v>
       </c>
@@ -14421,6 +15621,9 @@
       <c r="A400" t="s">
         <v>44</v>
       </c>
+      <c r="B400" t="s">
+        <v>1173</v>
+      </c>
       <c r="C400" t="s">
         <v>47</v>
       </c>
@@ -14447,6 +15650,9 @@
       <c r="A401" t="s">
         <v>44</v>
       </c>
+      <c r="B401" t="s">
+        <v>1173</v>
+      </c>
       <c r="C401" t="s">
         <v>47</v>
       </c>
@@ -14473,6 +15679,9 @@
       <c r="A402" t="s">
         <v>44</v>
       </c>
+      <c r="B402" t="s">
+        <v>1173</v>
+      </c>
       <c r="C402" t="s">
         <v>47</v>
       </c>
@@ -14499,6 +15708,9 @@
       <c r="A403" t="s">
         <v>44</v>
       </c>
+      <c r="B403" t="s">
+        <v>1173</v>
+      </c>
       <c r="C403" t="s">
         <v>47</v>
       </c>
@@ -14525,6 +15737,9 @@
       <c r="A404" t="s">
         <v>44</v>
       </c>
+      <c r="B404" t="s">
+        <v>1173</v>
+      </c>
       <c r="C404" t="s">
         <v>47</v>
       </c>
@@ -14551,6 +15766,9 @@
       <c r="A405" t="s">
         <v>44</v>
       </c>
+      <c r="B405" t="s">
+        <v>1173</v>
+      </c>
       <c r="C405" t="s">
         <v>47</v>
       </c>
@@ -14577,6 +15795,9 @@
       <c r="A406" t="s">
         <v>44</v>
       </c>
+      <c r="B406" t="s">
+        <v>1173</v>
+      </c>
       <c r="C406" t="s">
         <v>47</v>
       </c>
@@ -14603,6 +15824,9 @@
       <c r="A407" t="s">
         <v>44</v>
       </c>
+      <c r="B407" t="s">
+        <v>1173</v>
+      </c>
       <c r="C407" t="s">
         <v>47</v>
       </c>
@@ -14629,6 +15853,9 @@
       <c r="A408" t="s">
         <v>44</v>
       </c>
+      <c r="B408" t="s">
+        <v>1173</v>
+      </c>
       <c r="C408" t="s">
         <v>47</v>
       </c>
@@ -14655,6 +15882,9 @@
       <c r="A409" t="s">
         <v>44</v>
       </c>
+      <c r="B409" t="s">
+        <v>1173</v>
+      </c>
       <c r="C409" t="s">
         <v>47</v>
       </c>
@@ -14681,6 +15911,9 @@
       <c r="A410" t="s">
         <v>44</v>
       </c>
+      <c r="B410" t="s">
+        <v>1173</v>
+      </c>
       <c r="C410" t="s">
         <v>49</v>
       </c>
@@ -14707,6 +15940,9 @@
       <c r="A411" t="s">
         <v>44</v>
       </c>
+      <c r="B411" t="s">
+        <v>1174</v>
+      </c>
       <c r="C411" t="s">
         <v>90</v>
       </c>
@@ -14733,6 +15969,9 @@
       <c r="A412" t="s">
         <v>44</v>
       </c>
+      <c r="B412" t="s">
+        <v>1174</v>
+      </c>
       <c r="C412" t="s">
         <v>90</v>
       </c>
@@ -14759,6 +15998,9 @@
       <c r="A413" t="s">
         <v>44</v>
       </c>
+      <c r="B413" t="s">
+        <v>1174</v>
+      </c>
       <c r="C413" t="s">
         <v>90</v>
       </c>
@@ -14785,6 +16027,9 @@
       <c r="A414" t="s">
         <v>44</v>
       </c>
+      <c r="B414" t="s">
+        <v>1174</v>
+      </c>
       <c r="C414" t="s">
         <v>90</v>
       </c>
@@ -14811,6 +16056,9 @@
       <c r="A415" t="s">
         <v>44</v>
       </c>
+      <c r="B415" t="s">
+        <v>1174</v>
+      </c>
       <c r="C415" t="s">
         <v>90</v>
       </c>
@@ -14837,6 +16085,9 @@
       <c r="A416" t="s">
         <v>44</v>
       </c>
+      <c r="B416" t="s">
+        <v>1174</v>
+      </c>
       <c r="C416" t="s">
         <v>90</v>
       </c>
@@ -14863,6 +16114,9 @@
       <c r="A417" t="s">
         <v>44</v>
       </c>
+      <c r="B417" t="s">
+        <v>1174</v>
+      </c>
       <c r="C417" t="s">
         <v>90</v>
       </c>
@@ -14889,6 +16143,9 @@
       <c r="A418" t="s">
         <v>44</v>
       </c>
+      <c r="B418" t="s">
+        <v>1174</v>
+      </c>
       <c r="C418" t="s">
         <v>90</v>
       </c>
@@ -14915,6 +16172,9 @@
       <c r="A419" t="s">
         <v>44</v>
       </c>
+      <c r="B419" t="s">
+        <v>1174</v>
+      </c>
       <c r="C419" t="s">
         <v>90</v>
       </c>
@@ -14941,6 +16201,9 @@
       <c r="A420" t="s">
         <v>44</v>
       </c>
+      <c r="B420" t="s">
+        <v>1174</v>
+      </c>
       <c r="C420" t="s">
         <v>90</v>
       </c>
@@ -14967,6 +16230,9 @@
       <c r="A421" t="s">
         <v>44</v>
       </c>
+      <c r="B421" t="s">
+        <v>1174</v>
+      </c>
       <c r="C421" t="s">
         <v>90</v>
       </c>
@@ -14993,6 +16259,9 @@
       <c r="A422" t="s">
         <v>44</v>
       </c>
+      <c r="B422" t="s">
+        <v>1174</v>
+      </c>
       <c r="C422" t="s">
         <v>90</v>
       </c>
@@ -15019,6 +16288,9 @@
       <c r="A423" t="s">
         <v>44</v>
       </c>
+      <c r="B423" t="s">
+        <v>1174</v>
+      </c>
       <c r="C423" t="s">
         <v>90</v>
       </c>
@@ -15045,6 +16317,9 @@
       <c r="A424" t="s">
         <v>44</v>
       </c>
+      <c r="B424" t="s">
+        <v>1174</v>
+      </c>
       <c r="C424" t="s">
         <v>53</v>
       </c>
@@ -15071,6 +16346,9 @@
       <c r="A425" t="s">
         <v>44</v>
       </c>
+      <c r="B425" t="s">
+        <v>1174</v>
+      </c>
       <c r="C425" t="s">
         <v>53</v>
       </c>
@@ -15097,6 +16375,9 @@
       <c r="A426" t="s">
         <v>44</v>
       </c>
+      <c r="B426" t="s">
+        <v>1174</v>
+      </c>
       <c r="C426" t="s">
         <v>53</v>
       </c>
@@ -15123,6 +16404,9 @@
       <c r="A427" t="s">
         <v>44</v>
       </c>
+      <c r="B427" t="s">
+        <v>1174</v>
+      </c>
       <c r="C427" t="s">
         <v>53</v>
       </c>
@@ -15149,6 +16433,9 @@
       <c r="A428" t="s">
         <v>44</v>
       </c>
+      <c r="B428" t="s">
+        <v>1174</v>
+      </c>
       <c r="C428" t="s">
         <v>53</v>
       </c>
@@ -15175,6 +16462,9 @@
       <c r="A429" t="s">
         <v>44</v>
       </c>
+      <c r="B429" t="s">
+        <v>1174</v>
+      </c>
       <c r="C429" t="s">
         <v>53</v>
       </c>
@@ -15201,6 +16491,9 @@
       <c r="A430" t="s">
         <v>44</v>
       </c>
+      <c r="B430" t="s">
+        <v>1174</v>
+      </c>
       <c r="C430" t="s">
         <v>53</v>
       </c>
@@ -15227,6 +16520,9 @@
       <c r="A431" t="s">
         <v>44</v>
       </c>
+      <c r="B431" t="s">
+        <v>1174</v>
+      </c>
       <c r="C431" t="s">
         <v>53</v>
       </c>
@@ -15253,6 +16549,9 @@
       <c r="A432" t="s">
         <v>44</v>
       </c>
+      <c r="B432" t="s">
+        <v>1174</v>
+      </c>
       <c r="C432" t="s">
         <v>53</v>
       </c>
@@ -15279,6 +16578,9 @@
       <c r="A433" t="s">
         <v>44</v>
       </c>
+      <c r="B433" t="s">
+        <v>1174</v>
+      </c>
       <c r="C433" t="s">
         <v>53</v>
       </c>
@@ -15305,6 +16607,9 @@
       <c r="A434" t="s">
         <v>44</v>
       </c>
+      <c r="B434" t="s">
+        <v>1174</v>
+      </c>
       <c r="C434" t="s">
         <v>53</v>
       </c>
@@ -15331,6 +16636,9 @@
       <c r="A435" t="s">
         <v>44</v>
       </c>
+      <c r="B435" t="s">
+        <v>1174</v>
+      </c>
       <c r="C435" t="s">
         <v>53</v>
       </c>
@@ -15357,6 +16665,9 @@
       <c r="A436" t="s">
         <v>44</v>
       </c>
+      <c r="B436" t="s">
+        <v>1175</v>
+      </c>
       <c r="C436" t="s">
         <v>56</v>
       </c>
@@ -15383,6 +16694,9 @@
       <c r="A437" t="s">
         <v>44</v>
       </c>
+      <c r="B437" t="s">
+        <v>1175</v>
+      </c>
       <c r="C437" t="s">
         <v>56</v>
       </c>
@@ -15409,6 +16723,9 @@
       <c r="A438" t="s">
         <v>44</v>
       </c>
+      <c r="B438" t="s">
+        <v>1175</v>
+      </c>
       <c r="C438" t="s">
         <v>56</v>
       </c>
@@ -15435,6 +16752,9 @@
       <c r="A439" t="s">
         <v>44</v>
       </c>
+      <c r="B439" t="s">
+        <v>1175</v>
+      </c>
       <c r="C439" t="s">
         <v>56</v>
       </c>
@@ -15461,6 +16781,9 @@
       <c r="A440" t="s">
         <v>44</v>
       </c>
+      <c r="B440" t="s">
+        <v>1175</v>
+      </c>
       <c r="C440" t="s">
         <v>56</v>
       </c>
@@ -15487,6 +16810,9 @@
       <c r="A441" t="s">
         <v>44</v>
       </c>
+      <c r="B441" t="s">
+        <v>1175</v>
+      </c>
       <c r="C441" t="s">
         <v>56</v>
       </c>
@@ -15513,6 +16839,9 @@
       <c r="A442" t="s">
         <v>44</v>
       </c>
+      <c r="B442" t="s">
+        <v>1175</v>
+      </c>
       <c r="C442" t="s">
         <v>56</v>
       </c>
@@ -15539,6 +16868,9 @@
       <c r="A443" t="s">
         <v>44</v>
       </c>
+      <c r="B443" t="s">
+        <v>1175</v>
+      </c>
       <c r="C443" t="s">
         <v>56</v>
       </c>
@@ -15565,6 +16897,9 @@
       <c r="A444" t="s">
         <v>44</v>
       </c>
+      <c r="B444" t="s">
+        <v>1175</v>
+      </c>
       <c r="C444" t="s">
         <v>56</v>
       </c>
@@ -15591,6 +16926,9 @@
       <c r="A445" t="s">
         <v>44</v>
       </c>
+      <c r="B445" t="s">
+        <v>1175</v>
+      </c>
       <c r="C445" t="s">
         <v>56</v>
       </c>
@@ -15617,6 +16955,9 @@
       <c r="A446" t="s">
         <v>44</v>
       </c>
+      <c r="B446" t="s">
+        <v>1175</v>
+      </c>
       <c r="C446" t="s">
         <v>56</v>
       </c>
@@ -15643,6 +16984,9 @@
       <c r="A447" t="s">
         <v>44</v>
       </c>
+      <c r="B447" t="s">
+        <v>1175</v>
+      </c>
       <c r="C447" t="s">
         <v>56</v>
       </c>
@@ -15669,6 +17013,9 @@
       <c r="A448" t="s">
         <v>44</v>
       </c>
+      <c r="B448" t="s">
+        <v>1175</v>
+      </c>
       <c r="C448" t="s">
         <v>56</v>
       </c>
@@ -15695,6 +17042,9 @@
       <c r="A449" t="s">
         <v>44</v>
       </c>
+      <c r="B449" t="s">
+        <v>1175</v>
+      </c>
       <c r="C449" t="s">
         <v>56</v>
       </c>
@@ -15721,6 +17071,9 @@
       <c r="A450" t="s">
         <v>44</v>
       </c>
+      <c r="B450" t="s">
+        <v>1175</v>
+      </c>
       <c r="C450" t="s">
         <v>56</v>
       </c>
@@ -15747,6 +17100,9 @@
       <c r="A451" t="s">
         <v>44</v>
       </c>
+      <c r="B451" t="s">
+        <v>1175</v>
+      </c>
       <c r="C451" t="s">
         <v>56</v>
       </c>
@@ -15773,6 +17129,9 @@
       <c r="A452" t="s">
         <v>44</v>
       </c>
+      <c r="B452" t="s">
+        <v>1175</v>
+      </c>
       <c r="C452" t="s">
         <v>56</v>
       </c>
@@ -15799,6 +17158,9 @@
       <c r="A453" t="s">
         <v>44</v>
       </c>
+      <c r="B453" t="s">
+        <v>1175</v>
+      </c>
       <c r="C453" t="s">
         <v>56</v>
       </c>
@@ -15825,6 +17187,9 @@
       <c r="A454" t="s">
         <v>44</v>
       </c>
+      <c r="B454" t="s">
+        <v>1175</v>
+      </c>
       <c r="C454" t="s">
         <v>91</v>
       </c>
@@ -15851,6 +17216,9 @@
       <c r="A455" t="s">
         <v>44</v>
       </c>
+      <c r="B455" t="s">
+        <v>1175</v>
+      </c>
       <c r="C455" t="s">
         <v>91</v>
       </c>
@@ -15877,6 +17245,9 @@
       <c r="A456" t="s">
         <v>44</v>
       </c>
+      <c r="B456" t="s">
+        <v>1175</v>
+      </c>
       <c r="C456" t="s">
         <v>91</v>
       </c>
@@ -15903,6 +17274,9 @@
       <c r="A457" t="s">
         <v>44</v>
       </c>
+      <c r="B457" t="s">
+        <v>1175</v>
+      </c>
       <c r="C457" t="s">
         <v>91</v>
       </c>
@@ -15929,6 +17303,9 @@
       <c r="A458" t="s">
         <v>44</v>
       </c>
+      <c r="B458" t="s">
+        <v>1175</v>
+      </c>
       <c r="C458" t="s">
         <v>91</v>
       </c>
@@ -15955,6 +17332,9 @@
       <c r="A459" t="s">
         <v>44</v>
       </c>
+      <c r="B459" t="s">
+        <v>1175</v>
+      </c>
       <c r="C459" t="s">
         <v>91</v>
       </c>
@@ -15981,6 +17361,9 @@
       <c r="A460" t="s">
         <v>44</v>
       </c>
+      <c r="B460" t="s">
+        <v>1175</v>
+      </c>
       <c r="C460" t="s">
         <v>91</v>
       </c>
@@ -16007,6 +17390,9 @@
       <c r="A461" t="s">
         <v>44</v>
       </c>
+      <c r="B461" t="s">
+        <v>1175</v>
+      </c>
       <c r="C461" t="s">
         <v>91</v>
       </c>
@@ -16033,6 +17419,9 @@
       <c r="A462" t="s">
         <v>44</v>
       </c>
+      <c r="B462" t="s">
+        <v>1175</v>
+      </c>
       <c r="C462" t="s">
         <v>91</v>
       </c>
@@ -16059,6 +17448,9 @@
       <c r="A463" t="s">
         <v>44</v>
       </c>
+      <c r="B463" t="s">
+        <v>1175</v>
+      </c>
       <c r="C463" t="s">
         <v>91</v>
       </c>
@@ -16085,6 +17477,9 @@
       <c r="A464" t="s">
         <v>44</v>
       </c>
+      <c r="B464" t="s">
+        <v>1175</v>
+      </c>
       <c r="C464" t="s">
         <v>91</v>
       </c>
@@ -16111,6 +17506,9 @@
       <c r="A465" t="s">
         <v>44</v>
       </c>
+      <c r="B465" t="s">
+        <v>1175</v>
+      </c>
       <c r="C465" t="s">
         <v>91</v>
       </c>
@@ -16137,6 +17535,9 @@
       <c r="A466" t="s">
         <v>44</v>
       </c>
+      <c r="B466" t="s">
+        <v>1175</v>
+      </c>
       <c r="C466" t="s">
         <v>91</v>
       </c>
@@ -16163,6 +17564,9 @@
       <c r="A467" t="s">
         <v>44</v>
       </c>
+      <c r="B467" t="s">
+        <v>1175</v>
+      </c>
       <c r="C467" t="s">
         <v>91</v>
       </c>
@@ -16189,6 +17593,9 @@
       <c r="A468" t="s">
         <v>44</v>
       </c>
+      <c r="B468" t="s">
+        <v>1175</v>
+      </c>
       <c r="C468" t="s">
         <v>91</v>
       </c>
@@ -16215,6 +17622,9 @@
       <c r="A469" t="s">
         <v>44</v>
       </c>
+      <c r="B469" t="s">
+        <v>1175</v>
+      </c>
       <c r="C469" t="s">
         <v>91</v>
       </c>
@@ -16241,6 +17651,9 @@
       <c r="A470" t="s">
         <v>44</v>
       </c>
+      <c r="B470" t="s">
+        <v>1175</v>
+      </c>
       <c r="C470" t="s">
         <v>91</v>
       </c>
@@ -16267,6 +17680,9 @@
       <c r="A471" t="s">
         <v>44</v>
       </c>
+      <c r="B471" t="s">
+        <v>1175</v>
+      </c>
       <c r="C471" t="s">
         <v>91</v>
       </c>
@@ -16293,6 +17709,9 @@
       <c r="A472" t="s">
         <v>44</v>
       </c>
+      <c r="B472" t="s">
+        <v>1175</v>
+      </c>
       <c r="C472" t="s">
         <v>91</v>
       </c>
@@ -16319,6 +17738,9 @@
       <c r="A473" t="s">
         <v>44</v>
       </c>
+      <c r="B473" t="s">
+        <v>1175</v>
+      </c>
       <c r="C473" t="s">
         <v>91</v>
       </c>
@@ -16345,6 +17767,9 @@
       <c r="A474" t="s">
         <v>44</v>
       </c>
+      <c r="B474" t="s">
+        <v>1175</v>
+      </c>
       <c r="C474" t="s">
         <v>91</v>
       </c>
@@ -16371,6 +17796,9 @@
       <c r="A475" t="s">
         <v>44</v>
       </c>
+      <c r="B475" t="s">
+        <v>1175</v>
+      </c>
       <c r="C475" t="s">
         <v>91</v>
       </c>
@@ -16397,6 +17825,9 @@
       <c r="A476" t="s">
         <v>44</v>
       </c>
+      <c r="B476" t="s">
+        <v>1175</v>
+      </c>
       <c r="C476" t="s">
         <v>91</v>
       </c>
@@ -16423,6 +17854,9 @@
       <c r="A477" t="s">
         <v>44</v>
       </c>
+      <c r="B477" t="s">
+        <v>1175</v>
+      </c>
       <c r="C477" t="s">
         <v>91</v>
       </c>
@@ -16449,6 +17883,9 @@
       <c r="A478" t="s">
         <v>44</v>
       </c>
+      <c r="B478" t="s">
+        <v>1175</v>
+      </c>
       <c r="C478" t="s">
         <v>91</v>
       </c>
@@ -16475,6 +17912,9 @@
       <c r="A479" t="s">
         <v>44</v>
       </c>
+      <c r="B479" t="s">
+        <v>1175</v>
+      </c>
       <c r="C479" t="s">
         <v>91</v>
       </c>
@@ -16501,6 +17941,9 @@
       <c r="A480" t="s">
         <v>44</v>
       </c>
+      <c r="B480" t="s">
+        <v>1175</v>
+      </c>
       <c r="C480" t="s">
         <v>91</v>
       </c>
@@ -16527,6 +17970,9 @@
       <c r="A481" t="s">
         <v>44</v>
       </c>
+      <c r="B481" t="s">
+        <v>1175</v>
+      </c>
       <c r="C481" t="s">
         <v>91</v>
       </c>
@@ -16553,6 +17999,9 @@
       <c r="A482" t="s">
         <v>44</v>
       </c>
+      <c r="B482" t="s">
+        <v>1175</v>
+      </c>
       <c r="C482" t="s">
         <v>91</v>
       </c>
@@ -16579,6 +18028,9 @@
       <c r="A483" t="s">
         <v>44</v>
       </c>
+      <c r="B483" t="s">
+        <v>1175</v>
+      </c>
       <c r="C483" t="s">
         <v>91</v>
       </c>
@@ -16605,6 +18057,9 @@
       <c r="A484" t="s">
         <v>44</v>
       </c>
+      <c r="B484" t="s">
+        <v>1175</v>
+      </c>
       <c r="C484" t="s">
         <v>91</v>
       </c>
@@ -16631,6 +18086,9 @@
       <c r="A485" t="s">
         <v>44</v>
       </c>
+      <c r="B485" t="s">
+        <v>1175</v>
+      </c>
       <c r="C485" t="s">
         <v>91</v>
       </c>
@@ -16657,6 +18115,9 @@
       <c r="A486" t="s">
         <v>44</v>
       </c>
+      <c r="B486" t="s">
+        <v>1175</v>
+      </c>
       <c r="C486" t="s">
         <v>91</v>
       </c>
@@ -16683,6 +18144,9 @@
       <c r="A487" t="s">
         <v>44</v>
       </c>
+      <c r="B487" t="s">
+        <v>1175</v>
+      </c>
       <c r="C487" t="s">
         <v>91</v>
       </c>
@@ -16709,6 +18173,9 @@
       <c r="A488" t="s">
         <v>44</v>
       </c>
+      <c r="B488" t="s">
+        <v>1175</v>
+      </c>
       <c r="C488" t="s">
         <v>91</v>
       </c>
@@ -16735,6 +18202,9 @@
       <c r="A489" t="s">
         <v>44</v>
       </c>
+      <c r="B489" t="s">
+        <v>1175</v>
+      </c>
       <c r="C489" t="s">
         <v>57</v>
       </c>
@@ -16761,6 +18231,9 @@
       <c r="A490" t="s">
         <v>44</v>
       </c>
+      <c r="B490" t="s">
+        <v>1175</v>
+      </c>
       <c r="C490" t="s">
         <v>57</v>
       </c>
@@ -16787,6 +18260,9 @@
       <c r="A491" t="s">
         <v>44</v>
       </c>
+      <c r="B491" t="s">
+        <v>1175</v>
+      </c>
       <c r="C491" t="s">
         <v>57</v>
       </c>
@@ -16813,6 +18289,9 @@
       <c r="A492" t="s">
         <v>44</v>
       </c>
+      <c r="B492" t="s">
+        <v>1175</v>
+      </c>
       <c r="C492" t="s">
         <v>57</v>
       </c>
@@ -16839,6 +18318,9 @@
       <c r="A493" t="s">
         <v>44</v>
       </c>
+      <c r="B493" t="s">
+        <v>1175</v>
+      </c>
       <c r="C493" t="s">
         <v>57</v>
       </c>
@@ -16865,6 +18347,9 @@
       <c r="A494" t="s">
         <v>44</v>
       </c>
+      <c r="B494" t="s">
+        <v>1175</v>
+      </c>
       <c r="C494" t="s">
         <v>57</v>
       </c>
@@ -16891,6 +18376,9 @@
       <c r="A495" t="s">
         <v>44</v>
       </c>
+      <c r="B495" t="s">
+        <v>1175</v>
+      </c>
       <c r="C495" t="s">
         <v>57</v>
       </c>
@@ -16917,6 +18405,9 @@
       <c r="A496" t="s">
         <v>44</v>
       </c>
+      <c r="B496" t="s">
+        <v>1175</v>
+      </c>
       <c r="C496" t="s">
         <v>57</v>
       </c>
@@ -16943,6 +18434,9 @@
       <c r="A497" t="s">
         <v>44</v>
       </c>
+      <c r="B497" t="s">
+        <v>1175</v>
+      </c>
       <c r="C497" t="s">
         <v>57</v>
       </c>
@@ -16969,6 +18463,9 @@
       <c r="A498" t="s">
         <v>44</v>
       </c>
+      <c r="B498" t="s">
+        <v>1175</v>
+      </c>
       <c r="C498" t="s">
         <v>57</v>
       </c>
@@ -16995,6 +18492,9 @@
       <c r="A499" t="s">
         <v>44</v>
       </c>
+      <c r="B499" t="s">
+        <v>1175</v>
+      </c>
       <c r="C499" t="s">
         <v>57</v>
       </c>
@@ -17021,6 +18521,9 @@
       <c r="A500" t="s">
         <v>44</v>
       </c>
+      <c r="B500" t="s">
+        <v>1175</v>
+      </c>
       <c r="C500" t="s">
         <v>57</v>
       </c>
@@ -17047,6 +18550,9 @@
       <c r="A501" t="s">
         <v>44</v>
       </c>
+      <c r="B501" t="s">
+        <v>1175</v>
+      </c>
       <c r="C501" t="s">
         <v>57</v>
       </c>
@@ -17073,6 +18579,9 @@
       <c r="A502" t="s">
         <v>44</v>
       </c>
+      <c r="B502" t="s">
+        <v>1175</v>
+      </c>
       <c r="C502" t="s">
         <v>57</v>
       </c>
@@ -17099,6 +18608,9 @@
       <c r="A503" t="s">
         <v>44</v>
       </c>
+      <c r="B503" t="s">
+        <v>1175</v>
+      </c>
       <c r="C503" t="s">
         <v>58</v>
       </c>
@@ -17125,6 +18637,9 @@
       <c r="A504" t="s">
         <v>44</v>
       </c>
+      <c r="B504" t="s">
+        <v>1175</v>
+      </c>
       <c r="C504" t="s">
         <v>58</v>
       </c>
@@ -17151,6 +18666,9 @@
       <c r="A505" t="s">
         <v>44</v>
       </c>
+      <c r="B505" t="s">
+        <v>1175</v>
+      </c>
       <c r="C505" t="s">
         <v>92</v>
       </c>
@@ -17177,6 +18695,9 @@
       <c r="A506" t="s">
         <v>44</v>
       </c>
+      <c r="B506" t="s">
+        <v>1175</v>
+      </c>
       <c r="C506" t="s">
         <v>92</v>
       </c>
@@ -17203,6 +18724,9 @@
       <c r="A507" t="s">
         <v>44</v>
       </c>
+      <c r="B507" t="s">
+        <v>1175</v>
+      </c>
       <c r="C507" t="s">
         <v>92</v>
       </c>
@@ -17229,6 +18753,9 @@
       <c r="A508" t="s">
         <v>44</v>
       </c>
+      <c r="B508" t="s">
+        <v>1175</v>
+      </c>
       <c r="C508" t="s">
         <v>92</v>
       </c>
@@ -17255,6 +18782,9 @@
       <c r="A509" t="s">
         <v>44</v>
       </c>
+      <c r="B509" t="s">
+        <v>1175</v>
+      </c>
       <c r="C509" t="s">
         <v>92</v>
       </c>
@@ -17281,6 +18811,9 @@
       <c r="A510" t="s">
         <v>44</v>
       </c>
+      <c r="B510" t="s">
+        <v>1175</v>
+      </c>
       <c r="C510" t="s">
         <v>92</v>
       </c>
@@ -17307,6 +18840,9 @@
       <c r="A511" t="s">
         <v>44</v>
       </c>
+      <c r="B511" t="s">
+        <v>1175</v>
+      </c>
       <c r="C511" t="s">
         <v>92</v>
       </c>
@@ -17333,6 +18869,9 @@
       <c r="A512" t="s">
         <v>44</v>
       </c>
+      <c r="B512" t="s">
+        <v>1175</v>
+      </c>
       <c r="C512" t="s">
         <v>92</v>
       </c>
@@ -17359,6 +18898,9 @@
       <c r="A513" t="s">
         <v>44</v>
       </c>
+      <c r="B513" t="s">
+        <v>1175</v>
+      </c>
       <c r="C513" t="s">
         <v>92</v>
       </c>
@@ -17385,6 +18927,9 @@
       <c r="A514" t="s">
         <v>44</v>
       </c>
+      <c r="B514" t="s">
+        <v>1175</v>
+      </c>
       <c r="C514" t="s">
         <v>92</v>
       </c>
@@ -17411,6 +18956,9 @@
       <c r="A515" t="s">
         <v>44</v>
       </c>
+      <c r="B515" t="s">
+        <v>1175</v>
+      </c>
       <c r="C515" t="s">
         <v>92</v>
       </c>
@@ -17437,6 +18985,9 @@
       <c r="A516" t="s">
         <v>44</v>
       </c>
+      <c r="B516" t="s">
+        <v>1175</v>
+      </c>
       <c r="C516" t="s">
         <v>92</v>
       </c>
@@ -17463,6 +19014,9 @@
       <c r="A517" t="s">
         <v>44</v>
       </c>
+      <c r="B517" t="s">
+        <v>1175</v>
+      </c>
       <c r="C517" t="s">
         <v>92</v>
       </c>
@@ -17489,6 +19043,9 @@
       <c r="A518" t="s">
         <v>44</v>
       </c>
+      <c r="B518" t="s">
+        <v>1175</v>
+      </c>
       <c r="C518" t="s">
         <v>92</v>
       </c>
@@ -17515,6 +19072,9 @@
       <c r="A519" t="s">
         <v>44</v>
       </c>
+      <c r="B519" t="s">
+        <v>1175</v>
+      </c>
       <c r="C519" t="s">
         <v>92</v>
       </c>
@@ -17541,6 +19101,9 @@
       <c r="A520" t="s">
         <v>44</v>
       </c>
+      <c r="B520" t="s">
+        <v>1175</v>
+      </c>
       <c r="C520" t="s">
         <v>92</v>
       </c>
@@ -17567,6 +19130,9 @@
       <c r="A521" t="s">
         <v>44</v>
       </c>
+      <c r="B521" t="s">
+        <v>1175</v>
+      </c>
       <c r="C521" t="s">
         <v>92</v>
       </c>
@@ -17593,6 +19159,9 @@
       <c r="A522" t="s">
         <v>44</v>
       </c>
+      <c r="B522" t="s">
+        <v>1175</v>
+      </c>
       <c r="C522" t="s">
         <v>92</v>
       </c>
@@ -17619,6 +19188,9 @@
       <c r="A523" t="s">
         <v>44</v>
       </c>
+      <c r="B523" t="s">
+        <v>1175</v>
+      </c>
       <c r="C523" t="s">
         <v>60</v>
       </c>
@@ -17645,6 +19217,9 @@
       <c r="A524" t="s">
         <v>44</v>
       </c>
+      <c r="B524" t="s">
+        <v>1175</v>
+      </c>
       <c r="C524" t="s">
         <v>60</v>
       </c>
@@ -17671,6 +19246,9 @@
       <c r="A525" t="s">
         <v>44</v>
       </c>
+      <c r="B525" t="s">
+        <v>1175</v>
+      </c>
       <c r="C525" t="s">
         <v>60</v>
       </c>
@@ -17697,6 +19275,9 @@
       <c r="A526" t="s">
         <v>44</v>
       </c>
+      <c r="B526" t="s">
+        <v>1175</v>
+      </c>
       <c r="C526" t="s">
         <v>60</v>
       </c>
@@ -17723,6 +19304,9 @@
       <c r="A527" t="s">
         <v>44</v>
       </c>
+      <c r="B527" t="s">
+        <v>1175</v>
+      </c>
       <c r="C527" t="s">
         <v>60</v>
       </c>
@@ -17749,6 +19333,9 @@
       <c r="A528" t="s">
         <v>44</v>
       </c>
+      <c r="B528" t="s">
+        <v>1175</v>
+      </c>
       <c r="C528" t="s">
         <v>60</v>
       </c>
@@ -17775,6 +19362,9 @@
       <c r="A529" t="s">
         <v>44</v>
       </c>
+      <c r="B529" t="s">
+        <v>1175</v>
+      </c>
       <c r="C529" t="s">
         <v>60</v>
       </c>
@@ -17801,6 +19391,9 @@
       <c r="A530" t="s">
         <v>44</v>
       </c>
+      <c r="B530" t="s">
+        <v>1175</v>
+      </c>
       <c r="C530" t="s">
         <v>60</v>
       </c>
@@ -17827,6 +19420,9 @@
       <c r="A531" t="s">
         <v>44</v>
       </c>
+      <c r="B531" t="s">
+        <v>1175</v>
+      </c>
       <c r="C531" t="s">
         <v>60</v>
       </c>
@@ -17853,6 +19449,9 @@
       <c r="A532" t="s">
         <v>44</v>
       </c>
+      <c r="B532" t="s">
+        <v>1175</v>
+      </c>
       <c r="C532" t="s">
         <v>60</v>
       </c>
@@ -17879,6 +19478,9 @@
       <c r="A533" t="s">
         <v>44</v>
       </c>
+      <c r="B533" t="s">
+        <v>1175</v>
+      </c>
       <c r="C533" t="s">
         <v>60</v>
       </c>
@@ -17905,6 +19507,9 @@
       <c r="A534" t="s">
         <v>44</v>
       </c>
+      <c r="B534" t="s">
+        <v>1175</v>
+      </c>
       <c r="C534" t="s">
         <v>61</v>
       </c>
@@ -17931,6 +19536,9 @@
       <c r="A535" t="s">
         <v>44</v>
       </c>
+      <c r="B535" t="s">
+        <v>1175</v>
+      </c>
       <c r="C535" t="s">
         <v>61</v>
       </c>
@@ -17957,6 +19565,9 @@
       <c r="A536" t="s">
         <v>44</v>
       </c>
+      <c r="B536" t="s">
+        <v>1175</v>
+      </c>
       <c r="C536" t="s">
         <v>61</v>
       </c>
@@ -17983,6 +19594,9 @@
       <c r="A537" t="s">
         <v>44</v>
       </c>
+      <c r="B537" t="s">
+        <v>1175</v>
+      </c>
       <c r="C537" t="s">
         <v>61</v>
       </c>
@@ -18009,6 +19623,9 @@
       <c r="A538" t="s">
         <v>44</v>
       </c>
+      <c r="B538" t="s">
+        <v>1175</v>
+      </c>
       <c r="C538" t="s">
         <v>62</v>
       </c>
@@ -18035,6 +19652,9 @@
       <c r="A539" t="s">
         <v>44</v>
       </c>
+      <c r="B539" t="s">
+        <v>1175</v>
+      </c>
       <c r="C539" t="s">
         <v>64</v>
       </c>
@@ -18061,6 +19681,9 @@
       <c r="A540" t="s">
         <v>44</v>
       </c>
+      <c r="B540" t="s">
+        <v>1175</v>
+      </c>
       <c r="C540" t="s">
         <v>64</v>
       </c>
@@ -18087,6 +19710,9 @@
       <c r="A541" t="s">
         <v>44</v>
       </c>
+      <c r="B541" t="s">
+        <v>1175</v>
+      </c>
       <c r="C541" t="s">
         <v>64</v>
       </c>
@@ -18113,6 +19739,9 @@
       <c r="A542" t="s">
         <v>44</v>
       </c>
+      <c r="B542" t="s">
+        <v>1175</v>
+      </c>
       <c r="C542" t="s">
         <v>64</v>
       </c>
@@ -18139,6 +19768,9 @@
       <c r="A543" t="s">
         <v>44</v>
       </c>
+      <c r="B543" t="s">
+        <v>1175</v>
+      </c>
       <c r="C543" t="s">
         <v>64</v>
       </c>
@@ -18165,6 +19797,9 @@
       <c r="A544" t="s">
         <v>44</v>
       </c>
+      <c r="B544" t="s">
+        <v>1175</v>
+      </c>
       <c r="C544" t="s">
         <v>64</v>
       </c>
@@ -18191,6 +19826,9 @@
       <c r="A545" t="s">
         <v>44</v>
       </c>
+      <c r="B545" t="s">
+        <v>1175</v>
+      </c>
       <c r="C545" t="s">
         <v>64</v>
       </c>
@@ -18217,6 +19855,9 @@
       <c r="A546" t="s">
         <v>44</v>
       </c>
+      <c r="B546" t="s">
+        <v>1175</v>
+      </c>
       <c r="C546" t="s">
         <v>64</v>
       </c>
@@ -18243,6 +19884,9 @@
       <c r="A547" t="s">
         <v>44</v>
       </c>
+      <c r="B547" t="s">
+        <v>1175</v>
+      </c>
       <c r="C547" t="s">
         <v>64</v>
       </c>
@@ -18269,6 +19913,9 @@
       <c r="A548" t="s">
         <v>44</v>
       </c>
+      <c r="B548" t="s">
+        <v>1175</v>
+      </c>
       <c r="C548" t="s">
         <v>64</v>
       </c>
@@ -18295,6 +19942,9 @@
       <c r="A549" t="s">
         <v>44</v>
       </c>
+      <c r="B549" t="s">
+        <v>1175</v>
+      </c>
       <c r="C549" t="s">
         <v>93</v>
       </c>
@@ -18321,6 +19971,9 @@
       <c r="A550" t="s">
         <v>44</v>
       </c>
+      <c r="B550" t="s">
+        <v>1175</v>
+      </c>
       <c r="C550" t="s">
         <v>93</v>
       </c>
@@ -18347,6 +20000,9 @@
       <c r="A551" t="s">
         <v>44</v>
       </c>
+      <c r="B551" t="s">
+        <v>1175</v>
+      </c>
       <c r="C551" t="s">
         <v>93</v>
       </c>
@@ -18373,6 +20029,9 @@
       <c r="A552" t="s">
         <v>44</v>
       </c>
+      <c r="B552" t="s">
+        <v>1175</v>
+      </c>
       <c r="C552" t="s">
         <v>93</v>
       </c>
@@ -18399,6 +20058,9 @@
       <c r="A553" t="s">
         <v>44</v>
       </c>
+      <c r="B553" t="s">
+        <v>1175</v>
+      </c>
       <c r="C553" t="s">
         <v>93</v>
       </c>
@@ -18425,6 +20087,9 @@
       <c r="A554" t="s">
         <v>44</v>
       </c>
+      <c r="B554" t="s">
+        <v>1175</v>
+      </c>
       <c r="C554" t="s">
         <v>93</v>
       </c>
@@ -18451,6 +20116,9 @@
       <c r="A555" t="s">
         <v>44</v>
       </c>
+      <c r="B555" t="s">
+        <v>1175</v>
+      </c>
       <c r="C555" t="s">
         <v>93</v>
       </c>
@@ -18477,6 +20145,9 @@
       <c r="A556" t="s">
         <v>44</v>
       </c>
+      <c r="B556" t="s">
+        <v>1175</v>
+      </c>
       <c r="C556" t="s">
         <v>93</v>
       </c>
@@ -18503,6 +20174,9 @@
       <c r="A557" t="s">
         <v>44</v>
       </c>
+      <c r="B557" t="s">
+        <v>1175</v>
+      </c>
       <c r="C557" t="s">
         <v>93</v>
       </c>
@@ -18529,6 +20203,9 @@
       <c r="A558" t="s">
         <v>44</v>
       </c>
+      <c r="B558" t="s">
+        <v>1175</v>
+      </c>
       <c r="C558" t="s">
         <v>93</v>
       </c>
@@ -18555,6 +20232,9 @@
       <c r="A559" t="s">
         <v>44</v>
       </c>
+      <c r="B559" t="s">
+        <v>1175</v>
+      </c>
       <c r="C559" t="s">
         <v>93</v>
       </c>
@@ -18581,6 +20261,9 @@
       <c r="A560" t="s">
         <v>44</v>
       </c>
+      <c r="B560" t="s">
+        <v>1175</v>
+      </c>
       <c r="C560" t="s">
         <v>93</v>
       </c>
@@ -18607,6 +20290,9 @@
       <c r="A561" t="s">
         <v>44</v>
       </c>
+      <c r="B561" t="s">
+        <v>1175</v>
+      </c>
       <c r="C561" t="s">
         <v>93</v>
       </c>
@@ -18633,6 +20319,9 @@
       <c r="A562" t="s">
         <v>44</v>
       </c>
+      <c r="B562" t="s">
+        <v>1175</v>
+      </c>
       <c r="C562" t="s">
         <v>93</v>
       </c>
@@ -18659,6 +20348,9 @@
       <c r="A563" t="s">
         <v>44</v>
       </c>
+      <c r="B563" t="s">
+        <v>1175</v>
+      </c>
       <c r="C563" t="s">
         <v>93</v>
       </c>
@@ -18685,6 +20377,9 @@
       <c r="A564" t="s">
         <v>44</v>
       </c>
+      <c r="B564" t="s">
+        <v>1175</v>
+      </c>
       <c r="C564" t="s">
         <v>93</v>
       </c>
@@ -18711,6 +20406,9 @@
       <c r="A565" t="s">
         <v>44</v>
       </c>
+      <c r="B565" t="s">
+        <v>1175</v>
+      </c>
       <c r="C565" t="s">
         <v>93</v>
       </c>
@@ -18737,6 +20435,9 @@
       <c r="A566" t="s">
         <v>44</v>
       </c>
+      <c r="B566" t="s">
+        <v>1175</v>
+      </c>
       <c r="C566" t="s">
         <v>93</v>
       </c>
@@ -18763,6 +20464,9 @@
       <c r="A567" t="s">
         <v>44</v>
       </c>
+      <c r="B567" t="s">
+        <v>1175</v>
+      </c>
       <c r="C567" t="s">
         <v>93</v>
       </c>
@@ -18789,6 +20493,9 @@
       <c r="A568" t="s">
         <v>44</v>
       </c>
+      <c r="B568" t="s">
+        <v>1175</v>
+      </c>
       <c r="C568" t="s">
         <v>93</v>
       </c>
@@ -18815,6 +20522,9 @@
       <c r="A569" t="s">
         <v>44</v>
       </c>
+      <c r="B569" t="s">
+        <v>1175</v>
+      </c>
       <c r="C569" t="s">
         <v>93</v>
       </c>
@@ -18841,6 +20551,9 @@
       <c r="A570" t="s">
         <v>44</v>
       </c>
+      <c r="B570" t="s">
+        <v>1175</v>
+      </c>
       <c r="C570" t="s">
         <v>93</v>
       </c>
@@ -18867,6 +20580,9 @@
       <c r="A571" t="s">
         <v>44</v>
       </c>
+      <c r="B571" t="s">
+        <v>1175</v>
+      </c>
       <c r="C571" t="s">
         <v>93</v>
       </c>
@@ -18893,6 +20609,9 @@
       <c r="A572" t="s">
         <v>44</v>
       </c>
+      <c r="B572" t="s">
+        <v>1175</v>
+      </c>
       <c r="C572" t="s">
         <v>93</v>
       </c>
@@ -18919,6 +20638,9 @@
       <c r="A573" t="s">
         <v>44</v>
       </c>
+      <c r="B573" t="s">
+        <v>1175</v>
+      </c>
       <c r="C573" t="s">
         <v>93</v>
       </c>
@@ -18945,6 +20667,9 @@
       <c r="A574" t="s">
         <v>44</v>
       </c>
+      <c r="B574" t="s">
+        <v>1175</v>
+      </c>
       <c r="C574" t="s">
         <v>93</v>
       </c>
@@ -18971,6 +20696,9 @@
       <c r="A575" t="s">
         <v>44</v>
       </c>
+      <c r="B575" t="s">
+        <v>1175</v>
+      </c>
       <c r="C575" t="s">
         <v>93</v>
       </c>
@@ -18997,6 +20725,9 @@
       <c r="A576" t="s">
         <v>44</v>
       </c>
+      <c r="B576" t="s">
+        <v>1175</v>
+      </c>
       <c r="C576" t="s">
         <v>93</v>
       </c>
@@ -19023,6 +20754,9 @@
       <c r="A577" t="s">
         <v>44</v>
       </c>
+      <c r="B577" t="s">
+        <v>1175</v>
+      </c>
       <c r="C577" t="s">
         <v>93</v>
       </c>
@@ -19049,6 +20783,9 @@
       <c r="A578" t="s">
         <v>44</v>
       </c>
+      <c r="B578" t="s">
+        <v>1175</v>
+      </c>
       <c r="C578" t="s">
         <v>93</v>
       </c>
@@ -19075,6 +20812,9 @@
       <c r="A579" t="s">
         <v>44</v>
       </c>
+      <c r="B579" t="s">
+        <v>1176</v>
+      </c>
       <c r="C579" t="s">
         <v>67</v>
       </c>
@@ -19101,6 +20841,9 @@
       <c r="A580" t="s">
         <v>44</v>
       </c>
+      <c r="B580" t="s">
+        <v>1176</v>
+      </c>
       <c r="C580" t="s">
         <v>67</v>
       </c>
@@ -19127,6 +20870,9 @@
       <c r="A581" t="s">
         <v>44</v>
       </c>
+      <c r="B581" t="s">
+        <v>1176</v>
+      </c>
       <c r="C581" t="s">
         <v>67</v>
       </c>
@@ -19153,6 +20899,9 @@
       <c r="A582" t="s">
         <v>44</v>
       </c>
+      <c r="B582" t="s">
+        <v>1176</v>
+      </c>
       <c r="C582" t="s">
         <v>67</v>
       </c>
@@ -19179,6 +20928,9 @@
       <c r="A583" t="s">
         <v>44</v>
       </c>
+      <c r="B583" t="s">
+        <v>1176</v>
+      </c>
       <c r="C583" t="s">
         <v>67</v>
       </c>
@@ -19205,6 +20957,9 @@
       <c r="A584" t="s">
         <v>44</v>
       </c>
+      <c r="B584" t="s">
+        <v>1176</v>
+      </c>
       <c r="C584" t="s">
         <v>67</v>
       </c>
@@ -19231,6 +20986,9 @@
       <c r="A585" t="s">
         <v>44</v>
       </c>
+      <c r="B585" t="s">
+        <v>1176</v>
+      </c>
       <c r="C585" t="s">
         <v>67</v>
       </c>
@@ -19257,6 +21015,9 @@
       <c r="A586" t="s">
         <v>44</v>
       </c>
+      <c r="B586" t="s">
+        <v>1176</v>
+      </c>
       <c r="C586" t="s">
         <v>67</v>
       </c>
@@ -19283,6 +21044,9 @@
       <c r="A587" t="s">
         <v>44</v>
       </c>
+      <c r="B587" t="s">
+        <v>1176</v>
+      </c>
       <c r="C587" t="s">
         <v>67</v>
       </c>
@@ -19309,6 +21073,9 @@
       <c r="A588" t="s">
         <v>44</v>
       </c>
+      <c r="B588" t="s">
+        <v>1176</v>
+      </c>
       <c r="C588" t="s">
         <v>67</v>
       </c>
@@ -19335,6 +21102,9 @@
       <c r="A589" t="s">
         <v>44</v>
       </c>
+      <c r="B589" t="s">
+        <v>1176</v>
+      </c>
       <c r="C589" t="s">
         <v>67</v>
       </c>
@@ -19361,6 +21131,9 @@
       <c r="A590" t="s">
         <v>44</v>
       </c>
+      <c r="B590" t="s">
+        <v>1176</v>
+      </c>
       <c r="C590" t="s">
         <v>67</v>
       </c>
@@ -19387,6 +21160,9 @@
       <c r="A591" t="s">
         <v>44</v>
       </c>
+      <c r="B591" t="s">
+        <v>1176</v>
+      </c>
       <c r="C591" t="s">
         <v>67</v>
       </c>
@@ -19413,6 +21189,9 @@
       <c r="A592" t="s">
         <v>44</v>
       </c>
+      <c r="B592" t="s">
+        <v>1176</v>
+      </c>
       <c r="C592" t="s">
         <v>67</v>
       </c>
@@ -19439,6 +21218,9 @@
       <c r="A593" t="s">
         <v>44</v>
       </c>
+      <c r="B593" t="s">
+        <v>1176</v>
+      </c>
       <c r="C593" t="s">
         <v>67</v>
       </c>
@@ -19465,6 +21247,9 @@
       <c r="A594" t="s">
         <v>44</v>
       </c>
+      <c r="B594" t="s">
+        <v>1177</v>
+      </c>
       <c r="C594" t="s">
         <v>69</v>
       </c>
@@ -19491,6 +21276,9 @@
       <c r="A595" t="s">
         <v>44</v>
       </c>
+      <c r="B595" t="s">
+        <v>1177</v>
+      </c>
       <c r="C595" t="s">
         <v>69</v>
       </c>
@@ -19517,6 +21305,9 @@
       <c r="A596" t="s">
         <v>44</v>
       </c>
+      <c r="B596" t="s">
+        <v>1177</v>
+      </c>
       <c r="C596" t="s">
         <v>69</v>
       </c>
@@ -19543,6 +21334,9 @@
       <c r="A597" t="s">
         <v>44</v>
       </c>
+      <c r="B597" t="s">
+        <v>1177</v>
+      </c>
       <c r="C597" t="s">
         <v>69</v>
       </c>
@@ -19569,6 +21363,9 @@
       <c r="A598" t="s">
         <v>44</v>
       </c>
+      <c r="B598" t="s">
+        <v>1177</v>
+      </c>
       <c r="C598" t="s">
         <v>69</v>
       </c>
@@ -19595,6 +21392,9 @@
       <c r="A599" t="s">
         <v>44</v>
       </c>
+      <c r="B599" t="s">
+        <v>1177</v>
+      </c>
       <c r="C599" t="s">
         <v>69</v>
       </c>
@@ -19621,6 +21421,9 @@
       <c r="A600" t="s">
         <v>44</v>
       </c>
+      <c r="B600" t="s">
+        <v>1177</v>
+      </c>
       <c r="C600" t="s">
         <v>69</v>
       </c>
@@ -19647,6 +21450,9 @@
       <c r="A601" t="s">
         <v>44</v>
       </c>
+      <c r="B601" t="s">
+        <v>1177</v>
+      </c>
       <c r="C601" t="s">
         <v>69</v>
       </c>
@@ -19673,6 +21479,9 @@
       <c r="A602" t="s">
         <v>44</v>
       </c>
+      <c r="B602" t="s">
+        <v>1177</v>
+      </c>
       <c r="C602" t="s">
         <v>71</v>
       </c>
@@ -19699,6 +21508,9 @@
       <c r="A603" t="s">
         <v>44</v>
       </c>
+      <c r="B603" t="s">
+        <v>1177</v>
+      </c>
       <c r="C603" t="s">
         <v>71</v>
       </c>
@@ -19725,6 +21537,9 @@
       <c r="A604" t="s">
         <v>44</v>
       </c>
+      <c r="B604" t="s">
+        <v>1177</v>
+      </c>
       <c r="C604" t="s">
         <v>71</v>
       </c>
@@ -19751,6 +21566,9 @@
       <c r="A605" t="s">
         <v>44</v>
       </c>
+      <c r="B605" t="s">
+        <v>1177</v>
+      </c>
       <c r="C605" t="s">
         <v>71</v>
       </c>
@@ -19777,6 +21595,9 @@
       <c r="A606" t="s">
         <v>44</v>
       </c>
+      <c r="B606" t="s">
+        <v>1177</v>
+      </c>
       <c r="C606" t="s">
         <v>71</v>
       </c>
@@ -19803,6 +21624,9 @@
       <c r="A607" t="s">
         <v>44</v>
       </c>
+      <c r="B607" t="s">
+        <v>1177</v>
+      </c>
       <c r="C607" t="s">
         <v>72</v>
       </c>
@@ -19829,6 +21653,9 @@
       <c r="A608" t="s">
         <v>44</v>
       </c>
+      <c r="B608" t="s">
+        <v>1177</v>
+      </c>
       <c r="C608" t="s">
         <v>72</v>
       </c>
@@ -19855,6 +21682,9 @@
       <c r="A609" t="s">
         <v>44</v>
       </c>
+      <c r="B609" t="s">
+        <v>1177</v>
+      </c>
       <c r="C609" t="s">
         <v>72</v>
       </c>
@@ -19881,6 +21711,9 @@
       <c r="A610" t="s">
         <v>44</v>
       </c>
+      <c r="B610" t="s">
+        <v>1177</v>
+      </c>
       <c r="C610" t="s">
         <v>73</v>
       </c>
@@ -19907,6 +21740,9 @@
       <c r="A611" t="s">
         <v>44</v>
       </c>
+      <c r="B611" t="s">
+        <v>1177</v>
+      </c>
       <c r="C611" t="s">
         <v>73</v>
       </c>
@@ -19933,6 +21769,9 @@
       <c r="A612" t="s">
         <v>44</v>
       </c>
+      <c r="B612" t="s">
+        <v>1177</v>
+      </c>
       <c r="C612" t="s">
         <v>73</v>
       </c>
@@ -19959,6 +21798,9 @@
       <c r="A613" t="s">
         <v>44</v>
       </c>
+      <c r="B613" t="s">
+        <v>1177</v>
+      </c>
       <c r="C613" t="s">
         <v>74</v>
       </c>
@@ -19985,6 +21827,9 @@
       <c r="A614" t="s">
         <v>44</v>
       </c>
+      <c r="B614" t="s">
+        <v>1177</v>
+      </c>
       <c r="C614" t="s">
         <v>74</v>
       </c>
@@ -20011,6 +21856,9 @@
       <c r="A615" t="s">
         <v>44</v>
       </c>
+      <c r="B615" t="s">
+        <v>1177</v>
+      </c>
       <c r="C615" t="s">
         <v>74</v>
       </c>
@@ -20037,6 +21885,9 @@
       <c r="A616" t="s">
         <v>44</v>
       </c>
+      <c r="B616" t="s">
+        <v>1177</v>
+      </c>
       <c r="C616" t="s">
         <v>74</v>
       </c>
@@ -20063,6 +21914,9 @@
       <c r="A617" t="s">
         <v>44</v>
       </c>
+      <c r="B617" t="s">
+        <v>1177</v>
+      </c>
       <c r="C617" t="s">
         <v>74</v>
       </c>
@@ -20089,6 +21943,9 @@
       <c r="A618" t="s">
         <v>44</v>
       </c>
+      <c r="B618" t="s">
+        <v>1177</v>
+      </c>
       <c r="C618" t="s">
         <v>74</v>
       </c>
@@ -20115,6 +21972,9 @@
       <c r="A619" t="s">
         <v>44</v>
       </c>
+      <c r="B619" t="s">
+        <v>1177</v>
+      </c>
       <c r="C619" t="s">
         <v>74</v>
       </c>
@@ -20141,6 +22001,9 @@
       <c r="A620" t="s">
         <v>44</v>
       </c>
+      <c r="B620" t="s">
+        <v>1177</v>
+      </c>
       <c r="C620" t="s">
         <v>75</v>
       </c>
@@ -20167,6 +22030,9 @@
       <c r="A621" t="s">
         <v>44</v>
       </c>
+      <c r="B621" t="s">
+        <v>1177</v>
+      </c>
       <c r="C621" t="s">
         <v>75</v>
       </c>
@@ -20193,6 +22059,9 @@
       <c r="A622" t="s">
         <v>44</v>
       </c>
+      <c r="B622" t="s">
+        <v>1177</v>
+      </c>
       <c r="C622" t="s">
         <v>75</v>
       </c>
@@ -20219,6 +22088,9 @@
       <c r="A623" t="s">
         <v>44</v>
       </c>
+      <c r="B623" t="s">
+        <v>1177</v>
+      </c>
       <c r="C623" t="s">
         <v>76</v>
       </c>
@@ -20245,6 +22117,9 @@
       <c r="A624" t="s">
         <v>44</v>
       </c>
+      <c r="B624" t="s">
+        <v>1178</v>
+      </c>
       <c r="C624" t="s">
         <v>77</v>
       </c>
@@ -20271,6 +22146,9 @@
       <c r="A625" t="s">
         <v>44</v>
       </c>
+      <c r="B625" t="s">
+        <v>1178</v>
+      </c>
       <c r="C625" t="s">
         <v>77</v>
       </c>
@@ -20297,6 +22175,9 @@
       <c r="A626" t="s">
         <v>44</v>
       </c>
+      <c r="B626" t="s">
+        <v>1178</v>
+      </c>
       <c r="C626" t="s">
         <v>77</v>
       </c>
@@ -20323,6 +22204,9 @@
       <c r="A627" t="s">
         <v>44</v>
       </c>
+      <c r="B627" t="s">
+        <v>1178</v>
+      </c>
       <c r="C627" t="s">
         <v>77</v>
       </c>
@@ -20349,6 +22233,9 @@
       <c r="A628" t="s">
         <v>44</v>
       </c>
+      <c r="B628" t="s">
+        <v>1178</v>
+      </c>
       <c r="C628" t="s">
         <v>77</v>
       </c>
@@ -20375,6 +22262,9 @@
       <c r="A629" t="s">
         <v>44</v>
       </c>
+      <c r="B629" t="s">
+        <v>1178</v>
+      </c>
       <c r="C629" t="s">
         <v>77</v>
       </c>
@@ -20401,6 +22291,9 @@
       <c r="A630" t="s">
         <v>44</v>
       </c>
+      <c r="B630" t="s">
+        <v>1178</v>
+      </c>
       <c r="C630" t="s">
         <v>77</v>
       </c>
@@ -20427,6 +22320,9 @@
       <c r="A631" t="s">
         <v>44</v>
       </c>
+      <c r="B631" t="s">
+        <v>1178</v>
+      </c>
       <c r="C631" t="s">
         <v>77</v>
       </c>
@@ -20453,6 +22349,9 @@
       <c r="A632" t="s">
         <v>44</v>
       </c>
+      <c r="B632" t="s">
+        <v>1178</v>
+      </c>
       <c r="C632" t="s">
         <v>77</v>
       </c>
@@ -20479,6 +22378,9 @@
       <c r="A633" t="s">
         <v>44</v>
       </c>
+      <c r="B633" t="s">
+        <v>1178</v>
+      </c>
       <c r="C633" t="s">
         <v>77</v>
       </c>
@@ -20505,6 +22407,9 @@
       <c r="A634" t="s">
         <v>44</v>
       </c>
+      <c r="B634" t="s">
+        <v>1178</v>
+      </c>
       <c r="C634" t="s">
         <v>77</v>
       </c>
@@ -20531,6 +22436,9 @@
       <c r="A635" t="s">
         <v>44</v>
       </c>
+      <c r="B635" t="s">
+        <v>1178</v>
+      </c>
       <c r="C635" t="s">
         <v>77</v>
       </c>
@@ -20557,6 +22465,9 @@
       <c r="A636" t="s">
         <v>44</v>
       </c>
+      <c r="B636" t="s">
+        <v>1178</v>
+      </c>
       <c r="C636" t="s">
         <v>77</v>
       </c>
@@ -20583,6 +22494,9 @@
       <c r="A637" t="s">
         <v>44</v>
       </c>
+      <c r="B637" t="s">
+        <v>1178</v>
+      </c>
       <c r="C637" t="s">
         <v>77</v>
       </c>
@@ -20609,6 +22523,9 @@
       <c r="A638" t="s">
         <v>44</v>
       </c>
+      <c r="B638" t="s">
+        <v>1178</v>
+      </c>
       <c r="C638" t="s">
         <v>77</v>
       </c>
@@ -20635,6 +22552,9 @@
       <c r="A639" t="s">
         <v>44</v>
       </c>
+      <c r="B639" t="s">
+        <v>1178</v>
+      </c>
       <c r="C639" t="s">
         <v>78</v>
       </c>
@@ -20661,6 +22581,9 @@
       <c r="A640" t="s">
         <v>44</v>
       </c>
+      <c r="B640" t="s">
+        <v>1178</v>
+      </c>
       <c r="C640" t="s">
         <v>78</v>
       </c>
@@ -20687,6 +22610,9 @@
       <c r="A641" t="s">
         <v>44</v>
       </c>
+      <c r="B641" t="s">
+        <v>1178</v>
+      </c>
       <c r="C641" t="s">
         <v>78</v>
       </c>
@@ -20713,6 +22639,9 @@
       <c r="A642" t="s">
         <v>44</v>
       </c>
+      <c r="B642" t="s">
+        <v>1178</v>
+      </c>
       <c r="C642" t="s">
         <v>78</v>
       </c>
@@ -20739,6 +22668,9 @@
       <c r="A643" t="s">
         <v>44</v>
       </c>
+      <c r="B643" t="s">
+        <v>1178</v>
+      </c>
       <c r="C643" t="s">
         <v>78</v>
       </c>
@@ -20765,6 +22697,9 @@
       <c r="A644" t="s">
         <v>44</v>
       </c>
+      <c r="B644" t="s">
+        <v>1178</v>
+      </c>
       <c r="C644" t="s">
         <v>78</v>
       </c>
@@ -20791,6 +22726,9 @@
       <c r="A645" t="s">
         <v>44</v>
       </c>
+      <c r="B645" t="s">
+        <v>1178</v>
+      </c>
       <c r="C645" t="s">
         <v>78</v>
       </c>
@@ -20817,6 +22755,9 @@
       <c r="A646" t="s">
         <v>44</v>
       </c>
+      <c r="B646" t="s">
+        <v>1178</v>
+      </c>
       <c r="C646" t="s">
         <v>78</v>
       </c>
@@ -20843,6 +22784,9 @@
       <c r="A647" t="s">
         <v>44</v>
       </c>
+      <c r="B647" t="s">
+        <v>1178</v>
+      </c>
       <c r="C647" t="s">
         <v>78</v>
       </c>
@@ -20869,6 +22813,9 @@
       <c r="A648" t="s">
         <v>44</v>
       </c>
+      <c r="B648" t="s">
+        <v>1178</v>
+      </c>
       <c r="C648" t="s">
         <v>94</v>
       </c>
@@ -20895,6 +22842,9 @@
       <c r="A649" t="s">
         <v>44</v>
       </c>
+      <c r="B649" t="s">
+        <v>1178</v>
+      </c>
       <c r="C649" t="s">
         <v>94</v>
       </c>
@@ -20921,6 +22871,9 @@
       <c r="A650" t="s">
         <v>44</v>
       </c>
+      <c r="B650" t="s">
+        <v>1178</v>
+      </c>
       <c r="C650" t="s">
         <v>95</v>
       </c>
@@ -20947,6 +22900,9 @@
       <c r="A651" t="s">
         <v>44</v>
       </c>
+      <c r="B651" t="s">
+        <v>1178</v>
+      </c>
       <c r="C651" t="s">
         <v>95</v>
       </c>
@@ -20973,6 +22929,9 @@
       <c r="A652" t="s">
         <v>44</v>
       </c>
+      <c r="B652" t="s">
+        <v>1178</v>
+      </c>
       <c r="C652" t="s">
         <v>82</v>
       </c>
@@ -20999,6 +22958,9 @@
       <c r="A653" t="s">
         <v>44</v>
       </c>
+      <c r="B653" t="s">
+        <v>1178</v>
+      </c>
       <c r="C653" t="s">
         <v>83</v>
       </c>
@@ -21025,6 +22987,9 @@
       <c r="A654" t="s">
         <v>44</v>
       </c>
+      <c r="B654" t="s">
+        <v>1179</v>
+      </c>
       <c r="C654" t="s">
         <v>86</v>
       </c>
@@ -21050,6 +23015,9 @@
     <row r="655" spans="1:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>44</v>
+      </c>
+      <c r="B655" t="s">
+        <v>1179</v>
       </c>
       <c r="C655" t="s">
         <v>87</v>

--- a/es/es-global-request.xlsx
+++ b/es/es-global-request.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CNXK\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cnxmail-my.sharepoint.com/personal/sujeong_kang_concentrix_com/Documents/02.Operations/01.BU/01.ES/00.Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0204312E-C9C7-4AE9-8E9E-15C8E534DCC1}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1725" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LG DUALCOOL AI" sheetId="2" r:id="rId1"/>
@@ -4177,7 +4177,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">

--- a/es/es-global-request.xlsx
+++ b/es/es-global-request.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cnxmail-my.sharepoint.com/personal/sujeong_kang_concentrix_com/Documents/02.Operations/01.BU/01.ES/00.Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="274" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99E17DFF-48A6-48A3-BED6-E5C5776D4FFA}"/>
+  <xr:revisionPtr revIDLastSave="283" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81C8141A-DE1D-4953-94C7-CABBAA8F327C}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1725" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21570" yWindow="2640" windowWidth="23370" windowHeight="14895" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LG DUALCOOL AI" sheetId="2" r:id="rId1"/>
@@ -3841,10 +3841,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4080,20 +4080,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="13.5">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:8">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="13.5">
+      <c r="A3" s="9" t="s">
         <v>1199</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>1200</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="13.5">
@@ -23233,19 +23233,19 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="13.5">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:8">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="13.5">
+      <c r="A3" s="7" t="s">
         <v>1198</v>
       </c>
-      <c r="B2" s="8"/>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="B3" s="8"/>
     </row>
     <row r="4" spans="1:8" ht="13.5">
       <c r="A4" s="5" t="s">
@@ -23256,42 +23256,42 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="12" t="s">
         <v>1201</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="12" t="s">
         <v>1202</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="12" t="s">
         <v>1196</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10" t="s">
+      <c r="D6" s="12"/>
+      <c r="E6" s="12" t="s">
         <v>1197</v>
       </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="11" t="s">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="10" t="s">
         <v>1193</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="10" t="s">
         <v>1194</v>
       </c>
-      <c r="E7" s="12">
-        <v>1</v>
-      </c>
-      <c r="F7" s="12">
+      <c r="E7" s="11">
+        <v>1</v>
+      </c>
+      <c r="F7" s="11">
         <v>2</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="11">
         <v>3</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="11">
         <v>4</v>
       </c>
     </row>
@@ -23348,19 +23348,19 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="13.5">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:6">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="13.5">
+      <c r="A3" s="7" t="s">
         <v>1198</v>
       </c>
-      <c r="B2" s="1"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="B3" s="1"/>
     </row>
     <row r="4" spans="1:6" ht="13.5">
       <c r="A4" s="5" t="s">

--- a/es/es-global-request.xlsx
+++ b/es/es-global-request.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cnxmail-my.sharepoint.com/personal/sujeong_kang_concentrix_com/Documents/02.Operations/01.BU/01.ES/00.Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="283" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81C8141A-DE1D-4953-94C7-CABBAA8F327C}"/>
+  <xr:revisionPtr revIDLastSave="290" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B04CBDF-7469-439A-9AF0-A5912888B2F6}"/>
   <bookViews>
-    <workbookView xWindow="-21570" yWindow="2640" windowWidth="23370" windowHeight="14895" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26640" yWindow="2115" windowWidth="23370" windowHeight="14895" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LG DUALCOOL AI" sheetId="2" r:id="rId1"/>
@@ -3651,18 +3651,6 @@
   </si>
   <si>
     <t>EASTAFRICA : KE (en)</t>
-  </si>
-  <si>
-    <t>SG</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>TW</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>VN</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Microsite</t>
@@ -3744,6 +3732,16 @@
   <si>
     <t>Country</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SG-en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TW-zh</t>
+  </si>
+  <si>
+    <t>VN-vi</t>
   </si>
 </sst>
 </file>
@@ -4090,10 +4088,10 @@
     </row>
     <row r="3" spans="1:8" ht="13.5">
       <c r="A3" s="9" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="13.5">
@@ -23218,7 +23216,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F77BCE9D-002C-46A4-837D-945D35BE8D04}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
@@ -23243,7 +23241,7 @@
     </row>
     <row r="3" spans="1:8" ht="13.5">
       <c r="A3" s="7" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="B3" s="8"/>
     </row>
@@ -23257,17 +23255,17 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="12" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
@@ -23277,10 +23275,10 @@
       <c r="A7" s="12"/>
       <c r="B7" s="12"/>
       <c r="C7" s="10" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="E7" s="11">
         <v>1</v>
@@ -23297,28 +23295,32 @@
     </row>
     <row r="8" spans="1:8" ht="13.5">
       <c r="A8" s="1" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1190</v>
+        <v>1200</v>
       </c>
       <c r="C8" s="2"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1191</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1192</v>
-      </c>
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -23358,7 +23360,7 @@
     </row>
     <row r="3" spans="1:6" ht="13.5">
       <c r="A3" s="7" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="B3" s="1"/>
     </row>

--- a/es/es-global-request.xlsx
+++ b/es/es-global-request.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cnxmail-my.sharepoint.com/personal/sujeong_kang_concentrix_com/Documents/02.Operations/01.BU/01.ES/00.Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="290" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B04CBDF-7469-439A-9AF0-A5912888B2F6}"/>
+  <xr:revisionPtr revIDLastSave="305" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{736E9D1D-73DE-4DDE-BF21-8D7DC53A09C7}"/>
   <bookViews>
-    <workbookView xWindow="-26640" yWindow="2115" windowWidth="23370" windowHeight="14895" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25980" yWindow="2415" windowWidth="23370" windowHeight="14895" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LG DUALCOOL AI" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4712" uniqueCount="1203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4730" uniqueCount="1204">
   <si>
     <t>Title</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -3742,6 +3742,10 @@
   </si>
   <si>
     <t>VN-vi</t>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4078,20 +4082,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
+    <row r="2" spans="1:8" ht="13.5">
+      <c r="A2" s="9" t="s">
+        <v>1196</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>1175</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="13.5">
-      <c r="A3" s="9" t="s">
-        <v>1196</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="13.5">
@@ -23231,19 +23235,19 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:8" ht="13.5">
+      <c r="A2" s="7" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B2" s="8"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="13.5">
-      <c r="A3" s="7" t="s">
-        <v>1195</v>
-      </c>
-      <c r="B3" s="8"/>
     </row>
     <row r="4" spans="1:8" ht="13.5">
       <c r="A4" s="5" t="s">
@@ -23300,22 +23304,75 @@
       <c r="B8" s="1" t="s">
         <v>1200</v>
       </c>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="C8" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="13.5">
       <c r="A9" s="1" t="s">
         <v>1192</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1201</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="C9" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="13.5">
       <c r="A10" s="1" t="s">
         <v>1192</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>1202</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>1203</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -23350,19 +23407,19 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:6" ht="13.5">
+      <c r="A2" s="7" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B2" s="1"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="13.5">
-      <c r="A3" s="7" t="s">
-        <v>1195</v>
-      </c>
-      <c r="B3" s="1"/>
     </row>
     <row r="4" spans="1:6" ht="13.5">
       <c r="A4" s="5" t="s">

--- a/es/es-global-request.xlsx
+++ b/es/es-global-request.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cnxmail-my.sharepoint.com/personal/sujeong_kang_concentrix_com/Documents/02.Operations/01.BU/01.ES/00.Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="305" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{736E9D1D-73DE-4DDE-BF21-8D7DC53A09C7}"/>
+  <xr:revisionPtr revIDLastSave="380" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40498E01-A2FB-4688-92A8-0ABDBD880C42}"/>
   <bookViews>
-    <workbookView xWindow="-25980" yWindow="2415" windowWidth="23370" windowHeight="14895" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25290" yWindow="2430" windowWidth="23370" windowHeight="14895" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LG DUALCOOL AI" sheetId="2" r:id="rId1"/>
     <sheet name="SEO Title &amp; Description Automat" sheetId="3" r:id="rId2"/>
     <sheet name="Buying Guide &amp; Article" sheetId="4" r:id="rId3"/>
-    <sheet name="HVAC-B2B-SEO Correction" sheetId="5" r:id="rId4"/>
+    <sheet name="HVAC B2B SEO Correction" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HVAC-B2B-SEO Correction'!$A$6:$F$853</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SEO Title &amp; Description Automat'!$A$5:$J$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HVAC B2B SEO Correction'!$A$6:$F$853</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SEO Title &amp; Description Automat'!$A$6:$J$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4730" uniqueCount="1204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4763" uniqueCount="1210">
   <si>
     <t>Title</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -3653,23 +3653,7 @@
     <t>EASTAFRICA : KE (en)</t>
   </si>
   <si>
-    <t>Microsite</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GNB</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Asia</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buying Guide</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Article</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3744,7 +3728,47 @@
     <t>VN-vi</t>
   </si>
   <si>
-    <t>-</t>
+    <t>Microsite</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Category</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GNB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Article</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>How does an air purifier clean the air</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Air purifier for pets</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Caring for your air purifier</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>What is pm2.5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사전검토 필요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buying Guide</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buying guide air purifier</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3829,7 +3853,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3843,12 +3867,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4084,10 +4103,10 @@
     </row>
     <row r="2" spans="1:8" ht="13.5">
       <c r="A2" s="9" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4324,7 +4343,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB819BC4-E5C4-4402-898A-BE0A3820E230}">
-  <dimension ref="A1:J654"/>
+  <dimension ref="A1:J655"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="9" max="10" width="11" bestFit="1" customWidth="1"/>
@@ -4338,81 +4357,58 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:10" ht="13.5">
+      <c r="A2" s="9" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B2" s="1"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="13.5">
-      <c r="A3" s="5" t="s">
+    <row r="4" spans="1:10" ht="13.5">
+      <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="13.5">
-      <c r="A5" s="5" t="s">
+    <row r="6" spans="1:10" ht="13.5">
+      <c r="A6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>1180</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J6" s="5" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="13.5">
-      <c r="A6" t="s">
-        <v>1172</v>
-      </c>
-      <c r="B6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>1176</v>
-      </c>
-      <c r="D6" t="s">
-        <v>239</v>
-      </c>
-      <c r="E6" t="s">
-        <v>671</v>
-      </c>
-      <c r="F6" t="s">
-        <v>677</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="3">
-        <v>46219</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="13.5">
@@ -4429,10 +4425,10 @@
         <v>239</v>
       </c>
       <c r="E7" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="F7" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -4458,10 +4454,10 @@
         <v>239</v>
       </c>
       <c r="E8" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="F8" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -4478,7 +4474,7 @@
         <v>1172</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>1176</v>
@@ -4487,10 +4483,10 @@
         <v>239</v>
       </c>
       <c r="E9" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="F9" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -4516,10 +4512,10 @@
         <v>239</v>
       </c>
       <c r="E10" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="F10" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -4545,10 +4541,10 @@
         <v>239</v>
       </c>
       <c r="E11" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="F11" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -4562,10 +4558,10 @@
     </row>
     <row r="12" spans="1:10" ht="13.5">
       <c r="A12" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>1176</v>
@@ -4574,10 +4570,10 @@
         <v>239</v>
       </c>
       <c r="E12" t="s">
-        <v>379</v>
+        <v>675</v>
       </c>
       <c r="F12" t="s">
-        <v>380</v>
+        <v>676</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -4603,10 +4599,10 @@
         <v>239</v>
       </c>
       <c r="E13" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F13" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -4632,10 +4628,10 @@
         <v>239</v>
       </c>
       <c r="E14" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F14" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -4661,10 +4657,10 @@
         <v>239</v>
       </c>
       <c r="E15" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F15" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -4678,22 +4674,22 @@
     </row>
     <row r="16" spans="1:10" ht="13.5">
       <c r="A16" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>1176</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>239</v>
       </c>
       <c r="E16" t="s">
-        <v>242</v>
+        <v>385</v>
       </c>
       <c r="F16" t="s">
-        <v>243</v>
+        <v>386</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -4719,10 +4715,10 @@
         <v>90</v>
       </c>
       <c r="E17" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F17" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -4736,10 +4732,10 @@
     </row>
     <row r="18" spans="1:9" ht="13.5">
       <c r="A18" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>1176</v>
@@ -4748,10 +4744,10 @@
         <v>90</v>
       </c>
       <c r="E18" t="s">
-        <v>123</v>
+        <v>244</v>
       </c>
       <c r="F18" t="s">
-        <v>124</v>
+        <v>245</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -4777,10 +4773,10 @@
         <v>90</v>
       </c>
       <c r="E19" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -4806,10 +4802,10 @@
         <v>90</v>
       </c>
       <c r="E20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F20" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -4835,10 +4831,10 @@
         <v>90</v>
       </c>
       <c r="E21" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F21" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -4864,10 +4860,10 @@
         <v>90</v>
       </c>
       <c r="E22" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F22" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -4893,10 +4889,10 @@
         <v>90</v>
       </c>
       <c r="E23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F23" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -4922,10 +4918,10 @@
         <v>90</v>
       </c>
       <c r="E24" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F24" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -4951,39 +4947,39 @@
         <v>90</v>
       </c>
       <c r="E25" t="s">
+        <v>135</v>
+      </c>
+      <c r="F25" t="s">
+        <v>136</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I25" s="3">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="13.5">
+      <c r="A26" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D26" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" t="s">
         <v>137</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F26" t="s">
         <v>138</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I25" s="3">
-        <v>46219</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="13.5">
-      <c r="A26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>1176</v>
-      </c>
-      <c r="D26" t="s">
-        <v>90</v>
-      </c>
-      <c r="E26" t="s">
-        <v>246</v>
-      </c>
-      <c r="F26" t="s">
-        <v>247</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -5009,10 +5005,10 @@
         <v>90</v>
       </c>
       <c r="E27" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F27" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -5038,39 +5034,39 @@
         <v>90</v>
       </c>
       <c r="E28" t="s">
+        <v>248</v>
+      </c>
+      <c r="F28" t="s">
+        <v>249</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I28" s="3">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="13.5">
+      <c r="A29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D29" t="s">
+        <v>90</v>
+      </c>
+      <c r="E29" t="s">
         <v>250</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F29" t="s">
         <v>251</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I28" s="3">
-        <v>46219</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="13.5">
-      <c r="A29" t="s">
-        <v>1169</v>
-      </c>
-      <c r="B29" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>1176</v>
-      </c>
-      <c r="D29" t="s">
-        <v>239</v>
-      </c>
-      <c r="E29" t="s">
-        <v>252</v>
-      </c>
-      <c r="F29" t="s">
-        <v>253</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -5096,10 +5092,10 @@
         <v>239</v>
       </c>
       <c r="E30" t="s">
-        <v>323</v>
+        <v>252</v>
       </c>
       <c r="F30" t="s">
-        <v>867</v>
+        <v>253</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -5125,10 +5121,10 @@
         <v>239</v>
       </c>
       <c r="E31" t="s">
-        <v>246</v>
+        <v>323</v>
       </c>
       <c r="F31" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -5154,10 +5150,10 @@
         <v>239</v>
       </c>
       <c r="E32" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F32" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -5183,10 +5179,10 @@
         <v>239</v>
       </c>
       <c r="E33" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F33" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -5212,10 +5208,10 @@
         <v>239</v>
       </c>
       <c r="E34" t="s">
-        <v>315</v>
+        <v>250</v>
       </c>
       <c r="F34" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -5241,10 +5237,10 @@
         <v>239</v>
       </c>
       <c r="E35" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F35" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -5270,10 +5266,10 @@
         <v>239</v>
       </c>
       <c r="E36" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F36" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -5299,10 +5295,10 @@
         <v>239</v>
       </c>
       <c r="E37" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F37" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -5328,10 +5324,10 @@
         <v>239</v>
       </c>
       <c r="E38" t="s">
-        <v>242</v>
+        <v>321</v>
       </c>
       <c r="F38" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -5357,10 +5353,10 @@
         <v>239</v>
       </c>
       <c r="E39" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="F39" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -5386,10 +5382,10 @@
         <v>239</v>
       </c>
       <c r="E40" t="s">
-        <v>296</v>
+        <v>261</v>
       </c>
       <c r="F40" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -5415,10 +5411,10 @@
         <v>239</v>
       </c>
       <c r="E41" t="s">
-        <v>244</v>
+        <v>296</v>
       </c>
       <c r="F41" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -5444,10 +5440,10 @@
         <v>239</v>
       </c>
       <c r="E42" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="F42" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -5473,10 +5469,10 @@
         <v>239</v>
       </c>
       <c r="E43" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="F43" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -5502,10 +5498,10 @@
         <v>239</v>
       </c>
       <c r="E44" t="s">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="F44" t="s">
-        <v>255</v>
+        <v>880</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -5531,10 +5527,10 @@
         <v>239</v>
       </c>
       <c r="E45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -5560,10 +5556,10 @@
         <v>239</v>
       </c>
       <c r="E46" t="s">
-        <v>837</v>
+        <v>256</v>
       </c>
       <c r="F46" t="s">
-        <v>881</v>
+        <v>257</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -5589,10 +5585,10 @@
         <v>239</v>
       </c>
       <c r="E47" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F47" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -5618,10 +5614,10 @@
         <v>239</v>
       </c>
       <c r="E48" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="F48" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -5647,10 +5643,10 @@
         <v>239</v>
       </c>
       <c r="E49" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="F49" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -5664,22 +5660,22 @@
     </row>
     <row r="50" spans="1:9" ht="13.5">
       <c r="A50" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="B50" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>1176</v>
       </c>
       <c r="D50" t="s">
-        <v>90</v>
+        <v>239</v>
       </c>
       <c r="E50" t="s">
-        <v>387</v>
+        <v>843</v>
       </c>
       <c r="F50" t="s">
-        <v>388</v>
+        <v>884</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -5705,10 +5701,10 @@
         <v>90</v>
       </c>
       <c r="E51" t="s">
-        <v>1067</v>
+        <v>387</v>
       </c>
       <c r="F51" t="s">
-        <v>1068</v>
+        <v>388</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -5734,10 +5730,10 @@
         <v>90</v>
       </c>
       <c r="E52" t="s">
-        <v>395</v>
+        <v>1067</v>
       </c>
       <c r="F52" t="s">
-        <v>396</v>
+        <v>1068</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -5763,10 +5759,10 @@
         <v>90</v>
       </c>
       <c r="E53" t="s">
-        <v>1059</v>
+        <v>395</v>
       </c>
       <c r="F53" t="s">
-        <v>1060</v>
+        <v>396</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -5792,10 +5788,10 @@
         <v>90</v>
       </c>
       <c r="E54" t="s">
-        <v>397</v>
+        <v>1059</v>
       </c>
       <c r="F54" t="s">
-        <v>398</v>
+        <v>1060</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -5821,10 +5817,10 @@
         <v>90</v>
       </c>
       <c r="E55" t="s">
-        <v>1061</v>
+        <v>397</v>
       </c>
       <c r="F55" t="s">
-        <v>1062</v>
+        <v>398</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -5850,10 +5846,10 @@
         <v>90</v>
       </c>
       <c r="E56" t="s">
-        <v>1069</v>
+        <v>1061</v>
       </c>
       <c r="F56" t="s">
-        <v>1070</v>
+        <v>1062</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -5879,10 +5875,10 @@
         <v>90</v>
       </c>
       <c r="E57" t="s">
-        <v>399</v>
+        <v>1069</v>
       </c>
       <c r="F57" t="s">
-        <v>400</v>
+        <v>1070</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -5908,10 +5904,10 @@
         <v>90</v>
       </c>
       <c r="E58" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="F58" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -5937,10 +5933,10 @@
         <v>90</v>
       </c>
       <c r="E59" t="s">
-        <v>1071</v>
+        <v>389</v>
       </c>
       <c r="F59" t="s">
-        <v>1072</v>
+        <v>390</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -5966,10 +5962,10 @@
         <v>90</v>
       </c>
       <c r="E60" t="s">
-        <v>401</v>
+        <v>1071</v>
       </c>
       <c r="F60" t="s">
-        <v>402</v>
+        <v>1072</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -5995,10 +5991,10 @@
         <v>90</v>
       </c>
       <c r="E61" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F61" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -6024,10 +6020,10 @@
         <v>90</v>
       </c>
       <c r="E62" t="s">
-        <v>1063</v>
+        <v>403</v>
       </c>
       <c r="F62" t="s">
-        <v>1064</v>
+        <v>404</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -6053,10 +6049,10 @@
         <v>90</v>
       </c>
       <c r="E63" t="s">
-        <v>1073</v>
+        <v>1063</v>
       </c>
       <c r="F63" t="s">
-        <v>1074</v>
+        <v>1064</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -6082,10 +6078,10 @@
         <v>90</v>
       </c>
       <c r="E64" t="s">
-        <v>405</v>
+        <v>1073</v>
       </c>
       <c r="F64" t="s">
-        <v>406</v>
+        <v>1074</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -6111,10 +6107,10 @@
         <v>90</v>
       </c>
       <c r="E65" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="F65" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -6140,10 +6136,10 @@
         <v>90</v>
       </c>
       <c r="E66" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F66" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -6169,10 +6165,10 @@
         <v>90</v>
       </c>
       <c r="E67" t="s">
-        <v>1065</v>
+        <v>393</v>
       </c>
       <c r="F67" t="s">
-        <v>1066</v>
+        <v>394</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -6186,10 +6182,10 @@
     </row>
     <row r="68" spans="1:9" ht="13.5">
       <c r="A68" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="B68" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>1176</v>
@@ -6198,10 +6194,10 @@
         <v>90</v>
       </c>
       <c r="E68" t="s">
-        <v>680</v>
+        <v>1065</v>
       </c>
       <c r="F68" t="s">
-        <v>681</v>
+        <v>1066</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -6227,10 +6223,10 @@
         <v>90</v>
       </c>
       <c r="E69" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="F69" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -6256,10 +6252,10 @@
         <v>90</v>
       </c>
       <c r="E70" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F70" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -6285,10 +6281,10 @@
         <v>90</v>
       </c>
       <c r="E71" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F71" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -6314,10 +6310,10 @@
         <v>90</v>
       </c>
       <c r="E72" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="F72" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -6343,10 +6339,10 @@
         <v>90</v>
       </c>
       <c r="E73" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F73" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -6372,10 +6368,10 @@
         <v>90</v>
       </c>
       <c r="E74" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F74" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -6401,10 +6397,10 @@
         <v>90</v>
       </c>
       <c r="E75" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="F75" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -6430,10 +6426,10 @@
         <v>90</v>
       </c>
       <c r="E76" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="F76" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -6459,10 +6455,10 @@
         <v>90</v>
       </c>
       <c r="E77" t="s">
-        <v>387</v>
+        <v>696</v>
       </c>
       <c r="F77" t="s">
-        <v>1165</v>
+        <v>697</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -6479,7 +6475,7 @@
         <v>1173</v>
       </c>
       <c r="B78" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>1176</v>
@@ -6488,10 +6484,10 @@
         <v>90</v>
       </c>
       <c r="E78" t="s">
-        <v>682</v>
+        <v>387</v>
       </c>
       <c r="F78" t="s">
-        <v>698</v>
+        <v>1165</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -6517,10 +6513,10 @@
         <v>90</v>
       </c>
       <c r="E79" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F79" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -6546,10 +6542,10 @@
         <v>90</v>
       </c>
       <c r="E80" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="F80" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -6575,10 +6571,10 @@
         <v>90</v>
       </c>
       <c r="E81" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F81" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -6604,10 +6600,10 @@
         <v>90</v>
       </c>
       <c r="E82" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F82" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -6633,10 +6629,10 @@
         <v>90</v>
       </c>
       <c r="E83" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="F83" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="G83">
         <v>1</v>
@@ -6662,10 +6658,10 @@
         <v>90</v>
       </c>
       <c r="E84" t="s">
-        <v>387</v>
+        <v>694</v>
       </c>
       <c r="F84" t="s">
-        <v>1166</v>
+        <v>703</v>
       </c>
       <c r="G84">
         <v>1</v>
@@ -6679,22 +6675,22 @@
     </row>
     <row r="85" spans="1:9" ht="13.5">
       <c r="A85" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="B85" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>1176</v>
       </c>
       <c r="D85" t="s">
-        <v>239</v>
+        <v>90</v>
       </c>
       <c r="E85" t="s">
-        <v>464</v>
+        <v>387</v>
       </c>
       <c r="F85" t="s">
-        <v>465</v>
+        <v>1166</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -6720,10 +6716,10 @@
         <v>239</v>
       </c>
       <c r="E86" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="F86" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -6752,7 +6748,7 @@
         <v>450</v>
       </c>
       <c r="F87" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -6778,10 +6774,10 @@
         <v>239</v>
       </c>
       <c r="E88" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F88" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G88">
         <v>1</v>
@@ -6810,7 +6806,7 @@
         <v>452</v>
       </c>
       <c r="F89" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -6836,10 +6832,10 @@
         <v>239</v>
       </c>
       <c r="E90" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F90" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -6868,7 +6864,7 @@
         <v>454</v>
       </c>
       <c r="F91" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -6894,10 +6890,10 @@
         <v>239</v>
       </c>
       <c r="E92" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F92" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -6923,10 +6919,10 @@
         <v>239</v>
       </c>
       <c r="E93" t="s">
-        <v>1090</v>
+        <v>456</v>
       </c>
       <c r="F93" t="s">
-        <v>1091</v>
+        <v>472</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -6952,10 +6948,10 @@
         <v>239</v>
       </c>
       <c r="E94" t="s">
-        <v>1085</v>
+        <v>1090</v>
       </c>
       <c r="F94" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="G94">
         <v>1</v>
@@ -6981,10 +6977,10 @@
         <v>239</v>
       </c>
       <c r="E95" t="s">
-        <v>473</v>
+        <v>1085</v>
       </c>
       <c r="F95" t="s">
-        <v>474</v>
+        <v>1092</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -7010,10 +7006,10 @@
         <v>239</v>
       </c>
       <c r="E96" t="s">
-        <v>1088</v>
+        <v>473</v>
       </c>
       <c r="F96" t="s">
-        <v>1093</v>
+        <v>474</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -7039,10 +7035,10 @@
         <v>239</v>
       </c>
       <c r="E97" t="s">
-        <v>475</v>
+        <v>1088</v>
       </c>
       <c r="F97" t="s">
-        <v>476</v>
+        <v>1093</v>
       </c>
       <c r="G97">
         <v>1</v>
@@ -7068,10 +7064,10 @@
         <v>239</v>
       </c>
       <c r="E98" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F98" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G98">
         <v>1</v>
@@ -7088,19 +7084,19 @@
         <v>1171</v>
       </c>
       <c r="B99" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>1176</v>
       </c>
       <c r="D99" t="s">
-        <v>90</v>
+        <v>239</v>
       </c>
       <c r="E99" t="s">
-        <v>387</v>
+        <v>477</v>
       </c>
       <c r="F99" t="s">
-        <v>435</v>
+        <v>478</v>
       </c>
       <c r="G99">
         <v>1</v>
@@ -7126,10 +7122,10 @@
         <v>90</v>
       </c>
       <c r="E100" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="F100" t="s">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="G100">
         <v>1</v>
@@ -7155,10 +7151,10 @@
         <v>90</v>
       </c>
       <c r="E101" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F101" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G101">
         <v>1</v>
@@ -7184,10 +7180,10 @@
         <v>90</v>
       </c>
       <c r="E102" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F102" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="G102">
         <v>1</v>
@@ -7213,10 +7209,10 @@
         <v>90</v>
       </c>
       <c r="E103" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F103" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="G103">
         <v>1</v>
@@ -7242,10 +7238,10 @@
         <v>90</v>
       </c>
       <c r="E104" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F104" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="G104">
         <v>1</v>
@@ -7271,10 +7267,10 @@
         <v>90</v>
       </c>
       <c r="E105" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F105" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="G105">
         <v>1</v>
@@ -7300,10 +7296,10 @@
         <v>90</v>
       </c>
       <c r="E106" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F106" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="G106">
         <v>1</v>
@@ -7329,10 +7325,10 @@
         <v>90</v>
       </c>
       <c r="E107" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F107" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G107">
         <v>1</v>
@@ -7358,10 +7354,10 @@
         <v>90</v>
       </c>
       <c r="E108" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F108" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="G108">
         <v>1</v>
@@ -7387,10 +7383,10 @@
         <v>90</v>
       </c>
       <c r="E109" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="F109" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G109">
         <v>1</v>
@@ -7416,10 +7412,10 @@
         <v>90</v>
       </c>
       <c r="E110" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F110" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="G110">
         <v>1</v>
@@ -7445,10 +7441,10 @@
         <v>90</v>
       </c>
       <c r="E111" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F111" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G111">
         <v>1</v>
@@ -7474,10 +7470,10 @@
         <v>90</v>
       </c>
       <c r="E112" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F112" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="G112">
         <v>1</v>
@@ -7503,10 +7499,10 @@
         <v>90</v>
       </c>
       <c r="E113" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F113" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="G113">
         <v>1</v>
@@ -7523,7 +7519,7 @@
         <v>1171</v>
       </c>
       <c r="B114" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>1176</v>
@@ -7532,10 +7528,10 @@
         <v>90</v>
       </c>
       <c r="E114" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F114" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="G114">
         <v>1</v>
@@ -7561,10 +7557,10 @@
         <v>90</v>
       </c>
       <c r="E115" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F115" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="G115">
         <v>1</v>
@@ -7590,10 +7586,10 @@
         <v>90</v>
       </c>
       <c r="E116" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="F116" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="G116">
         <v>1</v>
@@ -7619,10 +7615,10 @@
         <v>90</v>
       </c>
       <c r="E117" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="F117" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="G117">
         <v>1</v>
@@ -7648,10 +7644,10 @@
         <v>90</v>
       </c>
       <c r="E118" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F118" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="G118">
         <v>1</v>
@@ -7677,10 +7673,10 @@
         <v>90</v>
       </c>
       <c r="E119" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F119" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="G119">
         <v>1</v>
@@ -7706,10 +7702,10 @@
         <v>90</v>
       </c>
       <c r="E120" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F120" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="G120">
         <v>1</v>
@@ -7735,10 +7731,10 @@
         <v>90</v>
       </c>
       <c r="E121" t="s">
-        <v>1075</v>
+        <v>446</v>
       </c>
       <c r="F121" t="s">
-        <v>1076</v>
+        <v>447</v>
       </c>
       <c r="G121">
         <v>1</v>
@@ -7764,10 +7760,10 @@
         <v>90</v>
       </c>
       <c r="E122" t="s">
-        <v>1083</v>
+        <v>1075</v>
       </c>
       <c r="F122" t="s">
-        <v>1084</v>
+        <v>1076</v>
       </c>
       <c r="G122">
         <v>1</v>
@@ -7793,10 +7789,10 @@
         <v>90</v>
       </c>
       <c r="E123" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
       <c r="F123" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="G123">
         <v>1</v>
@@ -7822,10 +7818,10 @@
         <v>90</v>
       </c>
       <c r="E124" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="F124" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="G124">
         <v>1</v>
@@ -7851,10 +7847,10 @@
         <v>90</v>
       </c>
       <c r="E125" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="F125" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="G125">
         <v>1</v>
@@ -7868,10 +7864,10 @@
     </row>
     <row r="126" spans="1:9" ht="13.5">
       <c r="A126" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="B126" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>1176</v>
@@ -7880,10 +7876,10 @@
         <v>90</v>
       </c>
       <c r="E126" t="s">
-        <v>845</v>
+        <v>1081</v>
       </c>
       <c r="F126" t="s">
-        <v>926</v>
+        <v>1082</v>
       </c>
       <c r="G126">
         <v>1</v>
@@ -7909,10 +7905,10 @@
         <v>90</v>
       </c>
       <c r="E127" t="s">
-        <v>246</v>
+        <v>845</v>
       </c>
       <c r="F127" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="G127">
         <v>1</v>
@@ -7938,10 +7934,10 @@
         <v>90</v>
       </c>
       <c r="E128" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F128" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G128">
         <v>1</v>
@@ -7967,10 +7963,10 @@
         <v>90</v>
       </c>
       <c r="E129" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F129" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="G129">
         <v>1</v>
@@ -7996,10 +7992,10 @@
         <v>90</v>
       </c>
       <c r="E130" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="F130" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G130">
         <v>1</v>
@@ -8025,10 +8021,10 @@
         <v>90</v>
       </c>
       <c r="E131" t="s">
-        <v>931</v>
+        <v>272</v>
       </c>
       <c r="F131" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="G131">
         <v>1</v>
@@ -8054,10 +8050,10 @@
         <v>90</v>
       </c>
       <c r="E132" t="s">
-        <v>242</v>
+        <v>931</v>
       </c>
       <c r="F132" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="G132">
         <v>1</v>
@@ -8083,10 +8079,10 @@
         <v>90</v>
       </c>
       <c r="E133" t="s">
-        <v>934</v>
+        <v>242</v>
       </c>
       <c r="F133" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="G133">
         <v>1</v>
@@ -8112,10 +8108,10 @@
         <v>90</v>
       </c>
       <c r="E134" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="F134" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="G134">
         <v>1</v>
@@ -8141,10 +8137,10 @@
         <v>90</v>
       </c>
       <c r="E135" t="s">
-        <v>244</v>
+        <v>936</v>
       </c>
       <c r="F135" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="G135">
         <v>1</v>
@@ -8170,10 +8166,10 @@
         <v>90</v>
       </c>
       <c r="E136" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="F136" t="s">
-        <v>259</v>
+        <v>938</v>
       </c>
       <c r="G136">
         <v>1</v>
@@ -8199,10 +8195,10 @@
         <v>90</v>
       </c>
       <c r="E137" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="F137" t="s">
-        <v>939</v>
+        <v>259</v>
       </c>
       <c r="G137">
         <v>1</v>
@@ -8228,10 +8224,10 @@
         <v>90</v>
       </c>
       <c r="E138" t="s">
-        <v>332</v>
+        <v>300</v>
       </c>
       <c r="F138" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="G138">
         <v>1</v>
@@ -8257,10 +8253,10 @@
         <v>90</v>
       </c>
       <c r="E139" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F139" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="G139">
         <v>1</v>
@@ -8286,10 +8282,10 @@
         <v>90</v>
       </c>
       <c r="E140" t="s">
-        <v>942</v>
+        <v>334</v>
       </c>
       <c r="F140" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="G140">
         <v>1</v>
@@ -8306,7 +8302,7 @@
         <v>1169</v>
       </c>
       <c r="B141" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>1176</v>
@@ -8315,10 +8311,10 @@
         <v>90</v>
       </c>
       <c r="E141" t="s">
-        <v>267</v>
+        <v>942</v>
       </c>
       <c r="F141" t="s">
-        <v>268</v>
+        <v>943</v>
       </c>
       <c r="G141">
         <v>1</v>
@@ -8344,10 +8340,10 @@
         <v>90</v>
       </c>
       <c r="E142" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="F142" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -8361,22 +8357,22 @@
     </row>
     <row r="143" spans="1:9" ht="13.5">
       <c r="A143" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="B143" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>1176</v>
       </c>
       <c r="D143" t="s">
-        <v>239</v>
+        <v>90</v>
       </c>
       <c r="E143" t="s">
-        <v>450</v>
+        <v>246</v>
       </c>
       <c r="F143" t="s">
-        <v>451</v>
+        <v>269</v>
       </c>
       <c r="G143">
         <v>1</v>
@@ -8402,10 +8398,10 @@
         <v>239</v>
       </c>
       <c r="E144" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F144" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G144">
         <v>1</v>
@@ -8431,10 +8427,10 @@
         <v>239</v>
       </c>
       <c r="E145" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F145" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="G145">
         <v>1</v>
@@ -8460,10 +8456,10 @@
         <v>239</v>
       </c>
       <c r="E146" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F146" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="G146">
         <v>1</v>
@@ -8489,10 +8485,10 @@
         <v>239</v>
       </c>
       <c r="E147" t="s">
-        <v>1085</v>
+        <v>456</v>
       </c>
       <c r="F147" t="s">
-        <v>1086</v>
+        <v>457</v>
       </c>
       <c r="G147">
         <v>1</v>
@@ -8518,10 +8514,10 @@
         <v>239</v>
       </c>
       <c r="E148" t="s">
-        <v>473</v>
+        <v>1085</v>
       </c>
       <c r="F148" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G148">
         <v>1</v>
@@ -8547,10 +8543,10 @@
         <v>239</v>
       </c>
       <c r="E149" t="s">
-        <v>1088</v>
+        <v>473</v>
       </c>
       <c r="F149" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="G149">
         <v>1</v>
@@ -8576,10 +8572,10 @@
         <v>239</v>
       </c>
       <c r="E150" t="s">
-        <v>458</v>
+        <v>1088</v>
       </c>
       <c r="F150" t="s">
-        <v>459</v>
+        <v>1089</v>
       </c>
       <c r="G150">
         <v>1</v>
@@ -8605,10 +8601,10 @@
         <v>239</v>
       </c>
       <c r="E151" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F151" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="G151">
         <v>1</v>
@@ -8634,10 +8630,10 @@
         <v>239</v>
       </c>
       <c r="E152" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F152" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G152">
         <v>1</v>
@@ -8651,22 +8647,22 @@
     </row>
     <row r="153" spans="1:9" ht="13.5">
       <c r="A153" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B153" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>1176</v>
       </c>
       <c r="D153" t="s">
-        <v>90</v>
+        <v>239</v>
       </c>
       <c r="E153" t="s">
-        <v>1115</v>
+        <v>462</v>
       </c>
       <c r="F153" t="s">
-        <v>1116</v>
+        <v>463</v>
       </c>
       <c r="G153">
         <v>1</v>
@@ -8692,10 +8688,10 @@
         <v>90</v>
       </c>
       <c r="E154" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="F154" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="G154">
         <v>1</v>
@@ -8721,10 +8717,10 @@
         <v>90</v>
       </c>
       <c r="E155" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="F155" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="G155">
         <v>1</v>
@@ -8750,10 +8746,10 @@
         <v>90</v>
       </c>
       <c r="E156" t="s">
-        <v>549</v>
+        <v>1119</v>
       </c>
       <c r="F156" t="s">
-        <v>550</v>
+        <v>1120</v>
       </c>
       <c r="G156">
         <v>1</v>
@@ -8779,10 +8775,10 @@
         <v>90</v>
       </c>
       <c r="E157" t="s">
-        <v>1121</v>
+        <v>549</v>
       </c>
       <c r="F157" t="s">
-        <v>1122</v>
+        <v>550</v>
       </c>
       <c r="G157">
         <v>1</v>
@@ -8808,10 +8804,10 @@
         <v>90</v>
       </c>
       <c r="E158" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="F158" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="G158">
         <v>1</v>
@@ -8837,10 +8833,10 @@
         <v>90</v>
       </c>
       <c r="E159" t="s">
-        <v>551</v>
+        <v>1123</v>
       </c>
       <c r="F159" t="s">
-        <v>552</v>
+        <v>1124</v>
       </c>
       <c r="G159">
         <v>1</v>
@@ -8866,10 +8862,10 @@
         <v>90</v>
       </c>
       <c r="E160" t="s">
-        <v>1125</v>
+        <v>551</v>
       </c>
       <c r="F160" t="s">
-        <v>1126</v>
+        <v>552</v>
       </c>
       <c r="G160">
         <v>1</v>
@@ -8895,10 +8891,10 @@
         <v>90</v>
       </c>
       <c r="E161" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="F161" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="G161">
         <v>1</v>
@@ -8924,10 +8920,10 @@
         <v>90</v>
       </c>
       <c r="E162" t="s">
-        <v>553</v>
+        <v>1127</v>
       </c>
       <c r="F162" t="s">
-        <v>554</v>
+        <v>1128</v>
       </c>
       <c r="G162">
         <v>1</v>
@@ -8953,10 +8949,10 @@
         <v>90</v>
       </c>
       <c r="E163" t="s">
-        <v>1129</v>
+        <v>553</v>
       </c>
       <c r="F163" t="s">
-        <v>1130</v>
+        <v>554</v>
       </c>
       <c r="G163">
         <v>1</v>
@@ -8982,10 +8978,10 @@
         <v>90</v>
       </c>
       <c r="E164" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="F164" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="G164">
         <v>1</v>
@@ -9011,10 +9007,10 @@
         <v>90</v>
       </c>
       <c r="E165" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="F165" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="G165">
         <v>1</v>
@@ -9040,10 +9036,10 @@
         <v>90</v>
       </c>
       <c r="E166" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="F166" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="G166">
         <v>1</v>
@@ -9069,10 +9065,10 @@
         <v>90</v>
       </c>
       <c r="E167" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="F167" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="G167">
         <v>1</v>
@@ -9098,10 +9094,10 @@
         <v>90</v>
       </c>
       <c r="E168" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="F168" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="G168">
         <v>1</v>
@@ -9127,10 +9123,10 @@
         <v>90</v>
       </c>
       <c r="E169" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="F169" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="G169">
         <v>1</v>
@@ -9156,10 +9152,10 @@
         <v>90</v>
       </c>
       <c r="E170" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="F170" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="G170">
         <v>1</v>
@@ -9176,7 +9172,7 @@
         <v>1172</v>
       </c>
       <c r="B171" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>1176</v>
@@ -9185,10 +9181,10 @@
         <v>90</v>
       </c>
       <c r="E171" t="s">
-        <v>555</v>
+        <v>1143</v>
       </c>
       <c r="F171" t="s">
-        <v>556</v>
+        <v>1144</v>
       </c>
       <c r="G171">
         <v>1</v>
@@ -9214,10 +9210,10 @@
         <v>90</v>
       </c>
       <c r="E172" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="F172" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="G172">
         <v>1</v>
@@ -9243,10 +9239,10 @@
         <v>90</v>
       </c>
       <c r="E173" t="s">
-        <v>1119</v>
+        <v>557</v>
       </c>
       <c r="F173" t="s">
-        <v>1145</v>
+        <v>558</v>
       </c>
       <c r="G173">
         <v>1</v>
@@ -9272,10 +9268,10 @@
         <v>90</v>
       </c>
       <c r="E174" t="s">
-        <v>549</v>
+        <v>1119</v>
       </c>
       <c r="F174" t="s">
-        <v>559</v>
+        <v>1145</v>
       </c>
       <c r="G174">
         <v>1</v>
@@ -9301,10 +9297,10 @@
         <v>90</v>
       </c>
       <c r="E175" t="s">
-        <v>1123</v>
+        <v>549</v>
       </c>
       <c r="F175" t="s">
-        <v>1146</v>
+        <v>559</v>
       </c>
       <c r="G175">
         <v>1</v>
@@ -9330,10 +9326,10 @@
         <v>90</v>
       </c>
       <c r="E176" t="s">
-        <v>551</v>
+        <v>1123</v>
       </c>
       <c r="F176" t="s">
-        <v>560</v>
+        <v>1146</v>
       </c>
       <c r="G176">
         <v>1</v>
@@ -9359,10 +9355,10 @@
         <v>90</v>
       </c>
       <c r="E177" t="s">
-        <v>1125</v>
+        <v>551</v>
       </c>
       <c r="F177" t="s">
-        <v>1147</v>
+        <v>560</v>
       </c>
       <c r="G177">
         <v>1</v>
@@ -9388,10 +9384,10 @@
         <v>90</v>
       </c>
       <c r="E178" t="s">
-        <v>553</v>
+        <v>1125</v>
       </c>
       <c r="F178" t="s">
-        <v>561</v>
+        <v>1147</v>
       </c>
       <c r="G178">
         <v>1</v>
@@ -9417,10 +9413,10 @@
         <v>90</v>
       </c>
       <c r="E179" t="s">
-        <v>1129</v>
+        <v>553</v>
       </c>
       <c r="F179" t="s">
-        <v>1148</v>
+        <v>561</v>
       </c>
       <c r="G179">
         <v>1</v>
@@ -9446,10 +9442,10 @@
         <v>90</v>
       </c>
       <c r="E180" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="F180" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="G180">
         <v>1</v>
@@ -9475,10 +9471,10 @@
         <v>90</v>
       </c>
       <c r="E181" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="F181" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="G181">
         <v>1</v>
@@ -9504,10 +9500,10 @@
         <v>90</v>
       </c>
       <c r="E182" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="F182" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="G182">
         <v>1</v>
@@ -9533,10 +9529,10 @@
         <v>90</v>
       </c>
       <c r="E183" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="F183" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G183">
         <v>1</v>
@@ -9562,10 +9558,10 @@
         <v>90</v>
       </c>
       <c r="E184" t="s">
-        <v>1153</v>
+        <v>1139</v>
       </c>
       <c r="F184" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="G184">
         <v>1</v>
@@ -9579,10 +9575,10 @@
     </row>
     <row r="185" spans="1:9" ht="13.5">
       <c r="A185" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="B185" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>1176</v>
@@ -9591,10 +9587,10 @@
         <v>90</v>
       </c>
       <c r="E185" t="s">
-        <v>363</v>
+        <v>1153</v>
       </c>
       <c r="F185" t="s">
-        <v>364</v>
+        <v>1154</v>
       </c>
       <c r="G185">
         <v>1</v>
@@ -9620,10 +9616,10 @@
         <v>90</v>
       </c>
       <c r="E186" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F186" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G186">
         <v>1</v>
@@ -9649,10 +9645,10 @@
         <v>90</v>
       </c>
       <c r="E187" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F187" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G187">
         <v>1</v>
@@ -9678,10 +9674,10 @@
         <v>90</v>
       </c>
       <c r="E188" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F188" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G188">
         <v>1</v>
@@ -9707,10 +9703,10 @@
         <v>90</v>
       </c>
       <c r="E189" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F189" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G189">
         <v>1</v>
@@ -9727,7 +9723,7 @@
         <v>1169</v>
       </c>
       <c r="B190" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>1176</v>
@@ -9736,10 +9732,10 @@
         <v>90</v>
       </c>
       <c r="E190" t="s">
-        <v>242</v>
+        <v>371</v>
       </c>
       <c r="F190" t="s">
-        <v>260</v>
+        <v>372</v>
       </c>
       <c r="G190">
         <v>1</v>
@@ -9765,10 +9761,10 @@
         <v>90</v>
       </c>
       <c r="E191" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="F191" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G191">
         <v>1</v>
@@ -9794,10 +9790,10 @@
         <v>90</v>
       </c>
       <c r="E192" t="s">
-        <v>944</v>
+        <v>261</v>
       </c>
       <c r="F192" t="s">
-        <v>945</v>
+        <v>262</v>
       </c>
       <c r="G192">
         <v>1</v>
@@ -9823,10 +9819,10 @@
         <v>90</v>
       </c>
       <c r="E193" t="s">
-        <v>263</v>
+        <v>944</v>
       </c>
       <c r="F193" t="s">
-        <v>264</v>
+        <v>945</v>
       </c>
       <c r="G193">
         <v>1</v>
@@ -9852,10 +9848,10 @@
         <v>90</v>
       </c>
       <c r="E194" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F194" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G194">
         <v>1</v>
@@ -9881,10 +9877,10 @@
         <v>90</v>
       </c>
       <c r="E195" t="s">
-        <v>340</v>
+        <v>265</v>
       </c>
       <c r="F195" t="s">
-        <v>946</v>
+        <v>266</v>
       </c>
       <c r="G195">
         <v>1</v>
@@ -9901,19 +9897,19 @@
         <v>1169</v>
       </c>
       <c r="B196" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>1176</v>
       </c>
       <c r="D196" t="s">
-        <v>239</v>
+        <v>90</v>
       </c>
       <c r="E196" t="s">
-        <v>252</v>
+        <v>340</v>
       </c>
       <c r="F196" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="G196">
         <v>1</v>
@@ -9939,10 +9935,10 @@
         <v>239</v>
       </c>
       <c r="E197" t="s">
-        <v>323</v>
+        <v>252</v>
       </c>
       <c r="F197" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="G197">
         <v>1</v>
@@ -9968,10 +9964,10 @@
         <v>239</v>
       </c>
       <c r="E198" t="s">
-        <v>246</v>
+        <v>323</v>
       </c>
       <c r="F198" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="G198">
         <v>1</v>
@@ -9997,10 +9993,10 @@
         <v>239</v>
       </c>
       <c r="E199" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F199" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="G199">
         <v>1</v>
@@ -10026,10 +10022,10 @@
         <v>239</v>
       </c>
       <c r="E200" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F200" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G200">
         <v>1</v>
@@ -10055,10 +10051,10 @@
         <v>239</v>
       </c>
       <c r="E201" t="s">
-        <v>890</v>
+        <v>250</v>
       </c>
       <c r="F201" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G201">
         <v>1</v>
@@ -10084,10 +10080,10 @@
         <v>239</v>
       </c>
       <c r="E202" t="s">
-        <v>315</v>
+        <v>890</v>
       </c>
       <c r="F202" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="G202">
         <v>1</v>
@@ -10113,10 +10109,10 @@
         <v>239</v>
       </c>
       <c r="E203" t="s">
-        <v>893</v>
+        <v>315</v>
       </c>
       <c r="F203" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="G203">
         <v>1</v>
@@ -10142,10 +10138,10 @@
         <v>239</v>
       </c>
       <c r="E204" t="s">
-        <v>317</v>
+        <v>893</v>
       </c>
       <c r="F204" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="G204">
         <v>1</v>
@@ -10171,10 +10167,10 @@
         <v>239</v>
       </c>
       <c r="E205" t="s">
-        <v>896</v>
+        <v>317</v>
       </c>
       <c r="F205" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="G205">
         <v>1</v>
@@ -10200,10 +10196,10 @@
         <v>239</v>
       </c>
       <c r="E206" t="s">
-        <v>319</v>
+        <v>896</v>
       </c>
       <c r="F206" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="G206">
         <v>1</v>
@@ -10229,10 +10225,10 @@
         <v>239</v>
       </c>
       <c r="E207" t="s">
-        <v>899</v>
+        <v>319</v>
       </c>
       <c r="F207" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="G207">
         <v>1</v>
@@ -10258,10 +10254,10 @@
         <v>239</v>
       </c>
       <c r="E208" t="s">
-        <v>321</v>
+        <v>899</v>
       </c>
       <c r="F208" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="G208">
         <v>1</v>
@@ -10287,10 +10283,10 @@
         <v>239</v>
       </c>
       <c r="E209" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="F209" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="G209">
         <v>1</v>
@@ -10316,10 +10312,10 @@
         <v>239</v>
       </c>
       <c r="E210" t="s">
-        <v>916</v>
+        <v>300</v>
       </c>
       <c r="F210" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="G210">
         <v>1</v>
@@ -10345,10 +10341,10 @@
         <v>239</v>
       </c>
       <c r="E211" t="s">
-        <v>348</v>
+        <v>916</v>
       </c>
       <c r="F211" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="G211">
         <v>1</v>
@@ -10374,10 +10370,10 @@
         <v>239</v>
       </c>
       <c r="E212" t="s">
-        <v>919</v>
+        <v>348</v>
       </c>
       <c r="F212" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G212">
         <v>1</v>
@@ -10403,10 +10399,10 @@
         <v>239</v>
       </c>
       <c r="E213" t="s">
-        <v>350</v>
+        <v>919</v>
       </c>
       <c r="F213" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="G213">
         <v>1</v>
@@ -10420,22 +10416,22 @@
     </row>
     <row r="214" spans="1:9" ht="13.5">
       <c r="A214" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="B214" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>1176</v>
       </c>
       <c r="D214" t="s">
-        <v>90</v>
+        <v>239</v>
       </c>
       <c r="E214" t="s">
-        <v>724</v>
+        <v>350</v>
       </c>
       <c r="F214" t="s">
-        <v>725</v>
+        <v>964</v>
       </c>
       <c r="G214">
         <v>1</v>
@@ -10461,10 +10457,10 @@
         <v>90</v>
       </c>
       <c r="E215" t="s">
-        <v>706</v>
+        <v>724</v>
       </c>
       <c r="F215" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="G215">
         <v>1</v>
@@ -10490,10 +10486,10 @@
         <v>90</v>
       </c>
       <c r="E216" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="F216" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G216">
         <v>1</v>
@@ -10519,10 +10515,10 @@
         <v>90</v>
       </c>
       <c r="E217" t="s">
-        <v>728</v>
+        <v>708</v>
       </c>
       <c r="F217" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G217">
         <v>1</v>
@@ -10548,10 +10544,10 @@
         <v>90</v>
       </c>
       <c r="E218" t="s">
-        <v>710</v>
+        <v>728</v>
       </c>
       <c r="F218" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G218">
         <v>1</v>
@@ -10577,10 +10573,10 @@
         <v>90</v>
       </c>
       <c r="E219" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="F219" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G219">
         <v>1</v>
@@ -10606,10 +10602,10 @@
         <v>90</v>
       </c>
       <c r="E220" t="s">
-        <v>732</v>
+        <v>712</v>
       </c>
       <c r="F220" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G220">
         <v>1</v>
@@ -10635,10 +10631,10 @@
         <v>90</v>
       </c>
       <c r="E221" t="s">
-        <v>714</v>
+        <v>732</v>
       </c>
       <c r="F221" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="G221">
         <v>1</v>
@@ -10664,10 +10660,10 @@
         <v>90</v>
       </c>
       <c r="E222" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="F222" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="G222">
         <v>1</v>
@@ -10693,10 +10689,10 @@
         <v>90</v>
       </c>
       <c r="E223" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="F223" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="G223">
         <v>1</v>
@@ -10722,10 +10718,10 @@
         <v>90</v>
       </c>
       <c r="E224" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="F224" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="G224">
         <v>1</v>
@@ -10751,10 +10747,10 @@
         <v>90</v>
       </c>
       <c r="E225" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="F225" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G225">
         <v>1</v>
@@ -10771,19 +10767,19 @@
         <v>1167</v>
       </c>
       <c r="B226" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="D226" t="s">
         <v>90</v>
       </c>
       <c r="E226" t="s">
-        <v>91</v>
+        <v>722</v>
       </c>
       <c r="F226" t="s">
-        <v>92</v>
+        <v>738</v>
       </c>
       <c r="G226">
         <v>1</v>
@@ -10803,16 +10799,16 @@
         <v>39</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="D227" t="s">
         <v>90</v>
       </c>
       <c r="E227" t="s">
-        <v>704</v>
+        <v>91</v>
       </c>
       <c r="F227" t="s">
-        <v>705</v>
+        <v>92</v>
       </c>
       <c r="G227">
         <v>1</v>
@@ -10838,10 +10834,10 @@
         <v>90</v>
       </c>
       <c r="E228" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="F228" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="G228">
         <v>1</v>
@@ -10867,10 +10863,10 @@
         <v>90</v>
       </c>
       <c r="E229" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="F229" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G229">
         <v>1</v>
@@ -10896,10 +10892,10 @@
         <v>90</v>
       </c>
       <c r="E230" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="F230" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="G230">
         <v>1</v>
@@ -10925,10 +10921,10 @@
         <v>90</v>
       </c>
       <c r="E231" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="F231" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="G231">
         <v>1</v>
@@ -10954,10 +10950,10 @@
         <v>90</v>
       </c>
       <c r="E232" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="F232" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="G232">
         <v>1</v>
@@ -10983,10 +10979,10 @@
         <v>90</v>
       </c>
       <c r="E233" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="F233" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="G233">
         <v>1</v>
@@ -11012,10 +11008,10 @@
         <v>90</v>
       </c>
       <c r="E234" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="F234" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="G234">
         <v>1</v>
@@ -11041,10 +11037,10 @@
         <v>90</v>
       </c>
       <c r="E235" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="F235" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="G235">
         <v>1</v>
@@ -11070,10 +11066,10 @@
         <v>90</v>
       </c>
       <c r="E236" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="F236" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="G236">
         <v>1</v>
@@ -11087,22 +11083,22 @@
     </row>
     <row r="237" spans="1:9" ht="13.5">
       <c r="A237" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B237" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>1176</v>
       </c>
       <c r="D237" t="s">
-        <v>239</v>
+        <v>90</v>
       </c>
       <c r="E237" t="s">
-        <v>252</v>
+        <v>722</v>
       </c>
       <c r="F237" t="s">
-        <v>885</v>
+        <v>723</v>
       </c>
       <c r="G237">
         <v>1</v>
@@ -11128,10 +11124,10 @@
         <v>239</v>
       </c>
       <c r="E238" t="s">
-        <v>323</v>
+        <v>252</v>
       </c>
       <c r="F238" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="G238">
         <v>1</v>
@@ -11157,10 +11153,10 @@
         <v>239</v>
       </c>
       <c r="E239" t="s">
-        <v>246</v>
+        <v>323</v>
       </c>
       <c r="F239" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="G239">
         <v>1</v>
@@ -11186,10 +11182,10 @@
         <v>239</v>
       </c>
       <c r="E240" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F240" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="G240">
         <v>1</v>
@@ -11215,10 +11211,10 @@
         <v>239</v>
       </c>
       <c r="E241" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F241" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G241">
         <v>1</v>
@@ -11244,10 +11240,10 @@
         <v>239</v>
       </c>
       <c r="E242" t="s">
-        <v>890</v>
+        <v>250</v>
       </c>
       <c r="F242" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G242">
         <v>1</v>
@@ -11273,10 +11269,10 @@
         <v>239</v>
       </c>
       <c r="E243" t="s">
-        <v>315</v>
+        <v>890</v>
       </c>
       <c r="F243" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G243">
         <v>1</v>
@@ -11302,10 +11298,10 @@
         <v>239</v>
       </c>
       <c r="E244" t="s">
-        <v>893</v>
+        <v>315</v>
       </c>
       <c r="F244" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="G244">
         <v>1</v>
@@ -11331,10 +11327,10 @@
         <v>239</v>
       </c>
       <c r="E245" t="s">
-        <v>317</v>
+        <v>893</v>
       </c>
       <c r="F245" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="G245">
         <v>1</v>
@@ -11360,10 +11356,10 @@
         <v>239</v>
       </c>
       <c r="E246" t="s">
-        <v>896</v>
+        <v>317</v>
       </c>
       <c r="F246" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="G246">
         <v>1</v>
@@ -11389,10 +11385,10 @@
         <v>239</v>
       </c>
       <c r="E247" t="s">
-        <v>319</v>
+        <v>896</v>
       </c>
       <c r="F247" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="G247">
         <v>1</v>
@@ -11418,10 +11414,10 @@
         <v>239</v>
       </c>
       <c r="E248" t="s">
-        <v>899</v>
+        <v>319</v>
       </c>
       <c r="F248" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="G248">
         <v>1</v>
@@ -11447,10 +11443,10 @@
         <v>239</v>
       </c>
       <c r="E249" t="s">
-        <v>321</v>
+        <v>899</v>
       </c>
       <c r="F249" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="G249">
         <v>1</v>
@@ -11476,10 +11472,10 @@
         <v>239</v>
       </c>
       <c r="E250" t="s">
-        <v>242</v>
+        <v>321</v>
       </c>
       <c r="F250" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="G250">
         <v>1</v>
@@ -11505,10 +11501,10 @@
         <v>239</v>
       </c>
       <c r="E251" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="F251" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G251">
         <v>1</v>
@@ -11534,10 +11530,10 @@
         <v>239</v>
       </c>
       <c r="E252" t="s">
-        <v>296</v>
+        <v>261</v>
       </c>
       <c r="F252" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="G252">
         <v>1</v>
@@ -11563,10 +11559,10 @@
         <v>239</v>
       </c>
       <c r="E253" t="s">
-        <v>244</v>
+        <v>296</v>
       </c>
       <c r="F253" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="G253">
         <v>1</v>
@@ -11592,10 +11588,10 @@
         <v>239</v>
       </c>
       <c r="E254" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="F254" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="G254">
         <v>1</v>
@@ -11621,10 +11617,10 @@
         <v>239</v>
       </c>
       <c r="E255" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="F255" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="G255">
         <v>1</v>
@@ -11650,10 +11646,10 @@
         <v>239</v>
       </c>
       <c r="E256" t="s">
-        <v>332</v>
+        <v>300</v>
       </c>
       <c r="F256" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="G256">
         <v>1</v>
@@ -11679,10 +11675,10 @@
         <v>239</v>
       </c>
       <c r="E257" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F257" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="G257">
         <v>1</v>
@@ -11708,10 +11704,10 @@
         <v>239</v>
       </c>
       <c r="E258" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F258" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="G258">
         <v>1</v>
@@ -11737,10 +11733,10 @@
         <v>239</v>
       </c>
       <c r="E259" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F259" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="G259">
         <v>1</v>
@@ -11766,10 +11762,10 @@
         <v>239</v>
       </c>
       <c r="E260" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F260" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="G260">
         <v>1</v>
@@ -11795,10 +11791,10 @@
         <v>239</v>
       </c>
       <c r="E261" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F261" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="G261">
         <v>1</v>
@@ -11824,10 +11820,10 @@
         <v>239</v>
       </c>
       <c r="E262" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F262" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="G262">
         <v>1</v>
@@ -11853,10 +11849,10 @@
         <v>239</v>
       </c>
       <c r="E263" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F263" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="G263">
         <v>1</v>
@@ -11882,10 +11878,10 @@
         <v>239</v>
       </c>
       <c r="E264" t="s">
-        <v>916</v>
+        <v>346</v>
       </c>
       <c r="F264" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="G264">
         <v>1</v>
@@ -11911,10 +11907,10 @@
         <v>239</v>
       </c>
       <c r="E265" t="s">
-        <v>348</v>
+        <v>916</v>
       </c>
       <c r="F265" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G265">
         <v>1</v>
@@ -11940,10 +11936,10 @@
         <v>239</v>
       </c>
       <c r="E266" t="s">
-        <v>919</v>
+        <v>348</v>
       </c>
       <c r="F266" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="G266">
         <v>1</v>
@@ -11969,10 +11965,10 @@
         <v>239</v>
       </c>
       <c r="E267" t="s">
-        <v>350</v>
+        <v>919</v>
       </c>
       <c r="F267" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="G267">
         <v>1</v>
@@ -11998,10 +11994,10 @@
         <v>239</v>
       </c>
       <c r="E268" t="s">
-        <v>837</v>
+        <v>350</v>
       </c>
       <c r="F268" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="G268">
         <v>1</v>
@@ -12027,10 +12023,10 @@
         <v>239</v>
       </c>
       <c r="E269" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F269" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="G269">
         <v>1</v>
@@ -12056,10 +12052,10 @@
         <v>239</v>
       </c>
       <c r="E270" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="F270" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="G270">
         <v>1</v>
@@ -12085,10 +12081,10 @@
         <v>239</v>
       </c>
       <c r="E271" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="F271" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="G271">
         <v>1</v>
@@ -12105,19 +12101,19 @@
         <v>1169</v>
       </c>
       <c r="B272" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>1176</v>
       </c>
       <c r="D272" t="s">
-        <v>90</v>
+        <v>239</v>
       </c>
       <c r="E272" t="s">
-        <v>248</v>
+        <v>843</v>
       </c>
       <c r="F272" t="s">
-        <v>965</v>
+        <v>925</v>
       </c>
       <c r="G272">
         <v>1</v>
@@ -12143,10 +12139,10 @@
         <v>90</v>
       </c>
       <c r="E273" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F273" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G273">
         <v>1</v>
@@ -12172,10 +12168,10 @@
         <v>90</v>
       </c>
       <c r="E274" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="F274" t="s">
-        <v>271</v>
+        <v>966</v>
       </c>
       <c r="G274">
         <v>1</v>
@@ -12201,10 +12197,10 @@
         <v>90</v>
       </c>
       <c r="E275" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F275" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G275">
         <v>1</v>
@@ -12230,10 +12226,10 @@
         <v>90</v>
       </c>
       <c r="E276" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F276" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G276">
         <v>1</v>
@@ -12259,10 +12255,10 @@
         <v>90</v>
       </c>
       <c r="E277" t="s">
-        <v>967</v>
+        <v>274</v>
       </c>
       <c r="F277" t="s">
-        <v>968</v>
+        <v>275</v>
       </c>
       <c r="G277">
         <v>1</v>
@@ -12288,10 +12284,10 @@
         <v>90</v>
       </c>
       <c r="E278" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="F278" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="G278">
         <v>1</v>
@@ -12317,10 +12313,10 @@
         <v>90</v>
       </c>
       <c r="E279" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="F279" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="G279">
         <v>1</v>
@@ -12346,10 +12342,10 @@
         <v>90</v>
       </c>
       <c r="E280" t="s">
-        <v>261</v>
+        <v>971</v>
       </c>
       <c r="F280" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="G280">
         <v>1</v>
@@ -12375,10 +12371,10 @@
         <v>90</v>
       </c>
       <c r="E281" t="s">
-        <v>296</v>
+        <v>261</v>
       </c>
       <c r="F281" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="G281">
         <v>1</v>
@@ -12404,10 +12400,10 @@
         <v>90</v>
       </c>
       <c r="E282" t="s">
-        <v>244</v>
+        <v>296</v>
       </c>
       <c r="F282" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="G282">
         <v>1</v>
@@ -12433,10 +12429,10 @@
         <v>90</v>
       </c>
       <c r="E283" t="s">
-        <v>976</v>
+        <v>244</v>
       </c>
       <c r="F283" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="G283">
         <v>1</v>
@@ -12462,10 +12458,10 @@
         <v>90</v>
       </c>
       <c r="E284" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="F284" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="G284">
         <v>1</v>
@@ -12491,10 +12487,10 @@
         <v>90</v>
       </c>
       <c r="E285" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="F285" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="G285">
         <v>1</v>
@@ -12508,10 +12504,10 @@
     </row>
     <row r="286" spans="1:9" ht="13.5">
       <c r="A286" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="B286" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>1176</v>
@@ -12520,10 +12516,10 @@
         <v>90</v>
       </c>
       <c r="E286" t="s">
-        <v>757</v>
+        <v>980</v>
       </c>
       <c r="F286" t="s">
-        <v>758</v>
+        <v>981</v>
       </c>
       <c r="G286">
         <v>1</v>
@@ -12549,10 +12545,10 @@
         <v>90</v>
       </c>
       <c r="E287" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="F287" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="G287">
         <v>1</v>
@@ -12578,10 +12574,10 @@
         <v>90</v>
       </c>
       <c r="E288" t="s">
-        <v>739</v>
+        <v>759</v>
       </c>
       <c r="F288" t="s">
-        <v>740</v>
+        <v>760</v>
       </c>
       <c r="G288">
         <v>1</v>
@@ -12607,10 +12603,10 @@
         <v>90</v>
       </c>
       <c r="E289" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="F289" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="G289">
         <v>1</v>
@@ -12636,10 +12632,10 @@
         <v>90</v>
       </c>
       <c r="E290" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="F290" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="G290">
         <v>1</v>
@@ -12665,10 +12661,10 @@
         <v>90</v>
       </c>
       <c r="E291" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="F291" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G291">
         <v>1</v>
@@ -12694,10 +12690,10 @@
         <v>90</v>
       </c>
       <c r="E292" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="F292" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="G292">
         <v>1</v>
@@ -12723,10 +12719,10 @@
         <v>90</v>
       </c>
       <c r="E293" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="F293" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="G293">
         <v>1</v>
@@ -12752,10 +12748,10 @@
         <v>90</v>
       </c>
       <c r="E294" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="F294" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="G294">
         <v>1</v>
@@ -12781,10 +12777,10 @@
         <v>90</v>
       </c>
       <c r="E295" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="F295" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="G295">
         <v>1</v>
@@ -12810,10 +12806,10 @@
         <v>90</v>
       </c>
       <c r="E296" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="F296" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="G296">
         <v>1</v>
@@ -12827,10 +12823,10 @@
     </row>
     <row r="297" spans="1:9" ht="13.5">
       <c r="A297" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="B297" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>1176</v>
@@ -12839,10 +12835,10 @@
         <v>90</v>
       </c>
       <c r="E297" t="s">
-        <v>1029</v>
+        <v>755</v>
       </c>
       <c r="F297" t="s">
-        <v>1030</v>
+        <v>756</v>
       </c>
       <c r="G297">
         <v>1</v>
@@ -12868,10 +12864,10 @@
         <v>90</v>
       </c>
       <c r="E298" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="F298" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="G298">
         <v>1</v>
@@ -12897,10 +12893,10 @@
         <v>90</v>
       </c>
       <c r="E299" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="F299" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="G299">
         <v>1</v>
@@ -12926,10 +12922,10 @@
         <v>90</v>
       </c>
       <c r="E300" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="F300" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="G300">
         <v>1</v>
@@ -12955,10 +12951,10 @@
         <v>90</v>
       </c>
       <c r="E301" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="F301" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="G301">
         <v>1</v>
@@ -12984,10 +12980,10 @@
         <v>90</v>
       </c>
       <c r="E302" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="F302" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G302">
         <v>1</v>
@@ -13013,10 +13009,10 @@
         <v>90</v>
       </c>
       <c r="E303" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="F303" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="G303">
         <v>1</v>
@@ -13042,10 +13038,10 @@
         <v>90</v>
       </c>
       <c r="E304" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="F304" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="G304">
         <v>1</v>
@@ -13071,10 +13067,10 @@
         <v>90</v>
       </c>
       <c r="E305" t="s">
-        <v>373</v>
+        <v>1043</v>
       </c>
       <c r="F305" t="s">
-        <v>374</v>
+        <v>1044</v>
       </c>
       <c r="G305">
         <v>1</v>
@@ -13100,10 +13096,10 @@
         <v>90</v>
       </c>
       <c r="E306" t="s">
-        <v>1045</v>
+        <v>373</v>
       </c>
       <c r="F306" t="s">
-        <v>1046</v>
+        <v>374</v>
       </c>
       <c r="G306">
         <v>1</v>
@@ -13129,10 +13125,10 @@
         <v>90</v>
       </c>
       <c r="E307" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="F307" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="G307">
         <v>1</v>
@@ -13158,10 +13154,10 @@
         <v>90</v>
       </c>
       <c r="E308" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="F308" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="G308">
         <v>1</v>
@@ -13187,10 +13183,10 @@
         <v>90</v>
       </c>
       <c r="E309" t="s">
-        <v>375</v>
+        <v>1049</v>
       </c>
       <c r="F309" t="s">
-        <v>376</v>
+        <v>1050</v>
       </c>
       <c r="G309">
         <v>1</v>
@@ -13216,10 +13212,10 @@
         <v>90</v>
       </c>
       <c r="E310" t="s">
-        <v>1051</v>
+        <v>375</v>
       </c>
       <c r="F310" t="s">
-        <v>1052</v>
+        <v>376</v>
       </c>
       <c r="G310">
         <v>1</v>
@@ -13245,10 +13241,10 @@
         <v>90</v>
       </c>
       <c r="E311" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="F311" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="G311">
         <v>1</v>
@@ -13274,10 +13270,10 @@
         <v>90</v>
       </c>
       <c r="E312" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="F312" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="G312">
         <v>1</v>
@@ -13303,10 +13299,10 @@
         <v>90</v>
       </c>
       <c r="E313" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F313" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="G313">
         <v>1</v>
@@ -13332,10 +13328,10 @@
         <v>90</v>
       </c>
       <c r="E314" t="s">
-        <v>377</v>
+        <v>1057</v>
       </c>
       <c r="F314" t="s">
-        <v>378</v>
+        <v>1058</v>
       </c>
       <c r="G314">
         <v>1</v>
@@ -13349,10 +13345,10 @@
     </row>
     <row r="315" spans="1:9" ht="13.5">
       <c r="A315" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B315" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>1176</v>
@@ -13361,10 +13357,10 @@
         <v>90</v>
       </c>
       <c r="E315" t="s">
-        <v>982</v>
+        <v>377</v>
       </c>
       <c r="F315" t="s">
-        <v>983</v>
+        <v>378</v>
       </c>
       <c r="G315">
         <v>1</v>
@@ -13390,10 +13386,10 @@
         <v>90</v>
       </c>
       <c r="E316" t="s">
-        <v>845</v>
+        <v>982</v>
       </c>
       <c r="F316" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="G316">
         <v>1</v>
@@ -13419,10 +13415,10 @@
         <v>90</v>
       </c>
       <c r="E317" t="s">
-        <v>276</v>
+        <v>845</v>
       </c>
       <c r="F317" t="s">
-        <v>277</v>
+        <v>984</v>
       </c>
       <c r="G317">
         <v>1</v>
@@ -13448,10 +13444,10 @@
         <v>90</v>
       </c>
       <c r="E318" t="s">
-        <v>985</v>
+        <v>276</v>
       </c>
       <c r="F318" t="s">
-        <v>986</v>
+        <v>277</v>
       </c>
       <c r="G318">
         <v>1</v>
@@ -13477,10 +13473,10 @@
         <v>90</v>
       </c>
       <c r="E319" t="s">
-        <v>278</v>
+        <v>985</v>
       </c>
       <c r="F319" t="s">
-        <v>279</v>
+        <v>986</v>
       </c>
       <c r="G319">
         <v>1</v>
@@ -13506,10 +13502,10 @@
         <v>90</v>
       </c>
       <c r="E320" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F320" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G320">
         <v>1</v>
@@ -13535,10 +13531,10 @@
         <v>90</v>
       </c>
       <c r="E321" t="s">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="F321" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G321">
         <v>1</v>
@@ -13564,10 +13560,10 @@
         <v>90</v>
       </c>
       <c r="E322" t="s">
-        <v>283</v>
+        <v>246</v>
       </c>
       <c r="F322" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G322">
         <v>1</v>
@@ -13593,10 +13589,10 @@
         <v>90</v>
       </c>
       <c r="E323" t="s">
-        <v>248</v>
+        <v>283</v>
       </c>
       <c r="F323" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G323">
         <v>1</v>
@@ -13622,10 +13618,10 @@
         <v>90</v>
       </c>
       <c r="E324" t="s">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="F324" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G324">
         <v>1</v>
@@ -13651,10 +13647,10 @@
         <v>90</v>
       </c>
       <c r="E325" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F325" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G325">
         <v>1</v>
@@ -13680,10 +13676,10 @@
         <v>90</v>
       </c>
       <c r="E326" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F326" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G326">
         <v>1</v>
@@ -13709,10 +13705,10 @@
         <v>90</v>
       </c>
       <c r="E327" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F327" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G327">
         <v>1</v>
@@ -13738,10 +13734,10 @@
         <v>90</v>
       </c>
       <c r="E328" t="s">
-        <v>242</v>
+        <v>292</v>
       </c>
       <c r="F328" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G328">
         <v>1</v>
@@ -13767,10 +13763,10 @@
         <v>90</v>
       </c>
       <c r="E329" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="F329" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G329">
         <v>1</v>
@@ -13796,10 +13792,10 @@
         <v>90</v>
       </c>
       <c r="E330" t="s">
-        <v>296</v>
+        <v>261</v>
       </c>
       <c r="F330" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G330">
         <v>1</v>
@@ -13825,10 +13821,10 @@
         <v>90</v>
       </c>
       <c r="E331" t="s">
-        <v>244</v>
+        <v>296</v>
       </c>
       <c r="F331" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G331">
         <v>1</v>
@@ -13854,10 +13850,10 @@
         <v>90</v>
       </c>
       <c r="E332" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="F332" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G332">
         <v>1</v>
@@ -13883,10 +13879,10 @@
         <v>90</v>
       </c>
       <c r="E333" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="F333" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G333">
         <v>1</v>
@@ -13912,10 +13908,10 @@
         <v>90</v>
       </c>
       <c r="E334" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F334" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G334">
         <v>1</v>
@@ -13941,10 +13937,10 @@
         <v>90</v>
       </c>
       <c r="E335" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F335" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G335">
         <v>1</v>
@@ -13970,10 +13966,10 @@
         <v>90</v>
       </c>
       <c r="E336" t="s">
-        <v>919</v>
+        <v>304</v>
       </c>
       <c r="F336" t="s">
-        <v>987</v>
+        <v>305</v>
       </c>
       <c r="G336">
         <v>1</v>
@@ -13999,10 +13995,10 @@
         <v>90</v>
       </c>
       <c r="E337" t="s">
-        <v>306</v>
+        <v>919</v>
       </c>
       <c r="F337" t="s">
-        <v>307</v>
+        <v>987</v>
       </c>
       <c r="G337">
         <v>1</v>
@@ -14028,10 +14024,10 @@
         <v>90</v>
       </c>
       <c r="E338" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F338" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G338">
         <v>1</v>
@@ -14057,10 +14053,10 @@
         <v>90</v>
       </c>
       <c r="E339" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F339" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G339">
         <v>1</v>
@@ -14086,10 +14082,10 @@
         <v>90</v>
       </c>
       <c r="E340" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F340" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G340">
         <v>1</v>
@@ -14103,10 +14099,10 @@
     </row>
     <row r="341" spans="1:9" ht="13.5">
       <c r="A341" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B341" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>1176</v>
@@ -14115,10 +14111,10 @@
         <v>90</v>
       </c>
       <c r="E341" t="s">
-        <v>822</v>
+        <v>312</v>
       </c>
       <c r="F341" t="s">
-        <v>823</v>
+        <v>313</v>
       </c>
       <c r="G341">
         <v>1</v>
@@ -14144,10 +14140,10 @@
         <v>90</v>
       </c>
       <c r="E342" t="s">
-        <v>270</v>
+        <v>822</v>
       </c>
       <c r="F342" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="G342">
         <v>1</v>
@@ -14173,10 +14169,10 @@
         <v>90</v>
       </c>
       <c r="E343" t="s">
-        <v>825</v>
+        <v>270</v>
       </c>
       <c r="F343" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="G343">
         <v>1</v>
@@ -14202,10 +14198,10 @@
         <v>90</v>
       </c>
       <c r="E344" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="F344" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="G344">
         <v>1</v>
@@ -14231,10 +14227,10 @@
         <v>90</v>
       </c>
       <c r="E345" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="F345" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="G345">
         <v>1</v>
@@ -14260,10 +14256,10 @@
         <v>90</v>
       </c>
       <c r="E346" t="s">
-        <v>657</v>
+        <v>829</v>
       </c>
       <c r="F346" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G346">
         <v>1</v>
@@ -14289,10 +14285,10 @@
         <v>90</v>
       </c>
       <c r="E347" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F347" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="G347">
         <v>1</v>
@@ -14318,10 +14314,10 @@
         <v>90</v>
       </c>
       <c r="E348" t="s">
-        <v>833</v>
+        <v>659</v>
       </c>
       <c r="F348" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="G348">
         <v>1</v>
@@ -14347,10 +14343,10 @@
         <v>90</v>
       </c>
       <c r="E349" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="F349" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="G349">
         <v>1</v>
@@ -14376,10 +14372,10 @@
         <v>90</v>
       </c>
       <c r="E350" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="F350" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="G350">
         <v>1</v>
@@ -14405,10 +14401,10 @@
         <v>90</v>
       </c>
       <c r="E351" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F351" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="G351">
         <v>1</v>
@@ -14434,10 +14430,10 @@
         <v>90</v>
       </c>
       <c r="E352" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="F352" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="G352">
         <v>1</v>
@@ -14463,10 +14459,10 @@
         <v>90</v>
       </c>
       <c r="E353" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="F353" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="G353">
         <v>1</v>
@@ -14480,22 +14476,22 @@
     </row>
     <row r="354" spans="1:9" ht="13.5">
       <c r="A354" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="B354" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>1176</v>
       </c>
       <c r="D354" t="s">
-        <v>239</v>
+        <v>90</v>
       </c>
       <c r="E354" t="s">
-        <v>1155</v>
+        <v>843</v>
       </c>
       <c r="F354" t="s">
-        <v>1156</v>
+        <v>844</v>
       </c>
       <c r="G354">
         <v>1</v>
@@ -14521,10 +14517,10 @@
         <v>239</v>
       </c>
       <c r="E355" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="F355" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="G355">
         <v>1</v>
@@ -14541,7 +14537,7 @@
         <v>1172</v>
       </c>
       <c r="B356" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>1176</v>
@@ -14550,10 +14546,10 @@
         <v>239</v>
       </c>
       <c r="E356" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="F356" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="G356">
         <v>1</v>
@@ -14579,10 +14575,10 @@
         <v>239</v>
       </c>
       <c r="E357" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="F357" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="G357">
         <v>1</v>
@@ -14599,19 +14595,19 @@
         <v>1172</v>
       </c>
       <c r="B358" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>1176</v>
       </c>
       <c r="D358" t="s">
-        <v>90</v>
+        <v>239</v>
       </c>
       <c r="E358" t="s">
-        <v>562</v>
+        <v>1157</v>
       </c>
       <c r="F358" t="s">
-        <v>563</v>
+        <v>1160</v>
       </c>
       <c r="G358">
         <v>1</v>
@@ -14637,10 +14633,10 @@
         <v>90</v>
       </c>
       <c r="E359" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="F359" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="G359">
         <v>1</v>
@@ -14666,10 +14662,10 @@
         <v>90</v>
       </c>
       <c r="E360" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="F360" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G360">
         <v>1</v>
@@ -14695,10 +14691,10 @@
         <v>90</v>
       </c>
       <c r="E361" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F361" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="G361">
         <v>1</v>
@@ -14724,10 +14720,10 @@
         <v>90</v>
       </c>
       <c r="E362" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F362" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="G362">
         <v>1</v>
@@ -14753,10 +14749,10 @@
         <v>90</v>
       </c>
       <c r="E363" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F363" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="G363">
         <v>1</v>
@@ -14770,10 +14766,10 @@
     </row>
     <row r="364" spans="1:9" ht="13.5">
       <c r="A364" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B364" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>1176</v>
@@ -14782,10 +14778,10 @@
         <v>90</v>
       </c>
       <c r="E364" t="s">
-        <v>533</v>
+        <v>572</v>
       </c>
       <c r="F364" t="s">
-        <v>534</v>
+        <v>573</v>
       </c>
       <c r="G364">
         <v>1</v>
@@ -14811,10 +14807,10 @@
         <v>90</v>
       </c>
       <c r="E365" t="s">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="F365" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="G365">
         <v>1</v>
@@ -14840,10 +14836,10 @@
         <v>90</v>
       </c>
       <c r="E366" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F366" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G366">
         <v>1</v>
@@ -14869,10 +14865,10 @@
         <v>90</v>
       </c>
       <c r="E367" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F367" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G367">
         <v>1</v>
@@ -14898,10 +14894,10 @@
         <v>90</v>
       </c>
       <c r="E368" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F368" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G368">
         <v>1</v>
@@ -14927,10 +14923,10 @@
         <v>90</v>
       </c>
       <c r="E369" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F369" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="G369">
         <v>1</v>
@@ -14956,10 +14952,10 @@
         <v>90</v>
       </c>
       <c r="E370" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F370" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="G370">
         <v>1</v>
@@ -14985,10 +14981,10 @@
         <v>90</v>
       </c>
       <c r="E371" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F371" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G371">
         <v>1</v>
@@ -15014,10 +15010,10 @@
         <v>90</v>
       </c>
       <c r="E372" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F372" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="G372">
         <v>1</v>
@@ -15043,10 +15039,10 @@
         <v>90</v>
       </c>
       <c r="E373" t="s">
-        <v>479</v>
+        <v>529</v>
       </c>
       <c r="F373" t="s">
-        <v>480</v>
+        <v>530</v>
       </c>
       <c r="G373">
         <v>1</v>
@@ -15072,10 +15068,10 @@
         <v>90</v>
       </c>
       <c r="E374" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F374" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="G374">
         <v>1</v>
@@ -15101,10 +15097,10 @@
         <v>90</v>
       </c>
       <c r="E375" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F375" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="G375">
         <v>1</v>
@@ -15130,10 +15126,10 @@
         <v>90</v>
       </c>
       <c r="E376" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F376" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="G376">
         <v>1</v>
@@ -15159,10 +15155,10 @@
         <v>90</v>
       </c>
       <c r="E377" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F377" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G377">
         <v>1</v>
@@ -15188,10 +15184,10 @@
         <v>90</v>
       </c>
       <c r="E378" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F378" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G378">
         <v>1</v>
@@ -15217,10 +15213,10 @@
         <v>90</v>
       </c>
       <c r="E379" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F379" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="G379">
         <v>1</v>
@@ -15246,10 +15242,10 @@
         <v>90</v>
       </c>
       <c r="E380" t="s">
-        <v>535</v>
+        <v>491</v>
       </c>
       <c r="F380" t="s">
-        <v>536</v>
+        <v>492</v>
       </c>
       <c r="G380">
         <v>1</v>
@@ -15275,10 +15271,10 @@
         <v>90</v>
       </c>
       <c r="E381" t="s">
-        <v>1094</v>
+        <v>535</v>
       </c>
       <c r="F381" t="s">
-        <v>1095</v>
+        <v>536</v>
       </c>
       <c r="G381">
         <v>1</v>
@@ -15304,10 +15300,10 @@
         <v>90</v>
       </c>
       <c r="E382" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="F382" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="G382">
         <v>1</v>
@@ -15333,10 +15329,10 @@
         <v>90</v>
       </c>
       <c r="E383" t="s">
-        <v>537</v>
+        <v>1096</v>
       </c>
       <c r="F383" t="s">
-        <v>538</v>
+        <v>1097</v>
       </c>
       <c r="G383">
         <v>1</v>
@@ -15362,10 +15358,10 @@
         <v>90</v>
       </c>
       <c r="E384" t="s">
-        <v>1098</v>
+        <v>537</v>
       </c>
       <c r="F384" t="s">
-        <v>1099</v>
+        <v>538</v>
       </c>
       <c r="G384">
         <v>1</v>
@@ -15391,10 +15387,10 @@
         <v>90</v>
       </c>
       <c r="E385" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="F385" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="G385">
         <v>1</v>
@@ -15420,10 +15416,10 @@
         <v>90</v>
       </c>
       <c r="E386" t="s">
-        <v>539</v>
+        <v>1100</v>
       </c>
       <c r="F386" t="s">
-        <v>540</v>
+        <v>1101</v>
       </c>
       <c r="G386">
         <v>1</v>
@@ -15449,10 +15445,10 @@
         <v>90</v>
       </c>
       <c r="E387" t="s">
-        <v>1102</v>
+        <v>539</v>
       </c>
       <c r="F387" t="s">
-        <v>1103</v>
+        <v>540</v>
       </c>
       <c r="G387">
         <v>1</v>
@@ -15478,10 +15474,10 @@
         <v>90</v>
       </c>
       <c r="E388" t="s">
-        <v>493</v>
+        <v>1102</v>
       </c>
       <c r="F388" t="s">
-        <v>494</v>
+        <v>1103</v>
       </c>
       <c r="G388">
         <v>1</v>
@@ -15507,10 +15503,10 @@
         <v>90</v>
       </c>
       <c r="E389" t="s">
-        <v>541</v>
+        <v>493</v>
       </c>
       <c r="F389" t="s">
-        <v>542</v>
+        <v>494</v>
       </c>
       <c r="G389">
         <v>1</v>
@@ -15536,10 +15532,10 @@
         <v>90</v>
       </c>
       <c r="E390" t="s">
-        <v>1104</v>
+        <v>541</v>
       </c>
       <c r="F390" t="s">
-        <v>1105</v>
+        <v>542</v>
       </c>
       <c r="G390">
         <v>1</v>
@@ -15565,10 +15561,10 @@
         <v>90</v>
       </c>
       <c r="E391" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="F391" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="G391">
         <v>1</v>
@@ -15594,10 +15590,10 @@
         <v>90</v>
       </c>
       <c r="E392" t="s">
-        <v>495</v>
+        <v>1106</v>
       </c>
       <c r="F392" t="s">
-        <v>496</v>
+        <v>1107</v>
       </c>
       <c r="G392">
         <v>1</v>
@@ -15623,10 +15619,10 @@
         <v>90</v>
       </c>
       <c r="E393" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F393" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="G393">
         <v>1</v>
@@ -15652,10 +15648,10 @@
         <v>90</v>
       </c>
       <c r="E394" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="F394" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G394">
         <v>1</v>
@@ -15681,10 +15677,10 @@
         <v>90</v>
       </c>
       <c r="E395" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F395" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="G395">
         <v>1</v>
@@ -15710,10 +15706,10 @@
         <v>90</v>
       </c>
       <c r="E396" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F396" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G396">
         <v>1</v>
@@ -15739,10 +15735,10 @@
         <v>90</v>
       </c>
       <c r="E397" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F397" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="G397">
         <v>1</v>
@@ -15768,10 +15764,10 @@
         <v>90</v>
       </c>
       <c r="E398" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F398" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="G398">
         <v>1</v>
@@ -15797,10 +15793,10 @@
         <v>90</v>
       </c>
       <c r="E399" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F399" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="G399">
         <v>1</v>
@@ -15826,10 +15822,10 @@
         <v>90</v>
       </c>
       <c r="E400" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F400" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G400">
         <v>1</v>
@@ -15855,10 +15851,10 @@
         <v>90</v>
       </c>
       <c r="E401" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F401" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="G401">
         <v>1</v>
@@ -15884,10 +15880,10 @@
         <v>90</v>
       </c>
       <c r="E402" t="s">
-        <v>531</v>
+        <v>513</v>
       </c>
       <c r="F402" t="s">
-        <v>532</v>
+        <v>514</v>
       </c>
       <c r="G402">
         <v>1</v>
@@ -15901,10 +15897,10 @@
     </row>
     <row r="403" spans="1:9" ht="13.5">
       <c r="A403" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="B403" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>1176</v>
@@ -15913,10 +15909,10 @@
         <v>90</v>
       </c>
       <c r="E403" t="s">
-        <v>139</v>
+        <v>531</v>
       </c>
       <c r="F403" t="s">
-        <v>140</v>
+        <v>532</v>
       </c>
       <c r="G403">
         <v>1</v>
@@ -15942,10 +15938,10 @@
         <v>90</v>
       </c>
       <c r="E404" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F404" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G404">
         <v>1</v>
@@ -15971,10 +15967,10 @@
         <v>90</v>
       </c>
       <c r="E405" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F405" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G405">
         <v>1</v>
@@ -16000,10 +15996,10 @@
         <v>90</v>
       </c>
       <c r="E406" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F406" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G406">
         <v>1</v>
@@ -16029,10 +16025,10 @@
         <v>90</v>
       </c>
       <c r="E407" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F407" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G407">
         <v>1</v>
@@ -16058,10 +16054,10 @@
         <v>90</v>
       </c>
       <c r="E408" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F408" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G408">
         <v>1</v>
@@ -16087,10 +16083,10 @@
         <v>90</v>
       </c>
       <c r="E409" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F409" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G409">
         <v>1</v>
@@ -16104,10 +16100,10 @@
     </row>
     <row r="410" spans="1:9" ht="13.5">
       <c r="A410" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="B410" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>1176</v>
@@ -16116,10 +16112,10 @@
         <v>90</v>
       </c>
       <c r="E410" t="s">
-        <v>450</v>
+        <v>151</v>
       </c>
       <c r="F410" t="s">
-        <v>543</v>
+        <v>152</v>
       </c>
       <c r="G410">
         <v>1</v>
@@ -16145,10 +16141,10 @@
         <v>90</v>
       </c>
       <c r="E411" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="F411" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G411">
         <v>1</v>
@@ -16174,10 +16170,10 @@
         <v>90</v>
       </c>
       <c r="E412" t="s">
-        <v>1108</v>
+        <v>456</v>
       </c>
       <c r="F412" t="s">
-        <v>1109</v>
+        <v>544</v>
       </c>
       <c r="G412">
         <v>1</v>
@@ -16203,10 +16199,10 @@
         <v>90</v>
       </c>
       <c r="E413" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="F413" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="G413">
         <v>1</v>
@@ -16232,10 +16228,10 @@
         <v>90</v>
       </c>
       <c r="E414" t="s">
-        <v>545</v>
+        <v>1110</v>
       </c>
       <c r="F414" t="s">
-        <v>546</v>
+        <v>1111</v>
       </c>
       <c r="G414">
         <v>1</v>
@@ -16261,10 +16257,10 @@
         <v>90</v>
       </c>
       <c r="E415" t="s">
-        <v>477</v>
+        <v>545</v>
       </c>
       <c r="F415" t="s">
-        <v>1112</v>
+        <v>546</v>
       </c>
       <c r="G415">
         <v>1</v>
@@ -16281,7 +16277,7 @@
         <v>1171</v>
       </c>
       <c r="B416" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>1176</v>
@@ -16290,10 +16286,10 @@
         <v>90</v>
       </c>
       <c r="E416" t="s">
-        <v>547</v>
+        <v>477</v>
       </c>
       <c r="F416" t="s">
-        <v>548</v>
+        <v>1112</v>
       </c>
       <c r="G416">
         <v>1</v>
@@ -16319,10 +16315,10 @@
         <v>90</v>
       </c>
       <c r="E417" t="s">
-        <v>1113</v>
+        <v>547</v>
       </c>
       <c r="F417" t="s">
-        <v>1114</v>
+        <v>548</v>
       </c>
       <c r="G417">
         <v>1</v>
@@ -16336,10 +16332,10 @@
     </row>
     <row r="418" spans="1:9" ht="13.5">
       <c r="A418" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="B418" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>1176</v>
@@ -16348,10 +16344,10 @@
         <v>90</v>
       </c>
       <c r="E418" t="s">
-        <v>153</v>
+        <v>1113</v>
       </c>
       <c r="F418" t="s">
-        <v>154</v>
+        <v>1114</v>
       </c>
       <c r="G418">
         <v>1</v>
@@ -16377,10 +16373,10 @@
         <v>90</v>
       </c>
       <c r="E419" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F419" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G419">
         <v>1</v>
@@ -16406,10 +16402,10 @@
         <v>90</v>
       </c>
       <c r="E420" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F420" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G420">
         <v>1</v>
@@ -16435,10 +16431,10 @@
         <v>90</v>
       </c>
       <c r="E421" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F421" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G421">
         <v>1</v>
@@ -16464,10 +16460,10 @@
         <v>90</v>
       </c>
       <c r="E422" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F422" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G422">
         <v>1</v>
@@ -16493,10 +16489,10 @@
         <v>90</v>
       </c>
       <c r="E423" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F423" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G423">
         <v>1</v>
@@ -16522,10 +16518,10 @@
         <v>90</v>
       </c>
       <c r="E424" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F424" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G424">
         <v>1</v>
@@ -16551,10 +16547,10 @@
         <v>90</v>
       </c>
       <c r="E425" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F425" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G425">
         <v>1</v>
@@ -16580,10 +16576,10 @@
         <v>90</v>
       </c>
       <c r="E426" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F426" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="G426">
         <v>1</v>
@@ -16609,10 +16605,10 @@
         <v>90</v>
       </c>
       <c r="E427" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F427" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="G427">
         <v>1</v>
@@ -16638,10 +16634,10 @@
         <v>90</v>
       </c>
       <c r="E428" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="F428" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G428">
         <v>1</v>
@@ -16667,10 +16663,10 @@
         <v>90</v>
       </c>
       <c r="E429" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F429" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G429">
         <v>1</v>
@@ -16684,10 +16680,10 @@
     </row>
     <row r="430" spans="1:9" ht="13.5">
       <c r="A430" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B430" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C430" s="1" t="s">
         <v>1176</v>
@@ -16696,10 +16692,10 @@
         <v>90</v>
       </c>
       <c r="E430" t="s">
-        <v>250</v>
+        <v>171</v>
       </c>
       <c r="F430" t="s">
-        <v>314</v>
+        <v>172</v>
       </c>
       <c r="G430">
         <v>1</v>
@@ -16725,10 +16721,10 @@
         <v>90</v>
       </c>
       <c r="E431" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="F431" t="s">
-        <v>988</v>
+        <v>314</v>
       </c>
       <c r="G431">
         <v>1</v>
@@ -16745,7 +16741,7 @@
         <v>1169</v>
       </c>
       <c r="B432" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C432" s="1" t="s">
         <v>1176</v>
@@ -16754,10 +16750,10 @@
         <v>90</v>
       </c>
       <c r="E432" t="s">
-        <v>315</v>
+        <v>244</v>
       </c>
       <c r="F432" t="s">
-        <v>316</v>
+        <v>988</v>
       </c>
       <c r="G432">
         <v>1</v>
@@ -16783,10 +16779,10 @@
         <v>90</v>
       </c>
       <c r="E433" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F433" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G433">
         <v>1</v>
@@ -16812,10 +16808,10 @@
         <v>90</v>
       </c>
       <c r="E434" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F434" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G434">
         <v>1</v>
@@ -16841,10 +16837,10 @@
         <v>90</v>
       </c>
       <c r="E435" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F435" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G435">
         <v>1</v>
@@ -16861,19 +16857,19 @@
         <v>1169</v>
       </c>
       <c r="B436" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C436" s="1" t="s">
         <v>1176</v>
       </c>
       <c r="D436" t="s">
-        <v>239</v>
+        <v>90</v>
       </c>
       <c r="E436" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F436" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G436">
         <v>1</v>
@@ -16899,10 +16895,10 @@
         <v>239</v>
       </c>
       <c r="E437" t="s">
-        <v>248</v>
+        <v>323</v>
       </c>
       <c r="F437" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G437">
         <v>1</v>
@@ -16928,10 +16924,10 @@
         <v>239</v>
       </c>
       <c r="E438" t="s">
-        <v>315</v>
+        <v>248</v>
       </c>
       <c r="F438" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G438">
         <v>1</v>
@@ -16957,10 +16953,10 @@
         <v>239</v>
       </c>
       <c r="E439" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F439" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G439">
         <v>1</v>
@@ -16986,10 +16982,10 @@
         <v>239</v>
       </c>
       <c r="E440" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F440" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G440">
         <v>1</v>
@@ -17015,10 +17011,10 @@
         <v>239</v>
       </c>
       <c r="E441" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F441" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G441">
         <v>1</v>
@@ -17044,10 +17040,10 @@
         <v>239</v>
       </c>
       <c r="E442" t="s">
-        <v>242</v>
+        <v>321</v>
       </c>
       <c r="F442" t="s">
-        <v>989</v>
+        <v>329</v>
       </c>
       <c r="G442">
         <v>1</v>
@@ -17073,10 +17069,10 @@
         <v>239</v>
       </c>
       <c r="E443" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="F443" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="G443">
         <v>1</v>
@@ -17102,10 +17098,10 @@
         <v>239</v>
       </c>
       <c r="E444" t="s">
-        <v>296</v>
+        <v>261</v>
       </c>
       <c r="F444" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="G444">
         <v>1</v>
@@ -17131,10 +17127,10 @@
         <v>239</v>
       </c>
       <c r="E445" t="s">
-        <v>244</v>
+        <v>296</v>
       </c>
       <c r="F445" t="s">
-        <v>330</v>
+        <v>991</v>
       </c>
       <c r="G445">
         <v>1</v>
@@ -17160,10 +17156,10 @@
         <v>239</v>
       </c>
       <c r="E446" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="F446" t="s">
-        <v>992</v>
+        <v>330</v>
       </c>
       <c r="G446">
         <v>1</v>
@@ -17189,10 +17185,10 @@
         <v>239</v>
       </c>
       <c r="E447" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="F447" t="s">
-        <v>331</v>
+        <v>992</v>
       </c>
       <c r="G447">
         <v>1</v>
@@ -17218,10 +17214,10 @@
         <v>239</v>
       </c>
       <c r="E448" t="s">
-        <v>332</v>
+        <v>300</v>
       </c>
       <c r="F448" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G448">
         <v>1</v>
@@ -17247,10 +17243,10 @@
         <v>239</v>
       </c>
       <c r="E449" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F449" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G449">
         <v>1</v>
@@ -17276,10 +17272,10 @@
         <v>239</v>
       </c>
       <c r="E450" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F450" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G450">
         <v>1</v>
@@ -17305,10 +17301,10 @@
         <v>239</v>
       </c>
       <c r="E451" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F451" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G451">
         <v>1</v>
@@ -17334,10 +17330,10 @@
         <v>239</v>
       </c>
       <c r="E452" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F452" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G452">
         <v>1</v>
@@ -17363,10 +17359,10 @@
         <v>239</v>
       </c>
       <c r="E453" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F453" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G453">
         <v>1</v>
@@ -17392,10 +17388,10 @@
         <v>239</v>
       </c>
       <c r="E454" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F454" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G454">
         <v>1</v>
@@ -17421,10 +17417,10 @@
         <v>239</v>
       </c>
       <c r="E455" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F455" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G455">
         <v>1</v>
@@ -17450,10 +17446,10 @@
         <v>239</v>
       </c>
       <c r="E456" t="s">
-        <v>916</v>
+        <v>346</v>
       </c>
       <c r="F456" t="s">
-        <v>993</v>
+        <v>347</v>
       </c>
       <c r="G456">
         <v>1</v>
@@ -17479,10 +17475,10 @@
         <v>239</v>
       </c>
       <c r="E457" t="s">
-        <v>348</v>
+        <v>916</v>
       </c>
       <c r="F457" t="s">
-        <v>349</v>
+        <v>993</v>
       </c>
       <c r="G457">
         <v>1</v>
@@ -17508,10 +17504,10 @@
         <v>239</v>
       </c>
       <c r="E458" t="s">
-        <v>919</v>
+        <v>348</v>
       </c>
       <c r="F458" t="s">
-        <v>994</v>
+        <v>349</v>
       </c>
       <c r="G458">
         <v>1</v>
@@ -17537,10 +17533,10 @@
         <v>239</v>
       </c>
       <c r="E459" t="s">
-        <v>350</v>
+        <v>919</v>
       </c>
       <c r="F459" t="s">
-        <v>351</v>
+        <v>994</v>
       </c>
       <c r="G459">
         <v>1</v>
@@ -17566,10 +17562,10 @@
         <v>239</v>
       </c>
       <c r="E460" t="s">
-        <v>837</v>
+        <v>350</v>
       </c>
       <c r="F460" t="s">
-        <v>995</v>
+        <v>351</v>
       </c>
       <c r="G460">
         <v>1</v>
@@ -17595,10 +17591,10 @@
         <v>239</v>
       </c>
       <c r="E461" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F461" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="G461">
         <v>1</v>
@@ -17624,10 +17620,10 @@
         <v>239</v>
       </c>
       <c r="E462" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="F462" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="G462">
         <v>1</v>
@@ -17653,10 +17649,10 @@
         <v>239</v>
       </c>
       <c r="E463" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="F463" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G463">
         <v>1</v>
@@ -17673,7 +17669,7 @@
         <v>1169</v>
       </c>
       <c r="B464" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>1176</v>
@@ -17682,10 +17678,10 @@
         <v>239</v>
       </c>
       <c r="E464" t="s">
-        <v>252</v>
+        <v>843</v>
       </c>
       <c r="F464" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="G464">
         <v>1</v>
@@ -17711,10 +17707,10 @@
         <v>239</v>
       </c>
       <c r="E465" t="s">
-        <v>323</v>
+        <v>252</v>
       </c>
       <c r="F465" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="G465">
         <v>1</v>
@@ -17740,10 +17736,10 @@
         <v>239</v>
       </c>
       <c r="E466" t="s">
-        <v>246</v>
+        <v>323</v>
       </c>
       <c r="F466" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="G466">
         <v>1</v>
@@ -17769,10 +17765,10 @@
         <v>239</v>
       </c>
       <c r="E467" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F467" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="G467">
         <v>1</v>
@@ -17798,10 +17794,10 @@
         <v>239</v>
       </c>
       <c r="E468" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F468" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="G468">
         <v>1</v>
@@ -17827,10 +17823,10 @@
         <v>239</v>
       </c>
       <c r="E469" t="s">
-        <v>890</v>
+        <v>250</v>
       </c>
       <c r="F469" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="G469">
         <v>1</v>
@@ -17856,10 +17852,10 @@
         <v>239</v>
       </c>
       <c r="E470" t="s">
-        <v>315</v>
+        <v>890</v>
       </c>
       <c r="F470" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="G470">
         <v>1</v>
@@ -17885,10 +17881,10 @@
         <v>239</v>
       </c>
       <c r="E471" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F471" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G471">
         <v>1</v>
@@ -17914,10 +17910,10 @@
         <v>239</v>
       </c>
       <c r="E472" t="s">
-        <v>896</v>
+        <v>317</v>
       </c>
       <c r="F472" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="G472">
         <v>1</v>
@@ -17943,10 +17939,10 @@
         <v>239</v>
       </c>
       <c r="E473" t="s">
-        <v>319</v>
+        <v>896</v>
       </c>
       <c r="F473" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="G473">
         <v>1</v>
@@ -17972,10 +17968,10 @@
         <v>239</v>
       </c>
       <c r="E474" t="s">
-        <v>899</v>
+        <v>319</v>
       </c>
       <c r="F474" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="G474">
         <v>1</v>
@@ -18001,10 +17997,10 @@
         <v>239</v>
       </c>
       <c r="E475" t="s">
-        <v>321</v>
+        <v>899</v>
       </c>
       <c r="F475" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G475">
         <v>1</v>
@@ -18030,10 +18026,10 @@
         <v>239</v>
       </c>
       <c r="E476" t="s">
-        <v>242</v>
+        <v>321</v>
       </c>
       <c r="F476" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="G476">
         <v>1</v>
@@ -18059,10 +18055,10 @@
         <v>239</v>
       </c>
       <c r="E477" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="F477" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="G477">
         <v>1</v>
@@ -18088,10 +18084,10 @@
         <v>239</v>
       </c>
       <c r="E478" t="s">
-        <v>296</v>
+        <v>261</v>
       </c>
       <c r="F478" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="G478">
         <v>1</v>
@@ -18117,10 +18113,10 @@
         <v>239</v>
       </c>
       <c r="E479" t="s">
-        <v>244</v>
+        <v>296</v>
       </c>
       <c r="F479" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="G479">
         <v>1</v>
@@ -18146,10 +18142,10 @@
         <v>239</v>
       </c>
       <c r="E480" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="F480" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="G480">
         <v>1</v>
@@ -18175,10 +18171,10 @@
         <v>239</v>
       </c>
       <c r="E481" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="F481" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="G481">
         <v>1</v>
@@ -18204,10 +18200,10 @@
         <v>239</v>
       </c>
       <c r="E482" t="s">
-        <v>332</v>
+        <v>300</v>
       </c>
       <c r="F482" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="G482">
         <v>1</v>
@@ -18233,10 +18229,10 @@
         <v>239</v>
       </c>
       <c r="E483" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F483" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="G483">
         <v>1</v>
@@ -18262,10 +18258,10 @@
         <v>239</v>
       </c>
       <c r="E484" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F484" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="G484">
         <v>1</v>
@@ -18291,10 +18287,10 @@
         <v>239</v>
       </c>
       <c r="E485" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F485" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="G485">
         <v>1</v>
@@ -18320,10 +18316,10 @@
         <v>239</v>
       </c>
       <c r="E486" t="s">
-        <v>916</v>
+        <v>338</v>
       </c>
       <c r="F486" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="G486">
         <v>1</v>
@@ -18349,10 +18345,10 @@
         <v>239</v>
       </c>
       <c r="E487" t="s">
-        <v>348</v>
+        <v>916</v>
       </c>
       <c r="F487" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="G487">
         <v>1</v>
@@ -18378,10 +18374,10 @@
         <v>239</v>
       </c>
       <c r="E488" t="s">
-        <v>919</v>
+        <v>348</v>
       </c>
       <c r="F488" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="G488">
         <v>1</v>
@@ -18407,10 +18403,10 @@
         <v>239</v>
       </c>
       <c r="E489" t="s">
-        <v>350</v>
+        <v>919</v>
       </c>
       <c r="F489" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="G489">
         <v>1</v>
@@ -18436,10 +18432,10 @@
         <v>239</v>
       </c>
       <c r="E490" t="s">
-        <v>837</v>
+        <v>350</v>
       </c>
       <c r="F490" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="G490">
         <v>1</v>
@@ -18465,10 +18461,10 @@
         <v>239</v>
       </c>
       <c r="E491" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F491" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="G491">
         <v>1</v>
@@ -18494,10 +18490,10 @@
         <v>239</v>
       </c>
       <c r="E492" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="F492" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="G492">
         <v>1</v>
@@ -18523,10 +18519,10 @@
         <v>239</v>
       </c>
       <c r="E493" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="F493" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="G493">
         <v>1</v>
@@ -18540,10 +18536,10 @@
     </row>
     <row r="494" spans="1:9" ht="13.5">
       <c r="A494" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B494" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="C494" s="1" t="s">
         <v>1176</v>
@@ -18552,10 +18548,10 @@
         <v>239</v>
       </c>
       <c r="E494" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="F494" t="s">
-        <v>846</v>
+        <v>1028</v>
       </c>
       <c r="G494">
         <v>1</v>
@@ -18581,10 +18577,10 @@
         <v>239</v>
       </c>
       <c r="E495" t="s">
-        <v>822</v>
+        <v>845</v>
       </c>
       <c r="F495" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="G495">
         <v>1</v>
@@ -18610,10 +18606,10 @@
         <v>239</v>
       </c>
       <c r="E496" t="s">
-        <v>270</v>
+        <v>822</v>
       </c>
       <c r="F496" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="G496">
         <v>1</v>
@@ -18639,10 +18635,10 @@
         <v>239</v>
       </c>
       <c r="E497" t="s">
-        <v>849</v>
+        <v>270</v>
       </c>
       <c r="F497" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="G497">
         <v>1</v>
@@ -18668,10 +18664,10 @@
         <v>239</v>
       </c>
       <c r="E498" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="F498" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="G498">
         <v>1</v>
@@ -18697,10 +18693,10 @@
         <v>239</v>
       </c>
       <c r="E499" t="s">
-        <v>240</v>
+        <v>851</v>
       </c>
       <c r="F499" t="s">
-        <v>241</v>
+        <v>852</v>
       </c>
       <c r="G499">
         <v>1</v>
@@ -18726,10 +18722,10 @@
         <v>239</v>
       </c>
       <c r="E500" t="s">
-        <v>853</v>
+        <v>240</v>
       </c>
       <c r="F500" t="s">
-        <v>854</v>
+        <v>241</v>
       </c>
       <c r="G500">
         <v>1</v>
@@ -18755,10 +18751,10 @@
         <v>239</v>
       </c>
       <c r="E501" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="F501" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="G501">
         <v>1</v>
@@ -18784,10 +18780,10 @@
         <v>239</v>
       </c>
       <c r="E502" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="F502" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="G502">
         <v>1</v>
@@ -18813,10 +18809,10 @@
         <v>239</v>
       </c>
       <c r="E503" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="F503" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G503">
         <v>1</v>
@@ -18842,10 +18838,10 @@
         <v>239</v>
       </c>
       <c r="E504" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="F504" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="G504">
         <v>1</v>
@@ -18871,10 +18867,10 @@
         <v>239</v>
       </c>
       <c r="E505" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="F505" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="G505">
         <v>1</v>
@@ -18900,10 +18896,10 @@
         <v>239</v>
       </c>
       <c r="E506" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="F506" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="G506">
         <v>1</v>
@@ -18917,22 +18913,22 @@
     </row>
     <row r="507" spans="1:9" ht="13.5">
       <c r="A507" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="B507" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C507" s="1" t="s">
         <v>1176</v>
       </c>
       <c r="D507" t="s">
-        <v>90</v>
+        <v>239</v>
       </c>
       <c r="E507" t="s">
-        <v>574</v>
+        <v>865</v>
       </c>
       <c r="F507" t="s">
-        <v>624</v>
+        <v>866</v>
       </c>
       <c r="G507">
         <v>1</v>
@@ -18958,10 +18954,10 @@
         <v>90</v>
       </c>
       <c r="E508" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F508" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="G508">
         <v>1</v>
@@ -18987,10 +18983,10 @@
         <v>90</v>
       </c>
       <c r="E509" t="s">
-        <v>622</v>
+        <v>576</v>
       </c>
       <c r="F509" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="G509">
         <v>1</v>
@@ -19016,10 +19012,10 @@
         <v>90</v>
       </c>
       <c r="E510" t="s">
-        <v>578</v>
+        <v>622</v>
       </c>
       <c r="F510" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="G510">
         <v>1</v>
@@ -19045,10 +19041,10 @@
         <v>90</v>
       </c>
       <c r="E511" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="F511" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G511">
         <v>1</v>
@@ -19074,10 +19070,10 @@
         <v>90</v>
       </c>
       <c r="E512" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F512" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G512">
         <v>1</v>
@@ -19103,10 +19099,10 @@
         <v>90</v>
       </c>
       <c r="E513" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="F513" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G513">
         <v>1</v>
@@ -19132,10 +19128,10 @@
         <v>90</v>
       </c>
       <c r="E514" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F514" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G514">
         <v>1</v>
@@ -19161,10 +19157,10 @@
         <v>90</v>
       </c>
       <c r="E515" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F515" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G515">
         <v>1</v>
@@ -19190,10 +19186,10 @@
         <v>90</v>
       </c>
       <c r="E516" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="F516" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="G516">
         <v>1</v>
@@ -19219,10 +19215,10 @@
         <v>90</v>
       </c>
       <c r="E517" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="F517" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="G517">
         <v>1</v>
@@ -19248,10 +19244,10 @@
         <v>90</v>
       </c>
       <c r="E518" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="F518" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G518">
         <v>1</v>
@@ -19277,10 +19273,10 @@
         <v>90</v>
       </c>
       <c r="E519" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="F519" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G519">
         <v>1</v>
@@ -19306,10 +19302,10 @@
         <v>90</v>
       </c>
       <c r="E520" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="F520" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G520">
         <v>1</v>
@@ -19335,10 +19331,10 @@
         <v>90</v>
       </c>
       <c r="E521" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F521" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G521">
         <v>1</v>
@@ -19364,10 +19360,10 @@
         <v>90</v>
       </c>
       <c r="E522" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F522" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="G522">
         <v>1</v>
@@ -19393,10 +19389,10 @@
         <v>90</v>
       </c>
       <c r="E523" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F523" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G523">
         <v>1</v>
@@ -19422,10 +19418,10 @@
         <v>90</v>
       </c>
       <c r="E524" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F524" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G524">
         <v>1</v>
@@ -19451,10 +19447,10 @@
         <v>90</v>
       </c>
       <c r="E525" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="F525" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G525">
         <v>1</v>
@@ -19480,10 +19476,10 @@
         <v>90</v>
       </c>
       <c r="E526" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="F526" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G526">
         <v>1</v>
@@ -19509,10 +19505,10 @@
         <v>90</v>
       </c>
       <c r="E527" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F527" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G527">
         <v>1</v>
@@ -19529,7 +19525,7 @@
         <v>1172</v>
       </c>
       <c r="B528" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C528" s="1" t="s">
         <v>1176</v>
@@ -19538,10 +19534,10 @@
         <v>90</v>
       </c>
       <c r="E528" t="s">
-        <v>574</v>
+        <v>614</v>
       </c>
       <c r="F528" t="s">
-        <v>575</v>
+        <v>643</v>
       </c>
       <c r="G528">
         <v>1</v>
@@ -19567,10 +19563,10 @@
         <v>90</v>
       </c>
       <c r="E529" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F529" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="G529">
         <v>1</v>
@@ -19596,10 +19592,10 @@
         <v>90</v>
       </c>
       <c r="E530" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="F530" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="G530">
         <v>1</v>
@@ -19625,10 +19621,10 @@
         <v>90</v>
       </c>
       <c r="E531" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F531" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="G531">
         <v>1</v>
@@ -19654,10 +19650,10 @@
         <v>90</v>
       </c>
       <c r="E532" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="F532" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="G532">
         <v>1</v>
@@ -19683,10 +19679,10 @@
         <v>90</v>
       </c>
       <c r="E533" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F533" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="G533">
         <v>1</v>
@@ -19712,10 +19708,10 @@
         <v>90</v>
       </c>
       <c r="E534" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="F534" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="G534">
         <v>1</v>
@@ -19741,10 +19737,10 @@
         <v>90</v>
       </c>
       <c r="E535" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F535" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G535">
         <v>1</v>
@@ -19770,10 +19766,10 @@
         <v>90</v>
       </c>
       <c r="E536" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F536" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G536">
         <v>1</v>
@@ -19799,10 +19795,10 @@
         <v>90</v>
       </c>
       <c r="E537" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="F537" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G537">
         <v>1</v>
@@ -19828,10 +19824,10 @@
         <v>90</v>
       </c>
       <c r="E538" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="F538" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="G538">
         <v>1</v>
@@ -19857,10 +19853,10 @@
         <v>90</v>
       </c>
       <c r="E539" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="F539" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="G539">
         <v>1</v>
@@ -19886,10 +19882,10 @@
         <v>90</v>
       </c>
       <c r="E540" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="F540" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="G540">
         <v>1</v>
@@ -19915,10 +19911,10 @@
         <v>90</v>
       </c>
       <c r="E541" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="F541" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="G541">
         <v>1</v>
@@ -19944,10 +19940,10 @@
         <v>90</v>
       </c>
       <c r="E542" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F542" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="G542">
         <v>1</v>
@@ -19973,10 +19969,10 @@
         <v>90</v>
       </c>
       <c r="E543" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F543" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G543">
         <v>1</v>
@@ -20002,10 +19998,10 @@
         <v>90</v>
       </c>
       <c r="E544" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F544" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="G544">
         <v>1</v>
@@ -20031,10 +20027,10 @@
         <v>90</v>
       </c>
       <c r="E545" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F545" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="G545">
         <v>1</v>
@@ -20060,10 +20056,10 @@
         <v>90</v>
       </c>
       <c r="E546" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="F546" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="G546">
         <v>1</v>
@@ -20089,10 +20085,10 @@
         <v>90</v>
       </c>
       <c r="E547" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="F547" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G547">
         <v>1</v>
@@ -20118,10 +20114,10 @@
         <v>90</v>
       </c>
       <c r="E548" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F548" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="G548">
         <v>1</v>
@@ -20147,10 +20143,10 @@
         <v>90</v>
       </c>
       <c r="E549" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="F549" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="G549">
         <v>1</v>
@@ -20176,10 +20172,10 @@
         <v>90</v>
       </c>
       <c r="E550" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="F550" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="G550">
         <v>1</v>
@@ -20205,10 +20201,10 @@
         <v>90</v>
       </c>
       <c r="E551" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="F551" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="G551">
         <v>1</v>
@@ -20222,22 +20218,22 @@
     </row>
     <row r="552" spans="1:9" ht="13.5">
       <c r="A552" t="s">
-        <v>1167</v>
+        <v>1172</v>
       </c>
       <c r="B552" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="C552" s="1" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="D552" t="s">
         <v>90</v>
       </c>
       <c r="E552" t="s">
-        <v>93</v>
+        <v>620</v>
       </c>
       <c r="F552" t="s">
-        <v>94</v>
+        <v>621</v>
       </c>
       <c r="G552">
         <v>1</v>
@@ -20263,10 +20259,10 @@
         <v>90</v>
       </c>
       <c r="E553" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F553" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G553">
         <v>1</v>
@@ -20292,10 +20288,10 @@
         <v>90</v>
       </c>
       <c r="E554" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F554" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G554">
         <v>1</v>
@@ -20321,10 +20317,10 @@
         <v>90</v>
       </c>
       <c r="E555" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F555" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G555">
         <v>1</v>
@@ -20344,16 +20340,16 @@
         <v>40</v>
       </c>
       <c r="C556" s="1" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="D556" t="s">
         <v>90</v>
       </c>
       <c r="E556" t="s">
-        <v>767</v>
+        <v>99</v>
       </c>
       <c r="F556" t="s">
-        <v>768</v>
+        <v>100</v>
       </c>
       <c r="G556">
         <v>1</v>
@@ -20379,10 +20375,10 @@
         <v>90</v>
       </c>
       <c r="E557" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="F557" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="G557">
         <v>1</v>
@@ -20408,10 +20404,10 @@
         <v>90</v>
       </c>
       <c r="E558" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="F558" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="G558">
         <v>1</v>
@@ -20437,10 +20433,10 @@
         <v>90</v>
       </c>
       <c r="E559" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="F559" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="G559">
         <v>1</v>
@@ -20466,10 +20462,10 @@
         <v>90</v>
       </c>
       <c r="E560" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="F560" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="G560">
         <v>1</v>
@@ -20495,10 +20491,10 @@
         <v>90</v>
       </c>
       <c r="E561" t="s">
-        <v>177</v>
+        <v>765</v>
       </c>
       <c r="F561" t="s">
-        <v>178</v>
+        <v>766</v>
       </c>
       <c r="G561">
         <v>1</v>
@@ -20524,10 +20520,10 @@
         <v>90</v>
       </c>
       <c r="E562" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F562" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G562">
         <v>1</v>
@@ -20553,10 +20549,10 @@
         <v>90</v>
       </c>
       <c r="E563" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F563" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G563">
         <v>1</v>
@@ -20582,10 +20578,10 @@
         <v>90</v>
       </c>
       <c r="E564" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F564" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G564">
         <v>1</v>
@@ -20611,10 +20607,10 @@
         <v>90</v>
       </c>
       <c r="E565" t="s">
-        <v>771</v>
+        <v>183</v>
       </c>
       <c r="F565" t="s">
-        <v>772</v>
+        <v>184</v>
       </c>
       <c r="G565">
         <v>1</v>
@@ -20640,10 +20636,10 @@
         <v>90</v>
       </c>
       <c r="E566" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="F566" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="G566">
         <v>1</v>
@@ -20669,10 +20665,10 @@
         <v>90</v>
       </c>
       <c r="E567" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="F567" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="G567">
         <v>1</v>
@@ -20698,10 +20694,10 @@
         <v>90</v>
       </c>
       <c r="E568" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F568" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="G568">
         <v>1</v>
@@ -20727,10 +20723,10 @@
         <v>90</v>
       </c>
       <c r="E569" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="F569" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="G569">
         <v>1</v>
@@ -20756,10 +20752,10 @@
         <v>90</v>
       </c>
       <c r="E570" t="s">
-        <v>185</v>
+        <v>779</v>
       </c>
       <c r="F570" t="s">
-        <v>186</v>
+        <v>780</v>
       </c>
       <c r="G570">
         <v>1</v>
@@ -20785,10 +20781,10 @@
         <v>90</v>
       </c>
       <c r="E571" t="s">
-        <v>781</v>
+        <v>185</v>
       </c>
       <c r="F571" t="s">
-        <v>782</v>
+        <v>186</v>
       </c>
       <c r="G571">
         <v>1</v>
@@ -20814,10 +20810,10 @@
         <v>90</v>
       </c>
       <c r="E572" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F572" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="G572">
         <v>1</v>
@@ -20843,10 +20839,10 @@
         <v>90</v>
       </c>
       <c r="E573" t="s">
-        <v>187</v>
+        <v>783</v>
       </c>
       <c r="F573" t="s">
-        <v>188</v>
+        <v>784</v>
       </c>
       <c r="G573">
         <v>1</v>
@@ -20860,22 +20856,22 @@
     </row>
     <row r="574" spans="1:9" ht="13.5">
       <c r="A574" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B574" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C574" s="1" t="s">
         <v>1176</v>
       </c>
       <c r="D574" t="s">
-        <v>239</v>
+        <v>90</v>
       </c>
       <c r="E574" t="s">
-        <v>242</v>
+        <v>187</v>
       </c>
       <c r="F574" t="s">
-        <v>352</v>
+        <v>188</v>
       </c>
       <c r="G574">
         <v>1</v>
@@ -20901,10 +20897,10 @@
         <v>239</v>
       </c>
       <c r="E575" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="F575" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G575">
         <v>1</v>
@@ -20930,10 +20926,10 @@
         <v>239</v>
       </c>
       <c r="E576" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="F576" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G576">
         <v>1</v>
@@ -20959,10 +20955,10 @@
         <v>239</v>
       </c>
       <c r="E577" t="s">
-        <v>355</v>
+        <v>300</v>
       </c>
       <c r="F577" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G577">
         <v>1</v>
@@ -20988,10 +20984,10 @@
         <v>239</v>
       </c>
       <c r="E578" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F578" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G578">
         <v>1</v>
@@ -21017,10 +21013,10 @@
         <v>239</v>
       </c>
       <c r="E579" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F579" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G579">
         <v>1</v>
@@ -21046,10 +21042,10 @@
         <v>239</v>
       </c>
       <c r="E580" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F580" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G580">
         <v>1</v>
@@ -21063,22 +21059,22 @@
     </row>
     <row r="581" spans="1:9" ht="13.5">
       <c r="A581" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="B581" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C581" s="1" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="D581" t="s">
-        <v>90</v>
+        <v>239</v>
       </c>
       <c r="E581" t="s">
-        <v>117</v>
+        <v>361</v>
       </c>
       <c r="F581" t="s">
-        <v>118</v>
+        <v>362</v>
       </c>
       <c r="G581">
         <v>1</v>
@@ -21104,10 +21100,10 @@
         <v>90</v>
       </c>
       <c r="E582" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F582" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G582">
         <v>1</v>
@@ -21121,22 +21117,22 @@
     </row>
     <row r="583" spans="1:9" ht="13.5">
       <c r="A583" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="B583" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="C583" s="1" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="D583" t="s">
         <v>90</v>
       </c>
       <c r="E583" t="s">
-        <v>267</v>
+        <v>119</v>
       </c>
       <c r="F583" t="s">
-        <v>646</v>
+        <v>120</v>
       </c>
       <c r="G583">
         <v>1</v>
@@ -21162,10 +21158,10 @@
         <v>90</v>
       </c>
       <c r="E584" t="s">
-        <v>647</v>
+        <v>267</v>
       </c>
       <c r="F584" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="G584">
         <v>1</v>
@@ -21191,10 +21187,10 @@
         <v>90</v>
       </c>
       <c r="E585" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="F585" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="G585">
         <v>1</v>
@@ -21220,10 +21216,10 @@
         <v>90</v>
       </c>
       <c r="E586" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="F586" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G586">
         <v>1</v>
@@ -21249,10 +21245,10 @@
         <v>90</v>
       </c>
       <c r="E587" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="F587" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G587">
         <v>1</v>
@@ -21278,10 +21274,10 @@
         <v>90</v>
       </c>
       <c r="E588" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="F588" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G588">
         <v>1</v>
@@ -21307,10 +21303,10 @@
         <v>90</v>
       </c>
       <c r="E589" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F589" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G589">
         <v>1</v>
@@ -21336,10 +21332,10 @@
         <v>90</v>
       </c>
       <c r="E590" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F590" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G590">
         <v>1</v>
@@ -21365,10 +21361,10 @@
         <v>90</v>
       </c>
       <c r="E591" t="s">
-        <v>1163</v>
+        <v>659</v>
       </c>
       <c r="F591" t="s">
-        <v>1164</v>
+        <v>660</v>
       </c>
       <c r="G591">
         <v>1</v>
@@ -21394,10 +21390,10 @@
         <v>90</v>
       </c>
       <c r="E592" t="s">
-        <v>661</v>
+        <v>1163</v>
       </c>
       <c r="F592" t="s">
-        <v>662</v>
+        <v>1164</v>
       </c>
       <c r="G592">
         <v>1</v>
@@ -21423,10 +21419,10 @@
         <v>90</v>
       </c>
       <c r="E593" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="F593" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="G593">
         <v>1</v>
@@ -21452,10 +21448,10 @@
         <v>90</v>
       </c>
       <c r="E594" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="F594" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="G594">
         <v>1</v>
@@ -21481,10 +21477,10 @@
         <v>90</v>
       </c>
       <c r="E595" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="F595" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="G595">
         <v>1</v>
@@ -21510,10 +21506,10 @@
         <v>90</v>
       </c>
       <c r="E596" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="F596" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="G596">
         <v>1</v>
@@ -21527,22 +21523,22 @@
     </row>
     <row r="597" spans="1:9" ht="13.5">
       <c r="A597" t="s">
-        <v>1167</v>
+        <v>1172</v>
       </c>
       <c r="B597" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="C597" s="1" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="D597" t="s">
         <v>90</v>
       </c>
       <c r="E597" t="s">
-        <v>101</v>
+        <v>669</v>
       </c>
       <c r="F597" t="s">
-        <v>102</v>
+        <v>670</v>
       </c>
       <c r="G597">
         <v>1</v>
@@ -21568,10 +21564,10 @@
         <v>90</v>
       </c>
       <c r="E598" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F598" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G598">
         <v>1</v>
@@ -21597,10 +21593,10 @@
         <v>90</v>
       </c>
       <c r="E599" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F599" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G599">
         <v>1</v>
@@ -21626,10 +21622,10 @@
         <v>90</v>
       </c>
       <c r="E600" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F600" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G600">
         <v>1</v>
@@ -21655,10 +21651,10 @@
         <v>90</v>
       </c>
       <c r="E601" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F601" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G601">
         <v>1</v>
@@ -21684,10 +21680,10 @@
         <v>90</v>
       </c>
       <c r="E602" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F602" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G602">
         <v>1</v>
@@ -21713,10 +21709,10 @@
         <v>90</v>
       </c>
       <c r="E603" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F603" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G603">
         <v>1</v>
@@ -21742,10 +21738,10 @@
         <v>90</v>
       </c>
       <c r="E604" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F604" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G604">
         <v>1</v>
@@ -21765,16 +21761,16 @@
         <v>41</v>
       </c>
       <c r="C605" s="1" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="D605" t="s">
         <v>90</v>
       </c>
       <c r="E605" t="s">
-        <v>785</v>
+        <v>115</v>
       </c>
       <c r="F605" t="s">
-        <v>786</v>
+        <v>116</v>
       </c>
       <c r="G605">
         <v>1</v>
@@ -21803,7 +21799,7 @@
         <v>785</v>
       </c>
       <c r="F606" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="G606">
         <v>1</v>
@@ -21829,10 +21825,10 @@
         <v>90</v>
       </c>
       <c r="E607" t="s">
-        <v>201</v>
+        <v>785</v>
       </c>
       <c r="F607" t="s">
-        <v>202</v>
+        <v>787</v>
       </c>
       <c r="G607">
         <v>1</v>
@@ -21858,10 +21854,10 @@
         <v>90</v>
       </c>
       <c r="E608" t="s">
-        <v>788</v>
+        <v>201</v>
       </c>
       <c r="F608" t="s">
-        <v>789</v>
+        <v>202</v>
       </c>
       <c r="G608">
         <v>1</v>
@@ -21887,10 +21883,10 @@
         <v>90</v>
       </c>
       <c r="E609" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="F609" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="G609">
         <v>1</v>
@@ -21919,7 +21915,7 @@
         <v>790</v>
       </c>
       <c r="F610" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="G610">
         <v>1</v>
@@ -21945,10 +21941,10 @@
         <v>90</v>
       </c>
       <c r="E611" t="s">
-        <v>203</v>
+        <v>790</v>
       </c>
       <c r="F611" t="s">
-        <v>204</v>
+        <v>792</v>
       </c>
       <c r="G611">
         <v>1</v>
@@ -21974,10 +21970,10 @@
         <v>90</v>
       </c>
       <c r="E612" t="s">
-        <v>793</v>
+        <v>203</v>
       </c>
       <c r="F612" t="s">
-        <v>794</v>
+        <v>204</v>
       </c>
       <c r="G612">
         <v>1</v>
@@ -22003,10 +21999,10 @@
         <v>90</v>
       </c>
       <c r="E613" t="s">
-        <v>205</v>
+        <v>793</v>
       </c>
       <c r="F613" t="s">
-        <v>206</v>
+        <v>794</v>
       </c>
       <c r="G613">
         <v>1</v>
@@ -22032,10 +22028,10 @@
         <v>90</v>
       </c>
       <c r="E614" t="s">
-        <v>795</v>
+        <v>205</v>
       </c>
       <c r="F614" t="s">
-        <v>796</v>
+        <v>206</v>
       </c>
       <c r="G614">
         <v>1</v>
@@ -22064,7 +22060,7 @@
         <v>795</v>
       </c>
       <c r="F615" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G615">
         <v>1</v>
@@ -22090,10 +22086,10 @@
         <v>90</v>
       </c>
       <c r="E616" t="s">
-        <v>207</v>
+        <v>795</v>
       </c>
       <c r="F616" t="s">
-        <v>208</v>
+        <v>797</v>
       </c>
       <c r="G616">
         <v>1</v>
@@ -22119,10 +22115,10 @@
         <v>90</v>
       </c>
       <c r="E617" t="s">
-        <v>798</v>
+        <v>207</v>
       </c>
       <c r="F617" t="s">
-        <v>799</v>
+        <v>208</v>
       </c>
       <c r="G617">
         <v>1</v>
@@ -22148,10 +22144,10 @@
         <v>90</v>
       </c>
       <c r="E618" t="s">
-        <v>209</v>
+        <v>798</v>
       </c>
       <c r="F618" t="s">
-        <v>210</v>
+        <v>799</v>
       </c>
       <c r="G618">
         <v>1</v>
@@ -22177,10 +22173,10 @@
         <v>90</v>
       </c>
       <c r="E619" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F619" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G619">
         <v>1</v>
@@ -22206,10 +22202,10 @@
         <v>90</v>
       </c>
       <c r="E620" t="s">
-        <v>800</v>
+        <v>211</v>
       </c>
       <c r="F620" t="s">
-        <v>801</v>
+        <v>212</v>
       </c>
       <c r="G620">
         <v>1</v>
@@ -22238,7 +22234,7 @@
         <v>800</v>
       </c>
       <c r="F621" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G621">
         <v>1</v>
@@ -22264,10 +22260,10 @@
         <v>90</v>
       </c>
       <c r="E622" t="s">
-        <v>213</v>
+        <v>800</v>
       </c>
       <c r="F622" t="s">
-        <v>214</v>
+        <v>802</v>
       </c>
       <c r="G622">
         <v>1</v>
@@ -22293,10 +22289,10 @@
         <v>90</v>
       </c>
       <c r="E623" t="s">
-        <v>803</v>
+        <v>213</v>
       </c>
       <c r="F623" t="s">
-        <v>804</v>
+        <v>214</v>
       </c>
       <c r="G623">
         <v>1</v>
@@ -22322,10 +22318,10 @@
         <v>90</v>
       </c>
       <c r="E624" t="s">
-        <v>215</v>
+        <v>803</v>
       </c>
       <c r="F624" t="s">
-        <v>216</v>
+        <v>804</v>
       </c>
       <c r="G624">
         <v>1</v>
@@ -22351,10 +22347,10 @@
         <v>90</v>
       </c>
       <c r="E625" t="s">
-        <v>805</v>
+        <v>215</v>
       </c>
       <c r="F625" t="s">
-        <v>806</v>
+        <v>216</v>
       </c>
       <c r="G625">
         <v>1</v>
@@ -22383,7 +22379,7 @@
         <v>805</v>
       </c>
       <c r="F626" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="G626">
         <v>1</v>
@@ -22409,10 +22405,10 @@
         <v>90</v>
       </c>
       <c r="E627" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="F627" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="G627">
         <v>1</v>
@@ -22438,10 +22434,10 @@
         <v>90</v>
       </c>
       <c r="E628" t="s">
-        <v>217</v>
+        <v>808</v>
       </c>
       <c r="F628" t="s">
-        <v>218</v>
+        <v>809</v>
       </c>
       <c r="G628">
         <v>1</v>
@@ -22467,10 +22463,10 @@
         <v>90</v>
       </c>
       <c r="E629" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F629" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G629">
         <v>1</v>
@@ -22496,10 +22492,10 @@
         <v>90</v>
       </c>
       <c r="E630" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F630" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G630">
         <v>1</v>
@@ -22525,10 +22521,10 @@
         <v>90</v>
       </c>
       <c r="E631" t="s">
-        <v>810</v>
+        <v>221</v>
       </c>
       <c r="F631" t="s">
-        <v>811</v>
+        <v>222</v>
       </c>
       <c r="G631">
         <v>1</v>
@@ -22557,7 +22553,7 @@
         <v>810</v>
       </c>
       <c r="F632" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="G632">
         <v>1</v>
@@ -22583,10 +22579,10 @@
         <v>90</v>
       </c>
       <c r="E633" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="F633" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="G633">
         <v>1</v>
@@ -22612,10 +22608,10 @@
         <v>90</v>
       </c>
       <c r="E634" t="s">
-        <v>223</v>
+        <v>813</v>
       </c>
       <c r="F634" t="s">
-        <v>224</v>
+        <v>814</v>
       </c>
       <c r="G634">
         <v>1</v>
@@ -22641,10 +22637,10 @@
         <v>90</v>
       </c>
       <c r="E635" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F635" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G635">
         <v>1</v>
@@ -22670,10 +22666,10 @@
         <v>90</v>
       </c>
       <c r="E636" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F636" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G636">
         <v>1</v>
@@ -22699,10 +22695,10 @@
         <v>90</v>
       </c>
       <c r="E637" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F637" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G637">
         <v>1</v>
@@ -22728,10 +22724,10 @@
         <v>90</v>
       </c>
       <c r="E638" t="s">
-        <v>815</v>
+        <v>229</v>
       </c>
       <c r="F638" t="s">
-        <v>816</v>
+        <v>230</v>
       </c>
       <c r="G638">
         <v>1</v>
@@ -22760,7 +22756,7 @@
         <v>815</v>
       </c>
       <c r="F639" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="G639">
         <v>1</v>
@@ -22786,10 +22782,10 @@
         <v>90</v>
       </c>
       <c r="E640" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="F640" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="G640">
         <v>1</v>
@@ -22815,10 +22811,10 @@
         <v>90</v>
       </c>
       <c r="E641" t="s">
-        <v>231</v>
+        <v>818</v>
       </c>
       <c r="F641" t="s">
-        <v>232</v>
+        <v>819</v>
       </c>
       <c r="G641">
         <v>1</v>
@@ -22844,10 +22840,10 @@
         <v>90</v>
       </c>
       <c r="E642" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F642" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G642">
         <v>1</v>
@@ -22873,10 +22869,10 @@
         <v>90</v>
       </c>
       <c r="E643" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F643" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G643">
         <v>1</v>
@@ -22902,10 +22898,10 @@
         <v>90</v>
       </c>
       <c r="E644" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F644" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G644">
         <v>1</v>
@@ -22931,10 +22927,10 @@
         <v>90</v>
       </c>
       <c r="E645" t="s">
-        <v>189</v>
+        <v>237</v>
       </c>
       <c r="F645" t="s">
-        <v>190</v>
+        <v>238</v>
       </c>
       <c r="G645">
         <v>1</v>
@@ -22960,10 +22956,10 @@
         <v>90</v>
       </c>
       <c r="E646" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F646" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G646">
         <v>1</v>
@@ -22989,10 +22985,10 @@
         <v>90</v>
       </c>
       <c r="E647" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F647" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G647">
         <v>1</v>
@@ -23018,10 +23014,10 @@
         <v>90</v>
       </c>
       <c r="E648" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F648" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G648">
         <v>1</v>
@@ -23047,10 +23043,10 @@
         <v>90</v>
       </c>
       <c r="E649" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F649" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G649">
         <v>1</v>
@@ -23076,10 +23072,10 @@
         <v>90</v>
       </c>
       <c r="E650" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F650" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G650">
         <v>1</v>
@@ -23096,19 +23092,19 @@
         <v>1167</v>
       </c>
       <c r="B651" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C651" s="1" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="D651" t="s">
         <v>90</v>
       </c>
       <c r="E651" t="s">
-        <v>121</v>
+        <v>199</v>
       </c>
       <c r="F651" t="s">
-        <v>122</v>
+        <v>200</v>
       </c>
       <c r="G651">
         <v>1</v>
@@ -23128,16 +23124,16 @@
         <v>43</v>
       </c>
       <c r="C652" s="1" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="D652" t="s">
         <v>90</v>
       </c>
       <c r="E652" t="s">
-        <v>820</v>
+        <v>121</v>
       </c>
       <c r="F652" t="s">
-        <v>821</v>
+        <v>122</v>
       </c>
       <c r="G652">
         <v>1</v>
@@ -23151,10 +23147,10 @@
     </row>
     <row r="653" spans="1:9" ht="13.5">
       <c r="A653" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="B653" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="C653" s="1" t="s">
         <v>1176</v>
@@ -23163,10 +23159,10 @@
         <v>90</v>
       </c>
       <c r="E653" t="s">
-        <v>1161</v>
+        <v>820</v>
       </c>
       <c r="F653" t="s">
-        <v>1162</v>
+        <v>821</v>
       </c>
       <c r="G653">
         <v>1</v>
@@ -23192,25 +23188,54 @@
         <v>90</v>
       </c>
       <c r="E654" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F654" t="s">
+        <v>1162</v>
+      </c>
+      <c r="G654">
+        <v>1</v>
+      </c>
+      <c r="H654" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I654" s="3">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="655" spans="1:9" ht="13.5">
+      <c r="A655" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B655" t="s">
+        <v>76</v>
+      </c>
+      <c r="C655" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D655" t="s">
+        <v>90</v>
+      </c>
+      <c r="E655" t="s">
         <v>644</v>
       </c>
-      <c r="F654" t="s">
+      <c r="F655" t="s">
         <v>645</v>
       </c>
-      <c r="G654">
-        <v>1</v>
-      </c>
-      <c r="H654" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I654" s="3">
+      <c r="G655">
+        <v>1</v>
+      </c>
+      <c r="H655" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I655" s="3">
         <v>46219</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:J5" xr:uid="{EB819BC4-E5C4-4402-898A-BE0A3820E230}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:J654">
-      <sortCondition ref="B5"/>
+  <autoFilter ref="A6:J6" xr:uid="{EB819BC4-E5C4-4402-898A-BE0A3820E230}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:J655">
+      <sortCondition ref="B6"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -23220,14 +23245,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F77BCE9D-002C-46A4-837D-945D35BE8D04}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
-  <cols>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -23235,13 +23256,13 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="13.5">
+    <row r="2" spans="1:10" ht="13.5">
       <c r="A2" s="7" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="B2" s="8"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -23249,7 +23270,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="13.5">
+    <row r="4" spans="1:10" ht="13.5">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -23257,134 +23278,340 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="12" t="s">
-        <v>1198</v>
-      </c>
-      <c r="B6" s="12" t="s">
+    <row r="6" spans="1:10" ht="13.5">
+      <c r="A6" s="10" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>1199</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>1193</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12" t="s">
-        <v>1194</v>
-      </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="10" t="s">
+      <c r="E7" s="11" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>1191</v>
-      </c>
-      <c r="E7" s="11">
-        <v>1</v>
-      </c>
-      <c r="F7" s="11">
-        <v>2</v>
-      </c>
-      <c r="G7" s="11">
-        <v>3</v>
-      </c>
-      <c r="H7" s="11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="13.5">
-      <c r="A8" s="1" t="s">
-        <v>1192</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>1200</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>1203</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="13.5">
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E8" s="11"/>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="13.5">
       <c r="A9" s="1" t="s">
-        <v>1192</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1201</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>1203</v>
+        <v>1190</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>1199</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>1203</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="13.5">
+      <c r="A14" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E14" s="11"/>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="13.5">
+      <c r="A15" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>1203</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E20" s="11"/>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="13.5">
+      <c r="A21" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>1203</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>1203</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="13.5">
-      <c r="A10" s="1" t="s">
-        <v>1192</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>1202</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>1203</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A6:A7"/>
+  <mergeCells count="15">
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="D15:D18"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="E7:E8"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23409,7 +23636,7 @@
     </row>
     <row r="2" spans="1:6" ht="13.5">
       <c r="A2" s="7" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="B2" s="1"/>
     </row>

--- a/es/es-global-request.xlsx
+++ b/es/es-global-request.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cnxmail-my.sharepoint.com/personal/sujeong_kang_concentrix_com/Documents/02.Operations/01.BU/01.ES/00.Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="380" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40498E01-A2FB-4688-92A8-0ABDBD880C42}"/>
+  <xr:revisionPtr revIDLastSave="399" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09462E4E-4E6B-4327-B299-D8D3540B7124}"/>
   <bookViews>
-    <workbookView xWindow="-25290" yWindow="2430" windowWidth="23370" windowHeight="14895" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24990" yWindow="2370" windowWidth="23370" windowHeight="14895" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LG DUALCOOL AI" sheetId="2" r:id="rId1"/>
     <sheet name="SEO Title &amp; Description Automat" sheetId="3" r:id="rId2"/>
     <sheet name="Buying Guide &amp; Article" sheetId="4" r:id="rId3"/>
-    <sheet name="HVAC B2B SEO Correction" sheetId="5" r:id="rId4"/>
+    <sheet name="Buying Guide &amp; Article (2)" sheetId="6" r:id="rId4"/>
+    <sheet name="HVAC B2B SEO Correction" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HVAC B2B SEO Correction'!$A$6:$F$853</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'HVAC B2B SEO Correction'!$A$6:$F$853</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SEO Title &amp; Description Automat'!$A$6:$J$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4763" uniqueCount="1210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4871" uniqueCount="1210">
   <si>
     <t>Title</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -3853,7 +3854,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3868,6 +3869,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -23597,11 +23599,7 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="C21:C24"/>
-    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="E7:E8"/>
     <mergeCell ref="D9:D12"/>
     <mergeCell ref="D15:D18"/>
     <mergeCell ref="D21:D24"/>
@@ -23611,7 +23609,11 @@
     <mergeCell ref="C15:C18"/>
     <mergeCell ref="B13:B18"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="B19:B24"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23619,6 +23621,442 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA03A5E1-3159-4BF6-BC00-37DB8C0157CE}">
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.5">
+      <c r="A2" s="7" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B2" s="8"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="13.5">
+      <c r="A4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="13.5">
+      <c r="A6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="13.5">
+      <c r="A9" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="13.5">
+      <c r="A14" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="13.5">
+      <c r="A15" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="13.5">
+      <c r="A21" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FABBF0C-ED98-4D26-8E61-5682FF5075DC}">
   <dimension ref="A1:F853"/>
   <sheetFormatPr defaultRowHeight="12.75"/>

--- a/es/es-global-request.xlsx
+++ b/es/es-global-request.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cnxmail-my.sharepoint.com/personal/sujeong_kang_concentrix_com/Documents/02.Operations/01.BU/01.ES/00.Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="399" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09462E4E-4E6B-4327-B299-D8D3540B7124}"/>
+  <xr:revisionPtr revIDLastSave="400" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EE3A052-B0EF-4BEA-8236-F45DA99E09C9}"/>
   <bookViews>
-    <workbookView xWindow="-24990" yWindow="2370" windowWidth="23370" windowHeight="14895" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28410" yWindow="2235" windowWidth="23370" windowHeight="14895" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LG DUALCOOL AI" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4871" uniqueCount="1210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4871" uniqueCount="1211">
   <si>
     <t>Title</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -3770,6 +3770,10 @@
   </si>
   <si>
     <t>Buying guide air purifier</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LDM 컨펌 필요</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3854,7 +3858,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3869,7 +3873,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -23599,21 +23602,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="D9:D12"/>
     <mergeCell ref="D15:D18"/>
     <mergeCell ref="D21:D24"/>
     <mergeCell ref="C9:C12"/>
-    <mergeCell ref="B7:B12"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="C7:C8"/>
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="C21:C24"/>
-    <mergeCell ref="B19:B24"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23691,16 +23694,16 @@
       <c r="A7" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="1" t="s">
         <v>1196</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="1" t="s">
         <v>1208</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>1199</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="1" t="s">
         <v>1209</v>
       </c>
       <c r="G7">
@@ -23711,16 +23714,16 @@
       <c r="A8" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="1" t="s">
         <v>1196</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="1" t="s">
         <v>1208</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>1201</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="1" t="s">
         <v>1209</v>
       </c>
       <c r="G8">
@@ -23731,13 +23734,13 @@
       <c r="A9" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="1" t="s">
         <v>1196</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="1" t="s">
         <v>1199</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -23751,13 +23754,13 @@
       <c r="A10" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="1" t="s">
         <v>1196</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="1" t="s">
         <v>1199</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -23771,13 +23774,13 @@
       <c r="A11" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="1" t="s">
         <v>1196</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="1" t="s">
         <v>1199</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -23791,13 +23794,13 @@
       <c r="A12" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="1" t="s">
         <v>1196</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="1" t="s">
         <v>1199</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -23811,16 +23814,16 @@
       <c r="A13" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="1" t="s">
         <v>1197</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="1" t="s">
         <v>1208</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>1199</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="1" t="s">
         <v>1209</v>
       </c>
       <c r="G13">
@@ -23831,36 +23834,36 @@
       <c r="A14" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="1" t="s">
         <v>1197</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="1" t="s">
         <v>1208</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>1201</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="1" t="s">
         <v>1209</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="13.5">
       <c r="A15" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="1" t="s">
         <v>1197</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="1" t="s">
         <v>1199</v>
       </c>
       <c r="E15" s="2" t="s">
@@ -23874,13 +23877,13 @@
       <c r="A16" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="1" t="s">
         <v>1197</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="1" t="s">
         <v>1199</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -23894,13 +23897,13 @@
       <c r="A17" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="1" t="s">
         <v>1197</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="1" t="s">
         <v>1199</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -23914,13 +23917,13 @@
       <c r="A18" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="1" t="s">
         <v>1197</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="1" t="s">
         <v>1199</v>
       </c>
       <c r="E18" s="1" t="s">
@@ -23934,16 +23937,16 @@
       <c r="A19" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="1" t="s">
         <v>1208</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>1199</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="1" t="s">
         <v>1209</v>
       </c>
       <c r="G19">
@@ -23954,16 +23957,16 @@
       <c r="A20" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="1" t="s">
         <v>1208</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>1201</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="1" t="s">
         <v>1209</v>
       </c>
       <c r="G20">
@@ -23974,13 +23977,13 @@
       <c r="A21" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="1" t="s">
         <v>1199</v>
       </c>
       <c r="E21" s="2" t="s">
@@ -23994,13 +23997,13 @@
       <c r="A22" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="1" t="s">
         <v>1199</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -24014,13 +24017,13 @@
       <c r="A23" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="1" t="s">
         <v>1199</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -24034,13 +24037,13 @@
       <c r="A24" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="1" t="s">
         <v>1199</v>
       </c>
       <c r="E24" s="1" t="s">

--- a/es/es-global-request.xlsx
+++ b/es/es-global-request.xlsx
@@ -8,19 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cnxmail-my.sharepoint.com/personal/sujeong_kang_concentrix_com/Documents/02.Operations/01.BU/01.ES/00.Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="400" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EE3A052-B0EF-4BEA-8236-F45DA99E09C9}"/>
+  <xr:revisionPtr revIDLastSave="431" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E980710-BD09-4D3D-ACEE-6AB9BC532489}"/>
   <bookViews>
-    <workbookView xWindow="-28410" yWindow="2235" windowWidth="23370" windowHeight="14895" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LG DUALCOOL AI" sheetId="2" r:id="rId1"/>
     <sheet name="SEO Title &amp; Description Automat" sheetId="3" r:id="rId2"/>
     <sheet name="Buying Guide &amp; Article" sheetId="4" r:id="rId3"/>
-    <sheet name="Buying Guide &amp; Article (2)" sheetId="6" r:id="rId4"/>
-    <sheet name="HVAC B2B SEO Correction" sheetId="5" r:id="rId5"/>
+    <sheet name="HVAC B2B SEO Correction" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'HVAC B2B SEO Correction'!$A$6:$F$853</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HVAC B2B SEO Correction'!$A$6:$F$853</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SEO Title &amp; Description Automat'!$A$6:$J$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4871" uniqueCount="1211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4719" uniqueCount="1209">
   <si>
     <t>Title</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -3652,10 +3651,6 @@
   </si>
   <si>
     <t>EASTAFRICA : KE (en)</t>
-  </si>
-  <si>
-    <t>Asia</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3711,6 +3706,16 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>SG-en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TW-zh</t>
+  </si>
+  <si>
+    <t>VN-vi</t>
+  </si>
+  <si>
     <t>Region</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3719,61 +3724,65 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>SG-en</t>
+    <t>Status</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>TW-zh</t>
-  </si>
-  <si>
-    <t>VN-vi</t>
-  </si>
-  <si>
-    <t>Microsite</t>
+    <t>Buying Guide
+Microsite</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Category</t>
+    <t>Buying Guide
+GNB</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>GNB</t>
+    <t>Article
+Clean the air</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Article</t>
+    <t>Article
+Pets</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>How does an air purifier clean the air</t>
+    <t>Article
+Caring</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Air purifier for pets</t>
+    <t>Article
+PM2.5</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Caring for your air purifier</t>
+    <t>완료일</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>What is pm2.5</t>
+    <t>Remarks</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>사전검토 필요</t>
+    <r>
+      <t xml:space="preserve">GNB </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사전 검토 필요</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Buying Guide</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buying guide air purifier</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LDM 컨펌 필요</t>
+    <t>Asia</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3869,10 +3878,10 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4108,10 +4117,10 @@
     </row>
     <row r="2" spans="1:8" ht="13.5">
       <c r="A2" s="9" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>1192</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4364,7 +4373,7 @@
     </row>
     <row r="2" spans="1:10" ht="13.5">
       <c r="A2" s="9" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -23250,10 +23259,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F77BCE9D-002C-46A4-837D-945D35BE8D04}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -23261,13 +23270,13 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.5">
+    <row r="2" spans="1:11" ht="13.5">
       <c r="A2" s="7" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B2" s="8"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -23275,7 +23284,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="13.5">
+    <row r="4" spans="1:11" ht="13.5">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -23283,783 +23292,129 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="13.5">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:11" ht="38.25">
+      <c r="A6" s="11" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>1200</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>1202</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>1203</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>1205</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="13.5">
+      <c r="A8" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>1194</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>1195</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>1200</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>1208</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>1209</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="1" t="s">
-        <v>1201</v>
-      </c>
-      <c r="E8" s="11"/>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="13.5">
-      <c r="A9" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1203</v>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="1" t="s">
-        <v>1204</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="1" t="s">
-        <v>1205</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="1" t="s">
-        <v>1206</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>1197</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>1208</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>1209</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="13.5">
-      <c r="A14" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="1" t="s">
-        <v>1201</v>
-      </c>
-      <c r="E14" s="11"/>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="13.5">
-      <c r="A15" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="1" t="s">
-        <v>1204</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="1" t="s">
-        <v>1205</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="1" t="s">
-        <v>1206</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>1198</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>1208</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>1209</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="1" t="s">
-        <v>1201</v>
-      </c>
-      <c r="E20" s="11"/>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="13.5">
-      <c r="A21" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="1" t="s">
-        <v>1204</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="1" t="s">
-        <v>1205</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="1" t="s">
-        <v>1206</v>
-      </c>
-      <c r="G24">
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B19:B24"/>
-    <mergeCell ref="B7:B12"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="D9:D12"/>
-    <mergeCell ref="D15:D18"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="C21:C24"/>
-  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA03A5E1-3159-4BF6-BC00-37DB8C0157CE}">
-  <dimension ref="A1:J24"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="13.5">
-      <c r="A2" s="7" t="s">
-        <v>1191</v>
-      </c>
-      <c r="B2" s="8"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="13.5">
-      <c r="A4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1177</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="13.5">
-      <c r="A6" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>1200</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>1209</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>1201</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>1209</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="13.5">
-      <c r="A9" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>1204</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>1205</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>1206</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>1197</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>1209</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="13.5">
-      <c r="A14" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>1197</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>1201</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>1209</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>1210</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="13.5">
-      <c r="A15" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>1197</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>1197</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>1204</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>1197</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>1205</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>1197</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>1206</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>1198</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>1209</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>1198</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>1201</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>1209</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="13.5">
-      <c r="A21" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>1198</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>1198</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>1204</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>1198</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>1205</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>1198</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>1206</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FABBF0C-ED98-4D26-8E61-5682FF5075DC}">
   <dimension ref="A1:F853"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
@@ -24077,7 +23432,7 @@
     </row>
     <row r="2" spans="1:6" ht="13.5">
       <c r="A2" s="7" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B2" s="1"/>
     </row>

--- a/es/es-global-request.xlsx
+++ b/es/es-global-request.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cnxmail-my.sharepoint.com/personal/sujeong_kang_concentrix_com/Documents/02.Operations/01.BU/01.ES/00.Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="431" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E980710-BD09-4D3D-ACEE-6AB9BC532489}"/>
+  <xr:revisionPtr revIDLastSave="432" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B23ACDC-1C11-4E22-8CE1-75B22C8C216B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LG DUALCOOL AI" sheetId="2" r:id="rId1"/>
@@ -3766,8 +3766,22 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Asia</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">GNB </t>
+      <t xml:space="preserve">GNB LMD </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>검토</t>
     </r>
     <r>
       <rPr>
@@ -3777,12 +3791,8 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>사전 검토 필요</t>
+      <t xml:space="preserve"> 필요</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Asia</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3867,7 +3877,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3878,7 +3888,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -23293,45 +23302,45 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="38.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="10" t="s">
         <v>1196</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>1197</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>1198</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="10" t="s">
         <v>1199</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="10" t="s">
         <v>1200</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="10" t="s">
         <v>1201</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="10" t="s">
         <v>1202</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="10" t="s">
         <v>1203</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="10" t="s">
         <v>1204</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="10" t="s">
         <v>1205</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="10" t="s">
         <v>1206</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="B7" s="10" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>1193</v>
       </c>
       <c r="D7">
@@ -23355,38 +23364,38 @@
     </row>
     <row r="8" spans="1:11" ht="13.5">
       <c r="A8" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>1208</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>1194</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="B9" s="10" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>1195</v>
       </c>
       <c r="D9">

--- a/es/es-global-request.xlsx
+++ b/es/es-global-request.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cnxmail-my.sharepoint.com/personal/sujeong_kang_concentrix_com/Documents/02.Operations/01.BU/01.ES/00.Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="432" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B23ACDC-1C11-4E22-8CE1-75B22C8C216B}"/>
+  <xr:revisionPtr revIDLastSave="438" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7DF17AE-8C17-41EB-94BB-BC762297A5B1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3728,36 +3728,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Buying Guide
-Microsite</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buying Guide
-GNB</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Article
-Clean the air</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Article
-Pets</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Article
-Caring</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Article
-PM2.5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>완료일</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3793,6 +3763,36 @@
       </rPr>
       <t xml:space="preserve"> 필요</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Buying Guide]
+Microsite</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Buying Guide] 
+GNB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Article] 
+Clean the air</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Article] 
+Pets</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Article] 
+Caring</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Article] 
+PM2.5</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -23312,33 +23312,33 @@
         <v>1198</v>
       </c>
       <c r="D6" s="10" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>1206</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>1207</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>1208</v>
+      </c>
+      <c r="J6" s="10" t="s">
         <v>1199</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="K6" s="10" t="s">
         <v>1200</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>1201</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>1202</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>1203</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>1204</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>1205</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>1193</v>
@@ -23364,7 +23364,7 @@
     </row>
     <row r="8" spans="1:11" ht="13.5">
       <c r="A8" s="1" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>1194</v>
@@ -23388,12 +23388,12 @@
         <v>1</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1195</v>

--- a/es/es-global-request.xlsx
+++ b/es/es-global-request.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cnxmail-my.sharepoint.com/personal/sujeong_kang_concentrix_com/Documents/02.Operations/01.BU/01.ES/00.Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="438" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7DF17AE-8C17-41EB-94BB-BC762297A5B1}"/>
+  <xr:revisionPtr revIDLastSave="443" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65AF0C57-61CF-4F86-930F-B58E2028325D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LG DUALCOOL AI" sheetId="2" r:id="rId1"/>
@@ -3653,59 +3653,6 @@
     <t>EASTAFRICA : KE (en)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이번주</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>추가</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이번주 추가</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">BR </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>법인 진행</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>SG-en</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3793,6 +3740,59 @@
   <si>
     <t>[Article] 
 PM2.5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">BR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>법인 진행으로 취소 처리</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번 주 추가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이번 주</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추가</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4126,10 +4126,10 @@
     </row>
     <row r="2" spans="1:8" ht="13.5">
       <c r="A2" s="9" t="s">
-        <v>1191</v>
+        <v>1207</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1192</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4382,7 +4382,7 @@
     </row>
     <row r="2" spans="1:10" ht="13.5">
       <c r="A2" s="9" t="s">
-        <v>1191</v>
+        <v>1207</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -23281,7 +23281,7 @@
     </row>
     <row r="2" spans="1:11" ht="13.5">
       <c r="A2" s="7" t="s">
-        <v>1190</v>
+        <v>1208</v>
       </c>
       <c r="B2" s="8"/>
     </row>
@@ -23303,45 +23303,45 @@
     </row>
     <row r="6" spans="1:11" ht="38.25">
       <c r="A6" s="10" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>1202</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>1203</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>1204</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>1205</v>
+      </c>
+      <c r="J6" s="10" t="s">
         <v>1196</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="K6" s="10" t="s">
         <v>1197</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>1198</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>1203</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>1204</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>1205</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>1206</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>1207</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>1208</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>1199</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>1200</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -23364,10 +23364,10 @@
     </row>
     <row r="8" spans="1:11" ht="13.5">
       <c r="A8" s="1" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -23388,15 +23388,15 @@
         <v>1</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -23441,7 +23441,7 @@
     </row>
     <row r="2" spans="1:6" ht="13.5">
       <c r="A2" s="7" t="s">
-        <v>1190</v>
+        <v>1208</v>
       </c>
       <c r="B2" s="1"/>
     </row>

--- a/es/es-global-request.xlsx
+++ b/es/es-global-request.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cnxmail-my.sharepoint.com/personal/sujeong_kang_concentrix_com/Documents/02.Operations/01.BU/01.ES/00.Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="443" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65AF0C57-61CF-4F86-930F-B58E2028325D}"/>
+  <xr:revisionPtr revIDLastSave="452" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38D759E8-0FB0-4DE3-8AB2-C25D74D2AD7D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1725" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LG DUALCOOL AI" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4719" uniqueCount="1209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4722" uniqueCount="1212">
   <si>
     <t>Title</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -3740,22 +3740,6 @@
   <si>
     <t>[Article] 
 PM2.5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">BR </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>법인 진행으로 취소 처리</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3795,12 +3779,104 @@
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>Jira Ticket</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">BR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>법인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>진행으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>취소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>처리</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://lge-gmc.atlassian.net/browse/LGCOMBU-1677</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3849,6 +3925,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -3873,11 +3957,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3891,10 +3976,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="1" xr:uid="{773E2C1C-49BD-46CA-A578-CF2F386C8F64}"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4107,7 +4194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{208B41D5-0159-4AEB-BF1C-F11A0E733526}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="2" max="2" width="9.140625" customWidth="1"/>
@@ -4126,11 +4213,9 @@
     </row>
     <row r="2" spans="1:8" ht="13.5">
       <c r="A2" s="9" t="s">
-        <v>1207</v>
-      </c>
-      <c r="B2" s="1" t="s">
         <v>1206</v>
       </c>
+      <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="4" t="s">
@@ -4148,136 +4233,104 @@
         <v>34</v>
       </c>
     </row>
+    <row r="5" spans="1:8" ht="13.5">
+      <c r="A5" s="5" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>1211</v>
+      </c>
+    </row>
     <row r="6" spans="1:8" ht="13.5">
       <c r="A6" s="5" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="13.5">
+      <c r="A8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="13.5">
-      <c r="A7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="3">
-        <v>46259</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="13.5">
-      <c r="A8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="3">
-        <v>46212</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="13.5">
       <c r="A9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="3">
-        <v>46219</v>
+        <v>16</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5">
       <c r="A10" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
+      </c>
+      <c r="G10" s="3">
+        <v>46212</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="13.5">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D11" t="s">
-        <v>23</v>
+      <c r="D11" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -4286,7 +4339,7 @@
         <v>12</v>
       </c>
       <c r="G11" s="3">
-        <v>46212</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="13.5">
@@ -4294,36 +4347,36 @@
         <v>30</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="3">
-        <v>46210</v>
+        <v>16</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="13.5">
       <c r="A13" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -4332,34 +4385,83 @@
         <v>12</v>
       </c>
       <c r="G13" s="3">
-        <v>46219</v>
+        <v>46212</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="13.5">
       <c r="A14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="3">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="13.5">
+      <c r="A15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="3">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="13.5">
+      <c r="A16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" t="s">
         <v>20</v>
       </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="3">
         <v>46212</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{1E435120-6749-4FD4-82FC-B22D7569A50B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4382,7 +4484,7 @@
     </row>
     <row r="2" spans="1:10" ht="13.5">
       <c r="A2" s="9" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -23281,7 +23383,7 @@
     </row>
     <row r="2" spans="1:11" ht="13.5">
       <c r="A2" s="7" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B2" s="8"/>
     </row>
@@ -23441,7 +23543,7 @@
     </row>
     <row r="2" spans="1:6" ht="13.5">
       <c r="A2" s="7" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B2" s="1"/>
     </row>

--- a/es/es-global-request.xlsx
+++ b/es/es-global-request.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cnxmail-my.sharepoint.com/personal/sujeong_kang_concentrix_com/Documents/02.Operations/01.BU/01.ES/00.Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="621" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FBBEE11-0183-4026-9024-E927E62928F0}"/>
+  <xr:revisionPtr revIDLastSave="623" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD82E32D-D536-4163-9CA7-639EF2528B7E}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1725" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10187" uniqueCount="2137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10735" uniqueCount="2138">
   <si>
     <t>Title</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -6574,6 +6574,10 @@
   </si>
   <si>
     <t>Completed Date</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>진행중</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -35244,7 +35248,9 @@
       <c r="F371">
         <v>1</v>
       </c>
-      <c r="G371" s="6"/>
+      <c r="G371" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H371" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35268,7 +35274,9 @@
       <c r="F372">
         <v>1</v>
       </c>
-      <c r="G372" s="6"/>
+      <c r="G372" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H372" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35292,7 +35300,9 @@
       <c r="F373">
         <v>1</v>
       </c>
-      <c r="G373" s="6"/>
+      <c r="G373" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H373" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35316,7 +35326,9 @@
       <c r="F374">
         <v>1</v>
       </c>
-      <c r="G374" s="6"/>
+      <c r="G374" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H374" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35340,7 +35352,9 @@
       <c r="F375">
         <v>1</v>
       </c>
-      <c r="G375" s="6"/>
+      <c r="G375" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H375" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35364,7 +35378,9 @@
       <c r="F376">
         <v>1</v>
       </c>
-      <c r="G376" s="6"/>
+      <c r="G376" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H376" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35388,7 +35404,9 @@
       <c r="F377">
         <v>1</v>
       </c>
-      <c r="G377" s="6"/>
+      <c r="G377" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H377" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35412,7 +35430,9 @@
       <c r="F378">
         <v>1</v>
       </c>
-      <c r="G378" s="6"/>
+      <c r="G378" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H378" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35436,7 +35456,9 @@
       <c r="F379">
         <v>1</v>
       </c>
-      <c r="G379" s="6"/>
+      <c r="G379" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H379" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35460,7 +35482,9 @@
       <c r="F380">
         <v>1</v>
       </c>
-      <c r="G380" s="6"/>
+      <c r="G380" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H380" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35484,7 +35508,9 @@
       <c r="F381">
         <v>1</v>
       </c>
-      <c r="G381" s="6"/>
+      <c r="G381" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H381" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35508,7 +35534,9 @@
       <c r="F382">
         <v>1</v>
       </c>
-      <c r="G382" s="6"/>
+      <c r="G382" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H382" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35532,7 +35560,9 @@
       <c r="F383">
         <v>1</v>
       </c>
-      <c r="G383" s="6"/>
+      <c r="G383" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H383" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35556,7 +35586,9 @@
       <c r="F384">
         <v>1</v>
       </c>
-      <c r="G384" s="6"/>
+      <c r="G384" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H384" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35580,7 +35612,9 @@
       <c r="F385">
         <v>1</v>
       </c>
-      <c r="G385" s="6"/>
+      <c r="G385" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H385" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35604,7 +35638,9 @@
       <c r="F386">
         <v>1</v>
       </c>
-      <c r="G386" s="6"/>
+      <c r="G386" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H386" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35628,7 +35664,9 @@
       <c r="F387">
         <v>1</v>
       </c>
-      <c r="G387" s="6"/>
+      <c r="G387" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H387" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35652,7 +35690,9 @@
       <c r="F388">
         <v>1</v>
       </c>
-      <c r="G388" s="6"/>
+      <c r="G388" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H388" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35676,7 +35716,9 @@
       <c r="F389">
         <v>1</v>
       </c>
-      <c r="G389" s="6"/>
+      <c r="G389" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H389" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35700,7 +35742,9 @@
       <c r="F390">
         <v>1</v>
       </c>
-      <c r="G390" s="6"/>
+      <c r="G390" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H390" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35724,7 +35768,9 @@
       <c r="F391">
         <v>1</v>
       </c>
-      <c r="G391" s="6"/>
+      <c r="G391" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H391" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35748,7 +35794,9 @@
       <c r="F392">
         <v>1</v>
       </c>
-      <c r="G392" s="6"/>
+      <c r="G392" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H392" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35772,7 +35820,9 @@
       <c r="F393">
         <v>1</v>
       </c>
-      <c r="G393" s="6"/>
+      <c r="G393" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H393" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35796,7 +35846,9 @@
       <c r="F394">
         <v>1</v>
       </c>
-      <c r="G394" s="6"/>
+      <c r="G394" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H394" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35820,7 +35872,9 @@
       <c r="F395">
         <v>1</v>
       </c>
-      <c r="G395" s="6"/>
+      <c r="G395" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H395" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35844,7 +35898,9 @@
       <c r="F396">
         <v>1</v>
       </c>
-      <c r="G396" s="6"/>
+      <c r="G396" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H396" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35868,7 +35924,9 @@
       <c r="F397">
         <v>1</v>
       </c>
-      <c r="G397" s="6"/>
+      <c r="G397" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H397" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35892,7 +35950,9 @@
       <c r="F398">
         <v>1</v>
       </c>
-      <c r="G398" s="6"/>
+      <c r="G398" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H398" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35916,7 +35976,9 @@
       <c r="F399">
         <v>1</v>
       </c>
-      <c r="G399" s="6"/>
+      <c r="G399" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H399" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35940,7 +36002,9 @@
       <c r="F400">
         <v>1</v>
       </c>
-      <c r="G400" s="6"/>
+      <c r="G400" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H400" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35964,7 +36028,9 @@
       <c r="F401">
         <v>1</v>
       </c>
-      <c r="G401" s="6"/>
+      <c r="G401" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H401" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35988,7 +36054,9 @@
       <c r="F402">
         <v>1</v>
       </c>
-      <c r="G402" s="6"/>
+      <c r="G402" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H402" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36012,7 +36080,9 @@
       <c r="F403">
         <v>1</v>
       </c>
-      <c r="G403" s="6"/>
+      <c r="G403" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H403" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36036,7 +36106,9 @@
       <c r="F404">
         <v>1</v>
       </c>
-      <c r="G404" s="6"/>
+      <c r="G404" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H404" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36060,7 +36132,9 @@
       <c r="F405">
         <v>1</v>
       </c>
-      <c r="G405" s="6"/>
+      <c r="G405" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H405" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36084,7 +36158,9 @@
       <c r="F406">
         <v>1</v>
       </c>
-      <c r="G406" s="6"/>
+      <c r="G406" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H406" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36108,7 +36184,9 @@
       <c r="F407">
         <v>1</v>
       </c>
-      <c r="G407" s="6"/>
+      <c r="G407" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H407" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36132,7 +36210,9 @@
       <c r="F408">
         <v>1</v>
       </c>
-      <c r="G408" s="6"/>
+      <c r="G408" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H408" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36156,7 +36236,9 @@
       <c r="F409">
         <v>1</v>
       </c>
-      <c r="G409" s="6"/>
+      <c r="G409" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H409" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36180,7 +36262,9 @@
       <c r="F410">
         <v>1</v>
       </c>
-      <c r="G410" s="6"/>
+      <c r="G410" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H410" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36204,7 +36288,9 @@
       <c r="F411">
         <v>1</v>
       </c>
-      <c r="G411" s="6"/>
+      <c r="G411" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H411" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36228,7 +36314,9 @@
       <c r="F412">
         <v>1</v>
       </c>
-      <c r="G412" s="6"/>
+      <c r="G412" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H412" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36252,7 +36340,9 @@
       <c r="F413">
         <v>1</v>
       </c>
-      <c r="G413" s="6"/>
+      <c r="G413" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H413" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36276,7 +36366,9 @@
       <c r="F414">
         <v>1</v>
       </c>
-      <c r="G414" s="6"/>
+      <c r="G414" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H414" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36300,7 +36392,9 @@
       <c r="F415">
         <v>1</v>
       </c>
-      <c r="G415" s="6"/>
+      <c r="G415" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H415" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36324,7 +36418,9 @@
       <c r="F416">
         <v>1</v>
       </c>
-      <c r="G416" s="6"/>
+      <c r="G416" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H416" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36348,7 +36444,9 @@
       <c r="F417">
         <v>1</v>
       </c>
-      <c r="G417" s="6"/>
+      <c r="G417" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H417" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36372,7 +36470,9 @@
       <c r="F418">
         <v>1</v>
       </c>
-      <c r="G418" s="6"/>
+      <c r="G418" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H418" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36396,7 +36496,9 @@
       <c r="F419">
         <v>1</v>
       </c>
-      <c r="G419" s="6"/>
+      <c r="G419" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H419" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36420,7 +36522,9 @@
       <c r="F420">
         <v>1</v>
       </c>
-      <c r="G420" s="6"/>
+      <c r="G420" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H420" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36444,7 +36548,9 @@
       <c r="F421">
         <v>1</v>
       </c>
-      <c r="G421" s="6"/>
+      <c r="G421" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H421" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36468,7 +36574,9 @@
       <c r="F422">
         <v>1</v>
       </c>
-      <c r="G422" s="6"/>
+      <c r="G422" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H422" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36492,7 +36600,9 @@
       <c r="F423">
         <v>1</v>
       </c>
-      <c r="G423" s="6"/>
+      <c r="G423" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H423" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36516,7 +36626,9 @@
       <c r="F424">
         <v>1</v>
       </c>
-      <c r="G424" s="6"/>
+      <c r="G424" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H424" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36540,7 +36652,9 @@
       <c r="F425">
         <v>1</v>
       </c>
-      <c r="G425" s="6"/>
+      <c r="G425" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H425" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36564,7 +36678,9 @@
       <c r="F426">
         <v>1</v>
       </c>
-      <c r="G426" s="6"/>
+      <c r="G426" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H426" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36588,7 +36704,9 @@
       <c r="F427">
         <v>1</v>
       </c>
-      <c r="G427" s="6"/>
+      <c r="G427" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H427" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36612,7 +36730,9 @@
       <c r="F428">
         <v>1</v>
       </c>
-      <c r="G428" s="6"/>
+      <c r="G428" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H428" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36636,7 +36756,9 @@
       <c r="F429">
         <v>1</v>
       </c>
-      <c r="G429" s="6"/>
+      <c r="G429" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H429" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36660,7 +36782,9 @@
       <c r="F430">
         <v>1</v>
       </c>
-      <c r="G430" s="6"/>
+      <c r="G430" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H430" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36684,7 +36808,9 @@
       <c r="F431">
         <v>1</v>
       </c>
-      <c r="G431" s="6"/>
+      <c r="G431" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H431" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36708,7 +36834,9 @@
       <c r="F432">
         <v>1</v>
       </c>
-      <c r="G432" s="6"/>
+      <c r="G432" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H432" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36732,7 +36860,9 @@
       <c r="F433">
         <v>1</v>
       </c>
-      <c r="G433" s="6"/>
+      <c r="G433" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H433" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36756,7 +36886,9 @@
       <c r="F434">
         <v>1</v>
       </c>
-      <c r="G434" s="6"/>
+      <c r="G434" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H434" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36780,7 +36912,9 @@
       <c r="F435">
         <v>1</v>
       </c>
-      <c r="G435" s="6"/>
+      <c r="G435" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H435" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36804,7 +36938,9 @@
       <c r="F436">
         <v>1</v>
       </c>
-      <c r="G436" s="6"/>
+      <c r="G436" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H436" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36828,7 +36964,9 @@
       <c r="F437">
         <v>1</v>
       </c>
-      <c r="G437" s="6"/>
+      <c r="G437" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H437" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36852,7 +36990,9 @@
       <c r="F438">
         <v>1</v>
       </c>
-      <c r="G438" s="6"/>
+      <c r="G438" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H438" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36876,7 +37016,9 @@
       <c r="F439">
         <v>1</v>
       </c>
-      <c r="G439" s="6"/>
+      <c r="G439" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H439" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36900,7 +37042,9 @@
       <c r="F440">
         <v>1</v>
       </c>
-      <c r="G440" s="6"/>
+      <c r="G440" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H440" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36924,7 +37068,9 @@
       <c r="F441">
         <v>1</v>
       </c>
-      <c r="G441" s="6"/>
+      <c r="G441" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H441" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36948,7 +37094,9 @@
       <c r="F442">
         <v>1</v>
       </c>
-      <c r="G442" s="6"/>
+      <c r="G442" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H442" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36972,7 +37120,9 @@
       <c r="F443">
         <v>1</v>
       </c>
-      <c r="G443" s="6"/>
+      <c r="G443" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H443" s="6" t="s">
         <v>2132</v>
       </c>
@@ -36996,7 +37146,9 @@
       <c r="F444">
         <v>1</v>
       </c>
-      <c r="G444" s="6"/>
+      <c r="G444" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H444" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37020,7 +37172,9 @@
       <c r="F445">
         <v>1</v>
       </c>
-      <c r="G445" s="6"/>
+      <c r="G445" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H445" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37044,7 +37198,9 @@
       <c r="F446">
         <v>1</v>
       </c>
-      <c r="G446" s="6"/>
+      <c r="G446" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H446" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37068,7 +37224,9 @@
       <c r="F447">
         <v>1</v>
       </c>
-      <c r="G447" s="6"/>
+      <c r="G447" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H447" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37092,7 +37250,9 @@
       <c r="F448">
         <v>1</v>
       </c>
-      <c r="G448" s="6"/>
+      <c r="G448" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H448" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37116,7 +37276,9 @@
       <c r="F449">
         <v>1</v>
       </c>
-      <c r="G449" s="6"/>
+      <c r="G449" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H449" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37140,7 +37302,9 @@
       <c r="F450">
         <v>1</v>
       </c>
-      <c r="G450" s="6"/>
+      <c r="G450" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H450" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37164,7 +37328,9 @@
       <c r="F451">
         <v>1</v>
       </c>
-      <c r="G451" s="6"/>
+      <c r="G451" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H451" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37188,7 +37354,9 @@
       <c r="F452">
         <v>1</v>
       </c>
-      <c r="G452" s="6"/>
+      <c r="G452" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H452" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37212,7 +37380,9 @@
       <c r="F453">
         <v>1</v>
       </c>
-      <c r="G453" s="6"/>
+      <c r="G453" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H453" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37236,7 +37406,9 @@
       <c r="F454">
         <v>1</v>
       </c>
-      <c r="G454" s="6"/>
+      <c r="G454" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H454" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37260,7 +37432,9 @@
       <c r="F455">
         <v>1</v>
       </c>
-      <c r="G455" s="6"/>
+      <c r="G455" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H455" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37284,7 +37458,9 @@
       <c r="F456">
         <v>1</v>
       </c>
-      <c r="G456" s="6"/>
+      <c r="G456" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H456" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37308,7 +37484,9 @@
       <c r="F457">
         <v>1</v>
       </c>
-      <c r="G457" s="6"/>
+      <c r="G457" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H457" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37332,7 +37510,9 @@
       <c r="F458">
         <v>1</v>
       </c>
-      <c r="G458" s="6"/>
+      <c r="G458" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H458" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37356,7 +37536,9 @@
       <c r="F459">
         <v>1</v>
       </c>
-      <c r="G459" s="6"/>
+      <c r="G459" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H459" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37380,7 +37562,9 @@
       <c r="F460">
         <v>1</v>
       </c>
-      <c r="G460" s="6"/>
+      <c r="G460" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H460" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37404,7 +37588,9 @@
       <c r="F461">
         <v>1</v>
       </c>
-      <c r="G461" s="6"/>
+      <c r="G461" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H461" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37428,7 +37614,9 @@
       <c r="F462">
         <v>1</v>
       </c>
-      <c r="G462" s="6"/>
+      <c r="G462" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H462" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37452,7 +37640,9 @@
       <c r="F463">
         <v>1</v>
       </c>
-      <c r="G463" s="6"/>
+      <c r="G463" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H463" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37476,7 +37666,9 @@
       <c r="F464">
         <v>1</v>
       </c>
-      <c r="G464" s="6"/>
+      <c r="G464" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H464" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37500,7 +37692,9 @@
       <c r="F465">
         <v>1</v>
       </c>
-      <c r="G465" s="6"/>
+      <c r="G465" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H465" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37524,7 +37718,9 @@
       <c r="F466">
         <v>1</v>
       </c>
-      <c r="G466" s="6"/>
+      <c r="G466" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H466" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37548,7 +37744,9 @@
       <c r="F467">
         <v>1</v>
       </c>
-      <c r="G467" s="6"/>
+      <c r="G467" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H467" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37572,7 +37770,9 @@
       <c r="F468">
         <v>1</v>
       </c>
-      <c r="G468" s="6"/>
+      <c r="G468" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H468" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37596,7 +37796,9 @@
       <c r="F469">
         <v>1</v>
       </c>
-      <c r="G469" s="6"/>
+      <c r="G469" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H469" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37620,7 +37822,9 @@
       <c r="F470">
         <v>1</v>
       </c>
-      <c r="G470" s="6"/>
+      <c r="G470" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H470" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37644,7 +37848,9 @@
       <c r="F471">
         <v>1</v>
       </c>
-      <c r="G471" s="6"/>
+      <c r="G471" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H471" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37668,7 +37874,9 @@
       <c r="F472">
         <v>1</v>
       </c>
-      <c r="G472" s="6"/>
+      <c r="G472" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H472" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37692,7 +37900,9 @@
       <c r="F473">
         <v>1</v>
       </c>
-      <c r="G473" s="6"/>
+      <c r="G473" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H473" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37716,7 +37926,9 @@
       <c r="F474">
         <v>1</v>
       </c>
-      <c r="G474" s="6"/>
+      <c r="G474" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H474" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37740,7 +37952,9 @@
       <c r="F475">
         <v>1</v>
       </c>
-      <c r="G475" s="6"/>
+      <c r="G475" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H475" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37764,7 +37978,9 @@
       <c r="F476">
         <v>1</v>
       </c>
-      <c r="G476" s="6"/>
+      <c r="G476" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H476" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37788,7 +38004,9 @@
       <c r="F477">
         <v>1</v>
       </c>
-      <c r="G477" s="6"/>
+      <c r="G477" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H477" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37812,7 +38030,9 @@
       <c r="F478">
         <v>1</v>
       </c>
-      <c r="G478" s="6"/>
+      <c r="G478" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H478" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37836,7 +38056,9 @@
       <c r="F479">
         <v>1</v>
       </c>
-      <c r="G479" s="6"/>
+      <c r="G479" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H479" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37860,7 +38082,9 @@
       <c r="F480">
         <v>1</v>
       </c>
-      <c r="G480" s="6"/>
+      <c r="G480" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H480" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37884,7 +38108,9 @@
       <c r="F481">
         <v>1</v>
       </c>
-      <c r="G481" s="6"/>
+      <c r="G481" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H481" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37908,7 +38134,9 @@
       <c r="F482">
         <v>1</v>
       </c>
-      <c r="G482" s="6"/>
+      <c r="G482" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H482" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37932,7 +38160,9 @@
       <c r="F483">
         <v>1</v>
       </c>
-      <c r="G483" s="6"/>
+      <c r="G483" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H483" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37956,7 +38186,9 @@
       <c r="F484">
         <v>1</v>
       </c>
-      <c r="G484" s="6"/>
+      <c r="G484" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H484" s="6" t="s">
         <v>2132</v>
       </c>
@@ -37980,7 +38212,9 @@
       <c r="F485">
         <v>1</v>
       </c>
-      <c r="G485" s="6"/>
+      <c r="G485" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H485" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38004,7 +38238,9 @@
       <c r="F486">
         <v>1</v>
       </c>
-      <c r="G486" s="6"/>
+      <c r="G486" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H486" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38028,7 +38264,9 @@
       <c r="F487">
         <v>1</v>
       </c>
-      <c r="G487" s="6"/>
+      <c r="G487" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H487" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38052,7 +38290,9 @@
       <c r="F488">
         <v>1</v>
       </c>
-      <c r="G488" s="6"/>
+      <c r="G488" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H488" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38076,7 +38316,9 @@
       <c r="F489">
         <v>1</v>
       </c>
-      <c r="G489" s="6"/>
+      <c r="G489" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H489" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38100,7 +38342,9 @@
       <c r="F490">
         <v>1</v>
       </c>
-      <c r="G490" s="6"/>
+      <c r="G490" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H490" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38124,7 +38368,9 @@
       <c r="F491">
         <v>1</v>
       </c>
-      <c r="G491" s="6"/>
+      <c r="G491" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H491" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38148,7 +38394,9 @@
       <c r="F492">
         <v>1</v>
       </c>
-      <c r="G492" s="6"/>
+      <c r="G492" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H492" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38172,7 +38420,9 @@
       <c r="F493">
         <v>1</v>
       </c>
-      <c r="G493" s="6"/>
+      <c r="G493" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H493" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38196,7 +38446,9 @@
       <c r="F494">
         <v>1</v>
       </c>
-      <c r="G494" s="6"/>
+      <c r="G494" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H494" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38220,7 +38472,9 @@
       <c r="F495">
         <v>1</v>
       </c>
-      <c r="G495" s="6"/>
+      <c r="G495" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H495" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38244,7 +38498,9 @@
       <c r="F496">
         <v>1</v>
       </c>
-      <c r="G496" s="6"/>
+      <c r="G496" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H496" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38268,7 +38524,9 @@
       <c r="F497">
         <v>1</v>
       </c>
-      <c r="G497" s="6"/>
+      <c r="G497" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H497" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38292,7 +38550,9 @@
       <c r="F498">
         <v>1</v>
       </c>
-      <c r="G498" s="6"/>
+      <c r="G498" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H498" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38316,7 +38576,9 @@
       <c r="F499">
         <v>1</v>
       </c>
-      <c r="G499" s="6"/>
+      <c r="G499" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H499" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38340,7 +38602,9 @@
       <c r="F500">
         <v>1</v>
       </c>
-      <c r="G500" s="6"/>
+      <c r="G500" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H500" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38364,7 +38628,9 @@
       <c r="F501">
         <v>1</v>
       </c>
-      <c r="G501" s="6"/>
+      <c r="G501" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H501" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38388,7 +38654,9 @@
       <c r="F502">
         <v>1</v>
       </c>
-      <c r="G502" s="6"/>
+      <c r="G502" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H502" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38412,7 +38680,9 @@
       <c r="F503">
         <v>1</v>
       </c>
-      <c r="G503" s="6"/>
+      <c r="G503" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H503" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38436,7 +38706,9 @@
       <c r="F504">
         <v>1</v>
       </c>
-      <c r="G504" s="6"/>
+      <c r="G504" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H504" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38460,7 +38732,9 @@
       <c r="F505">
         <v>1</v>
       </c>
-      <c r="G505" s="6"/>
+      <c r="G505" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H505" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38484,7 +38758,9 @@
       <c r="F506">
         <v>1</v>
       </c>
-      <c r="G506" s="6"/>
+      <c r="G506" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H506" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38508,7 +38784,9 @@
       <c r="F507">
         <v>1</v>
       </c>
-      <c r="G507" s="6"/>
+      <c r="G507" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H507" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38532,7 +38810,9 @@
       <c r="F508">
         <v>1</v>
       </c>
-      <c r="G508" s="6"/>
+      <c r="G508" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H508" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38556,7 +38836,9 @@
       <c r="F509">
         <v>1</v>
       </c>
-      <c r="G509" s="6"/>
+      <c r="G509" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H509" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38580,7 +38862,9 @@
       <c r="F510">
         <v>1</v>
       </c>
-      <c r="G510" s="6"/>
+      <c r="G510" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H510" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38604,7 +38888,9 @@
       <c r="F511">
         <v>1</v>
       </c>
-      <c r="G511" s="6"/>
+      <c r="G511" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H511" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38628,7 +38914,9 @@
       <c r="F512">
         <v>1</v>
       </c>
-      <c r="G512" s="6"/>
+      <c r="G512" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H512" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38652,7 +38940,9 @@
       <c r="F513">
         <v>1</v>
       </c>
-      <c r="G513" s="6"/>
+      <c r="G513" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H513" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38676,7 +38966,9 @@
       <c r="F514">
         <v>1</v>
       </c>
-      <c r="G514" s="6"/>
+      <c r="G514" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H514" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38700,7 +38992,9 @@
       <c r="F515">
         <v>1</v>
       </c>
-      <c r="G515" s="6"/>
+      <c r="G515" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H515" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38724,7 +39018,9 @@
       <c r="F516">
         <v>1</v>
       </c>
-      <c r="G516" s="6"/>
+      <c r="G516" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H516" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38748,7 +39044,9 @@
       <c r="F517">
         <v>1</v>
       </c>
-      <c r="G517" s="6"/>
+      <c r="G517" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H517" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38772,7 +39070,9 @@
       <c r="F518">
         <v>1</v>
       </c>
-      <c r="G518" s="6"/>
+      <c r="G518" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H518" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38796,7 +39096,9 @@
       <c r="F519">
         <v>1</v>
       </c>
-      <c r="G519" s="6"/>
+      <c r="G519" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H519" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38820,7 +39122,9 @@
       <c r="F520">
         <v>1</v>
       </c>
-      <c r="G520" s="6"/>
+      <c r="G520" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H520" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38844,7 +39148,9 @@
       <c r="F521">
         <v>1</v>
       </c>
-      <c r="G521" s="6"/>
+      <c r="G521" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H521" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38868,7 +39174,9 @@
       <c r="F522">
         <v>1</v>
       </c>
-      <c r="G522" s="6"/>
+      <c r="G522" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H522" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38892,7 +39200,9 @@
       <c r="F523">
         <v>1</v>
       </c>
-      <c r="G523" s="6"/>
+      <c r="G523" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H523" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38916,7 +39226,9 @@
       <c r="F524">
         <v>1</v>
       </c>
-      <c r="G524" s="6"/>
+      <c r="G524" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H524" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38940,7 +39252,9 @@
       <c r="F525">
         <v>1</v>
       </c>
-      <c r="G525" s="6"/>
+      <c r="G525" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H525" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38964,7 +39278,9 @@
       <c r="F526">
         <v>1</v>
       </c>
-      <c r="G526" s="6"/>
+      <c r="G526" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H526" s="6" t="s">
         <v>2132</v>
       </c>
@@ -38988,7 +39304,9 @@
       <c r="F527">
         <v>1</v>
       </c>
-      <c r="G527" s="6"/>
+      <c r="G527" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H527" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39012,7 +39330,9 @@
       <c r="F528">
         <v>1</v>
       </c>
-      <c r="G528" s="6"/>
+      <c r="G528" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H528" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39036,7 +39356,9 @@
       <c r="F529">
         <v>1</v>
       </c>
-      <c r="G529" s="6"/>
+      <c r="G529" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H529" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39060,7 +39382,9 @@
       <c r="F530">
         <v>1</v>
       </c>
-      <c r="G530" s="6"/>
+      <c r="G530" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H530" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39084,7 +39408,9 @@
       <c r="F531">
         <v>1</v>
       </c>
-      <c r="G531" s="6"/>
+      <c r="G531" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H531" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39108,7 +39434,9 @@
       <c r="F532">
         <v>1</v>
       </c>
-      <c r="G532" s="6"/>
+      <c r="G532" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H532" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39132,7 +39460,9 @@
       <c r="F533">
         <v>1</v>
       </c>
-      <c r="G533" s="6"/>
+      <c r="G533" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H533" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39156,7 +39486,9 @@
       <c r="F534">
         <v>1</v>
       </c>
-      <c r="G534" s="6"/>
+      <c r="G534" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H534" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39180,7 +39512,9 @@
       <c r="F535">
         <v>1</v>
       </c>
-      <c r="G535" s="6"/>
+      <c r="G535" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H535" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39204,7 +39538,9 @@
       <c r="F536">
         <v>1</v>
       </c>
-      <c r="G536" s="6"/>
+      <c r="G536" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H536" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39228,7 +39564,9 @@
       <c r="F537">
         <v>1</v>
       </c>
-      <c r="G537" s="6"/>
+      <c r="G537" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H537" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39252,7 +39590,9 @@
       <c r="F538">
         <v>1</v>
       </c>
-      <c r="G538" s="6"/>
+      <c r="G538" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H538" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39276,7 +39616,9 @@
       <c r="F539">
         <v>1</v>
       </c>
-      <c r="G539" s="6"/>
+      <c r="G539" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H539" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39300,7 +39642,9 @@
       <c r="F540">
         <v>1</v>
       </c>
-      <c r="G540" s="6"/>
+      <c r="G540" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H540" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39324,7 +39668,9 @@
       <c r="F541">
         <v>1</v>
       </c>
-      <c r="G541" s="6"/>
+      <c r="G541" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H541" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39348,7 +39694,9 @@
       <c r="F542">
         <v>1</v>
       </c>
-      <c r="G542" s="6"/>
+      <c r="G542" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H542" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39372,7 +39720,9 @@
       <c r="F543">
         <v>1</v>
       </c>
-      <c r="G543" s="6"/>
+      <c r="G543" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H543" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39396,7 +39746,9 @@
       <c r="F544">
         <v>1</v>
       </c>
-      <c r="G544" s="6"/>
+      <c r="G544" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H544" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39420,7 +39772,9 @@
       <c r="F545">
         <v>1</v>
       </c>
-      <c r="G545" s="6"/>
+      <c r="G545" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H545" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39444,7 +39798,9 @@
       <c r="F546">
         <v>1</v>
       </c>
-      <c r="G546" s="6"/>
+      <c r="G546" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H546" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39468,7 +39824,9 @@
       <c r="F547">
         <v>1</v>
       </c>
-      <c r="G547" s="6"/>
+      <c r="G547" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H547" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39492,7 +39850,9 @@
       <c r="F548">
         <v>1</v>
       </c>
-      <c r="G548" s="6"/>
+      <c r="G548" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H548" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39516,7 +39876,9 @@
       <c r="F549">
         <v>1</v>
       </c>
-      <c r="G549" s="6"/>
+      <c r="G549" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H549" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39540,7 +39902,9 @@
       <c r="F550">
         <v>1</v>
       </c>
-      <c r="G550" s="6"/>
+      <c r="G550" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H550" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39564,7 +39928,9 @@
       <c r="F551">
         <v>1</v>
       </c>
-      <c r="G551" s="6"/>
+      <c r="G551" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H551" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39588,7 +39954,9 @@
       <c r="F552">
         <v>1</v>
       </c>
-      <c r="G552" s="6"/>
+      <c r="G552" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H552" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39612,7 +39980,9 @@
       <c r="F553">
         <v>1</v>
       </c>
-      <c r="G553" s="6"/>
+      <c r="G553" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H553" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39636,7 +40006,9 @@
       <c r="F554">
         <v>1</v>
       </c>
-      <c r="G554" s="6"/>
+      <c r="G554" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H554" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39660,7 +40032,9 @@
       <c r="F555">
         <v>1</v>
       </c>
-      <c r="G555" s="6"/>
+      <c r="G555" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H555" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39684,7 +40058,9 @@
       <c r="F556">
         <v>1</v>
       </c>
-      <c r="G556" s="6"/>
+      <c r="G556" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H556" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39708,7 +40084,9 @@
       <c r="F557">
         <v>1</v>
       </c>
-      <c r="G557" s="6"/>
+      <c r="G557" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H557" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39732,7 +40110,9 @@
       <c r="F558">
         <v>1</v>
       </c>
-      <c r="G558" s="6"/>
+      <c r="G558" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H558" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39756,7 +40136,9 @@
       <c r="F559">
         <v>1</v>
       </c>
-      <c r="G559" s="6"/>
+      <c r="G559" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H559" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39780,7 +40162,9 @@
       <c r="F560">
         <v>1</v>
       </c>
-      <c r="G560" s="6"/>
+      <c r="G560" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H560" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39804,7 +40188,9 @@
       <c r="F561">
         <v>1</v>
       </c>
-      <c r="G561" s="6"/>
+      <c r="G561" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H561" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39828,7 +40214,9 @@
       <c r="F562">
         <v>1</v>
       </c>
-      <c r="G562" s="6"/>
+      <c r="G562" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H562" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39852,7 +40240,9 @@
       <c r="F563">
         <v>1</v>
       </c>
-      <c r="G563" s="6"/>
+      <c r="G563" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H563" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39876,7 +40266,9 @@
       <c r="F564">
         <v>1</v>
       </c>
-      <c r="G564" s="6"/>
+      <c r="G564" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H564" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39900,7 +40292,9 @@
       <c r="F565">
         <v>1</v>
       </c>
-      <c r="G565" s="6"/>
+      <c r="G565" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H565" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39924,7 +40318,9 @@
       <c r="F566">
         <v>1</v>
       </c>
-      <c r="G566" s="6"/>
+      <c r="G566" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H566" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39948,7 +40344,9 @@
       <c r="F567">
         <v>1</v>
       </c>
-      <c r="G567" s="6"/>
+      <c r="G567" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H567" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39972,7 +40370,9 @@
       <c r="F568">
         <v>1</v>
       </c>
-      <c r="G568" s="6"/>
+      <c r="G568" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H568" s="6" t="s">
         <v>2132</v>
       </c>
@@ -39996,7 +40396,9 @@
       <c r="F569">
         <v>1</v>
       </c>
-      <c r="G569" s="6"/>
+      <c r="G569" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H569" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40020,7 +40422,9 @@
       <c r="F570">
         <v>1</v>
       </c>
-      <c r="G570" s="6"/>
+      <c r="G570" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H570" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40044,7 +40448,9 @@
       <c r="F571">
         <v>1</v>
       </c>
-      <c r="G571" s="6"/>
+      <c r="G571" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H571" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40068,7 +40474,9 @@
       <c r="F572">
         <v>1</v>
       </c>
-      <c r="G572" s="6"/>
+      <c r="G572" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H572" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40092,7 +40500,9 @@
       <c r="F573">
         <v>1</v>
       </c>
-      <c r="G573" s="6"/>
+      <c r="G573" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H573" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40116,7 +40526,9 @@
       <c r="F574">
         <v>1</v>
       </c>
-      <c r="G574" s="6"/>
+      <c r="G574" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H574" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40140,7 +40552,9 @@
       <c r="F575">
         <v>1</v>
       </c>
-      <c r="G575" s="6"/>
+      <c r="G575" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H575" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40164,7 +40578,9 @@
       <c r="F576">
         <v>1</v>
       </c>
-      <c r="G576" s="6"/>
+      <c r="G576" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H576" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40188,7 +40604,9 @@
       <c r="F577">
         <v>1</v>
       </c>
-      <c r="G577" s="6"/>
+      <c r="G577" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H577" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40212,7 +40630,9 @@
       <c r="F578">
         <v>1</v>
       </c>
-      <c r="G578" s="6"/>
+      <c r="G578" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H578" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40236,7 +40656,9 @@
       <c r="F579">
         <v>1</v>
       </c>
-      <c r="G579" s="6"/>
+      <c r="G579" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H579" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40260,7 +40682,9 @@
       <c r="F580">
         <v>1</v>
       </c>
-      <c r="G580" s="6"/>
+      <c r="G580" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H580" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40284,7 +40708,9 @@
       <c r="F581">
         <v>1</v>
       </c>
-      <c r="G581" s="6"/>
+      <c r="G581" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H581" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40308,7 +40734,9 @@
       <c r="F582">
         <v>1</v>
       </c>
-      <c r="G582" s="6"/>
+      <c r="G582" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H582" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40332,7 +40760,9 @@
       <c r="F583">
         <v>1</v>
       </c>
-      <c r="G583" s="6"/>
+      <c r="G583" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H583" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40356,7 +40786,9 @@
       <c r="F584">
         <v>1</v>
       </c>
-      <c r="G584" s="6"/>
+      <c r="G584" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H584" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40380,7 +40812,9 @@
       <c r="F585">
         <v>1</v>
       </c>
-      <c r="G585" s="6"/>
+      <c r="G585" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H585" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40404,7 +40838,9 @@
       <c r="F586">
         <v>1</v>
       </c>
-      <c r="G586" s="6"/>
+      <c r="G586" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H586" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40428,7 +40864,9 @@
       <c r="F587">
         <v>1</v>
       </c>
-      <c r="G587" s="6"/>
+      <c r="G587" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H587" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40452,7 +40890,9 @@
       <c r="F588">
         <v>1</v>
       </c>
-      <c r="G588" s="6"/>
+      <c r="G588" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H588" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40476,7 +40916,9 @@
       <c r="F589">
         <v>1</v>
       </c>
-      <c r="G589" s="6"/>
+      <c r="G589" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H589" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40500,7 +40942,9 @@
       <c r="F590">
         <v>1</v>
       </c>
-      <c r="G590" s="6"/>
+      <c r="G590" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H590" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40524,7 +40968,9 @@
       <c r="F591">
         <v>1</v>
       </c>
-      <c r="G591" s="6"/>
+      <c r="G591" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H591" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40548,7 +40994,9 @@
       <c r="F592">
         <v>1</v>
       </c>
-      <c r="G592" s="6"/>
+      <c r="G592" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H592" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40572,7 +41020,9 @@
       <c r="F593">
         <v>1</v>
       </c>
-      <c r="G593" s="6"/>
+      <c r="G593" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H593" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40596,7 +41046,9 @@
       <c r="F594">
         <v>1</v>
       </c>
-      <c r="G594" s="6"/>
+      <c r="G594" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H594" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40620,7 +41072,9 @@
       <c r="F595">
         <v>1</v>
       </c>
-      <c r="G595" s="6"/>
+      <c r="G595" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H595" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40644,7 +41098,9 @@
       <c r="F596">
         <v>1</v>
       </c>
-      <c r="G596" s="6"/>
+      <c r="G596" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H596" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40668,7 +41124,9 @@
       <c r="F597">
         <v>1</v>
       </c>
-      <c r="G597" s="6"/>
+      <c r="G597" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H597" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40692,7 +41150,9 @@
       <c r="F598">
         <v>1</v>
       </c>
-      <c r="G598" s="6"/>
+      <c r="G598" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H598" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40716,7 +41176,9 @@
       <c r="F599">
         <v>1</v>
       </c>
-      <c r="G599" s="6"/>
+      <c r="G599" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H599" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40740,7 +41202,9 @@
       <c r="F600">
         <v>1</v>
       </c>
-      <c r="G600" s="6"/>
+      <c r="G600" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H600" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40764,7 +41228,9 @@
       <c r="F601">
         <v>1</v>
       </c>
-      <c r="G601" s="6"/>
+      <c r="G601" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H601" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40788,7 +41254,9 @@
       <c r="F602">
         <v>1</v>
       </c>
-      <c r="G602" s="6"/>
+      <c r="G602" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H602" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40812,7 +41280,9 @@
       <c r="F603">
         <v>1</v>
       </c>
-      <c r="G603" s="6"/>
+      <c r="G603" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H603" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40836,7 +41306,9 @@
       <c r="F604">
         <v>1</v>
       </c>
-      <c r="G604" s="6"/>
+      <c r="G604" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H604" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40860,7 +41332,9 @@
       <c r="F605">
         <v>1</v>
       </c>
-      <c r="G605" s="6"/>
+      <c r="G605" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H605" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40884,7 +41358,9 @@
       <c r="F606">
         <v>1</v>
       </c>
-      <c r="G606" s="6"/>
+      <c r="G606" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H606" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40908,7 +41384,9 @@
       <c r="F607">
         <v>1</v>
       </c>
-      <c r="G607" s="6"/>
+      <c r="G607" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H607" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40932,7 +41410,9 @@
       <c r="F608">
         <v>1</v>
       </c>
-      <c r="G608" s="6"/>
+      <c r="G608" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H608" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40956,7 +41436,9 @@
       <c r="F609">
         <v>1</v>
       </c>
-      <c r="G609" s="6"/>
+      <c r="G609" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H609" s="6" t="s">
         <v>2132</v>
       </c>
@@ -40980,7 +41462,9 @@
       <c r="F610">
         <v>1</v>
       </c>
-      <c r="G610" s="6"/>
+      <c r="G610" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H610" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41004,7 +41488,9 @@
       <c r="F611">
         <v>1</v>
       </c>
-      <c r="G611" s="6"/>
+      <c r="G611" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H611" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41028,7 +41514,9 @@
       <c r="F612">
         <v>1</v>
       </c>
-      <c r="G612" s="6"/>
+      <c r="G612" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H612" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41052,7 +41540,9 @@
       <c r="F613">
         <v>1</v>
       </c>
-      <c r="G613" s="6"/>
+      <c r="G613" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H613" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41076,7 +41566,9 @@
       <c r="F614">
         <v>1</v>
       </c>
-      <c r="G614" s="6"/>
+      <c r="G614" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H614" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41100,7 +41592,9 @@
       <c r="F615">
         <v>1</v>
       </c>
-      <c r="G615" s="6"/>
+      <c r="G615" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H615" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41124,7 +41618,9 @@
       <c r="F616">
         <v>1</v>
       </c>
-      <c r="G616" s="6"/>
+      <c r="G616" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H616" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41148,7 +41644,9 @@
       <c r="F617">
         <v>1</v>
       </c>
-      <c r="G617" s="6"/>
+      <c r="G617" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H617" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41172,7 +41670,9 @@
       <c r="F618">
         <v>1</v>
       </c>
-      <c r="G618" s="6"/>
+      <c r="G618" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H618" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41196,7 +41696,9 @@
       <c r="F619">
         <v>1</v>
       </c>
-      <c r="G619" s="6"/>
+      <c r="G619" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H619" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41220,7 +41722,9 @@
       <c r="F620">
         <v>1</v>
       </c>
-      <c r="G620" s="6"/>
+      <c r="G620" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H620" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41244,7 +41748,9 @@
       <c r="F621">
         <v>1</v>
       </c>
-      <c r="G621" s="6"/>
+      <c r="G621" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H621" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41268,7 +41774,9 @@
       <c r="F622">
         <v>1</v>
       </c>
-      <c r="G622" s="6"/>
+      <c r="G622" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H622" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41292,7 +41800,9 @@
       <c r="F623">
         <v>1</v>
       </c>
-      <c r="G623" s="6"/>
+      <c r="G623" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H623" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41316,7 +41826,9 @@
       <c r="F624">
         <v>1</v>
       </c>
-      <c r="G624" s="6"/>
+      <c r="G624" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H624" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41340,7 +41852,9 @@
       <c r="F625">
         <v>1</v>
       </c>
-      <c r="G625" s="6"/>
+      <c r="G625" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H625" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41364,7 +41878,9 @@
       <c r="F626">
         <v>1</v>
       </c>
-      <c r="G626" s="6"/>
+      <c r="G626" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H626" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41388,7 +41904,9 @@
       <c r="F627">
         <v>1</v>
       </c>
-      <c r="G627" s="6"/>
+      <c r="G627" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H627" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41412,7 +41930,9 @@
       <c r="F628">
         <v>1</v>
       </c>
-      <c r="G628" s="6"/>
+      <c r="G628" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H628" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41436,7 +41956,9 @@
       <c r="F629">
         <v>1</v>
       </c>
-      <c r="G629" s="6"/>
+      <c r="G629" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H629" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41460,7 +41982,9 @@
       <c r="F630">
         <v>1</v>
       </c>
-      <c r="G630" s="6"/>
+      <c r="G630" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H630" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41484,7 +42008,9 @@
       <c r="F631">
         <v>1</v>
       </c>
-      <c r="G631" s="6"/>
+      <c r="G631" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H631" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41508,7 +42034,9 @@
       <c r="F632">
         <v>1</v>
       </c>
-      <c r="G632" s="6"/>
+      <c r="G632" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H632" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41532,7 +42060,9 @@
       <c r="F633">
         <v>1</v>
       </c>
-      <c r="G633" s="6"/>
+      <c r="G633" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H633" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41556,7 +42086,9 @@
       <c r="F634">
         <v>1</v>
       </c>
-      <c r="G634" s="6"/>
+      <c r="G634" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H634" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41580,7 +42112,9 @@
       <c r="F635">
         <v>1</v>
       </c>
-      <c r="G635" s="6"/>
+      <c r="G635" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H635" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41604,7 +42138,9 @@
       <c r="F636">
         <v>1</v>
       </c>
-      <c r="G636" s="6"/>
+      <c r="G636" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H636" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41628,7 +42164,9 @@
       <c r="F637">
         <v>1</v>
       </c>
-      <c r="G637" s="6"/>
+      <c r="G637" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H637" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41652,7 +42190,9 @@
       <c r="F638">
         <v>1</v>
       </c>
-      <c r="G638" s="6"/>
+      <c r="G638" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H638" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41676,7 +42216,9 @@
       <c r="F639">
         <v>1</v>
       </c>
-      <c r="G639" s="6"/>
+      <c r="G639" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H639" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41700,7 +42242,9 @@
       <c r="F640">
         <v>1</v>
       </c>
-      <c r="G640" s="6"/>
+      <c r="G640" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H640" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41724,7 +42268,9 @@
       <c r="F641">
         <v>1</v>
       </c>
-      <c r="G641" s="6"/>
+      <c r="G641" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H641" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41748,7 +42294,9 @@
       <c r="F642">
         <v>1</v>
       </c>
-      <c r="G642" s="6"/>
+      <c r="G642" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H642" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41772,7 +42320,9 @@
       <c r="F643">
         <v>1</v>
       </c>
-      <c r="G643" s="6"/>
+      <c r="G643" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H643" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41796,7 +42346,9 @@
       <c r="F644">
         <v>1</v>
       </c>
-      <c r="G644" s="6"/>
+      <c r="G644" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H644" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41820,7 +42372,9 @@
       <c r="F645">
         <v>1</v>
       </c>
-      <c r="G645" s="6"/>
+      <c r="G645" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H645" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41844,7 +42398,9 @@
       <c r="F646">
         <v>1</v>
       </c>
-      <c r="G646" s="6"/>
+      <c r="G646" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H646" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41868,7 +42424,9 @@
       <c r="F647">
         <v>1</v>
       </c>
-      <c r="G647" s="6"/>
+      <c r="G647" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H647" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41892,7 +42450,9 @@
       <c r="F648">
         <v>1</v>
       </c>
-      <c r="G648" s="6"/>
+      <c r="G648" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H648" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41916,7 +42476,9 @@
       <c r="F649">
         <v>1</v>
       </c>
-      <c r="G649" s="6"/>
+      <c r="G649" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H649" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41940,7 +42502,9 @@
       <c r="F650">
         <v>1</v>
       </c>
-      <c r="G650" s="6"/>
+      <c r="G650" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H650" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41964,7 +42528,9 @@
       <c r="F651">
         <v>1</v>
       </c>
-      <c r="G651" s="6"/>
+      <c r="G651" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H651" s="6" t="s">
         <v>2132</v>
       </c>
@@ -41988,7 +42554,9 @@
       <c r="F652">
         <v>1</v>
       </c>
-      <c r="G652" s="6"/>
+      <c r="G652" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H652" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42012,7 +42580,9 @@
       <c r="F653">
         <v>1</v>
       </c>
-      <c r="G653" s="6"/>
+      <c r="G653" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H653" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42036,7 +42606,9 @@
       <c r="F654">
         <v>1</v>
       </c>
-      <c r="G654" s="6"/>
+      <c r="G654" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H654" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42060,7 +42632,9 @@
       <c r="F655">
         <v>1</v>
       </c>
-      <c r="G655" s="6"/>
+      <c r="G655" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H655" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42084,7 +42658,9 @@
       <c r="F656">
         <v>1</v>
       </c>
-      <c r="G656" s="6"/>
+      <c r="G656" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H656" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42108,7 +42684,9 @@
       <c r="F657">
         <v>1</v>
       </c>
-      <c r="G657" s="6"/>
+      <c r="G657" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H657" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42132,7 +42710,9 @@
       <c r="F658">
         <v>1</v>
       </c>
-      <c r="G658" s="6"/>
+      <c r="G658" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H658" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42156,7 +42736,9 @@
       <c r="F659">
         <v>1</v>
       </c>
-      <c r="G659" s="6"/>
+      <c r="G659" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H659" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42180,7 +42762,9 @@
       <c r="F660">
         <v>1</v>
       </c>
-      <c r="G660" s="6"/>
+      <c r="G660" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H660" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42204,7 +42788,9 @@
       <c r="F661">
         <v>1</v>
       </c>
-      <c r="G661" s="6"/>
+      <c r="G661" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H661" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42228,7 +42814,9 @@
       <c r="F662">
         <v>1</v>
       </c>
-      <c r="G662" s="6"/>
+      <c r="G662" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H662" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42252,7 +42840,9 @@
       <c r="F663">
         <v>1</v>
       </c>
-      <c r="G663" s="6"/>
+      <c r="G663" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H663" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42276,7 +42866,9 @@
       <c r="F664">
         <v>1</v>
       </c>
-      <c r="G664" s="6"/>
+      <c r="G664" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H664" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42300,7 +42892,9 @@
       <c r="F665">
         <v>1</v>
       </c>
-      <c r="G665" s="6"/>
+      <c r="G665" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H665" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42324,7 +42918,9 @@
       <c r="F666">
         <v>1</v>
       </c>
-      <c r="G666" s="6"/>
+      <c r="G666" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H666" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42348,7 +42944,9 @@
       <c r="F667">
         <v>1</v>
       </c>
-      <c r="G667" s="6"/>
+      <c r="G667" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H667" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42372,7 +42970,9 @@
       <c r="F668">
         <v>1</v>
       </c>
-      <c r="G668" s="6"/>
+      <c r="G668" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H668" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42396,7 +42996,9 @@
       <c r="F669">
         <v>1</v>
       </c>
-      <c r="G669" s="6"/>
+      <c r="G669" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H669" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42420,7 +43022,9 @@
       <c r="F670">
         <v>1</v>
       </c>
-      <c r="G670" s="6"/>
+      <c r="G670" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H670" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42444,7 +43048,9 @@
       <c r="F671">
         <v>1</v>
       </c>
-      <c r="G671" s="6"/>
+      <c r="G671" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H671" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42468,7 +43074,9 @@
       <c r="F672">
         <v>1</v>
       </c>
-      <c r="G672" s="6"/>
+      <c r="G672" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H672" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42492,7 +43100,9 @@
       <c r="F673">
         <v>1</v>
       </c>
-      <c r="G673" s="6"/>
+      <c r="G673" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H673" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42516,7 +43126,9 @@
       <c r="F674">
         <v>1</v>
       </c>
-      <c r="G674" s="6"/>
+      <c r="G674" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H674" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42540,7 +43152,9 @@
       <c r="F675">
         <v>1</v>
       </c>
-      <c r="G675" s="6"/>
+      <c r="G675" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H675" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42564,7 +43178,9 @@
       <c r="F676">
         <v>1</v>
       </c>
-      <c r="G676" s="6"/>
+      <c r="G676" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H676" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42588,7 +43204,9 @@
       <c r="F677">
         <v>1</v>
       </c>
-      <c r="G677" s="6"/>
+      <c r="G677" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H677" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42612,7 +43230,9 @@
       <c r="F678">
         <v>1</v>
       </c>
-      <c r="G678" s="6"/>
+      <c r="G678" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H678" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42636,7 +43256,9 @@
       <c r="F679">
         <v>1</v>
       </c>
-      <c r="G679" s="6"/>
+      <c r="G679" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H679" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42660,7 +43282,9 @@
       <c r="F680">
         <v>1</v>
       </c>
-      <c r="G680" s="6"/>
+      <c r="G680" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H680" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42684,7 +43308,9 @@
       <c r="F681">
         <v>1</v>
       </c>
-      <c r="G681" s="6"/>
+      <c r="G681" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H681" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42708,7 +43334,9 @@
       <c r="F682">
         <v>1</v>
       </c>
-      <c r="G682" s="6"/>
+      <c r="G682" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H682" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42732,7 +43360,9 @@
       <c r="F683">
         <v>1</v>
       </c>
-      <c r="G683" s="6"/>
+      <c r="G683" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H683" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42756,7 +43386,9 @@
       <c r="F684">
         <v>1</v>
       </c>
-      <c r="G684" s="6"/>
+      <c r="G684" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H684" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42780,7 +43412,9 @@
       <c r="F685">
         <v>1</v>
       </c>
-      <c r="G685" s="6"/>
+      <c r="G685" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H685" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42804,7 +43438,9 @@
       <c r="F686">
         <v>1</v>
       </c>
-      <c r="G686" s="6"/>
+      <c r="G686" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H686" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42828,7 +43464,9 @@
       <c r="F687">
         <v>1</v>
       </c>
-      <c r="G687" s="6"/>
+      <c r="G687" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H687" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42852,7 +43490,9 @@
       <c r="F688">
         <v>1</v>
       </c>
-      <c r="G688" s="6"/>
+      <c r="G688" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H688" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42876,7 +43516,9 @@
       <c r="F689">
         <v>1</v>
       </c>
-      <c r="G689" s="6"/>
+      <c r="G689" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H689" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42900,7 +43542,9 @@
       <c r="F690">
         <v>1</v>
       </c>
-      <c r="G690" s="6"/>
+      <c r="G690" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H690" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42924,7 +43568,9 @@
       <c r="F691">
         <v>1</v>
       </c>
-      <c r="G691" s="6"/>
+      <c r="G691" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H691" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42948,7 +43594,9 @@
       <c r="F692">
         <v>1</v>
       </c>
-      <c r="G692" s="6"/>
+      <c r="G692" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H692" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42972,7 +43620,9 @@
       <c r="F693">
         <v>1</v>
       </c>
-      <c r="G693" s="6"/>
+      <c r="G693" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H693" s="6" t="s">
         <v>2132</v>
       </c>
@@ -42996,7 +43646,9 @@
       <c r="F694">
         <v>1</v>
       </c>
-      <c r="G694" s="6"/>
+      <c r="G694" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H694" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43020,7 +43672,9 @@
       <c r="F695">
         <v>1</v>
       </c>
-      <c r="G695" s="6"/>
+      <c r="G695" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H695" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43044,7 +43698,9 @@
       <c r="F696">
         <v>1</v>
       </c>
-      <c r="G696" s="6"/>
+      <c r="G696" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H696" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43068,7 +43724,9 @@
       <c r="F697">
         <v>1</v>
       </c>
-      <c r="G697" s="6"/>
+      <c r="G697" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H697" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43092,7 +43750,9 @@
       <c r="F698">
         <v>1</v>
       </c>
-      <c r="G698" s="6"/>
+      <c r="G698" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H698" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43116,7 +43776,9 @@
       <c r="F699">
         <v>1</v>
       </c>
-      <c r="G699" s="6"/>
+      <c r="G699" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H699" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43140,7 +43802,9 @@
       <c r="F700">
         <v>1</v>
       </c>
-      <c r="G700" s="6"/>
+      <c r="G700" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H700" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43164,7 +43828,9 @@
       <c r="F701">
         <v>1</v>
       </c>
-      <c r="G701" s="6"/>
+      <c r="G701" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H701" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43188,7 +43854,9 @@
       <c r="F702">
         <v>1</v>
       </c>
-      <c r="G702" s="6"/>
+      <c r="G702" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H702" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43212,7 +43880,9 @@
       <c r="F703">
         <v>1</v>
       </c>
-      <c r="G703" s="6"/>
+      <c r="G703" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H703" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43236,7 +43906,9 @@
       <c r="F704">
         <v>1</v>
       </c>
-      <c r="G704" s="6"/>
+      <c r="G704" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H704" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43260,7 +43932,9 @@
       <c r="F705">
         <v>1</v>
       </c>
-      <c r="G705" s="6"/>
+      <c r="G705" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H705" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43284,7 +43958,9 @@
       <c r="F706">
         <v>1</v>
       </c>
-      <c r="G706" s="6"/>
+      <c r="G706" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H706" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43308,7 +43984,9 @@
       <c r="F707">
         <v>1</v>
       </c>
-      <c r="G707" s="6"/>
+      <c r="G707" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H707" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43332,7 +44010,9 @@
       <c r="F708">
         <v>1</v>
       </c>
-      <c r="G708" s="6"/>
+      <c r="G708" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H708" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43356,7 +44036,9 @@
       <c r="F709">
         <v>1</v>
       </c>
-      <c r="G709" s="6"/>
+      <c r="G709" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H709" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43380,7 +44062,9 @@
       <c r="F710">
         <v>1</v>
       </c>
-      <c r="G710" s="6"/>
+      <c r="G710" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H710" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43404,7 +44088,9 @@
       <c r="F711">
         <v>1</v>
       </c>
-      <c r="G711" s="6"/>
+      <c r="G711" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H711" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43428,7 +44114,9 @@
       <c r="F712">
         <v>1</v>
       </c>
-      <c r="G712" s="6"/>
+      <c r="G712" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H712" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43452,7 +44140,9 @@
       <c r="F713">
         <v>1</v>
       </c>
-      <c r="G713" s="6"/>
+      <c r="G713" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H713" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43476,7 +44166,9 @@
       <c r="F714">
         <v>1</v>
       </c>
-      <c r="G714" s="6"/>
+      <c r="G714" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H714" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43500,7 +44192,9 @@
       <c r="F715">
         <v>1</v>
       </c>
-      <c r="G715" s="6"/>
+      <c r="G715" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H715" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43524,7 +44218,9 @@
       <c r="F716">
         <v>1</v>
       </c>
-      <c r="G716" s="6"/>
+      <c r="G716" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H716" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43548,7 +44244,9 @@
       <c r="F717">
         <v>1</v>
       </c>
-      <c r="G717" s="6"/>
+      <c r="G717" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H717" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43572,7 +44270,9 @@
       <c r="F718">
         <v>1</v>
       </c>
-      <c r="G718" s="6"/>
+      <c r="G718" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H718" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43596,7 +44296,9 @@
       <c r="F719">
         <v>1</v>
       </c>
-      <c r="G719" s="6"/>
+      <c r="G719" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H719" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43620,7 +44322,9 @@
       <c r="F720">
         <v>1</v>
       </c>
-      <c r="G720" s="6"/>
+      <c r="G720" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H720" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43644,7 +44348,9 @@
       <c r="F721">
         <v>1</v>
       </c>
-      <c r="G721" s="6"/>
+      <c r="G721" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H721" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43668,7 +44374,9 @@
       <c r="F722">
         <v>1</v>
       </c>
-      <c r="G722" s="6"/>
+      <c r="G722" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H722" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43692,7 +44400,9 @@
       <c r="F723">
         <v>1</v>
       </c>
-      <c r="G723" s="6"/>
+      <c r="G723" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H723" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43716,7 +44426,9 @@
       <c r="F724">
         <v>1</v>
       </c>
-      <c r="G724" s="6"/>
+      <c r="G724" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H724" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43740,7 +44452,9 @@
       <c r="F725">
         <v>1</v>
       </c>
-      <c r="G725" s="6"/>
+      <c r="G725" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H725" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43764,7 +44478,9 @@
       <c r="F726">
         <v>1</v>
       </c>
-      <c r="G726" s="6"/>
+      <c r="G726" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H726" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43788,7 +44504,9 @@
       <c r="F727">
         <v>1</v>
       </c>
-      <c r="G727" s="6"/>
+      <c r="G727" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H727" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43812,7 +44530,9 @@
       <c r="F728">
         <v>1</v>
       </c>
-      <c r="G728" s="6"/>
+      <c r="G728" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H728" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43836,7 +44556,9 @@
       <c r="F729">
         <v>1</v>
       </c>
-      <c r="G729" s="6"/>
+      <c r="G729" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H729" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43860,7 +44582,9 @@
       <c r="F730">
         <v>1</v>
       </c>
-      <c r="G730" s="6"/>
+      <c r="G730" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H730" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43884,7 +44608,9 @@
       <c r="F731">
         <v>1</v>
       </c>
-      <c r="G731" s="6"/>
+      <c r="G731" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H731" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43908,7 +44634,9 @@
       <c r="F732">
         <v>1</v>
       </c>
-      <c r="G732" s="6"/>
+      <c r="G732" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H732" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43932,7 +44660,9 @@
       <c r="F733">
         <v>1</v>
       </c>
-      <c r="G733" s="6"/>
+      <c r="G733" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H733" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43956,7 +44686,9 @@
       <c r="F734">
         <v>1</v>
       </c>
-      <c r="G734" s="6"/>
+      <c r="G734" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H734" s="6" t="s">
         <v>2132</v>
       </c>
@@ -43980,7 +44712,9 @@
       <c r="F735">
         <v>1</v>
       </c>
-      <c r="G735" s="6"/>
+      <c r="G735" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H735" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44004,7 +44738,9 @@
       <c r="F736">
         <v>1</v>
       </c>
-      <c r="G736" s="6"/>
+      <c r="G736" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H736" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44028,7 +44764,9 @@
       <c r="F737">
         <v>1</v>
       </c>
-      <c r="G737" s="6"/>
+      <c r="G737" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H737" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44052,7 +44790,9 @@
       <c r="F738">
         <v>1</v>
       </c>
-      <c r="G738" s="6"/>
+      <c r="G738" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H738" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44076,7 +44816,9 @@
       <c r="F739">
         <v>1</v>
       </c>
-      <c r="G739" s="6"/>
+      <c r="G739" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H739" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44100,7 +44842,9 @@
       <c r="F740">
         <v>1</v>
       </c>
-      <c r="G740" s="6"/>
+      <c r="G740" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H740" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44124,7 +44868,9 @@
       <c r="F741">
         <v>1</v>
       </c>
-      <c r="G741" s="6"/>
+      <c r="G741" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H741" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44148,7 +44894,9 @@
       <c r="F742">
         <v>1</v>
       </c>
-      <c r="G742" s="6"/>
+      <c r="G742" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H742" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44172,7 +44920,9 @@
       <c r="F743">
         <v>1</v>
       </c>
-      <c r="G743" s="6"/>
+      <c r="G743" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H743" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44196,7 +44946,9 @@
       <c r="F744">
         <v>1</v>
       </c>
-      <c r="G744" s="6"/>
+      <c r="G744" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H744" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44220,7 +44972,9 @@
       <c r="F745">
         <v>1</v>
       </c>
-      <c r="G745" s="6"/>
+      <c r="G745" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H745" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44244,7 +44998,9 @@
       <c r="F746">
         <v>1</v>
       </c>
-      <c r="G746" s="6"/>
+      <c r="G746" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H746" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44268,7 +45024,9 @@
       <c r="F747">
         <v>1</v>
       </c>
-      <c r="G747" s="6"/>
+      <c r="G747" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H747" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44292,7 +45050,9 @@
       <c r="F748">
         <v>1</v>
       </c>
-      <c r="G748" s="6"/>
+      <c r="G748" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H748" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44316,7 +45076,9 @@
       <c r="F749">
         <v>1</v>
       </c>
-      <c r="G749" s="6"/>
+      <c r="G749" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H749" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44340,7 +45102,9 @@
       <c r="F750">
         <v>1</v>
       </c>
-      <c r="G750" s="6"/>
+      <c r="G750" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H750" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44364,7 +45128,9 @@
       <c r="F751">
         <v>1</v>
       </c>
-      <c r="G751" s="6"/>
+      <c r="G751" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H751" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44388,7 +45154,9 @@
       <c r="F752">
         <v>1</v>
       </c>
-      <c r="G752" s="6"/>
+      <c r="G752" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H752" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44412,7 +45180,9 @@
       <c r="F753">
         <v>1</v>
       </c>
-      <c r="G753" s="6"/>
+      <c r="G753" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H753" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44436,7 +45206,9 @@
       <c r="F754">
         <v>1</v>
       </c>
-      <c r="G754" s="6"/>
+      <c r="G754" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H754" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44460,7 +45232,9 @@
       <c r="F755">
         <v>1</v>
       </c>
-      <c r="G755" s="6"/>
+      <c r="G755" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H755" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44484,7 +45258,9 @@
       <c r="F756">
         <v>1</v>
       </c>
-      <c r="G756" s="6"/>
+      <c r="G756" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H756" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44508,7 +45284,9 @@
       <c r="F757">
         <v>1</v>
       </c>
-      <c r="G757" s="6"/>
+      <c r="G757" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H757" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44532,7 +45310,9 @@
       <c r="F758">
         <v>1</v>
       </c>
-      <c r="G758" s="6"/>
+      <c r="G758" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H758" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44556,7 +45336,9 @@
       <c r="F759">
         <v>1</v>
       </c>
-      <c r="G759" s="6"/>
+      <c r="G759" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H759" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44580,7 +45362,9 @@
       <c r="F760">
         <v>1</v>
       </c>
-      <c r="G760" s="6"/>
+      <c r="G760" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H760" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44604,7 +45388,9 @@
       <c r="F761">
         <v>1</v>
       </c>
-      <c r="G761" s="6"/>
+      <c r="G761" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H761" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44628,7 +45414,9 @@
       <c r="F762">
         <v>1</v>
       </c>
-      <c r="G762" s="6"/>
+      <c r="G762" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H762" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44652,7 +45440,9 @@
       <c r="F763">
         <v>1</v>
       </c>
-      <c r="G763" s="6"/>
+      <c r="G763" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H763" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44676,7 +45466,9 @@
       <c r="F764">
         <v>1</v>
       </c>
-      <c r="G764" s="6"/>
+      <c r="G764" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H764" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44700,7 +45492,9 @@
       <c r="F765">
         <v>1</v>
       </c>
-      <c r="G765" s="6"/>
+      <c r="G765" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H765" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44724,7 +45518,9 @@
       <c r="F766">
         <v>1</v>
       </c>
-      <c r="G766" s="6"/>
+      <c r="G766" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H766" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44748,7 +45544,9 @@
       <c r="F767">
         <v>1</v>
       </c>
-      <c r="G767" s="6"/>
+      <c r="G767" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H767" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44772,7 +45570,9 @@
       <c r="F768">
         <v>1</v>
       </c>
-      <c r="G768" s="6"/>
+      <c r="G768" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H768" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44796,7 +45596,9 @@
       <c r="F769">
         <v>1</v>
       </c>
-      <c r="G769" s="6"/>
+      <c r="G769" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H769" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44820,7 +45622,9 @@
       <c r="F770">
         <v>1</v>
       </c>
-      <c r="G770" s="6"/>
+      <c r="G770" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H770" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44844,7 +45648,9 @@
       <c r="F771">
         <v>1</v>
       </c>
-      <c r="G771" s="6"/>
+      <c r="G771" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H771" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44868,7 +45674,9 @@
       <c r="F772">
         <v>1</v>
       </c>
-      <c r="G772" s="6"/>
+      <c r="G772" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H772" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44892,7 +45700,9 @@
       <c r="F773">
         <v>1</v>
       </c>
-      <c r="G773" s="6"/>
+      <c r="G773" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H773" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44916,7 +45726,9 @@
       <c r="F774">
         <v>1</v>
       </c>
-      <c r="G774" s="6"/>
+      <c r="G774" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H774" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44940,7 +45752,9 @@
       <c r="F775">
         <v>1</v>
       </c>
-      <c r="G775" s="6"/>
+      <c r="G775" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H775" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44964,7 +45778,9 @@
       <c r="F776">
         <v>1</v>
       </c>
-      <c r="G776" s="6"/>
+      <c r="G776" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H776" s="6" t="s">
         <v>2132</v>
       </c>
@@ -44988,7 +45804,9 @@
       <c r="F777">
         <v>1</v>
       </c>
-      <c r="G777" s="6"/>
+      <c r="G777" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H777" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45012,7 +45830,9 @@
       <c r="F778">
         <v>1</v>
       </c>
-      <c r="G778" s="6"/>
+      <c r="G778" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H778" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45036,7 +45856,9 @@
       <c r="F779">
         <v>1</v>
       </c>
-      <c r="G779" s="6"/>
+      <c r="G779" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H779" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45060,7 +45882,9 @@
       <c r="F780">
         <v>1</v>
       </c>
-      <c r="G780" s="6"/>
+      <c r="G780" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H780" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45084,7 +45908,9 @@
       <c r="F781">
         <v>1</v>
       </c>
-      <c r="G781" s="6"/>
+      <c r="G781" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H781" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45108,7 +45934,9 @@
       <c r="F782">
         <v>1</v>
       </c>
-      <c r="G782" s="6"/>
+      <c r="G782" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H782" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45132,7 +45960,9 @@
       <c r="F783">
         <v>1</v>
       </c>
-      <c r="G783" s="6"/>
+      <c r="G783" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H783" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45156,7 +45986,9 @@
       <c r="F784">
         <v>1</v>
       </c>
-      <c r="G784" s="6"/>
+      <c r="G784" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H784" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45180,7 +46012,9 @@
       <c r="F785">
         <v>1</v>
       </c>
-      <c r="G785" s="6"/>
+      <c r="G785" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H785" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45204,7 +46038,9 @@
       <c r="F786">
         <v>1</v>
       </c>
-      <c r="G786" s="6"/>
+      <c r="G786" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H786" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45228,7 +46064,9 @@
       <c r="F787">
         <v>1</v>
       </c>
-      <c r="G787" s="6"/>
+      <c r="G787" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H787" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45252,7 +46090,9 @@
       <c r="F788">
         <v>1</v>
       </c>
-      <c r="G788" s="6"/>
+      <c r="G788" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H788" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45276,7 +46116,9 @@
       <c r="F789">
         <v>1</v>
       </c>
-      <c r="G789" s="6"/>
+      <c r="G789" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H789" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45300,7 +46142,9 @@
       <c r="F790">
         <v>1</v>
       </c>
-      <c r="G790" s="6"/>
+      <c r="G790" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H790" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45324,7 +46168,9 @@
       <c r="F791">
         <v>1</v>
       </c>
-      <c r="G791" s="6"/>
+      <c r="G791" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H791" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45348,7 +46194,9 @@
       <c r="F792">
         <v>1</v>
       </c>
-      <c r="G792" s="6"/>
+      <c r="G792" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H792" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45372,7 +46220,9 @@
       <c r="F793">
         <v>1</v>
       </c>
-      <c r="G793" s="6"/>
+      <c r="G793" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H793" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45396,7 +46246,9 @@
       <c r="F794">
         <v>1</v>
       </c>
-      <c r="G794" s="6"/>
+      <c r="G794" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H794" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45420,7 +46272,9 @@
       <c r="F795">
         <v>1</v>
       </c>
-      <c r="G795" s="6"/>
+      <c r="G795" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H795" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45444,7 +46298,9 @@
       <c r="F796">
         <v>1</v>
       </c>
-      <c r="G796" s="6"/>
+      <c r="G796" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H796" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45468,7 +46324,9 @@
       <c r="F797">
         <v>1</v>
       </c>
-      <c r="G797" s="6"/>
+      <c r="G797" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H797" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45492,7 +46350,9 @@
       <c r="F798">
         <v>1</v>
       </c>
-      <c r="G798" s="6"/>
+      <c r="G798" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H798" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45516,7 +46376,9 @@
       <c r="F799">
         <v>1</v>
       </c>
-      <c r="G799" s="6"/>
+      <c r="G799" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H799" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45540,7 +46402,9 @@
       <c r="F800">
         <v>1</v>
       </c>
-      <c r="G800" s="6"/>
+      <c r="G800" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H800" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45564,7 +46428,9 @@
       <c r="F801">
         <v>1</v>
       </c>
-      <c r="G801" s="6"/>
+      <c r="G801" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H801" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45588,7 +46454,9 @@
       <c r="F802">
         <v>1</v>
       </c>
-      <c r="G802" s="6"/>
+      <c r="G802" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H802" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45612,7 +46480,9 @@
       <c r="F803">
         <v>1</v>
       </c>
-      <c r="G803" s="6"/>
+      <c r="G803" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H803" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45636,7 +46506,9 @@
       <c r="F804">
         <v>1</v>
       </c>
-      <c r="G804" s="6"/>
+      <c r="G804" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H804" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45660,7 +46532,9 @@
       <c r="F805">
         <v>1</v>
       </c>
-      <c r="G805" s="6"/>
+      <c r="G805" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H805" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45684,7 +46558,9 @@
       <c r="F806">
         <v>1</v>
       </c>
-      <c r="G806" s="6"/>
+      <c r="G806" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H806" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45708,7 +46584,9 @@
       <c r="F807">
         <v>1</v>
       </c>
-      <c r="G807" s="6"/>
+      <c r="G807" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H807" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45732,7 +46610,9 @@
       <c r="F808">
         <v>1</v>
       </c>
-      <c r="G808" s="6"/>
+      <c r="G808" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H808" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45756,7 +46636,9 @@
       <c r="F809">
         <v>1</v>
       </c>
-      <c r="G809" s="6"/>
+      <c r="G809" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H809" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45780,7 +46662,9 @@
       <c r="F810">
         <v>1</v>
       </c>
-      <c r="G810" s="6"/>
+      <c r="G810" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H810" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45804,7 +46688,9 @@
       <c r="F811">
         <v>1</v>
       </c>
-      <c r="G811" s="6"/>
+      <c r="G811" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H811" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45828,7 +46714,9 @@
       <c r="F812">
         <v>1</v>
       </c>
-      <c r="G812" s="6"/>
+      <c r="G812" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H812" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45852,7 +46740,9 @@
       <c r="F813">
         <v>1</v>
       </c>
-      <c r="G813" s="6"/>
+      <c r="G813" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H813" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45876,7 +46766,9 @@
       <c r="F814">
         <v>1</v>
       </c>
-      <c r="G814" s="6"/>
+      <c r="G814" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H814" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45900,7 +46792,9 @@
       <c r="F815">
         <v>1</v>
       </c>
-      <c r="G815" s="6"/>
+      <c r="G815" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H815" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45924,7 +46818,9 @@
       <c r="F816">
         <v>1</v>
       </c>
-      <c r="G816" s="6"/>
+      <c r="G816" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H816" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45948,7 +46844,9 @@
       <c r="F817">
         <v>1</v>
       </c>
-      <c r="G817" s="6"/>
+      <c r="G817" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H817" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45972,7 +46870,9 @@
       <c r="F818">
         <v>1</v>
       </c>
-      <c r="G818" s="6"/>
+      <c r="G818" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H818" s="6" t="s">
         <v>2132</v>
       </c>
@@ -45996,7 +46896,9 @@
       <c r="F819">
         <v>1</v>
       </c>
-      <c r="G819" s="6"/>
+      <c r="G819" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H819" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46020,7 +46922,9 @@
       <c r="F820">
         <v>1</v>
       </c>
-      <c r="G820" s="6"/>
+      <c r="G820" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H820" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46044,7 +46948,9 @@
       <c r="F821">
         <v>1</v>
       </c>
-      <c r="G821" s="6"/>
+      <c r="G821" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H821" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46068,7 +46974,9 @@
       <c r="F822">
         <v>1</v>
       </c>
-      <c r="G822" s="6"/>
+      <c r="G822" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H822" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46092,7 +47000,9 @@
       <c r="F823">
         <v>1</v>
       </c>
-      <c r="G823" s="6"/>
+      <c r="G823" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H823" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46116,7 +47026,9 @@
       <c r="F824">
         <v>1</v>
       </c>
-      <c r="G824" s="6"/>
+      <c r="G824" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H824" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46140,7 +47052,9 @@
       <c r="F825">
         <v>1</v>
       </c>
-      <c r="G825" s="6"/>
+      <c r="G825" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H825" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46164,7 +47078,9 @@
       <c r="F826">
         <v>1</v>
       </c>
-      <c r="G826" s="6"/>
+      <c r="G826" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H826" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46188,7 +47104,9 @@
       <c r="F827">
         <v>1</v>
       </c>
-      <c r="G827" s="6"/>
+      <c r="G827" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H827" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46212,7 +47130,9 @@
       <c r="F828">
         <v>1</v>
       </c>
-      <c r="G828" s="6"/>
+      <c r="G828" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H828" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46236,7 +47156,9 @@
       <c r="F829">
         <v>1</v>
       </c>
-      <c r="G829" s="6"/>
+      <c r="G829" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H829" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46260,7 +47182,9 @@
       <c r="F830">
         <v>1</v>
       </c>
-      <c r="G830" s="6"/>
+      <c r="G830" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H830" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46284,7 +47208,9 @@
       <c r="F831">
         <v>1</v>
       </c>
-      <c r="G831" s="6"/>
+      <c r="G831" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H831" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46308,7 +47234,9 @@
       <c r="F832">
         <v>1</v>
       </c>
-      <c r="G832" s="6"/>
+      <c r="G832" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H832" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46332,7 +47260,9 @@
       <c r="F833">
         <v>1</v>
       </c>
-      <c r="G833" s="6"/>
+      <c r="G833" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H833" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46356,7 +47286,9 @@
       <c r="F834">
         <v>1</v>
       </c>
-      <c r="G834" s="6"/>
+      <c r="G834" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H834" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46380,7 +47312,9 @@
       <c r="F835">
         <v>1</v>
       </c>
-      <c r="G835" s="6"/>
+      <c r="G835" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H835" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46404,7 +47338,9 @@
       <c r="F836">
         <v>1</v>
       </c>
-      <c r="G836" s="6"/>
+      <c r="G836" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H836" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46428,7 +47364,9 @@
       <c r="F837">
         <v>1</v>
       </c>
-      <c r="G837" s="6"/>
+      <c r="G837" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H837" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46452,7 +47390,9 @@
       <c r="F838">
         <v>1</v>
       </c>
-      <c r="G838" s="6"/>
+      <c r="G838" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H838" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46476,7 +47416,9 @@
       <c r="F839">
         <v>1</v>
       </c>
-      <c r="G839" s="6"/>
+      <c r="G839" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H839" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46500,7 +47442,9 @@
       <c r="F840">
         <v>1</v>
       </c>
-      <c r="G840" s="6"/>
+      <c r="G840" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H840" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46524,7 +47468,9 @@
       <c r="F841">
         <v>1</v>
       </c>
-      <c r="G841" s="6"/>
+      <c r="G841" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H841" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46548,7 +47494,9 @@
       <c r="F842">
         <v>1</v>
       </c>
-      <c r="G842" s="6"/>
+      <c r="G842" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H842" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46572,7 +47520,9 @@
       <c r="F843">
         <v>1</v>
       </c>
-      <c r="G843" s="6"/>
+      <c r="G843" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H843" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46596,7 +47546,9 @@
       <c r="F844">
         <v>1</v>
       </c>
-      <c r="G844" s="6"/>
+      <c r="G844" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H844" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46620,7 +47572,9 @@
       <c r="F845">
         <v>1</v>
       </c>
-      <c r="G845" s="6"/>
+      <c r="G845" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H845" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46644,7 +47598,9 @@
       <c r="F846">
         <v>1</v>
       </c>
-      <c r="G846" s="6"/>
+      <c r="G846" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H846" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46668,7 +47624,9 @@
       <c r="F847">
         <v>1</v>
       </c>
-      <c r="G847" s="6"/>
+      <c r="G847" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H847" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46692,7 +47650,9 @@
       <c r="F848">
         <v>1</v>
       </c>
-      <c r="G848" s="6"/>
+      <c r="G848" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H848" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46716,7 +47676,9 @@
       <c r="F849">
         <v>1</v>
       </c>
-      <c r="G849" s="6"/>
+      <c r="G849" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H849" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46740,7 +47702,9 @@
       <c r="F850">
         <v>1</v>
       </c>
-      <c r="G850" s="6"/>
+      <c r="G850" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H850" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46764,7 +47728,9 @@
       <c r="F851">
         <v>1</v>
       </c>
-      <c r="G851" s="6"/>
+      <c r="G851" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H851" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46788,7 +47754,9 @@
       <c r="F852">
         <v>1</v>
       </c>
-      <c r="G852" s="6"/>
+      <c r="G852" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H852" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46812,7 +47780,9 @@
       <c r="F853">
         <v>1</v>
       </c>
-      <c r="G853" s="6"/>
+      <c r="G853" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H853" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46836,7 +47806,9 @@
       <c r="F854">
         <v>1</v>
       </c>
-      <c r="G854" s="6"/>
+      <c r="G854" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H854" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46860,7 +47832,9 @@
       <c r="F855">
         <v>1</v>
       </c>
-      <c r="G855" s="6"/>
+      <c r="G855" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H855" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46884,7 +47858,9 @@
       <c r="F856">
         <v>1</v>
       </c>
-      <c r="G856" s="6"/>
+      <c r="G856" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H856" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46908,7 +47884,9 @@
       <c r="F857">
         <v>1</v>
       </c>
-      <c r="G857" s="6"/>
+      <c r="G857" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H857" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46932,7 +47910,9 @@
       <c r="F858">
         <v>1</v>
       </c>
-      <c r="G858" s="6"/>
+      <c r="G858" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H858" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46956,7 +47936,9 @@
       <c r="F859">
         <v>1</v>
       </c>
-      <c r="G859" s="6"/>
+      <c r="G859" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H859" s="6" t="s">
         <v>2132</v>
       </c>
@@ -46980,7 +47962,9 @@
       <c r="F860">
         <v>1</v>
       </c>
-      <c r="G860" s="6"/>
+      <c r="G860" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H860" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47004,7 +47988,9 @@
       <c r="F861">
         <v>1</v>
       </c>
-      <c r="G861" s="6"/>
+      <c r="G861" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H861" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47028,7 +48014,9 @@
       <c r="F862">
         <v>1</v>
       </c>
-      <c r="G862" s="6"/>
+      <c r="G862" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H862" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47052,7 +48040,9 @@
       <c r="F863">
         <v>1</v>
       </c>
-      <c r="G863" s="6"/>
+      <c r="G863" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H863" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47076,7 +48066,9 @@
       <c r="F864">
         <v>1</v>
       </c>
-      <c r="G864" s="6"/>
+      <c r="G864" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H864" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47100,7 +48092,9 @@
       <c r="F865">
         <v>1</v>
       </c>
-      <c r="G865" s="6"/>
+      <c r="G865" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H865" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47124,7 +48118,9 @@
       <c r="F866">
         <v>1</v>
       </c>
-      <c r="G866" s="6"/>
+      <c r="G866" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H866" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47148,7 +48144,9 @@
       <c r="F867">
         <v>1</v>
       </c>
-      <c r="G867" s="6"/>
+      <c r="G867" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H867" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47172,7 +48170,9 @@
       <c r="F868">
         <v>1</v>
       </c>
-      <c r="G868" s="6"/>
+      <c r="G868" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H868" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47196,7 +48196,9 @@
       <c r="F869">
         <v>1</v>
       </c>
-      <c r="G869" s="6"/>
+      <c r="G869" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H869" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47220,7 +48222,9 @@
       <c r="F870">
         <v>1</v>
       </c>
-      <c r="G870" s="6"/>
+      <c r="G870" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H870" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47244,7 +48248,9 @@
       <c r="F871">
         <v>1</v>
       </c>
-      <c r="G871" s="6"/>
+      <c r="G871" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H871" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47268,7 +48274,9 @@
       <c r="F872">
         <v>1</v>
       </c>
-      <c r="G872" s="6"/>
+      <c r="G872" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H872" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47292,7 +48300,9 @@
       <c r="F873">
         <v>1</v>
       </c>
-      <c r="G873" s="6"/>
+      <c r="G873" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H873" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47316,7 +48326,9 @@
       <c r="F874">
         <v>1</v>
       </c>
-      <c r="G874" s="6"/>
+      <c r="G874" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H874" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47340,7 +48352,9 @@
       <c r="F875">
         <v>1</v>
       </c>
-      <c r="G875" s="6"/>
+      <c r="G875" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H875" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47364,7 +48378,9 @@
       <c r="F876">
         <v>1</v>
       </c>
-      <c r="G876" s="6"/>
+      <c r="G876" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H876" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47388,7 +48404,9 @@
       <c r="F877">
         <v>1</v>
       </c>
-      <c r="G877" s="6"/>
+      <c r="G877" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H877" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47412,7 +48430,9 @@
       <c r="F878">
         <v>1</v>
       </c>
-      <c r="G878" s="6"/>
+      <c r="G878" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H878" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47436,7 +48456,9 @@
       <c r="F879">
         <v>1</v>
       </c>
-      <c r="G879" s="6"/>
+      <c r="G879" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H879" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47460,7 +48482,9 @@
       <c r="F880">
         <v>1</v>
       </c>
-      <c r="G880" s="6"/>
+      <c r="G880" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H880" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47484,7 +48508,9 @@
       <c r="F881">
         <v>1</v>
       </c>
-      <c r="G881" s="6"/>
+      <c r="G881" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H881" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47508,7 +48534,9 @@
       <c r="F882">
         <v>1</v>
       </c>
-      <c r="G882" s="6"/>
+      <c r="G882" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H882" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47532,7 +48560,9 @@
       <c r="F883">
         <v>1</v>
       </c>
-      <c r="G883" s="6"/>
+      <c r="G883" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H883" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47556,7 +48586,9 @@
       <c r="F884">
         <v>1</v>
       </c>
-      <c r="G884" s="6"/>
+      <c r="G884" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H884" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47580,7 +48612,9 @@
       <c r="F885">
         <v>1</v>
       </c>
-      <c r="G885" s="6"/>
+      <c r="G885" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H885" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47604,7 +48638,9 @@
       <c r="F886">
         <v>1</v>
       </c>
-      <c r="G886" s="6"/>
+      <c r="G886" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H886" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47628,7 +48664,9 @@
       <c r="F887">
         <v>1</v>
       </c>
-      <c r="G887" s="6"/>
+      <c r="G887" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H887" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47652,7 +48690,9 @@
       <c r="F888">
         <v>1</v>
       </c>
-      <c r="G888" s="6"/>
+      <c r="G888" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H888" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47676,7 +48716,9 @@
       <c r="F889">
         <v>1</v>
       </c>
-      <c r="G889" s="6"/>
+      <c r="G889" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H889" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47700,7 +48742,9 @@
       <c r="F890">
         <v>1</v>
       </c>
-      <c r="G890" s="6"/>
+      <c r="G890" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H890" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47724,7 +48768,9 @@
       <c r="F891">
         <v>1</v>
       </c>
-      <c r="G891" s="6"/>
+      <c r="G891" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H891" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47748,7 +48794,9 @@
       <c r="F892">
         <v>1</v>
       </c>
-      <c r="G892" s="6"/>
+      <c r="G892" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H892" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47772,7 +48820,9 @@
       <c r="F893">
         <v>1</v>
       </c>
-      <c r="G893" s="6"/>
+      <c r="G893" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H893" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47796,7 +48846,9 @@
       <c r="F894">
         <v>1</v>
       </c>
-      <c r="G894" s="6"/>
+      <c r="G894" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H894" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47820,7 +48872,9 @@
       <c r="F895">
         <v>1</v>
       </c>
-      <c r="G895" s="6"/>
+      <c r="G895" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H895" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47844,7 +48898,9 @@
       <c r="F896">
         <v>1</v>
       </c>
-      <c r="G896" s="6"/>
+      <c r="G896" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H896" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47868,7 +48924,9 @@
       <c r="F897">
         <v>1</v>
       </c>
-      <c r="G897" s="6"/>
+      <c r="G897" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H897" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47892,7 +48950,9 @@
       <c r="F898">
         <v>1</v>
       </c>
-      <c r="G898" s="6"/>
+      <c r="G898" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H898" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47916,7 +48976,9 @@
       <c r="F899">
         <v>1</v>
       </c>
-      <c r="G899" s="6"/>
+      <c r="G899" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H899" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47940,7 +49002,9 @@
       <c r="F900">
         <v>1</v>
       </c>
-      <c r="G900" s="6"/>
+      <c r="G900" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H900" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47964,7 +49028,9 @@
       <c r="F901">
         <v>1</v>
       </c>
-      <c r="G901" s="6"/>
+      <c r="G901" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H901" s="6" t="s">
         <v>2132</v>
       </c>
@@ -47988,7 +49054,9 @@
       <c r="F902">
         <v>1</v>
       </c>
-      <c r="G902" s="6"/>
+      <c r="G902" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H902" s="6" t="s">
         <v>2132</v>
       </c>
@@ -48012,7 +49080,9 @@
       <c r="F903">
         <v>1</v>
       </c>
-      <c r="G903" s="6"/>
+      <c r="G903" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H903" s="6" t="s">
         <v>2132</v>
       </c>
@@ -48036,7 +49106,9 @@
       <c r="F904">
         <v>1</v>
       </c>
-      <c r="G904" s="6"/>
+      <c r="G904" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H904" s="6" t="s">
         <v>2132</v>
       </c>
@@ -48060,7 +49132,9 @@
       <c r="F905">
         <v>1</v>
       </c>
-      <c r="G905" s="6"/>
+      <c r="G905" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H905" s="6" t="s">
         <v>2132</v>
       </c>
@@ -48084,7 +49158,9 @@
       <c r="F906">
         <v>1</v>
       </c>
-      <c r="G906" s="6"/>
+      <c r="G906" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H906" s="6" t="s">
         <v>2132</v>
       </c>
@@ -48108,7 +49184,9 @@
       <c r="F907">
         <v>1</v>
       </c>
-      <c r="G907" s="6"/>
+      <c r="G907" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H907" s="6" t="s">
         <v>2132</v>
       </c>
@@ -48132,7 +49210,9 @@
       <c r="F908">
         <v>1</v>
       </c>
-      <c r="G908" s="6"/>
+      <c r="G908" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H908" s="6" t="s">
         <v>2132</v>
       </c>
@@ -48156,7 +49236,9 @@
       <c r="F909">
         <v>1</v>
       </c>
-      <c r="G909" s="6"/>
+      <c r="G909" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H909" s="6" t="s">
         <v>2132</v>
       </c>
@@ -48180,7 +49262,9 @@
       <c r="F910">
         <v>1</v>
       </c>
-      <c r="G910" s="6"/>
+      <c r="G910" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H910" s="6" t="s">
         <v>2132</v>
       </c>
@@ -48204,7 +49288,9 @@
       <c r="F911">
         <v>1</v>
       </c>
-      <c r="G911" s="6"/>
+      <c r="G911" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H911" s="6" t="s">
         <v>2132</v>
       </c>
@@ -48228,7 +49314,9 @@
       <c r="F912">
         <v>1</v>
       </c>
-      <c r="G912" s="6"/>
+      <c r="G912" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H912" s="6" t="s">
         <v>2132</v>
       </c>
@@ -48252,7 +49340,9 @@
       <c r="F913">
         <v>1</v>
       </c>
-      <c r="G913" s="6"/>
+      <c r="G913" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H913" s="6" t="s">
         <v>2132</v>
       </c>
@@ -48276,7 +49366,9 @@
       <c r="F914">
         <v>1</v>
       </c>
-      <c r="G914" s="6"/>
+      <c r="G914" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H914" s="6" t="s">
         <v>2132</v>
       </c>
@@ -48300,7 +49392,9 @@
       <c r="F915">
         <v>1</v>
       </c>
-      <c r="G915" s="6"/>
+      <c r="G915" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H915" s="6" t="s">
         <v>2132</v>
       </c>
@@ -48324,7 +49418,9 @@
       <c r="F916">
         <v>1</v>
       </c>
-      <c r="G916" s="6"/>
+      <c r="G916" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H916" s="6" t="s">
         <v>2132</v>
       </c>
@@ -48348,7 +49444,9 @@
       <c r="F917">
         <v>1</v>
       </c>
-      <c r="G917" s="6"/>
+      <c r="G917" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H917" s="6" t="s">
         <v>2132</v>
       </c>
@@ -48372,7 +49470,9 @@
       <c r="F918">
         <v>1</v>
       </c>
-      <c r="G918" s="6"/>
+      <c r="G918" s="6" t="s">
+        <v>2137</v>
+      </c>
       <c r="H918" s="6" t="s">
         <v>2132</v>
       </c>

--- a/es/es-global-request.xlsx
+++ b/es/es-global-request.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cnxmail-my.sharepoint.com/personal/sujeong_kang_concentrix_com/Documents/02.Operations/01.BU/01.ES/00.Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="628" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E25A479-CAFD-4DDD-B5E6-8CE374062A15}"/>
+  <xr:revisionPtr revIDLastSave="637" documentId="13_ncr:1_{81C237BA-F8DB-4490-B785-EDCAE037C059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB4AD0FA-56C7-4C88-A8D2-65829412156B}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1725" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1725" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LG DUALCOOL AI" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10762" uniqueCount="2138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11141" uniqueCount="2141">
   <si>
     <t>Title</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -6578,6 +6578,18 @@
   </si>
   <si>
     <t>09/07/2026</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>URL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>내부검토</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>진행중</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -26080,13 +26092,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F77BCE9D-002C-46A4-837D-945D35BE8D04}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="4" max="6" width="9.140625" customWidth="1"/>
+    <col min="3" max="4" width="9.140625" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -26094,13 +26107,13 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="13.5">
+    <row r="2" spans="1:9" ht="13.5">
       <c r="A2" s="7" t="s">
         <v>1197</v>
       </c>
       <c r="B2" s="8"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -26108,7 +26121,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="13.5">
+    <row r="4" spans="1:9" ht="13.5">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -26116,7 +26129,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="13.5">
+    <row r="5" spans="1:9" ht="13.5">
       <c r="A5" s="5" t="s">
         <v>1198</v>
       </c>
@@ -26124,7 +26137,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="13.5">
+    <row r="7" spans="1:9" ht="13.5">
       <c r="A7" s="10" t="s">
         <v>1191</v>
       </c>
@@ -26132,285 +26145,348 @@
         <v>1192</v>
       </c>
       <c r="C7" s="10" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>2120</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>1193</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>1201</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>2120</v>
-      </c>
       <c r="F7" s="10" t="s">
+        <v>2138</v>
+      </c>
+      <c r="G7" s="10" t="s">
         <v>2126</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>2135</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="I7" s="10" t="s">
         <v>1194</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="13.5">
+    <row r="8" spans="1:9" ht="13.5">
       <c r="A8" s="1" t="s">
         <v>1195</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>1188</v>
       </c>
+      <c r="C8" s="1" t="s">
+        <v>2117</v>
+      </c>
       <c r="D8" s="1" t="s">
-        <v>2117</v>
-      </c>
-      <c r="E8" s="1" t="s">
         <v>2121</v>
       </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="H8" s="1" t="s">
+      <c r="E8" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>2119</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9" ht="13.5">
       <c r="A9" s="1" t="s">
         <v>1195</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1188</v>
       </c>
+      <c r="C9" s="1" t="s">
+        <v>2118</v>
+      </c>
       <c r="D9" s="1" t="s">
-        <v>2118</v>
-      </c>
-      <c r="E9" s="1" t="s">
         <v>2122</v>
       </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="E9" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="13.5">
       <c r="A10" s="1" t="s">
         <v>1195</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>1188</v>
       </c>
+      <c r="C10" s="1" t="s">
+        <v>2118</v>
+      </c>
       <c r="D10" s="1" t="s">
-        <v>2118</v>
-      </c>
-      <c r="E10" s="1" t="s">
         <v>2123</v>
       </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="E10" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="13.5">
       <c r="A11" s="1" t="s">
         <v>1195</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>1188</v>
       </c>
+      <c r="C11" s="1" t="s">
+        <v>2118</v>
+      </c>
       <c r="D11" s="1" t="s">
-        <v>2118</v>
-      </c>
-      <c r="E11" s="1" t="s">
         <v>2124</v>
       </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="E11" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="13.5">
       <c r="A12" s="1" t="s">
         <v>1195</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>1188</v>
       </c>
+      <c r="C12" s="1" t="s">
+        <v>2118</v>
+      </c>
       <c r="D12" s="1" t="s">
-        <v>2118</v>
-      </c>
-      <c r="E12" s="1" t="s">
         <v>2125</v>
       </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="13.5">
+      <c r="E12" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="13.5">
       <c r="A13" s="1" t="s">
         <v>1195</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>1189</v>
       </c>
+      <c r="C13" s="1" t="s">
+        <v>2117</v>
+      </c>
       <c r="D13" s="1" t="s">
-        <v>2117</v>
-      </c>
-      <c r="E13" s="1" t="s">
         <v>2121</v>
       </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-      <c r="H13" s="1" t="s">
+      <c r="E13" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>2119</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:9" ht="13.5">
       <c r="A14" s="1" t="s">
         <v>1195</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>1189</v>
       </c>
+      <c r="C14" s="1" t="s">
+        <v>2118</v>
+      </c>
       <c r="D14" s="1" t="s">
-        <v>2118</v>
-      </c>
-      <c r="E14" s="1" t="s">
         <v>2122</v>
       </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="E14" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="13.5">
       <c r="A15" s="1" t="s">
         <v>1195</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1189</v>
       </c>
+      <c r="C15" s="1" t="s">
+        <v>2118</v>
+      </c>
       <c r="D15" s="1" t="s">
-        <v>2118</v>
-      </c>
-      <c r="E15" s="1" t="s">
         <v>2123</v>
       </c>
-      <c r="F15" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="E15" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="13.5">
       <c r="A16" s="1" t="s">
         <v>1195</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>1189</v>
       </c>
+      <c r="C16" s="1" t="s">
+        <v>2118</v>
+      </c>
       <c r="D16" s="1" t="s">
-        <v>2118</v>
-      </c>
-      <c r="E16" s="1" t="s">
         <v>2124</v>
       </c>
-      <c r="F16" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="E16" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="13.5">
       <c r="A17" s="1" t="s">
         <v>1195</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>1189</v>
       </c>
+      <c r="C17" s="1" t="s">
+        <v>2118</v>
+      </c>
       <c r="D17" s="1" t="s">
-        <v>2118</v>
-      </c>
-      <c r="E17" s="1" t="s">
         <v>2125</v>
       </c>
-      <c r="F17" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="13.5">
+      <c r="E17" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="13.5">
       <c r="A18" s="1" t="s">
         <v>1195</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>1190</v>
       </c>
+      <c r="C18" s="1" t="s">
+        <v>2117</v>
+      </c>
       <c r="D18" s="1" t="s">
-        <v>2117</v>
-      </c>
-      <c r="E18" s="1" t="s">
         <v>2121</v>
       </c>
-      <c r="F18" s="1">
-        <v>1</v>
-      </c>
-      <c r="H18" s="1" t="s">
+      <c r="E18" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>2119</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:9" ht="13.5">
       <c r="A19" s="1" t="s">
         <v>1195</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>1190</v>
       </c>
+      <c r="C19" s="1" t="s">
+        <v>2118</v>
+      </c>
       <c r="D19" s="1" t="s">
-        <v>2118</v>
-      </c>
-      <c r="E19" s="1" t="s">
         <v>2122</v>
       </c>
-      <c r="F19" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="E19" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="13.5">
       <c r="A20" s="1" t="s">
         <v>1195</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>1190</v>
       </c>
+      <c r="C20" s="1" t="s">
+        <v>2118</v>
+      </c>
       <c r="D20" s="1" t="s">
-        <v>2118</v>
-      </c>
-      <c r="E20" s="1" t="s">
         <v>2123</v>
       </c>
-      <c r="F20" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="E20" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="13.5">
       <c r="A21" s="1" t="s">
         <v>1195</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>1190</v>
       </c>
+      <c r="C21" s="1" t="s">
+        <v>2118</v>
+      </c>
       <c r="D21" s="1" t="s">
-        <v>2118</v>
-      </c>
-      <c r="E21" s="1" t="s">
         <v>2124</v>
       </c>
-      <c r="F21" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="E21" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="13.5">
       <c r="A22" s="1" t="s">
         <v>1195</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>1190</v>
       </c>
+      <c r="C22" s="1" t="s">
+        <v>2118</v>
+      </c>
       <c r="D22" s="1" t="s">
-        <v>2118</v>
-      </c>
-      <c r="E22" s="1" t="s">
         <v>2125</v>
       </c>
-      <c r="F22" s="1">
+      <c r="E22" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1">
         <v>1</v>
       </c>
     </row>
@@ -26534,7 +26610,9 @@
       <c r="F8">
         <v>1</v>
       </c>
-      <c r="G8" s="6"/>
+      <c r="G8" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H8" s="6" t="s">
         <v>2132</v>
       </c>
@@ -26558,7 +26636,9 @@
       <c r="F9">
         <v>1</v>
       </c>
-      <c r="G9" s="6"/>
+      <c r="G9" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H9" s="6" t="s">
         <v>2132</v>
       </c>
@@ -26582,7 +26662,9 @@
       <c r="F10">
         <v>1</v>
       </c>
-      <c r="G10" s="6"/>
+      <c r="G10" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H10" s="6" t="s">
         <v>2132</v>
       </c>
@@ -26606,7 +26688,9 @@
       <c r="F11">
         <v>1</v>
       </c>
-      <c r="G11" s="6"/>
+      <c r="G11" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H11" s="6" t="s">
         <v>2132</v>
       </c>
@@ -26630,7 +26714,9 @@
       <c r="F12">
         <v>1</v>
       </c>
-      <c r="G12" s="6"/>
+      <c r="G12" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H12" s="6" t="s">
         <v>2132</v>
       </c>
@@ -26654,7 +26740,9 @@
       <c r="F13">
         <v>1</v>
       </c>
-      <c r="G13" s="6"/>
+      <c r="G13" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H13" s="6" t="s">
         <v>2132</v>
       </c>
@@ -26678,7 +26766,9 @@
       <c r="F14">
         <v>1</v>
       </c>
-      <c r="G14" s="6"/>
+      <c r="G14" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H14" s="6" t="s">
         <v>2132</v>
       </c>
@@ -26702,7 +26792,9 @@
       <c r="F15">
         <v>1</v>
       </c>
-      <c r="G15" s="6"/>
+      <c r="G15" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H15" s="6" t="s">
         <v>2132</v>
       </c>
@@ -26726,7 +26818,9 @@
       <c r="F16">
         <v>1</v>
       </c>
-      <c r="G16" s="6"/>
+      <c r="G16" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H16" s="6" t="s">
         <v>2132</v>
       </c>
@@ -26750,7 +26844,9 @@
       <c r="F17">
         <v>1</v>
       </c>
-      <c r="G17" s="6"/>
+      <c r="G17" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H17" s="6" t="s">
         <v>2132</v>
       </c>
@@ -26774,7 +26870,9 @@
       <c r="F18">
         <v>1</v>
       </c>
-      <c r="G18" s="6"/>
+      <c r="G18" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H18" s="6" t="s">
         <v>2132</v>
       </c>
@@ -26798,7 +26896,9 @@
       <c r="F19">
         <v>1</v>
       </c>
-      <c r="G19" s="6"/>
+      <c r="G19" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H19" s="6" t="s">
         <v>2132</v>
       </c>
@@ -26822,7 +26922,9 @@
       <c r="F20">
         <v>1</v>
       </c>
-      <c r="G20" s="6"/>
+      <c r="G20" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H20" s="6" t="s">
         <v>2132</v>
       </c>
@@ -26846,7 +26948,9 @@
       <c r="F21">
         <v>1</v>
       </c>
-      <c r="G21" s="6"/>
+      <c r="G21" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H21" s="6" t="s">
         <v>2132</v>
       </c>
@@ -26870,7 +26974,9 @@
       <c r="F22">
         <v>1</v>
       </c>
-      <c r="G22" s="6"/>
+      <c r="G22" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H22" s="6" t="s">
         <v>2132</v>
       </c>
@@ -26894,7 +27000,9 @@
       <c r="F23">
         <v>1</v>
       </c>
-      <c r="G23" s="6"/>
+      <c r="G23" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H23" s="6" t="s">
         <v>2132</v>
       </c>
@@ -26918,7 +27026,9 @@
       <c r="F24">
         <v>1</v>
       </c>
-      <c r="G24" s="6"/>
+      <c r="G24" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H24" s="6" t="s">
         <v>2132</v>
       </c>
@@ -26942,7 +27052,9 @@
       <c r="F25">
         <v>1</v>
       </c>
-      <c r="G25" s="6"/>
+      <c r="G25" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H25" s="6" t="s">
         <v>2132</v>
       </c>
@@ -26966,7 +27078,9 @@
       <c r="F26">
         <v>1</v>
       </c>
-      <c r="G26" s="6"/>
+      <c r="G26" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H26" s="6" t="s">
         <v>2132</v>
       </c>
@@ -26990,7 +27104,9 @@
       <c r="F27">
         <v>1</v>
       </c>
-      <c r="G27" s="6"/>
+      <c r="G27" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H27" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27014,7 +27130,9 @@
       <c r="F28">
         <v>1</v>
       </c>
-      <c r="G28" s="6"/>
+      <c r="G28" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H28" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27038,7 +27156,9 @@
       <c r="F29">
         <v>1</v>
       </c>
-      <c r="G29" s="6"/>
+      <c r="G29" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H29" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27062,7 +27182,9 @@
       <c r="F30">
         <v>1</v>
       </c>
-      <c r="G30" s="6"/>
+      <c r="G30" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H30" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27086,7 +27208,9 @@
       <c r="F31">
         <v>1</v>
       </c>
-      <c r="G31" s="6"/>
+      <c r="G31" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H31" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27110,7 +27234,9 @@
       <c r="F32">
         <v>1</v>
       </c>
-      <c r="G32" s="6"/>
+      <c r="G32" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H32" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27134,7 +27260,9 @@
       <c r="F33">
         <v>1</v>
       </c>
-      <c r="G33" s="6"/>
+      <c r="G33" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H33" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27158,7 +27286,9 @@
       <c r="F34">
         <v>1</v>
       </c>
-      <c r="G34" s="6"/>
+      <c r="G34" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H34" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27182,7 +27312,9 @@
       <c r="F35">
         <v>1</v>
       </c>
-      <c r="G35" s="6"/>
+      <c r="G35" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H35" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27206,7 +27338,9 @@
       <c r="F36">
         <v>1</v>
       </c>
-      <c r="G36" s="6"/>
+      <c r="G36" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H36" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27230,7 +27364,9 @@
       <c r="F37">
         <v>1</v>
       </c>
-      <c r="G37" s="6"/>
+      <c r="G37" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H37" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27254,7 +27390,9 @@
       <c r="F38">
         <v>1</v>
       </c>
-      <c r="G38" s="6"/>
+      <c r="G38" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H38" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27278,7 +27416,9 @@
       <c r="F39">
         <v>1</v>
       </c>
-      <c r="G39" s="6"/>
+      <c r="G39" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H39" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27302,7 +27442,9 @@
       <c r="F40">
         <v>1</v>
       </c>
-      <c r="G40" s="6"/>
+      <c r="G40" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H40" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27326,7 +27468,9 @@
       <c r="F41">
         <v>1</v>
       </c>
-      <c r="G41" s="6"/>
+      <c r="G41" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H41" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27350,7 +27494,9 @@
       <c r="F42">
         <v>1</v>
       </c>
-      <c r="G42" s="6"/>
+      <c r="G42" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H42" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27374,7 +27520,9 @@
       <c r="F43">
         <v>1</v>
       </c>
-      <c r="G43" s="6"/>
+      <c r="G43" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H43" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27398,7 +27546,9 @@
       <c r="F44">
         <v>1</v>
       </c>
-      <c r="G44" s="6"/>
+      <c r="G44" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H44" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27422,7 +27572,9 @@
       <c r="F45">
         <v>1</v>
       </c>
-      <c r="G45" s="6"/>
+      <c r="G45" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H45" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27446,7 +27598,9 @@
       <c r="F46">
         <v>1</v>
       </c>
-      <c r="G46" s="6"/>
+      <c r="G46" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H46" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27470,7 +27624,9 @@
       <c r="F47">
         <v>1</v>
       </c>
-      <c r="G47" s="6"/>
+      <c r="G47" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H47" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27494,7 +27650,9 @@
       <c r="F48">
         <v>1</v>
       </c>
-      <c r="G48" s="6"/>
+      <c r="G48" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H48" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27518,7 +27676,9 @@
       <c r="F49">
         <v>1</v>
       </c>
-      <c r="G49" s="6"/>
+      <c r="G49" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H49" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27542,7 +27702,9 @@
       <c r="F50">
         <v>1</v>
       </c>
-      <c r="G50" s="6"/>
+      <c r="G50" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H50" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27566,7 +27728,9 @@
       <c r="F51">
         <v>1</v>
       </c>
-      <c r="G51" s="6"/>
+      <c r="G51" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H51" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27590,7 +27754,9 @@
       <c r="F52">
         <v>1</v>
       </c>
-      <c r="G52" s="6"/>
+      <c r="G52" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H52" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27614,7 +27780,9 @@
       <c r="F53">
         <v>1</v>
       </c>
-      <c r="G53" s="6"/>
+      <c r="G53" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H53" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27638,7 +27806,9 @@
       <c r="F54">
         <v>1</v>
       </c>
-      <c r="G54" s="6"/>
+      <c r="G54" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H54" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27662,7 +27832,9 @@
       <c r="F55">
         <v>1</v>
       </c>
-      <c r="G55" s="6"/>
+      <c r="G55" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H55" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27686,7 +27858,9 @@
       <c r="F56">
         <v>1</v>
       </c>
-      <c r="G56" s="6"/>
+      <c r="G56" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H56" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27710,7 +27884,9 @@
       <c r="F57">
         <v>1</v>
       </c>
-      <c r="G57" s="6"/>
+      <c r="G57" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H57" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27734,7 +27910,9 @@
       <c r="F58">
         <v>1</v>
       </c>
-      <c r="G58" s="6"/>
+      <c r="G58" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H58" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27758,7 +27936,9 @@
       <c r="F59">
         <v>1</v>
       </c>
-      <c r="G59" s="6"/>
+      <c r="G59" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H59" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27782,7 +27962,9 @@
       <c r="F60">
         <v>1</v>
       </c>
-      <c r="G60" s="6"/>
+      <c r="G60" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H60" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27806,7 +27988,9 @@
       <c r="F61">
         <v>1</v>
       </c>
-      <c r="G61" s="6"/>
+      <c r="G61" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H61" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27830,7 +28014,9 @@
       <c r="F62">
         <v>1</v>
       </c>
-      <c r="G62" s="6"/>
+      <c r="G62" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H62" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27854,7 +28040,9 @@
       <c r="F63">
         <v>1</v>
       </c>
-      <c r="G63" s="6"/>
+      <c r="G63" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H63" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27878,7 +28066,9 @@
       <c r="F64">
         <v>1</v>
       </c>
-      <c r="G64" s="6"/>
+      <c r="G64" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H64" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27902,7 +28092,9 @@
       <c r="F65">
         <v>1</v>
       </c>
-      <c r="G65" s="6"/>
+      <c r="G65" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H65" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27926,7 +28118,9 @@
       <c r="F66">
         <v>1</v>
       </c>
-      <c r="G66" s="6"/>
+      <c r="G66" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H66" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27950,7 +28144,9 @@
       <c r="F67">
         <v>1</v>
       </c>
-      <c r="G67" s="6"/>
+      <c r="G67" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H67" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27974,7 +28170,9 @@
       <c r="F68">
         <v>1</v>
       </c>
-      <c r="G68" s="6"/>
+      <c r="G68" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H68" s="6" t="s">
         <v>2132</v>
       </c>
@@ -27998,7 +28196,9 @@
       <c r="F69">
         <v>1</v>
       </c>
-      <c r="G69" s="6"/>
+      <c r="G69" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H69" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28022,7 +28222,9 @@
       <c r="F70">
         <v>1</v>
       </c>
-      <c r="G70" s="6"/>
+      <c r="G70" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H70" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28046,7 +28248,9 @@
       <c r="F71">
         <v>1</v>
       </c>
-      <c r="G71" s="6"/>
+      <c r="G71" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H71" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28070,7 +28274,9 @@
       <c r="F72">
         <v>1</v>
       </c>
-      <c r="G72" s="6"/>
+      <c r="G72" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H72" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28094,7 +28300,9 @@
       <c r="F73">
         <v>1</v>
       </c>
-      <c r="G73" s="6"/>
+      <c r="G73" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H73" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28118,7 +28326,9 @@
       <c r="F74">
         <v>1</v>
       </c>
-      <c r="G74" s="6"/>
+      <c r="G74" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H74" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28142,7 +28352,9 @@
       <c r="F75">
         <v>1</v>
       </c>
-      <c r="G75" s="6"/>
+      <c r="G75" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H75" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28166,7 +28378,9 @@
       <c r="F76">
         <v>1</v>
       </c>
-      <c r="G76" s="6"/>
+      <c r="G76" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H76" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28190,7 +28404,9 @@
       <c r="F77">
         <v>1</v>
       </c>
-      <c r="G77" s="6"/>
+      <c r="G77" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H77" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28214,7 +28430,9 @@
       <c r="F78">
         <v>1</v>
       </c>
-      <c r="G78" s="6"/>
+      <c r="G78" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H78" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28238,7 +28456,9 @@
       <c r="F79">
         <v>1</v>
       </c>
-      <c r="G79" s="6"/>
+      <c r="G79" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H79" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28262,7 +28482,9 @@
       <c r="F80">
         <v>1</v>
       </c>
-      <c r="G80" s="6"/>
+      <c r="G80" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H80" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28286,7 +28508,9 @@
       <c r="F81">
         <v>1</v>
       </c>
-      <c r="G81" s="6"/>
+      <c r="G81" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H81" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28310,7 +28534,9 @@
       <c r="F82">
         <v>1</v>
       </c>
-      <c r="G82" s="6"/>
+      <c r="G82" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H82" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28334,7 +28560,9 @@
       <c r="F83">
         <v>1</v>
       </c>
-      <c r="G83" s="6"/>
+      <c r="G83" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H83" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28358,7 +28586,9 @@
       <c r="F84">
         <v>1</v>
       </c>
-      <c r="G84" s="6"/>
+      <c r="G84" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H84" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28382,7 +28612,9 @@
       <c r="F85">
         <v>1</v>
       </c>
-      <c r="G85" s="6"/>
+      <c r="G85" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H85" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28406,7 +28638,9 @@
       <c r="F86">
         <v>1</v>
       </c>
-      <c r="G86" s="6"/>
+      <c r="G86" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H86" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28430,7 +28664,9 @@
       <c r="F87">
         <v>1</v>
       </c>
-      <c r="G87" s="6"/>
+      <c r="G87" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H87" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28454,7 +28690,9 @@
       <c r="F88">
         <v>1</v>
       </c>
-      <c r="G88" s="6"/>
+      <c r="G88" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H88" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28478,7 +28716,9 @@
       <c r="F89">
         <v>1</v>
       </c>
-      <c r="G89" s="6"/>
+      <c r="G89" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H89" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28502,7 +28742,9 @@
       <c r="F90">
         <v>1</v>
       </c>
-      <c r="G90" s="6"/>
+      <c r="G90" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H90" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28526,7 +28768,9 @@
       <c r="F91">
         <v>1</v>
       </c>
-      <c r="G91" s="6"/>
+      <c r="G91" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H91" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28550,7 +28794,9 @@
       <c r="F92">
         <v>1</v>
       </c>
-      <c r="G92" s="6"/>
+      <c r="G92" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H92" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28574,7 +28820,9 @@
       <c r="F93">
         <v>1</v>
       </c>
-      <c r="G93" s="6"/>
+      <c r="G93" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H93" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28598,7 +28846,9 @@
       <c r="F94">
         <v>1</v>
       </c>
-      <c r="G94" s="6"/>
+      <c r="G94" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H94" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28622,7 +28872,9 @@
       <c r="F95">
         <v>1</v>
       </c>
-      <c r="G95" s="6"/>
+      <c r="G95" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H95" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28646,7 +28898,9 @@
       <c r="F96">
         <v>1</v>
       </c>
-      <c r="G96" s="6"/>
+      <c r="G96" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H96" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28670,7 +28924,9 @@
       <c r="F97">
         <v>1</v>
       </c>
-      <c r="G97" s="6"/>
+      <c r="G97" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H97" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28694,7 +28950,9 @@
       <c r="F98">
         <v>1</v>
       </c>
-      <c r="G98" s="6"/>
+      <c r="G98" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H98" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28718,7 +28976,9 @@
       <c r="F99">
         <v>1</v>
       </c>
-      <c r="G99" s="6"/>
+      <c r="G99" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H99" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28742,7 +29002,9 @@
       <c r="F100">
         <v>1</v>
       </c>
-      <c r="G100" s="6"/>
+      <c r="G100" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H100" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28766,7 +29028,9 @@
       <c r="F101">
         <v>1</v>
       </c>
-      <c r="G101" s="6"/>
+      <c r="G101" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H101" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28790,7 +29054,9 @@
       <c r="F102">
         <v>1</v>
       </c>
-      <c r="G102" s="6"/>
+      <c r="G102" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H102" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28814,7 +29080,9 @@
       <c r="F103">
         <v>1</v>
       </c>
-      <c r="G103" s="6"/>
+      <c r="G103" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H103" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28838,7 +29106,9 @@
       <c r="F104">
         <v>1</v>
       </c>
-      <c r="G104" s="6"/>
+      <c r="G104" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H104" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28862,7 +29132,9 @@
       <c r="F105">
         <v>1</v>
       </c>
-      <c r="G105" s="6"/>
+      <c r="G105" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H105" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28886,7 +29158,9 @@
       <c r="F106">
         <v>1</v>
       </c>
-      <c r="G106" s="6"/>
+      <c r="G106" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H106" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28910,7 +29184,9 @@
       <c r="F107">
         <v>1</v>
       </c>
-      <c r="G107" s="6"/>
+      <c r="G107" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H107" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28934,7 +29210,9 @@
       <c r="F108">
         <v>1</v>
       </c>
-      <c r="G108" s="6"/>
+      <c r="G108" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H108" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28958,7 +29236,9 @@
       <c r="F109">
         <v>1</v>
       </c>
-      <c r="G109" s="6"/>
+      <c r="G109" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H109" s="6" t="s">
         <v>2132</v>
       </c>
@@ -28982,7 +29262,9 @@
       <c r="F110">
         <v>1</v>
       </c>
-      <c r="G110" s="6"/>
+      <c r="G110" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H110" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29006,7 +29288,9 @@
       <c r="F111">
         <v>1</v>
       </c>
-      <c r="G111" s="6"/>
+      <c r="G111" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H111" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29030,7 +29314,9 @@
       <c r="F112">
         <v>1</v>
       </c>
-      <c r="G112" s="6"/>
+      <c r="G112" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H112" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29054,7 +29340,9 @@
       <c r="F113">
         <v>1</v>
       </c>
-      <c r="G113" s="6"/>
+      <c r="G113" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H113" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29078,7 +29366,9 @@
       <c r="F114">
         <v>1</v>
       </c>
-      <c r="G114" s="6"/>
+      <c r="G114" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H114" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29102,7 +29392,9 @@
       <c r="F115">
         <v>1</v>
       </c>
-      <c r="G115" s="6"/>
+      <c r="G115" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H115" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29126,7 +29418,9 @@
       <c r="F116">
         <v>1</v>
       </c>
-      <c r="G116" s="6"/>
+      <c r="G116" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H116" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29150,7 +29444,9 @@
       <c r="F117">
         <v>1</v>
       </c>
-      <c r="G117" s="6"/>
+      <c r="G117" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H117" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29174,7 +29470,9 @@
       <c r="F118">
         <v>1</v>
       </c>
-      <c r="G118" s="6"/>
+      <c r="G118" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H118" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29198,7 +29496,9 @@
       <c r="F119">
         <v>1</v>
       </c>
-      <c r="G119" s="6"/>
+      <c r="G119" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H119" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29222,7 +29522,9 @@
       <c r="F120">
         <v>1</v>
       </c>
-      <c r="G120" s="6"/>
+      <c r="G120" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H120" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29246,7 +29548,9 @@
       <c r="F121">
         <v>1</v>
       </c>
-      <c r="G121" s="6"/>
+      <c r="G121" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H121" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29270,7 +29574,9 @@
       <c r="F122">
         <v>1</v>
       </c>
-      <c r="G122" s="6"/>
+      <c r="G122" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H122" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29294,7 +29600,9 @@
       <c r="F123">
         <v>1</v>
       </c>
-      <c r="G123" s="6"/>
+      <c r="G123" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H123" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29318,7 +29626,9 @@
       <c r="F124">
         <v>1</v>
       </c>
-      <c r="G124" s="6"/>
+      <c r="G124" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H124" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29342,7 +29652,9 @@
       <c r="F125">
         <v>1</v>
       </c>
-      <c r="G125" s="6"/>
+      <c r="G125" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H125" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29366,7 +29678,9 @@
       <c r="F126">
         <v>1</v>
       </c>
-      <c r="G126" s="6"/>
+      <c r="G126" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H126" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29390,7 +29704,9 @@
       <c r="F127">
         <v>1</v>
       </c>
-      <c r="G127" s="6"/>
+      <c r="G127" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H127" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29414,7 +29730,9 @@
       <c r="F128">
         <v>1</v>
       </c>
-      <c r="G128" s="6"/>
+      <c r="G128" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H128" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29438,7 +29756,9 @@
       <c r="F129">
         <v>1</v>
       </c>
-      <c r="G129" s="6"/>
+      <c r="G129" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H129" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29462,7 +29782,9 @@
       <c r="F130">
         <v>1</v>
       </c>
-      <c r="G130" s="6"/>
+      <c r="G130" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H130" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29486,7 +29808,9 @@
       <c r="F131">
         <v>1</v>
       </c>
-      <c r="G131" s="6"/>
+      <c r="G131" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H131" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29510,7 +29834,9 @@
       <c r="F132">
         <v>1</v>
       </c>
-      <c r="G132" s="6"/>
+      <c r="G132" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H132" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29534,7 +29860,9 @@
       <c r="F133">
         <v>1</v>
       </c>
-      <c r="G133" s="6"/>
+      <c r="G133" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H133" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29558,7 +29886,9 @@
       <c r="F134">
         <v>1</v>
       </c>
-      <c r="G134" s="6"/>
+      <c r="G134" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H134" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29582,7 +29912,9 @@
       <c r="F135">
         <v>1</v>
       </c>
-      <c r="G135" s="6"/>
+      <c r="G135" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H135" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29606,7 +29938,9 @@
       <c r="F136">
         <v>1</v>
       </c>
-      <c r="G136" s="6"/>
+      <c r="G136" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H136" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29630,7 +29964,9 @@
       <c r="F137">
         <v>1</v>
       </c>
-      <c r="G137" s="6"/>
+      <c r="G137" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H137" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29654,7 +29990,9 @@
       <c r="F138">
         <v>1</v>
       </c>
-      <c r="G138" s="6"/>
+      <c r="G138" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H138" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29678,7 +30016,9 @@
       <c r="F139">
         <v>1</v>
       </c>
-      <c r="G139" s="6"/>
+      <c r="G139" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H139" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29702,7 +30042,9 @@
       <c r="F140">
         <v>1</v>
       </c>
-      <c r="G140" s="6"/>
+      <c r="G140" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H140" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29726,7 +30068,9 @@
       <c r="F141">
         <v>1</v>
       </c>
-      <c r="G141" s="6"/>
+      <c r="G141" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H141" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29750,7 +30094,9 @@
       <c r="F142">
         <v>1</v>
       </c>
-      <c r="G142" s="6"/>
+      <c r="G142" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H142" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29774,7 +30120,9 @@
       <c r="F143">
         <v>1</v>
       </c>
-      <c r="G143" s="6"/>
+      <c r="G143" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H143" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29798,7 +30146,9 @@
       <c r="F144">
         <v>1</v>
       </c>
-      <c r="G144" s="6"/>
+      <c r="G144" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H144" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29822,7 +30172,9 @@
       <c r="F145">
         <v>1</v>
       </c>
-      <c r="G145" s="6"/>
+      <c r="G145" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H145" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29846,7 +30198,9 @@
       <c r="F146">
         <v>1</v>
       </c>
-      <c r="G146" s="6"/>
+      <c r="G146" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H146" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29870,7 +30224,9 @@
       <c r="F147">
         <v>1</v>
       </c>
-      <c r="G147" s="6"/>
+      <c r="G147" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H147" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29894,7 +30250,9 @@
       <c r="F148">
         <v>1</v>
       </c>
-      <c r="G148" s="6"/>
+      <c r="G148" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H148" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29918,7 +30276,9 @@
       <c r="F149">
         <v>1</v>
       </c>
-      <c r="G149" s="6"/>
+      <c r="G149" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H149" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29942,7 +30302,9 @@
       <c r="F150">
         <v>1</v>
       </c>
-      <c r="G150" s="6"/>
+      <c r="G150" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H150" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29966,7 +30328,9 @@
       <c r="F151">
         <v>1</v>
       </c>
-      <c r="G151" s="6"/>
+      <c r="G151" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H151" s="6" t="s">
         <v>2132</v>
       </c>
@@ -29990,7 +30354,9 @@
       <c r="F152">
         <v>1</v>
       </c>
-      <c r="G152" s="6"/>
+      <c r="G152" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H152" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30014,7 +30380,9 @@
       <c r="F153">
         <v>1</v>
       </c>
-      <c r="G153" s="6"/>
+      <c r="G153" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H153" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30038,7 +30406,9 @@
       <c r="F154">
         <v>1</v>
       </c>
-      <c r="G154" s="6"/>
+      <c r="G154" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H154" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30062,7 +30432,9 @@
       <c r="F155">
         <v>1</v>
       </c>
-      <c r="G155" s="6"/>
+      <c r="G155" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H155" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30086,7 +30458,9 @@
       <c r="F156">
         <v>1</v>
       </c>
-      <c r="G156" s="6"/>
+      <c r="G156" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H156" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30110,7 +30484,9 @@
       <c r="F157">
         <v>1</v>
       </c>
-      <c r="G157" s="6"/>
+      <c r="G157" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H157" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30134,7 +30510,9 @@
       <c r="F158">
         <v>1</v>
       </c>
-      <c r="G158" s="6"/>
+      <c r="G158" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H158" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30158,7 +30536,9 @@
       <c r="F159">
         <v>1</v>
       </c>
-      <c r="G159" s="6"/>
+      <c r="G159" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H159" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30182,7 +30562,9 @@
       <c r="F160">
         <v>1</v>
       </c>
-      <c r="G160" s="6"/>
+      <c r="G160" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H160" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30206,7 +30588,9 @@
       <c r="F161">
         <v>1</v>
       </c>
-      <c r="G161" s="6"/>
+      <c r="G161" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H161" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30230,7 +30614,9 @@
       <c r="F162">
         <v>1</v>
       </c>
-      <c r="G162" s="6"/>
+      <c r="G162" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H162" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30254,7 +30640,9 @@
       <c r="F163">
         <v>1</v>
       </c>
-      <c r="G163" s="6"/>
+      <c r="G163" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H163" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30278,7 +30666,9 @@
       <c r="F164">
         <v>1</v>
       </c>
-      <c r="G164" s="6"/>
+      <c r="G164" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H164" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30302,7 +30692,9 @@
       <c r="F165">
         <v>1</v>
       </c>
-      <c r="G165" s="6"/>
+      <c r="G165" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H165" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30326,7 +30718,9 @@
       <c r="F166">
         <v>1</v>
       </c>
-      <c r="G166" s="6"/>
+      <c r="G166" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H166" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30350,7 +30744,9 @@
       <c r="F167">
         <v>1</v>
       </c>
-      <c r="G167" s="6"/>
+      <c r="G167" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H167" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30374,7 +30770,9 @@
       <c r="F168">
         <v>1</v>
       </c>
-      <c r="G168" s="6"/>
+      <c r="G168" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H168" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30398,7 +30796,9 @@
       <c r="F169">
         <v>1</v>
       </c>
-      <c r="G169" s="6"/>
+      <c r="G169" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H169" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30422,7 +30822,9 @@
       <c r="F170">
         <v>1</v>
       </c>
-      <c r="G170" s="6"/>
+      <c r="G170" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H170" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30446,7 +30848,9 @@
       <c r="F171">
         <v>1</v>
       </c>
-      <c r="G171" s="6"/>
+      <c r="G171" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H171" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30470,7 +30874,9 @@
       <c r="F172">
         <v>1</v>
       </c>
-      <c r="G172" s="6"/>
+      <c r="G172" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H172" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30494,7 +30900,9 @@
       <c r="F173">
         <v>1</v>
       </c>
-      <c r="G173" s="6"/>
+      <c r="G173" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H173" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30518,7 +30926,9 @@
       <c r="F174">
         <v>1</v>
       </c>
-      <c r="G174" s="6"/>
+      <c r="G174" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H174" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30542,7 +30952,9 @@
       <c r="F175">
         <v>1</v>
       </c>
-      <c r="G175" s="6"/>
+      <c r="G175" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H175" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30566,7 +30978,9 @@
       <c r="F176">
         <v>1</v>
       </c>
-      <c r="G176" s="6"/>
+      <c r="G176" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H176" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30590,7 +31004,9 @@
       <c r="F177">
         <v>1</v>
       </c>
-      <c r="G177" s="6"/>
+      <c r="G177" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H177" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30614,7 +31030,9 @@
       <c r="F178">
         <v>1</v>
       </c>
-      <c r="G178" s="6"/>
+      <c r="G178" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H178" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30638,7 +31056,9 @@
       <c r="F179">
         <v>1</v>
       </c>
-      <c r="G179" s="6"/>
+      <c r="G179" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H179" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30662,7 +31082,9 @@
       <c r="F180">
         <v>1</v>
       </c>
-      <c r="G180" s="6"/>
+      <c r="G180" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H180" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30686,7 +31108,9 @@
       <c r="F181">
         <v>1</v>
       </c>
-      <c r="G181" s="6"/>
+      <c r="G181" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H181" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30710,7 +31134,9 @@
       <c r="F182">
         <v>1</v>
       </c>
-      <c r="G182" s="6"/>
+      <c r="G182" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H182" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30734,7 +31160,9 @@
       <c r="F183">
         <v>1</v>
       </c>
-      <c r="G183" s="6"/>
+      <c r="G183" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H183" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30758,7 +31186,9 @@
       <c r="F184">
         <v>1</v>
       </c>
-      <c r="G184" s="6"/>
+      <c r="G184" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H184" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30782,7 +31212,9 @@
       <c r="F185">
         <v>1</v>
       </c>
-      <c r="G185" s="6"/>
+      <c r="G185" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H185" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30806,7 +31238,9 @@
       <c r="F186">
         <v>1</v>
       </c>
-      <c r="G186" s="6"/>
+      <c r="G186" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H186" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30830,7 +31264,9 @@
       <c r="F187">
         <v>1</v>
       </c>
-      <c r="G187" s="6"/>
+      <c r="G187" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H187" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30854,7 +31290,9 @@
       <c r="F188">
         <v>1</v>
       </c>
-      <c r="G188" s="6"/>
+      <c r="G188" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H188" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30878,7 +31316,9 @@
       <c r="F189">
         <v>1</v>
       </c>
-      <c r="G189" s="6"/>
+      <c r="G189" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H189" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30902,7 +31342,9 @@
       <c r="F190">
         <v>1</v>
       </c>
-      <c r="G190" s="6"/>
+      <c r="G190" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H190" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30926,7 +31368,9 @@
       <c r="F191">
         <v>1</v>
       </c>
-      <c r="G191" s="6"/>
+      <c r="G191" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H191" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30950,7 +31394,9 @@
       <c r="F192">
         <v>1</v>
       </c>
-      <c r="G192" s="6"/>
+      <c r="G192" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H192" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30974,7 +31420,9 @@
       <c r="F193">
         <v>1</v>
       </c>
-      <c r="G193" s="6"/>
+      <c r="G193" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H193" s="6" t="s">
         <v>2132</v>
       </c>
@@ -30998,7 +31446,9 @@
       <c r="F194">
         <v>1</v>
       </c>
-      <c r="G194" s="6"/>
+      <c r="G194" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H194" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31022,7 +31472,9 @@
       <c r="F195">
         <v>1</v>
       </c>
-      <c r="G195" s="6"/>
+      <c r="G195" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H195" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31046,7 +31498,9 @@
       <c r="F196">
         <v>1</v>
       </c>
-      <c r="G196" s="6"/>
+      <c r="G196" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H196" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31070,7 +31524,9 @@
       <c r="F197">
         <v>1</v>
       </c>
-      <c r="G197" s="6"/>
+      <c r="G197" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H197" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31094,7 +31550,9 @@
       <c r="F198">
         <v>1</v>
       </c>
-      <c r="G198" s="6"/>
+      <c r="G198" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H198" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31118,7 +31576,9 @@
       <c r="F199">
         <v>1</v>
       </c>
-      <c r="G199" s="6"/>
+      <c r="G199" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H199" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31142,7 +31602,9 @@
       <c r="F200">
         <v>1</v>
       </c>
-      <c r="G200" s="6"/>
+      <c r="G200" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H200" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31166,7 +31628,9 @@
       <c r="F201">
         <v>1</v>
       </c>
-      <c r="G201" s="6"/>
+      <c r="G201" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H201" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31190,7 +31654,9 @@
       <c r="F202">
         <v>1</v>
       </c>
-      <c r="G202" s="6"/>
+      <c r="G202" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H202" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31214,7 +31680,9 @@
       <c r="F203">
         <v>1</v>
       </c>
-      <c r="G203" s="6"/>
+      <c r="G203" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H203" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31238,7 +31706,9 @@
       <c r="F204">
         <v>1</v>
       </c>
-      <c r="G204" s="6"/>
+      <c r="G204" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H204" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31262,7 +31732,9 @@
       <c r="F205">
         <v>1</v>
       </c>
-      <c r="G205" s="6"/>
+      <c r="G205" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H205" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31286,7 +31758,9 @@
       <c r="F206">
         <v>1</v>
       </c>
-      <c r="G206" s="6"/>
+      <c r="G206" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H206" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31310,7 +31784,9 @@
       <c r="F207">
         <v>1</v>
       </c>
-      <c r="G207" s="6"/>
+      <c r="G207" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H207" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31334,7 +31810,9 @@
       <c r="F208">
         <v>1</v>
       </c>
-      <c r="G208" s="6"/>
+      <c r="G208" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H208" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31358,7 +31836,9 @@
       <c r="F209">
         <v>1</v>
       </c>
-      <c r="G209" s="6"/>
+      <c r="G209" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H209" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31382,7 +31862,9 @@
       <c r="F210">
         <v>1</v>
       </c>
-      <c r="G210" s="6"/>
+      <c r="G210" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H210" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31406,7 +31888,9 @@
       <c r="F211">
         <v>1</v>
       </c>
-      <c r="G211" s="6"/>
+      <c r="G211" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H211" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31430,7 +31914,9 @@
       <c r="F212">
         <v>1</v>
       </c>
-      <c r="G212" s="6"/>
+      <c r="G212" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H212" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31454,7 +31940,9 @@
       <c r="F213">
         <v>1</v>
       </c>
-      <c r="G213" s="6"/>
+      <c r="G213" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H213" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31478,7 +31966,9 @@
       <c r="F214">
         <v>1</v>
       </c>
-      <c r="G214" s="6"/>
+      <c r="G214" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H214" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31502,7 +31992,9 @@
       <c r="F215">
         <v>1</v>
       </c>
-      <c r="G215" s="6"/>
+      <c r="G215" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H215" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31526,7 +32018,9 @@
       <c r="F216">
         <v>1</v>
       </c>
-      <c r="G216" s="6"/>
+      <c r="G216" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H216" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31550,7 +32044,9 @@
       <c r="F217">
         <v>1</v>
       </c>
-      <c r="G217" s="6"/>
+      <c r="G217" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H217" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31574,7 +32070,9 @@
       <c r="F218">
         <v>1</v>
       </c>
-      <c r="G218" s="6"/>
+      <c r="G218" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H218" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31598,7 +32096,9 @@
       <c r="F219">
         <v>1</v>
       </c>
-      <c r="G219" s="6"/>
+      <c r="G219" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H219" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31622,7 +32122,9 @@
       <c r="F220">
         <v>1</v>
       </c>
-      <c r="G220" s="6"/>
+      <c r="G220" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H220" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31646,7 +32148,9 @@
       <c r="F221">
         <v>1</v>
       </c>
-      <c r="G221" s="6"/>
+      <c r="G221" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H221" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31670,7 +32174,9 @@
       <c r="F222">
         <v>1</v>
       </c>
-      <c r="G222" s="6"/>
+      <c r="G222" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H222" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31694,7 +32200,9 @@
       <c r="F223">
         <v>1</v>
       </c>
-      <c r="G223" s="6"/>
+      <c r="G223" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H223" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31718,7 +32226,9 @@
       <c r="F224">
         <v>1</v>
       </c>
-      <c r="G224" s="6"/>
+      <c r="G224" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H224" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31742,7 +32252,9 @@
       <c r="F225">
         <v>1</v>
       </c>
-      <c r="G225" s="6"/>
+      <c r="G225" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H225" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31766,7 +32278,9 @@
       <c r="F226">
         <v>1</v>
       </c>
-      <c r="G226" s="6"/>
+      <c r="G226" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H226" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31790,7 +32304,9 @@
       <c r="F227">
         <v>1</v>
       </c>
-      <c r="G227" s="6"/>
+      <c r="G227" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H227" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31814,7 +32330,9 @@
       <c r="F228">
         <v>1</v>
       </c>
-      <c r="G228" s="6"/>
+      <c r="G228" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H228" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31838,7 +32356,9 @@
       <c r="F229">
         <v>1</v>
       </c>
-      <c r="G229" s="6"/>
+      <c r="G229" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H229" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31862,7 +32382,9 @@
       <c r="F230">
         <v>1</v>
       </c>
-      <c r="G230" s="6"/>
+      <c r="G230" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H230" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31886,7 +32408,9 @@
       <c r="F231">
         <v>1</v>
       </c>
-      <c r="G231" s="6"/>
+      <c r="G231" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H231" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31910,7 +32434,9 @@
       <c r="F232">
         <v>1</v>
       </c>
-      <c r="G232" s="6"/>
+      <c r="G232" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H232" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31934,7 +32460,9 @@
       <c r="F233">
         <v>1</v>
       </c>
-      <c r="G233" s="6"/>
+      <c r="G233" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H233" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31958,7 +32486,9 @@
       <c r="F234">
         <v>1</v>
       </c>
-      <c r="G234" s="6"/>
+      <c r="G234" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H234" s="6" t="s">
         <v>2132</v>
       </c>
@@ -31982,7 +32512,9 @@
       <c r="F235">
         <v>1</v>
       </c>
-      <c r="G235" s="6"/>
+      <c r="G235" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H235" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32006,7 +32538,9 @@
       <c r="F236">
         <v>1</v>
       </c>
-      <c r="G236" s="6"/>
+      <c r="G236" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H236" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32030,7 +32564,9 @@
       <c r="F237">
         <v>1</v>
       </c>
-      <c r="G237" s="6"/>
+      <c r="G237" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H237" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32054,7 +32590,9 @@
       <c r="F238">
         <v>1</v>
       </c>
-      <c r="G238" s="6"/>
+      <c r="G238" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H238" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32078,7 +32616,9 @@
       <c r="F239">
         <v>1</v>
       </c>
-      <c r="G239" s="6"/>
+      <c r="G239" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H239" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32102,7 +32642,9 @@
       <c r="F240">
         <v>1</v>
       </c>
-      <c r="G240" s="6"/>
+      <c r="G240" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H240" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32126,7 +32668,9 @@
       <c r="F241">
         <v>1</v>
       </c>
-      <c r="G241" s="6"/>
+      <c r="G241" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H241" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32150,7 +32694,9 @@
       <c r="F242">
         <v>1</v>
       </c>
-      <c r="G242" s="6"/>
+      <c r="G242" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H242" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32174,7 +32720,9 @@
       <c r="F243">
         <v>1</v>
       </c>
-      <c r="G243" s="6"/>
+      <c r="G243" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H243" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32198,7 +32746,9 @@
       <c r="F244">
         <v>1</v>
       </c>
-      <c r="G244" s="6"/>
+      <c r="G244" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H244" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32222,7 +32772,9 @@
       <c r="F245">
         <v>1</v>
       </c>
-      <c r="G245" s="6"/>
+      <c r="G245" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H245" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32246,7 +32798,9 @@
       <c r="F246">
         <v>1</v>
       </c>
-      <c r="G246" s="6"/>
+      <c r="G246" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H246" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32270,7 +32824,9 @@
       <c r="F247">
         <v>1</v>
       </c>
-      <c r="G247" s="6"/>
+      <c r="G247" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H247" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32294,7 +32850,9 @@
       <c r="F248">
         <v>1</v>
       </c>
-      <c r="G248" s="6"/>
+      <c r="G248" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H248" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32318,7 +32876,9 @@
       <c r="F249">
         <v>1</v>
       </c>
-      <c r="G249" s="6"/>
+      <c r="G249" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H249" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32342,7 +32902,9 @@
       <c r="F250">
         <v>1</v>
       </c>
-      <c r="G250" s="6"/>
+      <c r="G250" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H250" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32366,7 +32928,9 @@
       <c r="F251">
         <v>1</v>
       </c>
-      <c r="G251" s="6"/>
+      <c r="G251" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H251" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32390,7 +32954,9 @@
       <c r="F252">
         <v>1</v>
       </c>
-      <c r="G252" s="6"/>
+      <c r="G252" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H252" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32414,7 +32980,9 @@
       <c r="F253">
         <v>1</v>
       </c>
-      <c r="G253" s="6"/>
+      <c r="G253" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H253" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32438,7 +33006,9 @@
       <c r="F254">
         <v>1</v>
       </c>
-      <c r="G254" s="6"/>
+      <c r="G254" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H254" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32462,7 +33032,9 @@
       <c r="F255">
         <v>1</v>
       </c>
-      <c r="G255" s="6"/>
+      <c r="G255" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H255" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32486,7 +33058,9 @@
       <c r="F256">
         <v>1</v>
       </c>
-      <c r="G256" s="6"/>
+      <c r="G256" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H256" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32510,7 +33084,9 @@
       <c r="F257">
         <v>1</v>
       </c>
-      <c r="G257" s="6"/>
+      <c r="G257" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H257" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32534,7 +33110,9 @@
       <c r="F258">
         <v>1</v>
       </c>
-      <c r="G258" s="6"/>
+      <c r="G258" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H258" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32558,7 +33136,9 @@
       <c r="F259">
         <v>1</v>
       </c>
-      <c r="G259" s="6"/>
+      <c r="G259" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H259" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32582,7 +33162,9 @@
       <c r="F260">
         <v>1</v>
       </c>
-      <c r="G260" s="6"/>
+      <c r="G260" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H260" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32606,7 +33188,9 @@
       <c r="F261">
         <v>1</v>
       </c>
-      <c r="G261" s="6"/>
+      <c r="G261" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H261" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32630,7 +33214,9 @@
       <c r="F262">
         <v>1</v>
       </c>
-      <c r="G262" s="6"/>
+      <c r="G262" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H262" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32654,7 +33240,9 @@
       <c r="F263">
         <v>1</v>
       </c>
-      <c r="G263" s="6"/>
+      <c r="G263" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H263" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32678,7 +33266,9 @@
       <c r="F264">
         <v>1</v>
       </c>
-      <c r="G264" s="6"/>
+      <c r="G264" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H264" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32702,7 +33292,9 @@
       <c r="F265">
         <v>1</v>
       </c>
-      <c r="G265" s="6"/>
+      <c r="G265" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H265" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32726,7 +33318,9 @@
       <c r="F266">
         <v>1</v>
       </c>
-      <c r="G266" s="6"/>
+      <c r="G266" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H266" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32750,7 +33344,9 @@
       <c r="F267">
         <v>1</v>
       </c>
-      <c r="G267" s="6"/>
+      <c r="G267" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H267" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32774,7 +33370,9 @@
       <c r="F268">
         <v>1</v>
       </c>
-      <c r="G268" s="6"/>
+      <c r="G268" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H268" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32798,7 +33396,9 @@
       <c r="F269">
         <v>1</v>
       </c>
-      <c r="G269" s="6"/>
+      <c r="G269" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H269" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32822,7 +33422,9 @@
       <c r="F270">
         <v>1</v>
       </c>
-      <c r="G270" s="6"/>
+      <c r="G270" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H270" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32846,7 +33448,9 @@
       <c r="F271">
         <v>1</v>
       </c>
-      <c r="G271" s="6"/>
+      <c r="G271" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H271" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32870,7 +33474,9 @@
       <c r="F272">
         <v>1</v>
       </c>
-      <c r="G272" s="6"/>
+      <c r="G272" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H272" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32894,7 +33500,9 @@
       <c r="F273">
         <v>1</v>
       </c>
-      <c r="G273" s="6"/>
+      <c r="G273" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H273" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32918,7 +33526,9 @@
       <c r="F274">
         <v>1</v>
       </c>
-      <c r="G274" s="6"/>
+      <c r="G274" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H274" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32942,7 +33552,9 @@
       <c r="F275">
         <v>1</v>
       </c>
-      <c r="G275" s="6"/>
+      <c r="G275" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H275" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32966,7 +33578,9 @@
       <c r="F276">
         <v>1</v>
       </c>
-      <c r="G276" s="6"/>
+      <c r="G276" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H276" s="6" t="s">
         <v>2132</v>
       </c>
@@ -32990,7 +33604,9 @@
       <c r="F277">
         <v>1</v>
       </c>
-      <c r="G277" s="6"/>
+      <c r="G277" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H277" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33014,7 +33630,9 @@
       <c r="F278">
         <v>1</v>
       </c>
-      <c r="G278" s="6"/>
+      <c r="G278" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H278" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33038,7 +33656,9 @@
       <c r="F279">
         <v>1</v>
       </c>
-      <c r="G279" s="6"/>
+      <c r="G279" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H279" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33062,7 +33682,9 @@
       <c r="F280">
         <v>1</v>
       </c>
-      <c r="G280" s="6"/>
+      <c r="G280" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H280" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33086,7 +33708,9 @@
       <c r="F281">
         <v>1</v>
       </c>
-      <c r="G281" s="6"/>
+      <c r="G281" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H281" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33110,7 +33734,9 @@
       <c r="F282">
         <v>1</v>
       </c>
-      <c r="G282" s="6"/>
+      <c r="G282" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H282" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33134,7 +33760,9 @@
       <c r="F283">
         <v>1</v>
       </c>
-      <c r="G283" s="6"/>
+      <c r="G283" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H283" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33158,7 +33786,9 @@
       <c r="F284">
         <v>1</v>
       </c>
-      <c r="G284" s="6"/>
+      <c r="G284" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H284" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33182,7 +33812,9 @@
       <c r="F285">
         <v>1</v>
       </c>
-      <c r="G285" s="6"/>
+      <c r="G285" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H285" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33206,7 +33838,9 @@
       <c r="F286">
         <v>1</v>
       </c>
-      <c r="G286" s="6"/>
+      <c r="G286" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H286" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33230,7 +33864,9 @@
       <c r="F287">
         <v>1</v>
       </c>
-      <c r="G287" s="6"/>
+      <c r="G287" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H287" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33254,7 +33890,9 @@
       <c r="F288">
         <v>1</v>
       </c>
-      <c r="G288" s="6"/>
+      <c r="G288" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H288" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33278,7 +33916,9 @@
       <c r="F289">
         <v>1</v>
       </c>
-      <c r="G289" s="6"/>
+      <c r="G289" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H289" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33302,7 +33942,9 @@
       <c r="F290">
         <v>1</v>
       </c>
-      <c r="G290" s="6"/>
+      <c r="G290" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H290" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33326,7 +33968,9 @@
       <c r="F291">
         <v>1</v>
       </c>
-      <c r="G291" s="6"/>
+      <c r="G291" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H291" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33350,7 +33994,9 @@
       <c r="F292">
         <v>1</v>
       </c>
-      <c r="G292" s="6"/>
+      <c r="G292" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H292" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33374,7 +34020,9 @@
       <c r="F293">
         <v>1</v>
       </c>
-      <c r="G293" s="6"/>
+      <c r="G293" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H293" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33398,7 +34046,9 @@
       <c r="F294">
         <v>1</v>
       </c>
-      <c r="G294" s="6"/>
+      <c r="G294" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H294" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33422,7 +34072,9 @@
       <c r="F295">
         <v>1</v>
       </c>
-      <c r="G295" s="6"/>
+      <c r="G295" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H295" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33446,7 +34098,9 @@
       <c r="F296">
         <v>1</v>
       </c>
-      <c r="G296" s="6"/>
+      <c r="G296" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H296" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33470,7 +34124,9 @@
       <c r="F297">
         <v>1</v>
       </c>
-      <c r="G297" s="6"/>
+      <c r="G297" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H297" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33494,7 +34150,9 @@
       <c r="F298">
         <v>1</v>
       </c>
-      <c r="G298" s="6"/>
+      <c r="G298" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H298" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33518,7 +34176,9 @@
       <c r="F299">
         <v>1</v>
       </c>
-      <c r="G299" s="6"/>
+      <c r="G299" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H299" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33542,7 +34202,9 @@
       <c r="F300">
         <v>1</v>
       </c>
-      <c r="G300" s="6"/>
+      <c r="G300" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H300" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33566,7 +34228,9 @@
       <c r="F301">
         <v>1</v>
       </c>
-      <c r="G301" s="6"/>
+      <c r="G301" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H301" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33590,7 +34254,9 @@
       <c r="F302">
         <v>1</v>
       </c>
-      <c r="G302" s="6"/>
+      <c r="G302" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H302" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33614,7 +34280,9 @@
       <c r="F303">
         <v>1</v>
       </c>
-      <c r="G303" s="6"/>
+      <c r="G303" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H303" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33638,7 +34306,9 @@
       <c r="F304">
         <v>1</v>
       </c>
-      <c r="G304" s="6"/>
+      <c r="G304" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H304" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33662,7 +34332,9 @@
       <c r="F305">
         <v>1</v>
       </c>
-      <c r="G305" s="6"/>
+      <c r="G305" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H305" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33686,7 +34358,9 @@
       <c r="F306">
         <v>1</v>
       </c>
-      <c r="G306" s="6"/>
+      <c r="G306" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H306" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33710,7 +34384,9 @@
       <c r="F307">
         <v>1</v>
       </c>
-      <c r="G307" s="6"/>
+      <c r="G307" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H307" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33734,7 +34410,9 @@
       <c r="F308">
         <v>1</v>
       </c>
-      <c r="G308" s="6"/>
+      <c r="G308" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H308" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33758,7 +34436,9 @@
       <c r="F309">
         <v>1</v>
       </c>
-      <c r="G309" s="6"/>
+      <c r="G309" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H309" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33782,7 +34462,9 @@
       <c r="F310">
         <v>1</v>
       </c>
-      <c r="G310" s="6"/>
+      <c r="G310" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H310" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33806,7 +34488,9 @@
       <c r="F311">
         <v>1</v>
       </c>
-      <c r="G311" s="6"/>
+      <c r="G311" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H311" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33830,7 +34514,9 @@
       <c r="F312">
         <v>1</v>
       </c>
-      <c r="G312" s="6"/>
+      <c r="G312" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H312" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33854,7 +34540,9 @@
       <c r="F313">
         <v>1</v>
       </c>
-      <c r="G313" s="6"/>
+      <c r="G313" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H313" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33878,7 +34566,9 @@
       <c r="F314">
         <v>1</v>
       </c>
-      <c r="G314" s="6"/>
+      <c r="G314" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H314" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33902,7 +34592,9 @@
       <c r="F315">
         <v>1</v>
       </c>
-      <c r="G315" s="6"/>
+      <c r="G315" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H315" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33926,7 +34618,9 @@
       <c r="F316">
         <v>1</v>
       </c>
-      <c r="G316" s="6"/>
+      <c r="G316" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H316" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33950,7 +34644,9 @@
       <c r="F317">
         <v>1</v>
       </c>
-      <c r="G317" s="6"/>
+      <c r="G317" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H317" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33974,7 +34670,9 @@
       <c r="F318">
         <v>1</v>
       </c>
-      <c r="G318" s="6"/>
+      <c r="G318" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H318" s="6" t="s">
         <v>2132</v>
       </c>
@@ -33998,7 +34696,9 @@
       <c r="F319">
         <v>1</v>
       </c>
-      <c r="G319" s="6"/>
+      <c r="G319" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H319" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34022,7 +34722,9 @@
       <c r="F320">
         <v>1</v>
       </c>
-      <c r="G320" s="6"/>
+      <c r="G320" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H320" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34046,7 +34748,9 @@
       <c r="F321">
         <v>1</v>
       </c>
-      <c r="G321" s="6"/>
+      <c r="G321" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H321" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34070,7 +34774,9 @@
       <c r="F322">
         <v>1</v>
       </c>
-      <c r="G322" s="6"/>
+      <c r="G322" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H322" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34094,7 +34800,9 @@
       <c r="F323">
         <v>1</v>
       </c>
-      <c r="G323" s="6"/>
+      <c r="G323" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H323" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34118,7 +34826,9 @@
       <c r="F324">
         <v>1</v>
       </c>
-      <c r="G324" s="6"/>
+      <c r="G324" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H324" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34142,7 +34852,9 @@
       <c r="F325">
         <v>1</v>
       </c>
-      <c r="G325" s="6"/>
+      <c r="G325" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H325" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34166,7 +34878,9 @@
       <c r="F326">
         <v>1</v>
       </c>
-      <c r="G326" s="6"/>
+      <c r="G326" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H326" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34190,7 +34904,9 @@
       <c r="F327">
         <v>1</v>
       </c>
-      <c r="G327" s="6"/>
+      <c r="G327" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H327" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34214,7 +34930,9 @@
       <c r="F328">
         <v>1</v>
       </c>
-      <c r="G328" s="6"/>
+      <c r="G328" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H328" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34238,7 +34956,9 @@
       <c r="F329">
         <v>1</v>
       </c>
-      <c r="G329" s="6"/>
+      <c r="G329" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H329" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34262,7 +34982,9 @@
       <c r="F330">
         <v>1</v>
       </c>
-      <c r="G330" s="6"/>
+      <c r="G330" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H330" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34286,7 +35008,9 @@
       <c r="F331">
         <v>1</v>
       </c>
-      <c r="G331" s="6"/>
+      <c r="G331" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H331" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34310,7 +35034,9 @@
       <c r="F332">
         <v>1</v>
       </c>
-      <c r="G332" s="6"/>
+      <c r="G332" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H332" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34334,7 +35060,9 @@
       <c r="F333">
         <v>1</v>
       </c>
-      <c r="G333" s="6"/>
+      <c r="G333" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H333" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34358,7 +35086,9 @@
       <c r="F334">
         <v>1</v>
       </c>
-      <c r="G334" s="6"/>
+      <c r="G334" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H334" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34382,7 +35112,9 @@
       <c r="F335">
         <v>1</v>
       </c>
-      <c r="G335" s="6"/>
+      <c r="G335" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H335" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34406,7 +35138,9 @@
       <c r="F336">
         <v>1</v>
       </c>
-      <c r="G336" s="6"/>
+      <c r="G336" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H336" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34430,7 +35164,9 @@
       <c r="F337">
         <v>1</v>
       </c>
-      <c r="G337" s="6"/>
+      <c r="G337" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H337" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34454,7 +35190,9 @@
       <c r="F338">
         <v>1</v>
       </c>
-      <c r="G338" s="6"/>
+      <c r="G338" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H338" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34478,7 +35216,9 @@
       <c r="F339">
         <v>1</v>
       </c>
-      <c r="G339" s="6"/>
+      <c r="G339" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H339" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34502,7 +35242,9 @@
       <c r="F340">
         <v>1</v>
       </c>
-      <c r="G340" s="6"/>
+      <c r="G340" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H340" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34526,7 +35268,9 @@
       <c r="F341">
         <v>1</v>
       </c>
-      <c r="G341" s="6"/>
+      <c r="G341" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H341" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34550,7 +35294,9 @@
       <c r="F342">
         <v>1</v>
       </c>
-      <c r="G342" s="6"/>
+      <c r="G342" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H342" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34574,7 +35320,9 @@
       <c r="F343">
         <v>1</v>
       </c>
-      <c r="G343" s="6"/>
+      <c r="G343" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H343" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34598,7 +35346,9 @@
       <c r="F344">
         <v>1</v>
       </c>
-      <c r="G344" s="6"/>
+      <c r="G344" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H344" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34622,7 +35372,9 @@
       <c r="F345">
         <v>1</v>
       </c>
-      <c r="G345" s="6"/>
+      <c r="G345" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H345" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34646,7 +35398,9 @@
       <c r="F346">
         <v>1</v>
       </c>
-      <c r="G346" s="6"/>
+      <c r="G346" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H346" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34670,7 +35424,9 @@
       <c r="F347">
         <v>1</v>
       </c>
-      <c r="G347" s="6"/>
+      <c r="G347" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H347" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34694,7 +35450,9 @@
       <c r="F348">
         <v>1</v>
       </c>
-      <c r="G348" s="6"/>
+      <c r="G348" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H348" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34718,7 +35476,9 @@
       <c r="F349">
         <v>1</v>
       </c>
-      <c r="G349" s="6"/>
+      <c r="G349" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H349" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34742,7 +35502,9 @@
       <c r="F350">
         <v>1</v>
       </c>
-      <c r="G350" s="6"/>
+      <c r="G350" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H350" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34766,7 +35528,9 @@
       <c r="F351">
         <v>1</v>
       </c>
-      <c r="G351" s="6"/>
+      <c r="G351" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H351" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34790,7 +35554,9 @@
       <c r="F352">
         <v>1</v>
       </c>
-      <c r="G352" s="6"/>
+      <c r="G352" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H352" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34814,7 +35580,9 @@
       <c r="F353">
         <v>1</v>
       </c>
-      <c r="G353" s="6"/>
+      <c r="G353" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H353" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34838,7 +35606,9 @@
       <c r="F354">
         <v>1</v>
       </c>
-      <c r="G354" s="6"/>
+      <c r="G354" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H354" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34862,7 +35632,9 @@
       <c r="F355">
         <v>1</v>
       </c>
-      <c r="G355" s="6"/>
+      <c r="G355" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H355" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34886,7 +35658,9 @@
       <c r="F356">
         <v>1</v>
       </c>
-      <c r="G356" s="6"/>
+      <c r="G356" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H356" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34910,7 +35684,9 @@
       <c r="F357">
         <v>1</v>
       </c>
-      <c r="G357" s="6"/>
+      <c r="G357" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H357" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34934,7 +35710,9 @@
       <c r="F358">
         <v>1</v>
       </c>
-      <c r="G358" s="6"/>
+      <c r="G358" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H358" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34958,7 +35736,9 @@
       <c r="F359">
         <v>1</v>
       </c>
-      <c r="G359" s="6"/>
+      <c r="G359" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H359" s="6" t="s">
         <v>2132</v>
       </c>
@@ -34982,7 +35762,9 @@
       <c r="F360">
         <v>1</v>
       </c>
-      <c r="G360" s="6"/>
+      <c r="G360" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H360" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35006,7 +35788,9 @@
       <c r="F361">
         <v>1</v>
       </c>
-      <c r="G361" s="6"/>
+      <c r="G361" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H361" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35030,7 +35814,9 @@
       <c r="F362">
         <v>1</v>
       </c>
-      <c r="G362" s="6"/>
+      <c r="G362" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H362" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35054,7 +35840,9 @@
       <c r="F363">
         <v>1</v>
       </c>
-      <c r="G363" s="6"/>
+      <c r="G363" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H363" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35078,7 +35866,9 @@
       <c r="F364">
         <v>1</v>
       </c>
-      <c r="G364" s="6"/>
+      <c r="G364" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H364" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35102,7 +35892,9 @@
       <c r="F365">
         <v>1</v>
       </c>
-      <c r="G365" s="6"/>
+      <c r="G365" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H365" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35126,7 +35918,9 @@
       <c r="F366">
         <v>1</v>
       </c>
-      <c r="G366" s="6"/>
+      <c r="G366" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H366" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35150,7 +35944,9 @@
       <c r="F367">
         <v>1</v>
       </c>
-      <c r="G367" s="6"/>
+      <c r="G367" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H367" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35174,7 +35970,9 @@
       <c r="F368">
         <v>1</v>
       </c>
-      <c r="G368" s="6"/>
+      <c r="G368" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H368" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35198,7 +35996,9 @@
       <c r="F369">
         <v>1</v>
       </c>
-      <c r="G369" s="6"/>
+      <c r="G369" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H369" s="6" t="s">
         <v>2132</v>
       </c>
@@ -35222,7 +36022,9 @@
       <c r="F370">
         <v>1</v>
       </c>
-      <c r="G370" s="6"/>
+      <c r="G370" s="6" t="s">
+        <v>2140</v>
+      </c>
       <c r="H370" s="6" t="s">
         <v>2132</v>
       </c>
